--- a/output/quickfix_portfolio_daily.xlsx
+++ b/output/quickfix_portfolio_daily.xlsx
@@ -171,7 +171,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Portfolio capital (realized cash balance)</a:t>
+              <a:t>Quickfix portfolio capital (realized cash balance)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$177</f>
+              <f>'equity_curve'!$A$2:$A$180</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$177</f>
+              <f>'equity_curve'!$B$2:$B$180</f>
             </numRef>
           </val>
         </ser>
@@ -590,11 +590,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -607,216 +607,252 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>starting capital</t>
+          <t>rule 4</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>100,000</t>
+          <t>target = 5R, or an opposite reversal nearer than 5R</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>final capital (net)</t>
+          <t>starting capital</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>255,990.65</t>
+          <t>100,000</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>total return (net)</t>
+          <t>final capital (net)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>+155.99%</t>
+          <t>268,674.86</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>final capital (gross)</t>
+          <t>total return (net)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>264,080  (+164.08%)</t>
+          <t>+168.67%</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>slippage paid</t>
+          <t>final capital (gross)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5,106  (8.1 pts of return)</t>
+          <t>277,177  (+177.18%)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>max drawdown</t>
+          <t>slippage paid</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5.85%</t>
+          <t>5,118  (8.5 pts of return)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>closed trades</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>77</v>
+          <t>max drawdown</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>5.85%</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>win rate</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>40.3%</t>
-        </is>
+          <t>closed trades</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>78</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>longest win streak</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>7</v>
+          <t>win rate</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>41.0%</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>longest loss streak</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>6</v>
+          <t>average hold</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2.3 bars</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>average win</t>
+          <t>average winner</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7,455  (+4.79%)</t>
+          <t>+4.80R  (best +5.00R)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>average loss</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>-1,631  (-1.05%)</t>
-        </is>
+          <t>longest win streak</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>markets with trades</t>
+          <t>longest loss streak</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>max concurrent positions</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>5</v>
+          <t>average win</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>7,618  (+4.80%)</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>time in market</t>
+          <t>average loss</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>73% of trading days</t>
+          <t>-1,631  (-1.05%)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>peak risk committed</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>5.0% of live balance</t>
-        </is>
+          <t>markets with trades</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>window</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2025-12-18 -&gt; 2026-07-20</t>
-        </is>
+          <t>max concurrent positions</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>risk per trade</t>
+          <t>time in market</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1.0% of liquid capital</t>
+          <t>74% of trading days</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>peak risk committed</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>5.0% of live balance</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>window</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2025-12-18 -&gt; 2026-07-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>risk per trade</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1.0% of liquid capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
           <t>slippage model</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>entry 1t, target 1t, stop 3t</t>
         </is>
@@ -833,7 +869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H177"/>
+  <dimension ref="A1:H180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5389,22 +5425,98 @@
         <v>46223</v>
       </c>
       <c r="B177" s="5" t="n">
-        <v>255990.65</v>
+        <v>256010.24</v>
       </c>
       <c r="C177" s="5" t="n">
+        <v>4624.78</v>
+      </c>
+      <c r="D177" s="5" t="n">
+        <v>251385.46</v>
+      </c>
+      <c r="E177" t="n">
+        <v>2</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>EURO_Futures, Gold_Futures_COMEX</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="4" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B178" s="5" t="n">
+        <v>268682.41</v>
+      </c>
+      <c r="C178" s="5" t="n">
+        <v>2085.54</v>
+      </c>
+      <c r="D178" s="5" t="n">
+        <v>266596.88</v>
+      </c>
+      <c r="E178" t="n">
+        <v>1</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>EURO_Futures</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX target_5r (+12,672)</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="4" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B179" s="5" t="n">
+        <v>268682.41</v>
+      </c>
+      <c r="C179" s="5" t="n">
+        <v>2085.54</v>
+      </c>
+      <c r="D179" s="5" t="n">
+        <v>266596.88</v>
+      </c>
+      <c r="E179" t="n">
+        <v>1</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>EURO_Futures</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="4" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B180" s="5" t="n">
+        <v>268674.86</v>
+      </c>
+      <c r="C180" s="5" t="n">
         <v>-0</v>
       </c>
-      <c r="D177" s="5" t="n">
-        <v>255990.65</v>
-      </c>
-      <c r="E177" t="n">
+      <c r="D180" s="5" t="n">
+        <v>268674.86</v>
+      </c>
+      <c r="E180" t="n">
         <v>0</v>
       </c>
-      <c r="F177" t="inlineStr"/>
-      <c r="G177" t="inlineStr"/>
-      <c r="H177" t="inlineStr">
-        <is>
-          <t>EURO_Futures open_at_end (open-&gt;closed 0); Gold_Futures_COMEX open_at_end (open-&gt;closed 0)</t>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>EURO_Futures open_at_end (open-&gt;closed 0)</t>
         </is>
       </c>
     </row>
@@ -8898,7 +9010,7 @@
         <v>-7.56</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>256002.69</v>
+        <v>268674.86</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
@@ -9534,14 +9646,22 @@
           <t>2026-07-17</t>
         </is>
       </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2026-07-21</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>2</v>
+      </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G81" t="n">
-        <v>0.005</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H81" t="n">
-        <v>-0.005</v>
+        <v>4.991</v>
       </c>
       <c r="I81" s="5" t="n">
         <v>253924.71</v>
@@ -9549,15 +9669,15 @@
       <c r="J81" s="5" t="n">
         <v>2539.25</v>
       </c>
-      <c r="K81" s="7" t="n">
-        <v>-12.03</v>
+      <c r="K81" s="6" t="n">
+        <v>12672.17</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>255990.65</v>
+        <v>268682.41</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>open_at_end</t>
+          <t>target_5r</t>
         </is>
       </c>
     </row>

--- a/output/quickfix_portfolio_daily.xlsx
+++ b/output/quickfix_portfolio_daily.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>268,674.86</t>
+          <t>271,276.03</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+168.67%</t>
+          <t>+171.28%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>277,177  (+177.18%)</t>
+          <t>279,949  (+179.95%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5,118  (8.5 pts of return)</t>
+          <t>5,199  (8.7 pts of return)</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="11">
@@ -706,7 +706,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>41.8%</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2.3 bars</t>
+          <t>2.2 bars</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>+4.80R  (best +5.00R)</t>
+          <t>+4.68R  (best +5.00R)</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>7,618  (+4.80%)</t>
+          <t>7,479  (+4.68%)</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-1,631  (-1.05%)</t>
+          <t>-1,642  (-1.05%)</t>
         </is>
       </c>
     </row>
@@ -3641,13 +3641,13 @@
         <v>46129</v>
       </c>
       <c r="B112" s="5" t="n">
-        <v>157938.96</v>
+        <v>159454.29</v>
       </c>
       <c r="C112" s="5" t="n">
         <v>1410.75</v>
       </c>
       <c r="D112" s="5" t="n">
-        <v>156528.22</v>
+        <v>158043.54</v>
       </c>
       <c r="E112" t="n">
         <v>1</v>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance stop (-1,459); USD_EUR_Cross_Rate open_at_end (open-&gt;closed 0)</t>
+          <t>Bitcoin_Per_USD_Binance stop (-1,459); USD_EUR_Cross_Rate data_end (+1,465)</t>
         </is>
       </c>
     </row>
@@ -3673,13 +3673,13 @@
         <v>46130</v>
       </c>
       <c r="B113" s="5" t="n">
-        <v>157938.96</v>
+        <v>159454.29</v>
       </c>
       <c r="C113" s="5" t="n">
         <v>1410.75</v>
       </c>
       <c r="D113" s="5" t="n">
-        <v>156528.22</v>
+        <v>158043.54</v>
       </c>
       <c r="E113" t="n">
         <v>1</v>
@@ -3697,13 +3697,13 @@
         <v>46132</v>
       </c>
       <c r="B114" s="5" t="n">
-        <v>157938.96</v>
+        <v>159454.29</v>
       </c>
       <c r="C114" s="5" t="n">
         <v>1410.75</v>
       </c>
       <c r="D114" s="5" t="n">
-        <v>156528.22</v>
+        <v>158043.54</v>
       </c>
       <c r="E114" t="n">
         <v>1</v>
@@ -3721,13 +3721,13 @@
         <v>46133</v>
       </c>
       <c r="B115" s="5" t="n">
-        <v>157938.96</v>
+        <v>159454.29</v>
       </c>
       <c r="C115" s="5" t="n">
         <v>1410.75</v>
       </c>
       <c r="D115" s="5" t="n">
-        <v>156528.22</v>
+        <v>158043.54</v>
       </c>
       <c r="E115" t="n">
         <v>1</v>
@@ -3745,13 +3745,13 @@
         <v>46134</v>
       </c>
       <c r="B116" s="5" t="n">
-        <v>156517.47</v>
+        <v>158032.8</v>
       </c>
       <c r="C116" s="5" t="n">
-        <v>1565.28</v>
+        <v>1580.44</v>
       </c>
       <c r="D116" s="5" t="n">
-        <v>154952.19</v>
+        <v>156452.36</v>
       </c>
       <c r="E116" t="n">
         <v>1</v>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini short (risk 1,565)</t>
+          <t>Dow_Futures_E_mini short (risk 1,580)</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -3777,13 +3777,13 @@
         <v>46135</v>
       </c>
       <c r="B117" s="5" t="n">
-        <v>164292.56</v>
+        <v>165883.16</v>
       </c>
       <c r="C117" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D117" s="5" t="n">
-        <v>164292.56</v>
+        <v>165883.16</v>
       </c>
       <c r="E117" t="n">
         <v>0</v>
@@ -3792,7 +3792,7 @@
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini target_5r (+7,775)</t>
+          <t>Dow_Futures_E_mini target_5r (+7,850)</t>
         </is>
       </c>
     </row>
@@ -3801,13 +3801,13 @@
         <v>46136</v>
       </c>
       <c r="B118" s="5" t="n">
-        <v>164292.56</v>
+        <v>165883.16</v>
       </c>
       <c r="C118" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D118" s="5" t="n">
-        <v>164292.56</v>
+        <v>165883.16</v>
       </c>
       <c r="E118" t="n">
         <v>0</v>
@@ -3821,13 +3821,13 @@
         <v>46139</v>
       </c>
       <c r="B119" s="5" t="n">
-        <v>164292.56</v>
+        <v>165883.16</v>
       </c>
       <c r="C119" s="5" t="n">
-        <v>1642.93</v>
+        <v>1658.83</v>
       </c>
       <c r="D119" s="5" t="n">
-        <v>162649.63</v>
+        <v>164224.32</v>
       </c>
       <c r="E119" t="n">
         <v>1</v>
@@ -3839,7 +3839,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME short (risk 1,643)</t>
+          <t>Bitcoin_Per_USD_CME short (risk 1,659)</t>
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
@@ -3849,13 +3849,13 @@
         <v>46140</v>
       </c>
       <c r="B120" s="5" t="n">
-        <v>172500.43</v>
+        <v>174170.49</v>
       </c>
       <c r="C120" s="5" t="n">
-        <v>1626.5</v>
+        <v>1642.24</v>
       </c>
       <c r="D120" s="5" t="n">
-        <v>170873.93</v>
+        <v>172528.24</v>
       </c>
       <c r="E120" t="n">
         <v>1</v>
@@ -3867,12 +3867,12 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini short (risk 1,626)</t>
+          <t>S_P_500_E_mini short (risk 1,642)</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME target_5r (+8,208)</t>
+          <t>Bitcoin_Per_USD_CME target_5r (+8,287)</t>
         </is>
       </c>
     </row>
@@ -3881,13 +3881,13 @@
         <v>46141</v>
       </c>
       <c r="B121" s="5" t="n">
-        <v>172500.43</v>
+        <v>174170.49</v>
       </c>
       <c r="C121" s="5" t="n">
-        <v>3335.24</v>
+        <v>3367.53</v>
       </c>
       <c r="D121" s="5" t="n">
-        <v>169165.19</v>
+        <v>170802.96</v>
       </c>
       <c r="E121" t="n">
         <v>2</v>
@@ -3899,7 +3899,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 1,709)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 1,725)</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
@@ -3909,13 +3909,13 @@
         <v>46142</v>
       </c>
       <c r="B122" s="5" t="n">
-        <v>170870.04</v>
+        <v>172524.31</v>
       </c>
       <c r="C122" s="5" t="n">
-        <v>3400.39</v>
+        <v>3433.31</v>
       </c>
       <c r="D122" s="5" t="n">
-        <v>167469.64</v>
+        <v>169091</v>
       </c>
       <c r="E122" t="n">
         <v>2</v>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures short (risk 1,692)</t>
+          <t>Corn_CBOT_Futures short (risk 1,708)</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini stop (-1,630)</t>
+          <t>S_P_500_E_mini stop (-1,646)</t>
         </is>
       </c>
     </row>
@@ -3941,13 +3941,13 @@
         <v>46143</v>
       </c>
       <c r="B123" s="5" t="n">
-        <v>168822.25</v>
+        <v>170456.7</v>
       </c>
       <c r="C123" s="5" t="n">
-        <v>6682.76</v>
+        <v>6747.45</v>
       </c>
       <c r="D123" s="5" t="n">
-        <v>162139.49</v>
+        <v>163709.24</v>
       </c>
       <c r="E123" t="n">
         <v>4</v>
@@ -3959,12 +3959,12 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Japanese_Yen_Futures short (risk 1,675); Live_Cattle_Futures_CME short (risk 1,658); US_Dollar_Index_Futures long (risk 1,641)</t>
+          <t>Japanese_Yen_Futures short (risk 1,691); Live_Cattle_Futures_CME short (risk 1,674); US_Dollar_Index_Futures long (risk 1,657)</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures stop (-2,048)</t>
+          <t>Corn_CBOT_Futures stop (-2,068)</t>
         </is>
       </c>
     </row>
@@ -3973,13 +3973,13 @@
         <v>46146</v>
       </c>
       <c r="B124" s="5" t="n">
-        <v>168822.25</v>
+        <v>170456.7</v>
       </c>
       <c r="C124" s="5" t="n">
-        <v>8304.15</v>
+        <v>8384.549999999999</v>
       </c>
       <c r="D124" s="5" t="n">
-        <v>160518.1</v>
+        <v>162072.15</v>
       </c>
       <c r="E124" t="n">
         <v>5</v>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini short (risk 1,621)</t>
+          <t>Nasdaq_100_E_mini short (risk 1,637)</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
@@ -4001,13 +4001,13 @@
         <v>46147</v>
       </c>
       <c r="B125" s="5" t="n">
-        <v>167199.75</v>
+        <v>168818.49</v>
       </c>
       <c r="C125" s="5" t="n">
-        <v>8287.940000000001</v>
+        <v>8368.18</v>
       </c>
       <c r="D125" s="5" t="n">
-        <v>158911.81</v>
+        <v>160450.31</v>
       </c>
       <c r="E125" t="n">
         <v>5</v>
@@ -4019,12 +4019,12 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures short (risk 1,605)</t>
+          <t>Corn_CBOT_Futures short (risk 1,621)</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini stop (-1,622)</t>
+          <t>Nasdaq_100_E_mini stop (-1,638)</t>
         </is>
       </c>
     </row>
@@ -4033,13 +4033,13 @@
         <v>46148</v>
       </c>
       <c r="B126" s="5" t="n">
-        <v>179915.19</v>
+        <v>181657.03</v>
       </c>
       <c r="C126" s="5" t="n">
-        <v>3247.07</v>
+        <v>3278.5</v>
       </c>
       <c r="D126" s="5" t="n">
-        <v>176668.12</v>
+        <v>178378.53</v>
       </c>
       <c r="E126" t="n">
         <v>2</v>
@@ -4051,12 +4051,12 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME short (risk 1,589)</t>
+          <t>Bitcoin_Per_USD_CME short (risk 1,605)</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT target_5r (+8,505); Corn_CBOT_Futures target_5r (+7,734); Japanese_Yen_Futures stop (-1,856); US_Dollar_Index_Futures stop (-1,668)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT target_5r (+8,588); Corn_CBOT_Futures target_5r (+7,809); Japanese_Yen_Futures stop (-1,874); US_Dollar_Index_Futures stop (-1,684)</t>
         </is>
       </c>
     </row>
@@ -4065,13 +4065,13 @@
         <v>46149</v>
       </c>
       <c r="B127" s="5" t="n">
-        <v>196118.27</v>
+        <v>198016.99</v>
       </c>
       <c r="C127" s="5" t="n">
-        <v>3515.7</v>
+        <v>3549.73</v>
       </c>
       <c r="D127" s="5" t="n">
-        <v>192602.58</v>
+        <v>194467.26</v>
       </c>
       <c r="E127" t="n">
         <v>2</v>
@@ -4083,12 +4083,12 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>EURO_Futures short (risk 1,767); NY_Platinum_Futures short (risk 1,749)</t>
+          <t>EURO_Futures short (risk 1,784); NY_Platinum_Futures short (risk 1,766)</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME target_5r (+7,940); Live_Cattle_Futures_CME target_5r (+8,263)</t>
+          <t>Bitcoin_Per_USD_CME target_5r (+8,017); Live_Cattle_Futures_CME target_5r (+8,343)</t>
         </is>
       </c>
     </row>
@@ -4097,13 +4097,13 @@
         <v>46150</v>
       </c>
       <c r="B128" s="5" t="n">
-        <v>194306.29</v>
+        <v>196187.46</v>
       </c>
       <c r="C128" s="5" t="n">
-        <v>1749.01</v>
+        <v>1765.95</v>
       </c>
       <c r="D128" s="5" t="n">
-        <v>192557.28</v>
+        <v>194421.52</v>
       </c>
       <c r="E128" t="n">
         <v>1</v>
@@ -4116,7 +4116,7 @@
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
-          <t>EURO_Futures stop (-1,812)</t>
+          <t>EURO_Futures stop (-1,830)</t>
         </is>
       </c>
     </row>
@@ -4125,13 +4125,13 @@
         <v>46153</v>
       </c>
       <c r="B129" s="5" t="n">
-        <v>192533.23</v>
+        <v>194397.24</v>
       </c>
       <c r="C129" s="5" t="n">
-        <v>1925.57</v>
+        <v>1944.22</v>
       </c>
       <c r="D129" s="5" t="n">
-        <v>190607.66</v>
+        <v>192453.03</v>
       </c>
       <c r="E129" t="n">
         <v>1</v>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX short (risk 1,926)</t>
+          <t>Gold_Futures_COMEX short (risk 1,944)</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures stop (-1,773)</t>
+          <t>NY_Platinum_Futures stop (-1,790)</t>
         </is>
       </c>
     </row>
@@ -4157,13 +4157,13 @@
         <v>46154</v>
       </c>
       <c r="B130" s="5" t="n">
-        <v>190546.04</v>
+        <v>192390.81</v>
       </c>
       <c r="C130" s="5" t="n">
-        <v>1906.08</v>
+        <v>1924.53</v>
       </c>
       <c r="D130" s="5" t="n">
-        <v>188639.97</v>
+        <v>190466.28</v>
       </c>
       <c r="E130" t="n">
         <v>1</v>
@@ -4175,12 +4175,12 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX short (risk 1,906)</t>
+          <t>Silver_Futures_COMEX short (risk 1,925)</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX unknown_pl (-1,987)</t>
+          <t>Gold_Futures_COMEX unknown_pl (-2,006)</t>
         </is>
       </c>
     </row>
@@ -4189,13 +4189,13 @@
         <v>46155</v>
       </c>
       <c r="B131" s="5" t="n">
-        <v>188636</v>
+        <v>190462.27</v>
       </c>
       <c r="C131" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D131" s="5" t="n">
-        <v>188636</v>
+        <v>190462.27</v>
       </c>
       <c r="E131" t="n">
         <v>0</v>
@@ -4204,7 +4204,7 @@
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX stop (-1,910)</t>
+          <t>Silver_Futures_COMEX stop (-1,929)</t>
         </is>
       </c>
     </row>
@@ -4213,13 +4213,13 @@
         <v>46156</v>
       </c>
       <c r="B132" s="5" t="n">
-        <v>188636</v>
+        <v>190462.27</v>
       </c>
       <c r="C132" s="5" t="n">
-        <v>1886.36</v>
+        <v>1904.62</v>
       </c>
       <c r="D132" s="5" t="n">
-        <v>186749.64</v>
+        <v>188557.65</v>
       </c>
       <c r="E132" t="n">
         <v>1</v>
@@ -4231,7 +4231,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 1,886)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 1,905)</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
@@ -4241,13 +4241,13 @@
         <v>46157</v>
       </c>
       <c r="B133" s="5" t="n">
-        <v>198016.11</v>
+        <v>199933.21</v>
       </c>
       <c r="C133" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D133" s="5" t="n">
-        <v>198016.11</v>
+        <v>199933.21</v>
       </c>
       <c r="E133" t="n">
         <v>0</v>
@@ -4256,7 +4256,7 @@
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT target_5r (+9,380)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT target_5r (+9,471)</t>
         </is>
       </c>
     </row>
@@ -4265,13 +4265,13 @@
         <v>46160</v>
       </c>
       <c r="B134" s="5" t="n">
-        <v>198016.11</v>
+        <v>199933.21</v>
       </c>
       <c r="C134" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>198016.11</v>
+        <v>199933.21</v>
       </c>
       <c r="E134" t="n">
         <v>0</v>
@@ -4285,13 +4285,13 @@
         <v>46161</v>
       </c>
       <c r="B135" s="5" t="n">
-        <v>198016.11</v>
+        <v>199933.21</v>
       </c>
       <c r="C135" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>198016.11</v>
+        <v>199933.21</v>
       </c>
       <c r="E135" t="n">
         <v>0</v>
@@ -4305,13 +4305,13 @@
         <v>46162</v>
       </c>
       <c r="B136" s="5" t="n">
-        <v>198016.11</v>
+        <v>199933.21</v>
       </c>
       <c r="C136" s="5" t="n">
-        <v>1980.16</v>
+        <v>1999.33</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>196035.95</v>
+        <v>197933.87</v>
       </c>
       <c r="E136" t="n">
         <v>1</v>
@@ -4323,7 +4323,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures short (risk 1,980)</t>
+          <t>US_Dollar_Index_Futures short (risk 1,999)</t>
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
@@ -4333,13 +4333,13 @@
         <v>46163</v>
       </c>
       <c r="B137" s="5" t="n">
-        <v>198016.11</v>
+        <v>199933.21</v>
       </c>
       <c r="C137" s="5" t="n">
-        <v>3940.52</v>
+        <v>3978.67</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>194075.59</v>
+        <v>195954.53</v>
       </c>
       <c r="E137" t="n">
         <v>2</v>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures long (risk 1,960)</t>
+          <t>NY_Palladium_Futures long (risk 1,979)</t>
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
@@ -4361,13 +4361,13 @@
         <v>46164</v>
       </c>
       <c r="B138" s="5" t="n">
-        <v>198016.11</v>
+        <v>199933.21</v>
       </c>
       <c r="C138" s="5" t="n">
-        <v>3940.52</v>
+        <v>3978.67</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>194075.59</v>
+        <v>195954.53</v>
       </c>
       <c r="E138" t="n">
         <v>2</v>
@@ -4385,13 +4385,13 @@
         <v>46167</v>
       </c>
       <c r="B139" s="5" t="n">
-        <v>198016.11</v>
+        <v>199933.21</v>
       </c>
       <c r="C139" s="5" t="n">
-        <v>3940.52</v>
+        <v>3978.67</v>
       </c>
       <c r="D139" s="5" t="n">
-        <v>194075.59</v>
+        <v>195954.53</v>
       </c>
       <c r="E139" t="n">
         <v>2</v>
@@ -4409,13 +4409,13 @@
         <v>46168</v>
       </c>
       <c r="B140" s="5" t="n">
-        <v>198016.11</v>
+        <v>199933.21</v>
       </c>
       <c r="C140" s="5" t="n">
-        <v>3940.52</v>
+        <v>3978.67</v>
       </c>
       <c r="D140" s="5" t="n">
-        <v>194075.59</v>
+        <v>195954.53</v>
       </c>
       <c r="E140" t="n">
         <v>2</v>
@@ -4433,13 +4433,13 @@
         <v>46169</v>
       </c>
       <c r="B141" s="5" t="n">
-        <v>198016.11</v>
+        <v>199933.21</v>
       </c>
       <c r="C141" s="5" t="n">
-        <v>3940.52</v>
+        <v>3978.67</v>
       </c>
       <c r="D141" s="5" t="n">
-        <v>194075.59</v>
+        <v>195954.53</v>
       </c>
       <c r="E141" t="n">
         <v>2</v>
@@ -4457,13 +4457,13 @@
         <v>46170</v>
       </c>
       <c r="B142" s="5" t="n">
-        <v>198016.11</v>
+        <v>199933.21</v>
       </c>
       <c r="C142" s="5" t="n">
-        <v>5881.28</v>
+        <v>5938.22</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>192134.84</v>
+        <v>193994.99</v>
       </c>
       <c r="E142" t="n">
         <v>3</v>
@@ -4475,7 +4475,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX long (risk 1,941)</t>
+          <t>Silver_Futures_COMEX long (risk 1,960)</t>
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
@@ -4485,13 +4485,13 @@
         <v>46174</v>
       </c>
       <c r="B143" s="5" t="n">
-        <v>198016.11</v>
+        <v>199933.21</v>
       </c>
       <c r="C143" s="5" t="n">
-        <v>5881.28</v>
+        <v>5938.22</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>192134.84</v>
+        <v>193994.99</v>
       </c>
       <c r="E143" t="n">
         <v>3</v>
@@ -4509,13 +4509,13 @@
         <v>46175</v>
       </c>
       <c r="B144" s="5" t="n">
-        <v>198016.11</v>
+        <v>199933.21</v>
       </c>
       <c r="C144" s="5" t="n">
-        <v>5881.28</v>
+        <v>5938.22</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>192134.84</v>
+        <v>193994.99</v>
       </c>
       <c r="E144" t="n">
         <v>3</v>
@@ -4533,13 +4533,13 @@
         <v>46176</v>
       </c>
       <c r="B145" s="5" t="n">
-        <v>196009.63</v>
+        <v>197907.29</v>
       </c>
       <c r="C145" s="5" t="n">
-        <v>3920.92</v>
+        <v>3958.88</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>192088.71</v>
+        <v>193948.42</v>
       </c>
       <c r="E145" t="n">
         <v>2</v>
@@ -4552,7 +4552,7 @@
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures stop (-2,006)</t>
+          <t>NY_Palladium_Futures stop (-2,026)</t>
         </is>
       </c>
     </row>
@@ -4561,13 +4561,13 @@
         <v>46177</v>
       </c>
       <c r="B146" s="5" t="n">
-        <v>196009.63</v>
+        <v>197907.29</v>
       </c>
       <c r="C146" s="5" t="n">
-        <v>3920.92</v>
+        <v>3958.88</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>192088.71</v>
+        <v>193948.42</v>
       </c>
       <c r="E146" t="n">
         <v>2</v>
@@ -4585,13 +4585,13 @@
         <v>46178</v>
       </c>
       <c r="B147" s="5" t="n">
-        <v>192043.89</v>
+        <v>193903.16</v>
       </c>
       <c r="C147" s="5" t="n">
-        <v>1920.89</v>
+        <v>1939.48</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>190123</v>
+        <v>191963.67</v>
       </c>
       <c r="E147" t="n">
         <v>1</v>
@@ -4603,12 +4603,12 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini short (risk 1,921)</t>
+          <t>Dow_Futures_E_mini short (risk 1,939)</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX stop (-1,945); US_Dollar_Index_Futures stop (-2,021)</t>
+          <t>Silver_Futures_COMEX stop (-1,964); US_Dollar_Index_Futures stop (-2,040)</t>
         </is>
       </c>
     </row>
@@ -4617,13 +4617,13 @@
         <v>46181</v>
       </c>
       <c r="B148" s="5" t="n">
-        <v>201612.08</v>
+        <v>203563.98</v>
       </c>
       <c r="C148" s="5" t="n">
-        <v>3783.45</v>
+        <v>3820.08</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>197828.63</v>
+        <v>199743.91</v>
       </c>
       <c r="E148" t="n">
         <v>2</v>
@@ -4635,12 +4635,12 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX long (risk 1,901); US_Dollar_Index_Futures short (risk 1,882)</t>
+          <t>Gold_Futures_COMEX long (risk 1,920); US_Dollar_Index_Futures short (risk 1,900)</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini target_5r (+9,568)</t>
+          <t>Dow_Futures_E_mini target_5r (+9,661)</t>
         </is>
       </c>
     </row>
@@ -4649,13 +4649,13 @@
         <v>46182</v>
       </c>
       <c r="B149" s="5" t="n">
-        <v>199696.79</v>
+        <v>201630.15</v>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1882.22</v>
+        <v>1900.44</v>
       </c>
       <c r="D149" s="5" t="n">
-        <v>197814.57</v>
+        <v>199729.71</v>
       </c>
       <c r="E149" t="n">
         <v>1</v>
@@ -4668,7 +4668,7 @@
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX stop (-1,915)</t>
+          <t>Gold_Futures_COMEX stop (-1,934)</t>
         </is>
       </c>
     </row>
@@ -4677,13 +4677,13 @@
         <v>46183</v>
       </c>
       <c r="B150" s="5" t="n">
-        <v>199696.79</v>
+        <v>201630.15</v>
       </c>
       <c r="C150" s="5" t="n">
-        <v>1882.22</v>
+        <v>1900.44</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>197814.57</v>
+        <v>199729.71</v>
       </c>
       <c r="E150" t="n">
         <v>1</v>
@@ -4701,13 +4701,13 @@
         <v>46184</v>
       </c>
       <c r="B151" s="5" t="n">
-        <v>197758.8</v>
+        <v>199673.4</v>
       </c>
       <c r="C151" s="5" t="n">
-        <v>1978.15</v>
+        <v>1997.3</v>
       </c>
       <c r="D151" s="5" t="n">
-        <v>195780.66</v>
+        <v>197676.11</v>
       </c>
       <c r="E151" t="n">
         <v>1</v>
@@ -4719,12 +4719,12 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX long (risk 1,978)</t>
+          <t>Gold_Futures_COMEX long (risk 1,997)</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures stop (-1,938)</t>
+          <t>US_Dollar_Index_Futures stop (-1,957)</t>
         </is>
       </c>
     </row>
@@ -4733,13 +4733,13 @@
         <v>46185</v>
       </c>
       <c r="B152" s="5" t="n">
-        <v>197758.8</v>
+        <v>199673.4</v>
       </c>
       <c r="C152" s="5" t="n">
-        <v>3935.95</v>
+        <v>3974.06</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>193822.85</v>
+        <v>195699.35</v>
       </c>
       <c r="E152" t="n">
         <v>2</v>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures long (risk 1,958)</t>
+          <t>Corn_CBOT_Futures long (risk 1,977)</t>
         </is>
       </c>
       <c r="H152" t="inlineStr"/>
@@ -4761,13 +4761,13 @@
         <v>46188</v>
       </c>
       <c r="B153" s="5" t="n">
-        <v>205394.73</v>
+        <v>207383.25</v>
       </c>
       <c r="C153" s="5" t="n">
-        <v>1938.23</v>
+        <v>1956.99</v>
       </c>
       <c r="D153" s="5" t="n">
-        <v>203456.5</v>
+        <v>205426.26</v>
       </c>
       <c r="E153" t="n">
         <v>1</v>
@@ -4779,12 +4779,12 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT long (risk 1,938)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT long (risk 1,957)</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures stop (-2,248); Gold_Futures_COMEX target_5r (+9,884)</t>
+          <t>Corn_CBOT_Futures stop (-2,270); Gold_Futures_COMEX target_5r (+9,979)</t>
         </is>
       </c>
     </row>
@@ -4793,13 +4793,13 @@
         <v>46189</v>
       </c>
       <c r="B154" s="5" t="n">
-        <v>205394.73</v>
+        <v>207383.25</v>
       </c>
       <c r="C154" s="5" t="n">
-        <v>1938.23</v>
+        <v>1956.99</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>203456.5</v>
+        <v>205426.26</v>
       </c>
       <c r="E154" t="n">
         <v>1</v>
@@ -4817,13 +4817,13 @@
         <v>46190</v>
       </c>
       <c r="B155" s="5" t="n">
-        <v>214880.22</v>
+        <v>216960.58</v>
       </c>
       <c r="C155" s="5" t="n">
-        <v>2034.56</v>
+        <v>2054.26</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>212845.65</v>
+        <v>214906.32</v>
       </c>
       <c r="E155" t="n">
         <v>1</v>
@@ -4835,12 +4835,12 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures short (risk 2,035)</t>
+          <t>US_Dollar_Index_Futures short (risk 2,054)</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT bullish_reversal (+9,485)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT bullish_reversal (+9,577)</t>
         </is>
       </c>
     </row>
@@ -4849,13 +4849,13 @@
         <v>46191</v>
       </c>
       <c r="B156" s="5" t="n">
-        <v>212818.07</v>
+        <v>214878.46</v>
       </c>
       <c r="C156" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>212818.07</v>
+        <v>214878.46</v>
       </c>
       <c r="E156" t="n">
         <v>0</v>
@@ -4864,7 +4864,7 @@
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures stop (-2,062)</t>
+          <t>US_Dollar_Index_Futures stop (-2,082)</t>
         </is>
       </c>
     </row>
@@ -4873,13 +4873,13 @@
         <v>46192</v>
       </c>
       <c r="B157" s="5" t="n">
-        <v>212818.07</v>
+        <v>214878.46</v>
       </c>
       <c r="C157" s="5" t="n">
-        <v>2128.18</v>
+        <v>2148.78</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>210689.88</v>
+        <v>212729.68</v>
       </c>
       <c r="E157" t="n">
         <v>1</v>
@@ -4891,7 +4891,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures short (risk 2,128)</t>
+          <t>US_Dollar_Index_Futures short (risk 2,149)</t>
         </is>
       </c>
       <c r="H157" t="inlineStr"/>
@@ -4901,13 +4901,13 @@
         <v>46195</v>
       </c>
       <c r="B158" s="5" t="n">
-        <v>212818.07</v>
+        <v>214878.46</v>
       </c>
       <c r="C158" s="5" t="n">
-        <v>2128.18</v>
+        <v>2148.78</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>210689.88</v>
+        <v>212729.68</v>
       </c>
       <c r="E158" t="n">
         <v>1</v>
@@ -4925,13 +4925,13 @@
         <v>46196</v>
       </c>
       <c r="B159" s="5" t="n">
-        <v>210660.53</v>
+        <v>212700.04</v>
       </c>
       <c r="C159" s="5" t="n">
-        <v>2106.9</v>
+        <v>2127.3</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>208553.63</v>
+        <v>210572.74</v>
       </c>
       <c r="E159" t="n">
         <v>1</v>
@@ -4943,12 +4943,12 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures long (risk 2,107)</t>
+          <t>NY_Platinum_Futures long (risk 2,127)</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures stop (-2,158)</t>
+          <t>US_Dollar_Index_Futures stop (-2,178)</t>
         </is>
       </c>
     </row>
@@ -4957,13 +4957,13 @@
         <v>46197</v>
       </c>
       <c r="B160" s="5" t="n">
-        <v>208512.52</v>
+        <v>210531.23</v>
       </c>
       <c r="C160" s="5" t="n">
-        <v>2085.54</v>
+        <v>2105.73</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>206426.98</v>
+        <v>208425.51</v>
       </c>
       <c r="E160" t="n">
         <v>1</v>
@@ -4975,12 +4975,12 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>EURO_Futures long (risk 2,086)</t>
+          <t>EURO_Futures long (risk 2,106)</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures stop (-2,148)</t>
+          <t>NY_Platinum_Futures stop (-2,169)</t>
         </is>
       </c>
     </row>
@@ -4989,13 +4989,13 @@
         <v>46198</v>
       </c>
       <c r="B161" s="5" t="n">
-        <v>208512.52</v>
+        <v>210531.23</v>
       </c>
       <c r="C161" s="5" t="n">
-        <v>10219.58</v>
+        <v>10318.52</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>198292.94</v>
+        <v>200212.71</v>
       </c>
       <c r="E161" t="n">
         <v>5</v>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures short (risk 2,064); NY_Palladium_Futures long (risk 2,044); NY_Platinum_Futures long (risk 2,023); US_Dollar_Index_Futures short (risk 2,003)</t>
+          <t>NY_Natural_Gas_Futures short (risk 2,084); NY_Palladium_Futures long (risk 2,063); NY_Platinum_Futures long (risk 2,043); US_Dollar_Index_Futures short (risk 2,022)</t>
         </is>
       </c>
       <c r="H161" t="inlineStr"/>
@@ -5017,13 +5017,13 @@
         <v>46199</v>
       </c>
       <c r="B162" s="5" t="n">
-        <v>226424.06</v>
+        <v>228616.18</v>
       </c>
       <c r="C162" s="5" t="n">
-        <v>4108.73</v>
+        <v>4148.51</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>222315.33</v>
+        <v>224467.67</v>
       </c>
       <c r="E162" t="n">
         <v>2</v>
@@ -5036,7 +5036,7 @@
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures stop (-2,233); NY_Palladium_Futures target_5r (+10,164); US_Dollar_Index_Futures target_5r (+9,980)</t>
+          <t>NY_Natural_Gas_Futures stop (-2,254); NY_Palladium_Futures target_5r (+10,263); US_Dollar_Index_Futures target_5r (+10,077)</t>
         </is>
       </c>
     </row>
@@ -5045,13 +5045,13 @@
         <v>46202</v>
       </c>
       <c r="B163" s="5" t="n">
-        <v>226424.06</v>
+        <v>228616.18</v>
       </c>
       <c r="C163" s="5" t="n">
-        <v>4108.73</v>
+        <v>4148.51</v>
       </c>
       <c r="D163" s="5" t="n">
-        <v>222315.33</v>
+        <v>224467.67</v>
       </c>
       <c r="E163" t="n">
         <v>2</v>
@@ -5069,13 +5069,13 @@
         <v>46203</v>
       </c>
       <c r="B164" s="5" t="n">
-        <v>226424.06</v>
+        <v>228616.18</v>
       </c>
       <c r="C164" s="5" t="n">
-        <v>10711.71</v>
+        <v>10815.42</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>215712.34</v>
+        <v>217800.76</v>
       </c>
       <c r="E164" t="n">
         <v>5</v>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT long (risk 2,223); German_Long_Bund short (risk 2,201); Gold_Futures_COMEX long (risk 2,179)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT long (risk 2,245); German_Long_Bund short (risk 2,222); Gold_Futures_COMEX long (risk 2,200)</t>
         </is>
       </c>
       <c r="H164" t="inlineStr"/>
@@ -5097,13 +5097,13 @@
         <v>46204</v>
       </c>
       <c r="B165" s="5" t="n">
-        <v>246263.69</v>
+        <v>248647.89</v>
       </c>
       <c r="C165" s="5" t="n">
-        <v>8579.129999999999</v>
+        <v>8662.190000000001</v>
       </c>
       <c r="D165" s="5" t="n">
-        <v>237684.56</v>
+        <v>239985.7</v>
       </c>
       <c r="E165" t="n">
         <v>4</v>
@@ -5115,12 +5115,12 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini short (risk 2,157); Sugar_World_CSCE_Futures short (risk 2,136)</t>
+          <t>Dow_Futures_E_mini short (risk 2,178); Sugar_World_CSCE_Futures short (risk 2,156)</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT target_5r (+11,007); Gold_Futures_COMEX target_5r (+10,879); NY_Platinum_Futures stop (-2,047)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT target_5r (+11,114); Gold_Futures_COMEX target_5r (+10,985); NY_Platinum_Futures stop (-2,067)</t>
         </is>
       </c>
     </row>
@@ -5129,13 +5129,13 @@
         <v>46205</v>
       </c>
       <c r="B166" s="5" t="n">
-        <v>244083.37</v>
+        <v>246446.46</v>
       </c>
       <c r="C166" s="5" t="n">
-        <v>6422.01</v>
+        <v>6484.18</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>237661.36</v>
+        <v>239962.28</v>
       </c>
       <c r="E166" t="n">
         <v>3</v>
@@ -5148,7 +5148,7 @@
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini stop (-2,180)</t>
+          <t>Dow_Futures_E_mini stop (-2,201)</t>
         </is>
       </c>
     </row>
@@ -5157,13 +5157,13 @@
         <v>46206</v>
       </c>
       <c r="B167" s="5" t="n">
-        <v>244083.37</v>
+        <v>246446.46</v>
       </c>
       <c r="C167" s="5" t="n">
-        <v>6422.01</v>
+        <v>6484.18</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>237661.36</v>
+        <v>239962.28</v>
       </c>
       <c r="E167" t="n">
         <v>3</v>
@@ -5181,13 +5181,13 @@
         <v>46210</v>
       </c>
       <c r="B168" s="5" t="n">
-        <v>252432.5</v>
+        <v>254876.42</v>
       </c>
       <c r="C168" s="5" t="n">
-        <v>2085.54</v>
+        <v>2105.73</v>
       </c>
       <c r="D168" s="5" t="n">
-        <v>250346.96</v>
+        <v>252770.69</v>
       </c>
       <c r="E168" t="n">
         <v>1</v>
@@ -5200,7 +5200,7 @@
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr">
         <is>
-          <t>German_Long_Bund target_5r (+10,813); Sugar_World_CSCE_Futures stop (-2,464)</t>
+          <t>German_Long_Bund target_5r (+10,918); Sugar_World_CSCE_Futures stop (-2,488)</t>
         </is>
       </c>
     </row>
@@ -5209,13 +5209,13 @@
         <v>46211</v>
       </c>
       <c r="B169" s="5" t="n">
-        <v>252432.5</v>
+        <v>254876.42</v>
       </c>
       <c r="C169" s="5" t="n">
-        <v>7067.44</v>
+        <v>7135.86</v>
       </c>
       <c r="D169" s="5" t="n">
-        <v>245365.06</v>
+        <v>247740.56</v>
       </c>
       <c r="E169" t="n">
         <v>3</v>
@@ -5227,7 +5227,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME long (risk 2,503); NY_Natural_Gas_Futures short (risk 2,478)</t>
+          <t>Live_Cattle_Futures_CME long (risk 2,528); NY_Natural_Gas_Futures short (risk 2,502)</t>
         </is>
       </c>
       <c r="H169" t="inlineStr"/>
@@ -5237,13 +5237,13 @@
         <v>46212</v>
       </c>
       <c r="B170" s="5" t="n">
-        <v>261325.83</v>
+        <v>263855.85</v>
       </c>
       <c r="C170" s="5" t="n">
-        <v>4589.01</v>
+        <v>4633.43</v>
       </c>
       <c r="D170" s="5" t="n">
-        <v>256736.82</v>
+        <v>259222.42</v>
       </c>
       <c r="E170" t="n">
         <v>2</v>
@@ -5256,7 +5256,7 @@
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures bearish_reversal (+8,893)</t>
+          <t>NY_Natural_Gas_Futures bearish_reversal (+8,979)</t>
         </is>
       </c>
     </row>
@@ -5265,13 +5265,13 @@
         <v>46213</v>
       </c>
       <c r="B171" s="5" t="n">
-        <v>258703.15</v>
+        <v>261207.78</v>
       </c>
       <c r="C171" s="5" t="n">
-        <v>2085.54</v>
+        <v>2105.73</v>
       </c>
       <c r="D171" s="5" t="n">
-        <v>256617.61</v>
+        <v>259102.05</v>
       </c>
       <c r="E171" t="n">
         <v>1</v>
@@ -5284,7 +5284,7 @@
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME stop (-2,623)</t>
+          <t>Live_Cattle_Futures_CME stop (-2,648)</t>
         </is>
       </c>
     </row>
@@ -5293,13 +5293,13 @@
         <v>46216</v>
       </c>
       <c r="B172" s="5" t="n">
-        <v>258703.15</v>
+        <v>261207.78</v>
       </c>
       <c r="C172" s="5" t="n">
-        <v>4651.71</v>
+        <v>4696.75</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>254051.43</v>
+        <v>256511.03</v>
       </c>
       <c r="E172" t="n">
         <v>2</v>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 2,566)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 2,591)</t>
         </is>
       </c>
       <c r="H172" t="inlineStr"/>
@@ -5321,13 +5321,13 @@
         <v>46217</v>
       </c>
       <c r="B173" s="5" t="n">
-        <v>258703.15</v>
+        <v>261207.78</v>
       </c>
       <c r="C173" s="5" t="n">
-        <v>4651.71</v>
+        <v>4696.75</v>
       </c>
       <c r="D173" s="5" t="n">
-        <v>254051.43</v>
+        <v>256511.03</v>
       </c>
       <c r="E173" t="n">
         <v>2</v>
@@ -5345,13 +5345,13 @@
         <v>46218</v>
       </c>
       <c r="B174" s="5" t="n">
-        <v>256010.24</v>
+        <v>258488.81</v>
       </c>
       <c r="C174" s="5" t="n">
-        <v>2085.54</v>
+        <v>2105.73</v>
       </c>
       <c r="D174" s="5" t="n">
-        <v>253924.71</v>
+        <v>256383.08</v>
       </c>
       <c r="E174" t="n">
         <v>1</v>
@@ -5364,7 +5364,7 @@
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT stop (-2,693)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT stop (-2,719)</t>
         </is>
       </c>
     </row>
@@ -5373,13 +5373,13 @@
         <v>46219</v>
       </c>
       <c r="B175" s="5" t="n">
-        <v>256010.24</v>
+        <v>258488.81</v>
       </c>
       <c r="C175" s="5" t="n">
-        <v>2085.54</v>
+        <v>2105.73</v>
       </c>
       <c r="D175" s="5" t="n">
-        <v>253924.71</v>
+        <v>256383.08</v>
       </c>
       <c r="E175" t="n">
         <v>1</v>
@@ -5397,13 +5397,13 @@
         <v>46220</v>
       </c>
       <c r="B176" s="5" t="n">
-        <v>256010.24</v>
+        <v>258488.81</v>
       </c>
       <c r="C176" s="5" t="n">
-        <v>4624.78</v>
+        <v>4669.56</v>
       </c>
       <c r="D176" s="5" t="n">
-        <v>251385.46</v>
+        <v>253819.25</v>
       </c>
       <c r="E176" t="n">
         <v>2</v>
@@ -5415,7 +5415,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX long (risk 2,539)</t>
+          <t>Gold_Futures_COMEX long (risk 2,564)</t>
         </is>
       </c>
       <c r="H176" t="inlineStr"/>
@@ -5425,13 +5425,13 @@
         <v>46223</v>
       </c>
       <c r="B177" s="5" t="n">
-        <v>256010.24</v>
+        <v>258488.81</v>
       </c>
       <c r="C177" s="5" t="n">
-        <v>4624.78</v>
+        <v>4669.56</v>
       </c>
       <c r="D177" s="5" t="n">
-        <v>251385.46</v>
+        <v>253819.25</v>
       </c>
       <c r="E177" t="n">
         <v>2</v>
@@ -5449,13 +5449,13 @@
         <v>46224</v>
       </c>
       <c r="B178" s="5" t="n">
-        <v>268682.41</v>
+        <v>271283.66</v>
       </c>
       <c r="C178" s="5" t="n">
-        <v>2085.54</v>
+        <v>2105.73</v>
       </c>
       <c r="D178" s="5" t="n">
-        <v>266596.88</v>
+        <v>269177.93</v>
       </c>
       <c r="E178" t="n">
         <v>1</v>
@@ -5468,7 +5468,7 @@
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX target_5r (+12,672)</t>
+          <t>Gold_Futures_COMEX target_5r (+12,795)</t>
         </is>
       </c>
     </row>
@@ -5477,13 +5477,13 @@
         <v>46225</v>
       </c>
       <c r="B179" s="5" t="n">
-        <v>268682.41</v>
+        <v>271283.66</v>
       </c>
       <c r="C179" s="5" t="n">
-        <v>2085.54</v>
+        <v>2105.73</v>
       </c>
       <c r="D179" s="5" t="n">
-        <v>266596.88</v>
+        <v>269177.93</v>
       </c>
       <c r="E179" t="n">
         <v>1</v>
@@ -5501,13 +5501,13 @@
         <v>46226</v>
       </c>
       <c r="B180" s="5" t="n">
-        <v>268674.86</v>
+        <v>271276.03</v>
       </c>
       <c r="C180" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D180" s="5" t="n">
-        <v>268674.86</v>
+        <v>271276.03</v>
       </c>
       <c r="E180" t="n">
         <v>0</v>
@@ -7496,7 +7496,7 @@
         <v>-1421.49</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>156517.47</v>
+        <v>158032.8</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -7520,14 +7520,22 @@
           <t>2026-04-17</t>
         </is>
       </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>0</v>
+      </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>0.032</v>
+        <v>0.065</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.032</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="I39" s="5" t="n">
         <v>156583.83</v>
@@ -7535,15 +7543,15 @@
       <c r="J39" s="5" t="n">
         <v>1565.84</v>
       </c>
-      <c r="K39" s="7" t="n">
-        <v>-50.51</v>
+      <c r="K39" s="6" t="n">
+        <v>1464.82</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>157938.96</v>
+        <v>159454.29</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>open_at_end</t>
+          <t>data_end</t>
         </is>
       </c>
     </row>
@@ -7581,16 +7589,16 @@
         <v>4.967</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>156528.22</v>
+        <v>158043.54</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>1565.28</v>
+        <v>1580.44</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>7775.09</v>
+        <v>7850.36</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>164292.56</v>
+        <v>165883.16</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -7632,16 +7640,16 @@
         <v>4.996</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>164292.56</v>
+        <v>165883.16</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>1642.93</v>
+        <v>1658.83</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>8207.870000000001</v>
+        <v>8287.33</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>172500.43</v>
+        <v>174170.49</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -7683,16 +7691,16 @@
         <v>-1.002</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>162649.63</v>
+        <v>164224.32</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>1626.5</v>
+        <v>1642.24</v>
       </c>
       <c r="K42" s="7" t="n">
-        <v>-1630.39</v>
+        <v>-1646.17</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>170870.04</v>
+        <v>172524.31</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -7734,16 +7742,16 @@
         <v>4.978</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>170873.93</v>
+        <v>172528.24</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>1708.74</v>
+        <v>1725.28</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>8505.299999999999</v>
+        <v>8587.639999999999</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>175705.05</v>
+        <v>177406.13</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -7785,16 +7793,16 @@
         <v>-1.211</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>169165.19</v>
+        <v>170802.96</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>1691.65</v>
+        <v>1708.03</v>
       </c>
       <c r="K44" s="7" t="n">
-        <v>-2047.79</v>
+        <v>-2067.61</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>168822.25</v>
+        <v>170456.7</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -7836,16 +7844,16 @@
         <v>-1.108</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>167469.64</v>
+        <v>169091</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>1674.7</v>
+        <v>1690.91</v>
       </c>
       <c r="K45" s="7" t="n">
-        <v>-1855.74</v>
+        <v>-1873.71</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>181583.35</v>
+        <v>183341.35</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -7887,16 +7895,16 @@
         <v>4.984</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>165794.95</v>
+        <v>167400.09</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>1657.95</v>
+        <v>1674</v>
       </c>
       <c r="K46" s="6" t="n">
-        <v>8263.219999999999</v>
+        <v>8343.219999999999</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>196118.27</v>
+        <v>198016.99</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -7938,16 +7946,16 @@
         <v>-1.016</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>164137</v>
+        <v>165726.09</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>1641.37</v>
+        <v>1657.26</v>
       </c>
       <c r="K47" s="7" t="n">
-        <v>-1668.17</v>
+        <v>-1684.32</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>179915.19</v>
+        <v>181657.03</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -7989,16 +7997,16 @@
         <v>-1.001</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>162139.49</v>
+        <v>163709.24</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>1621.39</v>
+        <v>1637.09</v>
       </c>
       <c r="K48" s="7" t="n">
-        <v>-1622.5</v>
+        <v>-1638.21</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>167199.75</v>
+        <v>168818.49</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -8040,16 +8048,16 @@
         <v>4.818</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>160518.1</v>
+        <v>162072.15</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>1605.18</v>
+        <v>1620.72</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>7734.05</v>
+        <v>7808.93</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>183439.1</v>
+        <v>185215.06</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -8091,16 +8099,16 @@
         <v>4.996</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>158911.81</v>
+        <v>160450.31</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>1589.12</v>
+        <v>1604.5</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>7939.86</v>
+        <v>8016.73</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>187855.05</v>
+        <v>189673.77</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
@@ -8142,16 +8150,16 @@
         <v>-1.026</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>176668.12</v>
+        <v>178378.53</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>1766.68</v>
+        <v>1783.79</v>
       </c>
       <c r="K51" s="7" t="n">
-        <v>-1811.98</v>
+        <v>-1829.52</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>194306.29</v>
+        <v>196187.46</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -8193,16 +8201,16 @@
         <v>-1.014</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>174901.44</v>
+        <v>176594.74</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>1749.01</v>
+        <v>1765.95</v>
       </c>
       <c r="K52" s="7" t="n">
-        <v>-1773.06</v>
+        <v>-1790.22</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>192533.23</v>
+        <v>194397.24</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -8244,16 +8252,16 @@
         <v>-1.032</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>192557.28</v>
+        <v>194421.52</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>1925.57</v>
+        <v>1944.22</v>
       </c>
       <c r="K53" s="7" t="n">
-        <v>-1987.19</v>
+        <v>-2006.43</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>190546.04</v>
+        <v>192390.81</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -8295,16 +8303,16 @@
         <v>-1.002</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>190607.66</v>
+        <v>192453.03</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>1906.08</v>
+        <v>1924.53</v>
       </c>
       <c r="K54" s="7" t="n">
-        <v>-1910.05</v>
+        <v>-1928.54</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>188636</v>
+        <v>190462.27</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -8346,16 +8354,16 @@
         <v>4.973</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>188636</v>
+        <v>190462.27</v>
       </c>
       <c r="J55" s="5" t="n">
-        <v>1886.36</v>
+        <v>1904.62</v>
       </c>
       <c r="K55" s="6" t="n">
-        <v>9380.120000000001</v>
+        <v>9470.93</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>198016.11</v>
+        <v>199933.21</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
@@ -8397,16 +8405,16 @@
         <v>-1.021</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>198016.11</v>
+        <v>199933.21</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>1980.16</v>
+        <v>1999.33</v>
       </c>
       <c r="K56" s="7" t="n">
-        <v>-2020.78</v>
+        <v>-2040.34</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>192043.89</v>
+        <v>193903.16</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -8448,16 +8456,16 @@
         <v>-1.024</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>196035.95</v>
+        <v>197933.87</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>1960.36</v>
+        <v>1979.34</v>
       </c>
       <c r="K57" s="7" t="n">
-        <v>-2006.49</v>
+        <v>-2025.91</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>196009.63</v>
+        <v>197907.29</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -8499,16 +8507,16 @@
         <v>-1.002</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>194075.59</v>
+        <v>195954.53</v>
       </c>
       <c r="J58" s="5" t="n">
-        <v>1940.76</v>
+        <v>1959.55</v>
       </c>
       <c r="K58" s="7" t="n">
-        <v>-1944.96</v>
+        <v>-1963.79</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>194064.66</v>
+        <v>195943.5</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -8550,16 +8558,16 @@
         <v>4.981</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>192088.71</v>
+        <v>193948.42</v>
       </c>
       <c r="J59" s="5" t="n">
-        <v>1920.89</v>
+        <v>1939.48</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>9568.190000000001</v>
+        <v>9660.83</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>201612.08</v>
+        <v>203563.98</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -8601,16 +8609,16 @@
         <v>-1.007</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>190123</v>
+        <v>191963.67</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>1901.23</v>
+        <v>1919.64</v>
       </c>
       <c r="K60" s="7" t="n">
-        <v>-1915.29</v>
+        <v>-1933.83</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>199696.79</v>
+        <v>201630.15</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -8652,16 +8660,16 @@
         <v>-1.03</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>188221.77</v>
+        <v>190044.04</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>1882.22</v>
+        <v>1900.44</v>
       </c>
       <c r="K61" s="7" t="n">
-        <v>-1937.99</v>
+        <v>-1956.75</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>197758.8</v>
+        <v>199673.4</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
@@ -8703,16 +8711,16 @@
         <v>4.996</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>197814.57</v>
+        <v>199729.71</v>
       </c>
       <c r="J62" s="5" t="n">
-        <v>1978.15</v>
+        <v>1997.3</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>9883.780000000001</v>
+        <v>9979.469999999999</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>205394.73</v>
+        <v>207383.25</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -8754,16 +8762,16 @@
         <v>-1.148</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>195780.66</v>
+        <v>197676.11</v>
       </c>
       <c r="J63" s="5" t="n">
-        <v>1957.81</v>
+        <v>1976.76</v>
       </c>
       <c r="K63" s="7" t="n">
-        <v>-2247.85</v>
+        <v>-2269.61</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>195510.95</v>
+        <v>197403.79</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -8805,16 +8813,16 @@
         <v>4.894</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>193822.85</v>
+        <v>195699.35</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>1938.23</v>
+        <v>1956.99</v>
       </c>
       <c r="K64" s="6" t="n">
-        <v>9485.49</v>
+        <v>9577.32</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>214880.22</v>
+        <v>216960.58</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
@@ -8856,16 +8864,16 @@
         <v>-1.014</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>203456.5</v>
+        <v>205426.26</v>
       </c>
       <c r="J65" s="5" t="n">
-        <v>2034.56</v>
+        <v>2054.26</v>
       </c>
       <c r="K65" s="7" t="n">
-        <v>-2062.15</v>
+        <v>-2082.12</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>212818.07</v>
+        <v>214878.46</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
@@ -8907,16 +8915,16 @@
         <v>-1.014</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>212818.07</v>
+        <v>214878.46</v>
       </c>
       <c r="J66" s="5" t="n">
-        <v>2128.18</v>
+        <v>2148.78</v>
       </c>
       <c r="K66" s="7" t="n">
-        <v>-2157.53</v>
+        <v>-2178.42</v>
       </c>
       <c r="L66" s="5" t="n">
-        <v>210660.53</v>
+        <v>212700.04</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
@@ -8958,16 +8966,16 @@
         <v>-1.02</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>210689.88</v>
+        <v>212729.68</v>
       </c>
       <c r="J67" s="5" t="n">
-        <v>2106.9</v>
+        <v>2127.3</v>
       </c>
       <c r="K67" s="7" t="n">
-        <v>-2148.01</v>
+        <v>-2168.8</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>208512.52</v>
+        <v>210531.23</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
@@ -9001,16 +9009,16 @@
         <v>-0.004</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>208553.63</v>
+        <v>210572.74</v>
       </c>
       <c r="J68" s="5" t="n">
-        <v>2085.54</v>
+        <v>2105.73</v>
       </c>
       <c r="K68" s="7" t="n">
-        <v>-7.56</v>
+        <v>-7.63</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>268674.86</v>
+        <v>271276.03</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
@@ -9052,16 +9060,16 @@
         <v>-1.082</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>206426.98</v>
+        <v>208425.51</v>
       </c>
       <c r="J69" s="5" t="n">
-        <v>2064.27</v>
+        <v>2084.26</v>
       </c>
       <c r="K69" s="7" t="n">
-        <v>-2232.78</v>
+        <v>-2254.4</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>206279.74</v>
+        <v>208276.83</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
@@ -9103,16 +9111,16 @@
         <v>4.974</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>204362.72</v>
+        <v>206341.25</v>
       </c>
       <c r="J70" s="5" t="n">
-        <v>2043.63</v>
+        <v>2063.41</v>
       </c>
       <c r="K70" s="6" t="n">
-        <v>10164.36</v>
+        <v>10262.76</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>216444.1</v>
+        <v>218539.6</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
@@ -9154,16 +9162,16 @@
         <v>-1.012</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>202319.09</v>
+        <v>204277.84</v>
       </c>
       <c r="J71" s="5" t="n">
-        <v>2023.19</v>
+        <v>2042.78</v>
       </c>
       <c r="K71" s="7" t="n">
-        <v>-2047.06</v>
+        <v>-2066.88</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>246263.69</v>
+        <v>248647.89</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
@@ -9205,16 +9213,16 @@
         <v>4.983</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>200295.9</v>
+        <v>202235.06</v>
       </c>
       <c r="J72" s="5" t="n">
-        <v>2002.96</v>
+        <v>2022.35</v>
       </c>
       <c r="K72" s="6" t="n">
-        <v>9979.959999999999</v>
+        <v>10076.58</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>226424.06</v>
+        <v>228616.18</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
@@ -9256,16 +9264,16 @@
         <v>4.951</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>222315.33</v>
+        <v>224467.67</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>2223.15</v>
+        <v>2244.68</v>
       </c>
       <c r="K73" s="6" t="n">
-        <v>11007.32</v>
+        <v>11113.89</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>237431.38</v>
+        <v>239730.07</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -9307,16 +9315,16 @@
         <v>4.913</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>220092.18</v>
+        <v>222223</v>
       </c>
       <c r="J74" s="5" t="n">
-        <v>2200.92</v>
+        <v>2222.23</v>
       </c>
       <c r="K74" s="6" t="n">
-        <v>10813.22</v>
+        <v>10917.91</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>254896.6</v>
+        <v>257364.38</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
@@ -9358,16 +9366,16 @@
         <v>4.993</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>217891.25</v>
+        <v>220000.77</v>
       </c>
       <c r="J75" s="5" t="n">
-        <v>2178.91</v>
+        <v>2200.01</v>
       </c>
       <c r="K75" s="6" t="n">
-        <v>10879.38</v>
+        <v>10984.71</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>248310.76</v>
+        <v>250714.77</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
@@ -9409,16 +9417,16 @@
         <v>-1.011</v>
       </c>
       <c r="I76" s="5" t="n">
-        <v>215712.34</v>
+        <v>217800.76</v>
       </c>
       <c r="J76" s="5" t="n">
-        <v>2157.12</v>
+        <v>2178.01</v>
       </c>
       <c r="K76" s="7" t="n">
-        <v>-2180.32</v>
+        <v>-2201.43</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>244083.37</v>
+        <v>246446.46</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
@@ -9460,16 +9468,16 @@
         <v>-1.154</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>213555.22</v>
+        <v>215622.75</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>2135.55</v>
+        <v>2156.23</v>
       </c>
       <c r="K77" s="7" t="n">
-        <v>-2464.1</v>
+        <v>-2487.95</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>252432.5</v>
+        <v>254876.42</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
@@ -9511,16 +9519,16 @@
         <v>-1.048</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>250346.96</v>
+        <v>252770.69</v>
       </c>
       <c r="J78" s="5" t="n">
-        <v>2503.47</v>
+        <v>2527.71</v>
       </c>
       <c r="K78" s="7" t="n">
-        <v>-2622.68</v>
+        <v>-2648.07</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>258703.15</v>
+        <v>261207.78</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -9562,16 +9570,16 @@
         <v>3.588</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>247843.49</v>
+        <v>250242.99</v>
       </c>
       <c r="J79" s="5" t="n">
-        <v>2478.43</v>
+        <v>2502.43</v>
       </c>
       <c r="K79" s="6" t="n">
-        <v>8893.33</v>
+        <v>8979.43</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>261325.83</v>
+        <v>263855.85</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
@@ -9613,16 +9621,16 @@
         <v>-1.049</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>256617.61</v>
+        <v>259102.05</v>
       </c>
       <c r="J80" s="5" t="n">
-        <v>2566.18</v>
+        <v>2591.02</v>
       </c>
       <c r="K80" s="7" t="n">
-        <v>-2692.9</v>
+        <v>-2718.97</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>256010.24</v>
+        <v>258488.81</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -9664,16 +9672,16 @@
         <v>4.991</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>253924.71</v>
+        <v>256383.08</v>
       </c>
       <c r="J81" s="5" t="n">
-        <v>2539.25</v>
+        <v>2563.83</v>
       </c>
       <c r="K81" s="6" t="n">
-        <v>12672.17</v>
+        <v>12794.85</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>268682.41</v>
+        <v>271283.66</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>

--- a/output/quickfix_portfolio_daily.xlsx
+++ b/output/quickfix_portfolio_daily.xlsx
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B24"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -691,168 +691,180 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>closed trades</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>79</v>
+          <t>return / drawdown</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>29.3x</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>win rate</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>41.8%</t>
-        </is>
+          <t>closed trades</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>79</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>average hold</t>
+          <t>win rate</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2.2 bars</t>
+          <t>41.8%</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>average winner</t>
+          <t>average hold</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>+4.68R  (best +5.00R)</t>
+          <t>2.2 bars</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>longest win streak</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>7</v>
+          <t>average winner</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>+4.68R  (best +5.00R)</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>longest loss streak</t>
+          <t>longest win streak</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>average win</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>7,479  (+4.68%)</t>
-        </is>
+          <t>longest loss streak</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>average loss</t>
+          <t>average win</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-1,642  (-1.05%)</t>
+          <t>7,479  (+4.68%)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>markets with trades</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>28</v>
+          <t>average loss</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>-1,642  (-1.05%)</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>max concurrent positions</t>
+          <t>markets with trades</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>time in market</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>74% of trading days</t>
-        </is>
+          <t>max concurrent positions</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>peak risk committed</t>
+          <t>time in market</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5.0% of live balance</t>
+          <t>74% of trading days</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>window</t>
+          <t>peak risk committed</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-07-23</t>
+          <t>5.0% of live balance</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>risk per trade</t>
+          <t>window</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1.0% of liquid capital</t>
+          <t>2025-12-18 -&gt; 2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>risk per trade</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1.0% of liquid capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
           <t>slippage model</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>entry 1t, target 1t, stop 3t</t>
         </is>

--- a/output/quickfix_portfolio_daily.xlsx
+++ b/output/quickfix_portfolio_daily.xlsx
@@ -590,7 +590,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -793,78 +793,88 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>markets with trades</t>
+          <t>markets tested</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>max concurrent positions</t>
+          <t>markets with trades</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>time in market</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>74% of trading days</t>
-        </is>
+          <t>max concurrent positions</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>peak risk committed</t>
+          <t>time in market</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5.0% of live balance</t>
+          <t>74% of trading days</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>window</t>
+          <t>peak risk committed</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-07-23</t>
+          <t>5.0% of live balance</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>risk per trade</t>
+          <t>window</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1.0% of liquid capital</t>
+          <t>2025-12-18 -&gt; 2026-07-23</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>risk per trade</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1.0% of liquid capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t>slippage model</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>entry 1t, target 1t, stop 3t</t>
         </is>

--- a/output/quickfix_portfolio_daily.xlsx
+++ b/output/quickfix_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$180</f>
+              <f>'equity_curve'!$A$2:$A$181</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$180</f>
+              <f>'equity_curve'!$B$2:$B$181</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>271,276.03</t>
+          <t>271,158.62</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+171.28%</t>
+          <t>+171.16%</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5,199  (8.7 pts of return)</t>
+          <t>5,317  (8.8 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>29.3x</t>
+          <t>29.2x</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-07-23</t>
+          <t>2025-12-18 -&gt; 2026-07-24</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H180"/>
+  <dimension ref="A1:H181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -994,7 +994,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX target_5r (+4,988)</t>
+          <t>Gold_Futures_COMEX target_r (+4,988)</t>
         </is>
       </c>
     </row>
@@ -1234,7 +1234,7 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Coffee_NYCSCE_Futures stop (-1,047); S_P_500_Index target_5r (+5,142)</t>
+          <t>Coffee_NYCSCE_Futures stop (-1,047); S_P_500_Index target_r (+5,142)</t>
         </is>
       </c>
     </row>
@@ -1762,7 +1762,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Ethereum_Per_USD_Binance stop (-1,168); Live_Cattle_Futures_CME stop (-1,147); S_P_500_Index target_5r (+5,354)</t>
+          <t>Ethereum_Per_USD_Binance stop (-1,168); Live_Cattle_Futures_CME stop (-1,147); S_P_500_Index target_r (+5,354)</t>
         </is>
       </c>
     </row>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>EURO_STOXX_50_Index target_5r (+5,440)</t>
+          <t>EURO_STOXX_50_Index target_r (+5,440)</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Ethereum_Per_USD_Binance target_5r (+5,153)</t>
+          <t>Ethereum_Per_USD_Binance target_r (+5,153)</t>
         </is>
       </c>
     </row>
@@ -2970,7 +2970,7 @@
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance target_5r (+5,740)</t>
+          <t>Bitcoin_Per_USD_Binance target_r (+5,740)</t>
         </is>
       </c>
     </row>
@@ -3098,7 +3098,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP target_5r (+6,012)</t>
+          <t>United_States_Oil_Fund_LP target_r (+6,012)</t>
         </is>
       </c>
     </row>
@@ -3154,7 +3154,7 @@
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX target_5r (+6,262)</t>
+          <t>Gold_Futures_COMEX target_r (+6,262)</t>
         </is>
       </c>
     </row>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures target_5r (+5,966)</t>
+          <t>NY_Copper_Futures target_r (+5,966)</t>
         </is>
       </c>
     </row>
@@ -3330,7 +3330,7 @@
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP target_5r (+6,550)</t>
+          <t>United_States_Oil_Fund_LP target_r (+6,550)</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Ethereum_Per_USD_Binance target_5r (+7,017); Live_Cattle_Futures_CME target_5r (+7,039)</t>
+          <t>Ethereum_Per_USD_Binance target_r (+7,017); Live_Cattle_Futures_CME target_r (+7,039)</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini target_5r (+7,850)</t>
+          <t>Dow_Futures_E_mini target_r (+7,850)</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME target_5r (+8,287)</t>
+          <t>Bitcoin_Per_USD_CME target_r (+8,287)</t>
         </is>
       </c>
     </row>
@@ -4078,7 +4078,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT target_5r (+8,588); Corn_CBOT_Futures target_5r (+7,809); Japanese_Yen_Futures stop (-1,874); US_Dollar_Index_Futures stop (-1,684)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT target_r (+8,588); Corn_CBOT_Futures target_r (+7,809); Japanese_Yen_Futures stop (-1,874); US_Dollar_Index_Futures stop (-1,684)</t>
         </is>
       </c>
     </row>
@@ -4110,7 +4110,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME target_5r (+8,017); Live_Cattle_Futures_CME target_5r (+8,343)</t>
+          <t>Bitcoin_Per_USD_CME target_r (+8,017); Live_Cattle_Futures_CME target_r (+8,343)</t>
         </is>
       </c>
     </row>
@@ -4278,7 +4278,7 @@
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT target_5r (+9,471)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT target_r (+9,471)</t>
         </is>
       </c>
     </row>
@@ -4662,7 +4662,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini target_5r (+9,661)</t>
+          <t>Dow_Futures_E_mini target_r (+9,661)</t>
         </is>
       </c>
     </row>
@@ -4806,7 +4806,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures stop (-2,270); Gold_Futures_COMEX target_5r (+9,979)</t>
+          <t>Corn_CBOT_Futures stop (-2,270); Gold_Futures_COMEX target_r (+9,979)</t>
         </is>
       </c>
     </row>
@@ -5058,7 +5058,7 @@
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures stop (-2,254); NY_Palladium_Futures target_5r (+10,263); US_Dollar_Index_Futures target_5r (+10,077)</t>
+          <t>NY_Natural_Gas_Futures stop (-2,254); NY_Palladium_Futures target_r (+10,263); US_Dollar_Index_Futures target_r (+10,077)</t>
         </is>
       </c>
     </row>
@@ -5142,7 +5142,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT target_5r (+11,114); Gold_Futures_COMEX target_5r (+10,985); NY_Platinum_Futures stop (-2,067)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT target_r (+11,114); Gold_Futures_COMEX target_r (+10,985); NY_Platinum_Futures stop (-2,067)</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr">
         <is>
-          <t>German_Long_Bund target_5r (+10,918); Sugar_World_CSCE_Futures stop (-2,488)</t>
+          <t>German_Long_Bund target_r (+10,918); Sugar_World_CSCE_Futures stop (-2,488)</t>
         </is>
       </c>
     </row>
@@ -5490,7 +5490,7 @@
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX target_5r (+12,795)</t>
+          <t>Gold_Futures_COMEX target_r (+12,795)</t>
         </is>
       </c>
     </row>
@@ -5523,22 +5523,50 @@
         <v>46226</v>
       </c>
       <c r="B180" s="5" t="n">
-        <v>271276.03</v>
+        <v>271283.66</v>
       </c>
       <c r="C180" s="5" t="n">
+        <v>2105.73</v>
+      </c>
+      <c r="D180" s="5" t="n">
+        <v>269177.93</v>
+      </c>
+      <c r="E180" t="n">
+        <v>1</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>EURO_Futures</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="4" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B181" s="5" t="n">
+        <v>271158.62</v>
+      </c>
+      <c r="C181" s="5" t="n">
         <v>-0</v>
       </c>
-      <c r="D180" s="5" t="n">
-        <v>271276.03</v>
-      </c>
-      <c r="E180" t="n">
+      <c r="D181" s="5" t="n">
+        <v>271158.62</v>
+      </c>
+      <c r="E181" t="n">
         <v>0</v>
       </c>
-      <c r="F180" t="inlineStr"/>
-      <c r="G180" t="inlineStr"/>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>EURO_Futures open_at_end (open-&gt;closed 0)</t>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 2,692); Corn_CBOT_Futures short (risk 2,665)</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT open_at_end (open-&gt;closed 0); Corn_CBOT_Futures open_at_end (open-&gt;closed 0); EURO_Futures open_at_end (open-&gt;closed 0)</t>
         </is>
       </c>
     </row>
@@ -5554,7 +5582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M81"/>
+  <dimension ref="A1:M83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -5686,7 +5714,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
@@ -5839,7 +5867,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
@@ -6196,7 +6224,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
@@ -6400,7 +6428,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
@@ -6859,7 +6887,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
@@ -7114,7 +7142,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
@@ -7165,7 +7193,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
@@ -7216,7 +7244,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
@@ -7267,7 +7295,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
@@ -7318,7 +7346,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7448,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
@@ -7471,7 +7499,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
@@ -7624,7 +7652,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
@@ -7675,7 +7703,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
@@ -7777,7 +7805,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
@@ -7930,7 +7958,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
@@ -8083,7 +8111,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
@@ -8134,7 +8162,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
@@ -8389,7 +8417,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
@@ -8593,7 +8621,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
@@ -8746,7 +8774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
@@ -9040,7 +9068,7 @@
         <v>-7.63</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>271276.03</v>
+        <v>271158.62</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
@@ -9146,7 +9174,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
@@ -9248,7 +9276,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
@@ -9299,7 +9327,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
@@ -9350,7 +9378,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
@@ -9401,7 +9429,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
@@ -9707,7 +9735,93 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>target_5r</t>
+          <t>target_r</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="H82" t="n">
+        <v>-0.019</v>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>269177.93</v>
+      </c>
+      <c r="J82" s="5" t="n">
+        <v>2691.78</v>
+      </c>
+      <c r="K82" s="7" t="n">
+        <v>-50.79</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>271232.87</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Corn_CBOT_Futures</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="H83" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>266486.15</v>
+      </c>
+      <c r="J83" s="5" t="n">
+        <v>2664.86</v>
+      </c>
+      <c r="K83" s="7" t="n">
+        <v>-66.62</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>271166.25</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
         </is>
       </c>
     </row>

--- a/output/quickfix_portfolio_daily.xlsx
+++ b/output/quickfix_portfolio_daily.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>target = 5R, or an opposite reversal nearer than 5R</t>
+          <t>target = 2.5R, or an opposite reversal nearer than 2.5R</t>
         </is>
       </c>
     </row>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>271,158.62</t>
+          <t>310,742.28</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+171.16%</t>
+          <t>+210.74%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>279,949  (+179.95%)</t>
+          <t>325,673  (+225.67%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5,317  (8.8 pts of return)</t>
+          <t>8,611  (14.9 pts of return)</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5.85%</t>
+          <t>6.00%</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>29.2x</t>
+          <t>35.1x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>56.0%</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2.2 bars</t>
+          <t>1.4 bars</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>+4.68R  (best +5.00R)</t>
+          <t>+2.44R  (best +2.50R)</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -774,7 +774,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7,479  (+4.68%)</t>
+          <t>6,696  (+3.84%)</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-1,642  (-1.05%)</t>
+          <t>-2,804  (-1.65%)</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>74% of trading days</t>
+          <t>52% of trading days</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5.0% of live balance</t>
+          <t>7.6% of live balance</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.0% of liquid capital</t>
+          <t>1.573% of liquid capital</t>
         </is>
       </c>
     </row>
@@ -954,10 +954,10 @@
         <v>100000</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>1000</v>
+        <v>1573</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>99000</v>
+        <v>98427</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX short (risk 1,000)</t>
+          <t>Gold_Futures_COMEX short (risk 1,573)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -979,13 +979,13 @@
         <v>46010</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>104987.95</v>
+        <v>103913.55</v>
       </c>
       <c r="C3" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>104987.95</v>
+        <v>103913.55</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -994,7 +994,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX target_r (+4,988)</t>
+          <t>Gold_Futures_COMEX target_r (+3,914)</t>
         </is>
       </c>
     </row>
@@ -1003,13 +1003,13 @@
         <v>46011</v>
       </c>
       <c r="B4" s="5" t="n">
-        <v>104987.95</v>
+        <v>103913.55</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>104987.95</v>
+        <v>103913.55</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -1023,13 +1023,13 @@
         <v>46021</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>104987.95</v>
+        <v>103913.55</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1049.88</v>
+        <v>1634.56</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>103938.07</v>
+        <v>102278.99</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX short (risk 1,050)</t>
+          <t>Gold_Futures_COMEX short (risk 1,635)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -1051,13 +1051,13 @@
         <v>46023</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>104987.95</v>
+        <v>103913.55</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1049.88</v>
+        <v>1634.56</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>103938.07</v>
+        <v>102278.99</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -1075,46 +1075,42 @@
         <v>46024</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>104987.95</v>
+        <v>107988.1</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1049.88</v>
+        <v>0</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>103938.07</v>
+        <v>107988.1</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Gold_Futures_COMEX</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX target_r (+4,075)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
         <v>46025</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>104987.95</v>
+        <v>107988.1</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1049.88</v>
+        <v>0</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>103938.07</v>
+        <v>107988.1</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Gold_Futures_COMEX</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -1123,22 +1119,18 @@
         <v>46026</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>104987.95</v>
+        <v>107988.1</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1049.88</v>
+        <v>0</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>103938.07</v>
+        <v>107988.1</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Gold_Futures_COMEX</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -1147,37 +1139,33 @@
         <v>46027</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>103922.86</v>
+        <v>107988.1</v>
       </c>
       <c r="C10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>103922.86</v>
+        <v>107988.1</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Gold_Futures_COMEX stop (-1,065)</t>
-        </is>
-      </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
         <v>46028</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>103922.86</v>
+        <v>107988.1</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>103922.86</v>
+        <v>107988.1</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -1191,13 +1179,13 @@
         <v>46029</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>103922.86</v>
+        <v>107988.1</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>2068.06</v>
+        <v>3370.59</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>101854.79</v>
+        <v>104617.52</v>
       </c>
       <c r="E12" t="n">
         <v>2</v>
@@ -1209,7 +1197,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Coffee_NYCSCE_Futures short (risk 1,039); S_P_500_Index short (risk 1,029)</t>
+          <t>Coffee_NYCSCE_Futures short (risk 1,699); S_P_500_Index short (risk 1,672)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -1219,13 +1207,13 @@
         <v>46030</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>108017.11</v>
+        <v>110451.81</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>108017.11</v>
+        <v>110451.81</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1234,7 +1222,7 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Coffee_NYCSCE_Futures stop (-1,047); S_P_500_Index target_r (+5,142)</t>
+          <t>Coffee_NYCSCE_Futures stop (-1,712); S_P_500_Index target_r (+4,176)</t>
         </is>
       </c>
     </row>
@@ -1243,13 +1231,13 @@
         <v>46031</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>108017.11</v>
+        <v>110451.81</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>108017.11</v>
+        <v>110451.81</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1263,13 +1251,13 @@
         <v>46032</v>
       </c>
       <c r="B15" s="5" t="n">
-        <v>108017.11</v>
+        <v>110451.81</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>108017.11</v>
+        <v>110451.81</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1283,13 +1271,13 @@
         <v>46033</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>108017.11</v>
+        <v>110451.81</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>108017.11</v>
+        <v>110451.81</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -1303,13 +1291,13 @@
         <v>46034</v>
       </c>
       <c r="B17" s="5" t="n">
-        <v>108017.11</v>
+        <v>110451.81</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>108017.11</v>
+        <v>110451.81</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -1323,13 +1311,13 @@
         <v>46035</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>108017.11</v>
+        <v>110451.81</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>1080.17</v>
+        <v>1737.41</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>106936.94</v>
+        <v>108714.41</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -1341,7 +1329,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures long (risk 1,080)</t>
+          <t>Cocoa_NYCSCE_Futures long (risk 1,737)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -1351,13 +1339,13 @@
         <v>46036</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>106845.01</v>
+        <v>108566.54</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>106845.01</v>
+        <v>108566.54</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -1366,7 +1354,7 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures stop (-1,172)</t>
+          <t>Cocoa_NYCSCE_Futures unknown_pl (-1,885)</t>
         </is>
       </c>
     </row>
@@ -1375,13 +1363,13 @@
         <v>46037</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>106845.01</v>
+        <v>108566.54</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>106845.01</v>
+        <v>108566.54</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -1395,13 +1383,13 @@
         <v>46038</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>106845.01</v>
+        <v>108566.54</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>106845.01</v>
+        <v>108566.54</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -1415,13 +1403,13 @@
         <v>46039</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>106845.01</v>
+        <v>108566.54</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>106845.01</v>
+        <v>108566.54</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -1435,13 +1423,13 @@
         <v>46040</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>106845.01</v>
+        <v>108566.54</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>106845.01</v>
+        <v>108566.54</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -1455,13 +1443,13 @@
         <v>46041</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>106845.01</v>
+        <v>108566.54</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>106845.01</v>
+        <v>108566.54</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -1475,13 +1463,13 @@
         <v>46042</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>106845.01</v>
+        <v>108566.54</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>106845.01</v>
+        <v>108566.54</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -1495,13 +1483,13 @@
         <v>46043</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>106845.01</v>
+        <v>108566.54</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>1068.45</v>
+        <v>1707.75</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>105776.56</v>
+        <v>106858.79</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -1513,7 +1501,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Coffee_NYCSCE_Futures long (risk 1,068)</t>
+          <t>Coffee_NYCSCE_Futures long (risk 1,708)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -1523,13 +1511,13 @@
         <v>46044</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>106845.01</v>
+        <v>108566.54</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>1068.45</v>
+        <v>1707.75</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>105776.56</v>
+        <v>106858.79</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -1547,46 +1535,42 @@
         <v>46045</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>106845.01</v>
+        <v>112825.6</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>1068.45</v>
+        <v>-0</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>105776.56</v>
+        <v>112825.6</v>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Coffee_NYCSCE_Futures</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Coffee_NYCSCE_Futures target_r (+4,259)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
         <v>46046</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>106845.01</v>
+        <v>112825.6</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>1068.45</v>
+        <v>-0</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>105776.56</v>
+        <v>112825.6</v>
       </c>
       <c r="E29" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Coffee_NYCSCE_Futures</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1595,22 +1579,18 @@
         <v>46047</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>106845.01</v>
+        <v>112825.6</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>1068.45</v>
+        <v>-0</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>105776.56</v>
+        <v>112825.6</v>
       </c>
       <c r="E30" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Coffee_NYCSCE_Futures</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1619,22 +1599,18 @@
         <v>46048</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>106845.01</v>
+        <v>112825.6</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>1068.45</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>105776.56</v>
+        <v>112825.6</v>
       </c>
       <c r="E31" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Coffee_NYCSCE_Futures</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1643,13 +1619,13 @@
         <v>46049</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>111454.47</v>
+        <v>112825.6</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>1057.77</v>
+        <v>1774.75</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>110396.7</v>
+        <v>111050.85</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -1661,27 +1637,23 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>S_P_500_Index short (risk 1,058)</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Coffee_NYCSCE_Futures bullish_reversal (+4,609)</t>
-        </is>
-      </c>
+          <t>S_P_500_Index short (risk 1,775)</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
         <v>46050</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>110390.12</v>
+        <v>111039.81</v>
       </c>
       <c r="C33" s="5" t="n">
-        <v>1103.97</v>
+        <v>1746.83</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>109286.15</v>
+        <v>109292.98</v>
       </c>
       <c r="E33" t="n">
         <v>1</v>
@@ -1693,12 +1665,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Teucrium_Wheat_Fund short (risk 1,104)</t>
+          <t>Teucrium_Wheat_Fund short (risk 1,747)</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>S_P_500_Index stop (-1,064)</t>
+          <t>S_P_500_Index unknown_pl (-1,786)</t>
         </is>
       </c>
     </row>
@@ -1707,13 +1679,13 @@
         <v>46051</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>109040.83</v>
+        <v>108904.8</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>3245.91</v>
+        <v>5076.83</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>105794.92</v>
+        <v>103827.97</v>
       </c>
       <c r="E34" t="n">
         <v>3</v>
@@ -1725,12 +1697,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ethereum_Per_USD_Binance long (risk 1,093); Live_Cattle_Futures_CME short (risk 1,082); S_P_500_Index short (risk 1,071)</t>
+          <t>Ethereum_Per_USD_Binance long (risk 1,719); Live_Cattle_Futures_CME short (risk 1,692); S_P_500_Index short (risk 1,666)</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Teucrium_Wheat_Fund stop (-1,349)</t>
+          <t>Teucrium_Wheat_Fund stop (-2,135)</t>
         </is>
       </c>
     </row>
@@ -1739,13 +1711,13 @@
         <v>46052</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>112079.59</v>
+        <v>109434.51</v>
       </c>
       <c r="C35" s="5" t="n">
-        <v>1057.95</v>
+        <v>1633.21</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>111021.64</v>
+        <v>107801.29</v>
       </c>
       <c r="E35" t="n">
         <v>1</v>
@@ -1757,12 +1729,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures long (risk 1,058)</t>
+          <t>Cocoa_NYCSCE_Futures long (risk 1,633)</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Ethereum_Per_USD_Binance stop (-1,168); Live_Cattle_Futures_CME stop (-1,147); S_P_500_Index target_r (+5,354)</t>
+          <t>Ethereum_Per_USD_Binance stop (-1,838); Live_Cattle_Futures_CME unknown_pl (-1,793); S_P_500_Index target_r (+4,161)</t>
         </is>
       </c>
     </row>
@@ -1771,13 +1743,13 @@
         <v>46053</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>112079.59</v>
+        <v>109434.51</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>1057.95</v>
+        <v>1633.21</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>111021.64</v>
+        <v>107801.29</v>
       </c>
       <c r="E36" t="n">
         <v>1</v>
@@ -1795,13 +1767,13 @@
         <v>46054</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>112079.59</v>
+        <v>109434.51</v>
       </c>
       <c r="C37" s="5" t="n">
-        <v>1057.95</v>
+        <v>1633.21</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>111021.64</v>
+        <v>107801.29</v>
       </c>
       <c r="E37" t="n">
         <v>1</v>
@@ -1819,13 +1791,13 @@
         <v>46055</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>112079.59</v>
+        <v>109434.51</v>
       </c>
       <c r="C38" s="5" t="n">
-        <v>3267.28</v>
+        <v>4997.97</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>108812.31</v>
+        <v>104436.54</v>
       </c>
       <c r="E38" t="n">
         <v>3</v>
@@ -1837,7 +1809,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance long (risk 1,110); S_P_500_Index short (risk 1,099)</t>
+          <t>Bitcoin_Per_USD_Binance long (risk 1,696); S_P_500_Index short (risk 1,669)</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -1847,13 +1819,13 @@
         <v>46056</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>109863.3</v>
+        <v>106059.16</v>
       </c>
       <c r="C39" s="5" t="n">
-        <v>2146.07</v>
+        <v>3276</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>107717.22</v>
+        <v>102783.16</v>
       </c>
       <c r="E39" t="n">
         <v>2</v>
@@ -1865,12 +1837,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>EURO_STOXX_50_Index short (risk 1,088)</t>
+          <t>EURO_STOXX_50_Index short (risk 1,643)</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance stop (-1,113); S_P_500_Index unknown_pl (-1,104)</t>
+          <t>Bitcoin_Per_USD_Binance stop (-1,699); S_P_500_Index unknown_pl (-1,676)</t>
         </is>
       </c>
     </row>
@@ -1879,13 +1851,13 @@
         <v>46057</v>
       </c>
       <c r="B40" s="5" t="n">
-        <v>109863.3</v>
+        <v>106059.16</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>2146.07</v>
+        <v>3276</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>107717.22</v>
+        <v>102783.16</v>
       </c>
       <c r="E40" t="n">
         <v>2</v>
@@ -1903,13 +1875,13 @@
         <v>46058</v>
       </c>
       <c r="B41" s="5" t="n">
-        <v>115303.18</v>
+        <v>110165.03</v>
       </c>
       <c r="C41" s="5" t="n">
-        <v>2135.12</v>
+        <v>3249.99</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>113168.06</v>
+        <v>106915.03</v>
       </c>
       <c r="E41" t="n">
         <v>2</v>
@@ -1921,12 +1893,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures long (risk 1,077)</t>
+          <t>NY_Copper_Futures long (risk 1,617)</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>EURO_STOXX_50_Index target_r (+5,440)</t>
+          <t>EURO_STOXX_50_Index target_r (+4,106)</t>
         </is>
       </c>
     </row>
@@ -1935,13 +1907,13 @@
         <v>46059</v>
       </c>
       <c r="B42" s="5" t="n">
-        <v>114221.03</v>
+        <v>108540.77</v>
       </c>
       <c r="C42" s="5" t="n">
-        <v>2189.63</v>
+        <v>3314.99</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>112031.4</v>
+        <v>105225.78</v>
       </c>
       <c r="E42" t="n">
         <v>2</v>
@@ -1953,12 +1925,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance long (risk 1,132)</t>
+          <t>Bitcoin_Per_USD_Binance long (risk 1,682)</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures stop (-1,082)</t>
+          <t>NY_Copper_Futures stop (-1,624)</t>
         </is>
       </c>
     </row>
@@ -1967,44 +1939,48 @@
         <v>46060</v>
       </c>
       <c r="B43" s="5" t="n">
-        <v>114221.03</v>
+        <v>112743.89</v>
       </c>
       <c r="C43" s="5" t="n">
-        <v>2189.63</v>
+        <v>1633.21</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>112031.4</v>
+        <v>111110.68</v>
       </c>
       <c r="E43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance, Cocoa_NYCSCE_Futures</t>
+          <t>Cocoa_NYCSCE_Futures</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Bitcoin_Per_USD_Binance target_r (+4,203)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
         <v>46061</v>
       </c>
       <c r="B44" s="5" t="n">
-        <v>114221.03</v>
+        <v>112743.89</v>
       </c>
       <c r="C44" s="5" t="n">
-        <v>2189.63</v>
+        <v>1633.21</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>112031.4</v>
+        <v>111110.68</v>
       </c>
       <c r="E44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance, Cocoa_NYCSCE_Futures</t>
+          <t>Cocoa_NYCSCE_Futures</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -2015,20 +1991,20 @@
         <v>46062</v>
       </c>
       <c r="B45" s="5" t="n">
-        <v>114221.03</v>
+        <v>112743.89</v>
       </c>
       <c r="C45" s="5" t="n">
-        <v>2189.63</v>
+        <v>1633.21</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>112031.4</v>
+        <v>111110.68</v>
       </c>
       <c r="E45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance, Cocoa_NYCSCE_Futures</t>
+          <t>Cocoa_NYCSCE_Futures</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -2039,30 +2015,30 @@
         <v>46063</v>
       </c>
       <c r="B46" s="5" t="n">
-        <v>113135.24</v>
+        <v>111067.7</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>3361.11</v>
+        <v>3468.05</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>109774.14</v>
+        <v>107599.65</v>
       </c>
       <c r="E46" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance, EURO_STOXX_50_Index, S_P_500_Index</t>
+          <t>EURO_STOXX_50_Index, S_P_500_Index</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>EURO_STOXX_50_Index short (risk 1,120); S_P_500_Index short (risk 1,109)</t>
+          <t>EURO_STOXX_50_Index short (risk 1,748); S_P_500_Index short (risk 1,720)</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures stop (-1,086)</t>
+          <t>Cocoa_NYCSCE_Futures stop (-1,676)</t>
         </is>
       </c>
     </row>
@@ -2071,30 +2047,30 @@
         <v>46064</v>
       </c>
       <c r="B47" s="5" t="n">
-        <v>112016.14</v>
+        <v>113699.41</v>
       </c>
       <c r="C47" s="5" t="n">
-        <v>3349.74</v>
+        <v>1692.54</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>108666.4</v>
+        <v>112006.87</v>
       </c>
       <c r="E47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance, EURO_STOXX_50_Index, US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT short (risk 1,098)</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT short (risk 1,693)</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>S_P_500_Index unknown_pl (-1,119)</t>
+          <t>EURO_STOXX_50_Index target_r (+4,367); S_P_500_Index unknown_pl (-1,736)</t>
         </is>
       </c>
     </row>
@@ -2103,26 +2079,30 @@
         <v>46065</v>
       </c>
       <c r="B48" s="5" t="n">
-        <v>109644.19</v>
+        <v>111773.42</v>
       </c>
       <c r="C48" s="5" t="n">
-        <v>1131.68</v>
+        <v>1761.87</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>108512.51</v>
+        <v>110011.55</v>
       </c>
       <c r="E48" t="n">
         <v>1</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
+          <t>EURO_STOXX_50_Index</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>EURO_STOXX_50_Index short (risk 1,762)</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>EURO_STOXX_50_Index stop (-1,123); US_30_Year_T_Bond_Futures_CBOT stop (-1,249)</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT stop (-1,926)</t>
         </is>
       </c>
     </row>
@@ -2131,48 +2111,52 @@
         <v>46066</v>
       </c>
       <c r="B49" s="5" t="n">
-        <v>109644.19</v>
+        <v>116177.18</v>
       </c>
       <c r="C49" s="5" t="n">
-        <v>2216.81</v>
+        <v>1730.48</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>107427.38</v>
+        <v>114446.7</v>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance, NY_Copper_Futures</t>
+          <t>NY_Copper_Futures</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures long (risk 1,085)</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
+          <t>NY_Copper_Futures long (risk 1,730)</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>EURO_STOXX_50_Index target_r (+4,404)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
         <v>46067</v>
       </c>
       <c r="B50" s="5" t="n">
-        <v>109644.19</v>
+        <v>116177.18</v>
       </c>
       <c r="C50" s="5" t="n">
-        <v>2216.81</v>
+        <v>1730.48</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>107427.38</v>
+        <v>114446.7</v>
       </c>
       <c r="E50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance, NY_Copper_Futures</t>
+          <t>NY_Copper_Futures</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -2183,20 +2167,20 @@
         <v>46068</v>
       </c>
       <c r="B51" s="5" t="n">
-        <v>109644.19</v>
+        <v>116177.18</v>
       </c>
       <c r="C51" s="5" t="n">
-        <v>2216.81</v>
+        <v>1730.48</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>107427.38</v>
+        <v>114446.7</v>
       </c>
       <c r="E51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance, NY_Copper_Futures</t>
+          <t>NY_Copper_Futures</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -2207,20 +2191,20 @@
         <v>46069</v>
       </c>
       <c r="B52" s="5" t="n">
-        <v>109644.19</v>
+        <v>116177.18</v>
       </c>
       <c r="C52" s="5" t="n">
-        <v>2216.81</v>
+        <v>1730.48</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>107427.38</v>
+        <v>114446.7</v>
       </c>
       <c r="E52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance, NY_Copper_Futures</t>
+          <t>NY_Copper_Futures</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -2231,26 +2215,22 @@
         <v>46070</v>
       </c>
       <c r="B53" s="5" t="n">
-        <v>108554.45</v>
+        <v>114439.33</v>
       </c>
       <c r="C53" s="5" t="n">
-        <v>1131.68</v>
+        <v>-0</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>107422.77</v>
+        <v>114439.33</v>
       </c>
       <c r="E53" t="n">
-        <v>1</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Bitcoin_Per_USD_Binance</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures stop (-1,090)</t>
+          <t>NY_Copper_Futures stop (-1,738)</t>
         </is>
       </c>
     </row>
@@ -2259,22 +2239,18 @@
         <v>46071</v>
       </c>
       <c r="B54" s="5" t="n">
-        <v>108554.45</v>
+        <v>114439.33</v>
       </c>
       <c r="C54" s="5" t="n">
-        <v>1131.68</v>
+        <v>-0</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>107422.77</v>
+        <v>114439.33</v>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Bitcoin_Per_USD_Binance</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -2283,22 +2259,18 @@
         <v>46072</v>
       </c>
       <c r="B55" s="5" t="n">
-        <v>108554.45</v>
+        <v>114439.33</v>
       </c>
       <c r="C55" s="5" t="n">
-        <v>1131.68</v>
+        <v>-0</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>107422.77</v>
+        <v>114439.33</v>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Bitcoin_Per_USD_Binance</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -2307,22 +2279,18 @@
         <v>46073</v>
       </c>
       <c r="B56" s="5" t="n">
-        <v>108554.45</v>
+        <v>114439.33</v>
       </c>
       <c r="C56" s="5" t="n">
-        <v>1131.68</v>
+        <v>-0</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>107422.77</v>
+        <v>114439.33</v>
       </c>
       <c r="E56" t="n">
-        <v>1</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Bitcoin_Per_USD_Binance</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
     </row>
@@ -2331,22 +2299,18 @@
         <v>46074</v>
       </c>
       <c r="B57" s="5" t="n">
-        <v>108554.45</v>
+        <v>114439.33</v>
       </c>
       <c r="C57" s="5" t="n">
-        <v>1131.68</v>
+        <v>-0</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>107422.77</v>
+        <v>114439.33</v>
       </c>
       <c r="E57" t="n">
-        <v>1</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Bitcoin_Per_USD_Binance</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
     </row>
@@ -2355,22 +2319,18 @@
         <v>46075</v>
       </c>
       <c r="B58" s="5" t="n">
-        <v>108554.45</v>
+        <v>114439.33</v>
       </c>
       <c r="C58" s="5" t="n">
-        <v>1131.68</v>
+        <v>-0</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>107422.77</v>
+        <v>114439.33</v>
       </c>
       <c r="E58" t="n">
-        <v>1</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Bitcoin_Per_USD_Binance</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -2379,25 +2339,25 @@
         <v>46076</v>
       </c>
       <c r="B59" s="5" t="n">
-        <v>108554.45</v>
+        <v>114439.33</v>
       </c>
       <c r="C59" s="5" t="n">
-        <v>2205.91</v>
+        <v>1800.13</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>106348.54</v>
+        <v>112639.2</v>
       </c>
       <c r="E59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance, US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT short (risk 1,074)</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT short (risk 1,800)</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
@@ -2407,25 +2367,25 @@
         <v>46077</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>108554.45</v>
+        <v>114439.33</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>4322.24</v>
+        <v>5315.89</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>104232.2</v>
+        <v>109123.44</v>
       </c>
       <c r="E60" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance, Cocoa_NYCSCE_Futures, Ethereum_Per_USD_Binance, US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>Cocoa_NYCSCE_Futures, Ethereum_Per_USD_Binance, US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures long (risk 1,063); Ethereum_Per_USD_Binance long (risk 1,053)</t>
+          <t>Cocoa_NYCSCE_Futures long (risk 1,772); Ethereum_Per_USD_Binance long (risk 1,744)</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
@@ -2435,26 +2395,22 @@
         <v>46078</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>113707.87</v>
+        <v>127197.46</v>
       </c>
       <c r="C61" s="5" t="n">
-        <v>3269.39</v>
+        <v>-0</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>110438.48</v>
+        <v>127197.46</v>
       </c>
       <c r="E61" t="n">
-        <v>3</v>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Bitcoin_Per_USD_Binance, Cocoa_NYCSCE_Futures, US_30_Year_T_Bond_Futures_CBOT</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F61" t="inlineStr"/>
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Ethereum_Per_USD_Binance target_r (+5,153)</t>
+          <t>Cocoa_NYCSCE_Futures target_r (+4,339); Ethereum_Per_USD_Binance target_r (+4,176); US_30_Year_T_Bond_Futures_CBOT target_r (+4,243)</t>
         </is>
       </c>
     </row>
@@ -2463,78 +2419,58 @@
         <v>46079</v>
       </c>
       <c r="B62" s="5" t="n">
-        <v>112326.72</v>
+        <v>127197.46</v>
       </c>
       <c r="C62" s="5" t="n">
-        <v>2195.17</v>
+        <v>-0</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>110131.56</v>
+        <v>127197.46</v>
       </c>
       <c r="E62" t="n">
-        <v>2</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Bitcoin_Per_USD_Binance, Cocoa_NYCSCE_Futures</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT stop (-1,381)</t>
-        </is>
-      </c>
+      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
         <v>46080</v>
       </c>
       <c r="B63" s="5" t="n">
-        <v>111154.16</v>
+        <v>127197.46</v>
       </c>
       <c r="C63" s="5" t="n">
-        <v>1131.68</v>
+        <v>-0</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>110022.48</v>
+        <v>127197.46</v>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Bitcoin_Per_USD_Binance</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Cocoa_NYCSCE_Futures stop (-1,173)</t>
-        </is>
-      </c>
+      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="4" t="n">
         <v>46081</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>111154.16</v>
+        <v>127197.46</v>
       </c>
       <c r="C64" s="5" t="n">
-        <v>1131.68</v>
+        <v>-0</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>110022.48</v>
+        <v>127197.46</v>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>Bitcoin_Per_USD_Binance</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -2543,22 +2479,18 @@
         <v>46082</v>
       </c>
       <c r="B65" s="5" t="n">
-        <v>111154.16</v>
+        <v>127197.46</v>
       </c>
       <c r="C65" s="5" t="n">
-        <v>1131.68</v>
+        <v>-0</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>110022.48</v>
+        <v>127197.46</v>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Bitcoin_Per_USD_Binance</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
     </row>
@@ -2567,13 +2499,13 @@
         <v>46083</v>
       </c>
       <c r="B66" s="5" t="n">
-        <v>113838.98</v>
+        <v>127197.46</v>
       </c>
       <c r="C66" s="5" t="n">
-        <v>1100.22</v>
+        <v>2000.82</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>112738.76</v>
+        <v>125196.64</v>
       </c>
       <c r="E66" t="n">
         <v>1</v>
@@ -2585,63 +2517,59 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX short (risk 1,100)</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>Bitcoin_Per_USD_Binance bullish_reversal (+2,685)</t>
-        </is>
-      </c>
+          <t>Gold_Futures_COMEX short (risk 2,001)</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n">
         <v>46084</v>
       </c>
       <c r="B67" s="5" t="n">
-        <v>113838.98</v>
+        <v>132194.24</v>
       </c>
       <c r="C67" s="5" t="n">
-        <v>1100.22</v>
+        <v>-0</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>112738.76</v>
+        <v>132194.24</v>
       </c>
       <c r="E67" t="n">
-        <v>1</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Gold_Futures_COMEX</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX target_r (+4,997)</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="n">
         <v>46085</v>
       </c>
       <c r="B68" s="5" t="n">
-        <v>113838.98</v>
+        <v>132194.24</v>
       </c>
       <c r="C68" s="5" t="n">
-        <v>2227.61</v>
+        <v>2079.42</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>111611.37</v>
+        <v>130114.83</v>
       </c>
       <c r="E68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX, USD_EUR_Cross_Rate</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate short (risk 1,127)</t>
+          <t>USD_EUR_Cross_Rate short (risk 2,079)</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
@@ -2651,30 +2579,30 @@
         <v>46086</v>
       </c>
       <c r="B69" s="5" t="n">
-        <v>112515.53</v>
+        <v>129753.19</v>
       </c>
       <c r="C69" s="5" t="n">
-        <v>2216.34</v>
+        <v>2046.71</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>110299.19</v>
+        <v>127706.48</v>
       </c>
       <c r="E69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX, S_P_500_Index</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>S_P_500_Index long (risk 1,116)</t>
+          <t>S_P_500_Index long (risk 2,047)</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate stop (-1,323)</t>
+          <t>USD_EUR_Cross_Rate stop (-2,441)</t>
         </is>
       </c>
     </row>
@@ -2683,30 +2611,30 @@
         <v>46087</v>
       </c>
       <c r="B70" s="5" t="n">
-        <v>111397.52</v>
+        <v>127703.02</v>
       </c>
       <c r="C70" s="5" t="n">
-        <v>2203.22</v>
+        <v>2008.82</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>109194.31</v>
+        <v>125694.19</v>
       </c>
       <c r="E70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX, USD_EUR_Cross_Rate</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate short (risk 1,103)</t>
+          <t>USD_EUR_Cross_Rate short (risk 2,009)</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>S_P_500_Index stop (-1,118)</t>
+          <t>S_P_500_Index stop (-2,050)</t>
         </is>
       </c>
     </row>
@@ -2715,20 +2643,20 @@
         <v>46088</v>
       </c>
       <c r="B71" s="5" t="n">
-        <v>111397.52</v>
+        <v>127703.02</v>
       </c>
       <c r="C71" s="5" t="n">
-        <v>2203.22</v>
+        <v>2008.82</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>109194.31</v>
+        <v>125694.19</v>
       </c>
       <c r="E71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX, USD_EUR_Cross_Rate</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="G71" t="inlineStr"/>
@@ -2739,20 +2667,20 @@
         <v>46089</v>
       </c>
       <c r="B72" s="5" t="n">
-        <v>111397.52</v>
+        <v>127703.02</v>
       </c>
       <c r="C72" s="5" t="n">
-        <v>2203.22</v>
+        <v>2008.82</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>109194.31</v>
+        <v>125694.19</v>
       </c>
       <c r="E72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX, USD_EUR_Cross_Rate</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="G72" t="inlineStr"/>
@@ -2763,13 +2691,13 @@
         <v>46090</v>
       </c>
       <c r="B73" s="5" t="n">
-        <v>114862.59</v>
+        <v>125511.57</v>
       </c>
       <c r="C73" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>114862.59</v>
+        <v>125511.57</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
@@ -2778,7 +2706,7 @@
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX bearish_reversal (+4,668); USD_EUR_Cross_Rate stop (-1,203)</t>
+          <t>USD_EUR_Cross_Rate stop (-2,191)</t>
         </is>
       </c>
     </row>
@@ -2787,13 +2715,13 @@
         <v>46091</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>114862.59</v>
+        <v>125511.57</v>
       </c>
       <c r="C74" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>114862.59</v>
+        <v>125511.57</v>
       </c>
       <c r="E74" t="n">
         <v>0</v>
@@ -2807,13 +2735,13 @@
         <v>46092</v>
       </c>
       <c r="B75" s="5" t="n">
-        <v>114862.59</v>
+        <v>125511.57</v>
       </c>
       <c r="C75" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>114862.59</v>
+        <v>125511.57</v>
       </c>
       <c r="E75" t="n">
         <v>0</v>
@@ -2827,13 +2755,13 @@
         <v>46093</v>
       </c>
       <c r="B76" s="5" t="n">
-        <v>114862.59</v>
+        <v>125511.57</v>
       </c>
       <c r="C76" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>114862.59</v>
+        <v>125511.57</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
@@ -2847,13 +2775,13 @@
         <v>46094</v>
       </c>
       <c r="B77" s="5" t="n">
-        <v>114862.59</v>
+        <v>125511.57</v>
       </c>
       <c r="C77" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>114862.59</v>
+        <v>125511.57</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
@@ -2867,13 +2795,13 @@
         <v>46095</v>
       </c>
       <c r="B78" s="5" t="n">
-        <v>114862.59</v>
+        <v>125511.57</v>
       </c>
       <c r="C78" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>114862.59</v>
+        <v>125511.57</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
@@ -2887,13 +2815,13 @@
         <v>46096</v>
       </c>
       <c r="B79" s="5" t="n">
-        <v>114862.59</v>
+        <v>125511.57</v>
       </c>
       <c r="C79" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>114862.59</v>
+        <v>125511.57</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
@@ -2907,13 +2835,13 @@
         <v>46097</v>
       </c>
       <c r="B80" s="5" t="n">
-        <v>114862.59</v>
+        <v>125511.57</v>
       </c>
       <c r="C80" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>114862.59</v>
+        <v>125511.57</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
@@ -2927,13 +2855,13 @@
         <v>46098</v>
       </c>
       <c r="B81" s="5" t="n">
-        <v>114862.59</v>
+        <v>125511.57</v>
       </c>
       <c r="C81" s="5" t="n">
-        <v>1148.63</v>
+        <v>1974.3</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>113713.97</v>
+        <v>123537.28</v>
       </c>
       <c r="E81" t="n">
         <v>1</v>
@@ -2945,7 +2873,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance short (risk 1,149)</t>
+          <t>Bitcoin_Per_USD_Binance short (risk 1,974)</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
@@ -2955,13 +2883,13 @@
         <v>46099</v>
       </c>
       <c r="B82" s="5" t="n">
-        <v>120602.26</v>
+        <v>130441.36</v>
       </c>
       <c r="C82" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>120602.26</v>
+        <v>130441.36</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
@@ -2970,7 +2898,7 @@
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance target_r (+5,740)</t>
+          <t>Bitcoin_Per_USD_Binance target_r (+4,930)</t>
         </is>
       </c>
     </row>
@@ -2979,13 +2907,13 @@
         <v>46100</v>
       </c>
       <c r="B83" s="5" t="n">
-        <v>120602.26</v>
+        <v>130441.36</v>
       </c>
       <c r="C83" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>120602.26</v>
+        <v>130441.36</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
@@ -2999,13 +2927,13 @@
         <v>46101</v>
       </c>
       <c r="B84" s="5" t="n">
-        <v>120602.26</v>
+        <v>130441.36</v>
       </c>
       <c r="C84" s="5" t="n">
-        <v>1206.02</v>
+        <v>2051.84</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>119396.23</v>
+        <v>128389.52</v>
       </c>
       <c r="E84" t="n">
         <v>1</v>
@@ -3017,7 +2945,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP short (risk 1,206)</t>
+          <t>United_States_Oil_Fund_LP short (risk 2,052)</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
@@ -3027,13 +2955,13 @@
         <v>46102</v>
       </c>
       <c r="B85" s="5" t="n">
-        <v>120602.26</v>
+        <v>130441.36</v>
       </c>
       <c r="C85" s="5" t="n">
-        <v>1206.02</v>
+        <v>2051.84</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>119396.23</v>
+        <v>128389.52</v>
       </c>
       <c r="E85" t="n">
         <v>1</v>
@@ -3051,13 +2979,13 @@
         <v>46103</v>
       </c>
       <c r="B86" s="5" t="n">
-        <v>120602.26</v>
+        <v>130441.36</v>
       </c>
       <c r="C86" s="5" t="n">
-        <v>1206.02</v>
+        <v>2051.84</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>119396.23</v>
+        <v>128389.52</v>
       </c>
       <c r="E86" t="n">
         <v>1</v>
@@ -3075,13 +3003,13 @@
         <v>46104</v>
       </c>
       <c r="B87" s="5" t="n">
-        <v>126613.96</v>
+        <v>135539.64</v>
       </c>
       <c r="C87" s="5" t="n">
-        <v>1193.96</v>
+        <v>2019.57</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>125420</v>
+        <v>133520.08</v>
       </c>
       <c r="E87" t="n">
         <v>1</v>
@@ -3093,12 +3021,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures long (risk 1,194)</t>
+          <t>NY_Copper_Futures long (risk 2,020)</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP target_r (+6,012)</t>
+          <t>United_States_Oil_Fund_LP target_r (+5,098)</t>
         </is>
       </c>
     </row>
@@ -3107,54 +3035,54 @@
         <v>46105</v>
       </c>
       <c r="B88" s="5" t="n">
-        <v>126613.96</v>
+        <v>140582.57</v>
       </c>
       <c r="C88" s="5" t="n">
-        <v>2448.16</v>
+        <v>2100.27</v>
       </c>
       <c r="D88" s="5" t="n">
-        <v>124165.8</v>
+        <v>138482.3</v>
       </c>
       <c r="E88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX, NY_Copper_Futures</t>
+          <t>Gold_Futures_COMEX</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX long (risk 1,254)</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
+          <t>Gold_Futures_COMEX long (risk 2,100)</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>NY_Copper_Futures target_r (+5,043)</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="n">
         <v>46106</v>
       </c>
       <c r="B89" s="5" t="n">
-        <v>132876.25</v>
+        <v>145818.66</v>
       </c>
       <c r="C89" s="5" t="n">
-        <v>1193.96</v>
+        <v>-0</v>
       </c>
       <c r="D89" s="5" t="n">
-        <v>131682.29</v>
+        <v>145818.66</v>
       </c>
       <c r="E89" t="n">
-        <v>1</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>NY_Copper_Futures</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX target_r (+6,262)</t>
+          <t>Gold_Futures_COMEX target_r (+5,236)</t>
         </is>
       </c>
     </row>
@@ -3163,22 +3091,18 @@
         <v>46107</v>
       </c>
       <c r="B90" s="5" t="n">
-        <v>132876.25</v>
+        <v>145818.66</v>
       </c>
       <c r="C90" s="5" t="n">
-        <v>1193.96</v>
+        <v>-0</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>131682.29</v>
+        <v>145818.66</v>
       </c>
       <c r="E90" t="n">
-        <v>1</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>NY_Copper_Futures</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr"/>
     </row>
@@ -3187,22 +3111,18 @@
         <v>46108</v>
       </c>
       <c r="B91" s="5" t="n">
-        <v>132876.25</v>
+        <v>145818.66</v>
       </c>
       <c r="C91" s="5" t="n">
-        <v>1193.96</v>
+        <v>-0</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>131682.29</v>
+        <v>145818.66</v>
       </c>
       <c r="E91" t="n">
-        <v>1</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>NY_Copper_Futures</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr"/>
     </row>
@@ -3211,22 +3131,18 @@
         <v>46109</v>
       </c>
       <c r="B92" s="5" t="n">
-        <v>132876.25</v>
+        <v>145818.66</v>
       </c>
       <c r="C92" s="5" t="n">
-        <v>1193.96</v>
+        <v>-0</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>131682.29</v>
+        <v>145818.66</v>
       </c>
       <c r="E92" t="n">
-        <v>1</v>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>NY_Copper_Futures</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr"/>
     </row>
@@ -3235,22 +3151,18 @@
         <v>46110</v>
       </c>
       <c r="B93" s="5" t="n">
-        <v>132876.25</v>
+        <v>145818.66</v>
       </c>
       <c r="C93" s="5" t="n">
-        <v>1193.96</v>
+        <v>-0</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>131682.29</v>
+        <v>145818.66</v>
       </c>
       <c r="E93" t="n">
-        <v>1</v>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>NY_Copper_Futures</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr"/>
     </row>
@@ -3259,22 +3171,18 @@
         <v>46111</v>
       </c>
       <c r="B94" s="5" t="n">
-        <v>132876.25</v>
+        <v>145818.66</v>
       </c>
       <c r="C94" s="5" t="n">
-        <v>1193.96</v>
+        <v>-0</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>131682.29</v>
+        <v>145818.66</v>
       </c>
       <c r="E94" t="n">
-        <v>1</v>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>NY_Copper_Futures</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr"/>
     </row>
@@ -3283,13 +3191,13 @@
         <v>46112</v>
       </c>
       <c r="B95" s="5" t="n">
-        <v>138842.52</v>
+        <v>145818.66</v>
       </c>
       <c r="C95" s="5" t="n">
-        <v>1316.82</v>
+        <v>2293.73</v>
       </c>
       <c r="D95" s="5" t="n">
-        <v>137525.69</v>
+        <v>143524.93</v>
       </c>
       <c r="E95" t="n">
         <v>1</v>
@@ -3301,27 +3209,23 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP short (risk 1,317)</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>NY_Copper_Futures target_r (+5,966)</t>
-        </is>
-      </c>
+          <t>United_States_Oil_Fund_LP short (risk 2,294)</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="4" t="n">
         <v>46113</v>
       </c>
       <c r="B96" s="5" t="n">
-        <v>145392.87</v>
+        <v>151494.16</v>
       </c>
       <c r="C96" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D96" s="5" t="n">
-        <v>145392.87</v>
+        <v>151494.16</v>
       </c>
       <c r="E96" t="n">
         <v>0</v>
@@ -3330,7 +3234,7 @@
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP target_r (+6,550)</t>
+          <t>United_States_Oil_Fund_LP target_r (+5,676)</t>
         </is>
       </c>
     </row>
@@ -3339,13 +3243,13 @@
         <v>46114</v>
       </c>
       <c r="B97" s="5" t="n">
-        <v>145392.87</v>
+        <v>151494.16</v>
       </c>
       <c r="C97" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D97" s="5" t="n">
-        <v>145392.87</v>
+        <v>151494.16</v>
       </c>
       <c r="E97" t="n">
         <v>0</v>
@@ -3359,13 +3263,13 @@
         <v>46115</v>
       </c>
       <c r="B98" s="5" t="n">
-        <v>145392.87</v>
+        <v>151494.16</v>
       </c>
       <c r="C98" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D98" s="5" t="n">
-        <v>145392.87</v>
+        <v>151494.16</v>
       </c>
       <c r="E98" t="n">
         <v>0</v>
@@ -3379,13 +3283,13 @@
         <v>46116</v>
       </c>
       <c r="B99" s="5" t="n">
-        <v>145392.87</v>
+        <v>151494.16</v>
       </c>
       <c r="C99" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D99" s="5" t="n">
-        <v>145392.87</v>
+        <v>151494.16</v>
       </c>
       <c r="E99" t="n">
         <v>0</v>
@@ -3399,13 +3303,13 @@
         <v>46117</v>
       </c>
       <c r="B100" s="5" t="n">
-        <v>145392.87</v>
+        <v>151494.16</v>
       </c>
       <c r="C100" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>145392.87</v>
+        <v>151494.16</v>
       </c>
       <c r="E100" t="n">
         <v>0</v>
@@ -3419,13 +3323,13 @@
         <v>46118</v>
       </c>
       <c r="B101" s="5" t="n">
-        <v>145392.87</v>
+        <v>151494.16</v>
       </c>
       <c r="C101" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>145392.87</v>
+        <v>151494.16</v>
       </c>
       <c r="E101" t="n">
         <v>0</v>
@@ -3439,13 +3343,13 @@
         <v>46119</v>
       </c>
       <c r="B102" s="5" t="n">
-        <v>145392.87</v>
+        <v>151494.16</v>
       </c>
       <c r="C102" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D102" s="5" t="n">
-        <v>145392.87</v>
+        <v>151494.16</v>
       </c>
       <c r="E102" t="n">
         <v>0</v>
@@ -3459,13 +3363,13 @@
         <v>46120</v>
       </c>
       <c r="B103" s="5" t="n">
-        <v>145392.87</v>
+        <v>151494.16</v>
       </c>
       <c r="C103" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D103" s="5" t="n">
-        <v>145392.87</v>
+        <v>151494.16</v>
       </c>
       <c r="E103" t="n">
         <v>0</v>
@@ -3479,13 +3383,13 @@
         <v>46121</v>
       </c>
       <c r="B104" s="5" t="n">
-        <v>145392.87</v>
+        <v>151494.16</v>
       </c>
       <c r="C104" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D104" s="5" t="n">
-        <v>145392.87</v>
+        <v>151494.16</v>
       </c>
       <c r="E104" t="n">
         <v>0</v>
@@ -3499,13 +3403,13 @@
         <v>46122</v>
       </c>
       <c r="B105" s="5" t="n">
-        <v>145392.87</v>
+        <v>151494.16</v>
       </c>
       <c r="C105" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D105" s="5" t="n">
-        <v>145392.87</v>
+        <v>151494.16</v>
       </c>
       <c r="E105" t="n">
         <v>0</v>
@@ -3519,13 +3423,13 @@
         <v>46123</v>
       </c>
       <c r="B106" s="5" t="n">
-        <v>145392.87</v>
+        <v>151494.16</v>
       </c>
       <c r="C106" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D106" s="5" t="n">
-        <v>145392.87</v>
+        <v>151494.16</v>
       </c>
       <c r="E106" t="n">
         <v>0</v>
@@ -3539,13 +3443,13 @@
         <v>46124</v>
       </c>
       <c r="B107" s="5" t="n">
-        <v>145392.87</v>
+        <v>151494.16</v>
       </c>
       <c r="C107" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D107" s="5" t="n">
-        <v>145392.87</v>
+        <v>151494.16</v>
       </c>
       <c r="E107" t="n">
         <v>0</v>
@@ -3559,13 +3463,13 @@
         <v>46125</v>
       </c>
       <c r="B108" s="5" t="n">
-        <v>145392.87</v>
+        <v>151494.16</v>
       </c>
       <c r="C108" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>145392.87</v>
+        <v>151494.16</v>
       </c>
       <c r="E108" t="n">
         <v>0</v>
@@ -3579,13 +3483,13 @@
         <v>46126</v>
       </c>
       <c r="B109" s="5" t="n">
-        <v>145392.87</v>
+        <v>151494.16</v>
       </c>
       <c r="C109" s="5" t="n">
-        <v>1453.93</v>
+        <v>2383</v>
       </c>
       <c r="D109" s="5" t="n">
-        <v>143938.94</v>
+        <v>149111.16</v>
       </c>
       <c r="E109" t="n">
         <v>1</v>
@@ -3597,7 +3501,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance short (risk 1,454)</t>
+          <t>Bitcoin_Per_USD_Binance short (risk 2,383)</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
@@ -3607,13 +3511,13 @@
         <v>46127</v>
       </c>
       <c r="B110" s="5" t="n">
-        <v>145392.87</v>
+        <v>151494.16</v>
       </c>
       <c r="C110" s="5" t="n">
-        <v>5729.06</v>
+        <v>9309.450000000001</v>
       </c>
       <c r="D110" s="5" t="n">
-        <v>139663.81</v>
+        <v>142184.71</v>
       </c>
       <c r="E110" t="n">
         <v>4</v>
@@ -3625,7 +3529,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Ethereum_Per_USD_Binance short (risk 1,439); Live_Cattle_Futures_CME short (risk 1,425); NY_Copper_Futures short (risk 1,411)</t>
+          <t>Ethereum_Per_USD_Binance short (risk 2,346); Live_Cattle_Futures_CME short (risk 2,309); NY_Copper_Futures short (risk 2,272)</t>
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
@@ -3635,13 +3539,13 @@
         <v>46128</v>
       </c>
       <c r="B111" s="5" t="n">
-        <v>159448.5</v>
+        <v>162696.41</v>
       </c>
       <c r="C111" s="5" t="n">
-        <v>2864.67</v>
+        <v>4655.31</v>
       </c>
       <c r="D111" s="5" t="n">
-        <v>156583.83</v>
+        <v>158041.1</v>
       </c>
       <c r="E111" t="n">
         <v>2</v>
@@ -3654,7 +3558,7 @@
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Ethereum_Per_USD_Binance target_r (+7,017); Live_Cattle_Futures_CME target_r (+7,039)</t>
+          <t>Ethereum_Per_USD_Binance target_r (+5,571); Live_Cattle_Futures_CME target_r (+5,632)</t>
         </is>
       </c>
     </row>
@@ -3663,13 +3567,13 @@
         <v>46129</v>
       </c>
       <c r="B112" s="5" t="n">
-        <v>159454.29</v>
+        <v>162630.65</v>
       </c>
       <c r="C112" s="5" t="n">
-        <v>1410.75</v>
+        <v>2272.31</v>
       </c>
       <c r="D112" s="5" t="n">
-        <v>158043.54</v>
+        <v>160358.34</v>
       </c>
       <c r="E112" t="n">
         <v>1</v>
@@ -3681,12 +3585,12 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate long (risk 1,566)</t>
+          <t>USD_EUR_Cross_Rate long (risk 2,486)</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance stop (-1,459); USD_EUR_Cross_Rate data_end (+1,465)</t>
+          <t>Bitcoin_Per_USD_Binance stop (-2,391); USD_EUR_Cross_Rate data_end (+2,326)</t>
         </is>
       </c>
     </row>
@@ -3695,13 +3599,13 @@
         <v>46130</v>
       </c>
       <c r="B113" s="5" t="n">
-        <v>159454.29</v>
+        <v>162630.65</v>
       </c>
       <c r="C113" s="5" t="n">
-        <v>1410.75</v>
+        <v>2272.31</v>
       </c>
       <c r="D113" s="5" t="n">
-        <v>158043.54</v>
+        <v>160358.34</v>
       </c>
       <c r="E113" t="n">
         <v>1</v>
@@ -3719,13 +3623,13 @@
         <v>46132</v>
       </c>
       <c r="B114" s="5" t="n">
-        <v>159454.29</v>
+        <v>162630.65</v>
       </c>
       <c r="C114" s="5" t="n">
-        <v>1410.75</v>
+        <v>2272.31</v>
       </c>
       <c r="D114" s="5" t="n">
-        <v>158043.54</v>
+        <v>160358.34</v>
       </c>
       <c r="E114" t="n">
         <v>1</v>
@@ -3743,13 +3647,13 @@
         <v>46133</v>
       </c>
       <c r="B115" s="5" t="n">
-        <v>159454.29</v>
+        <v>162630.65</v>
       </c>
       <c r="C115" s="5" t="n">
-        <v>1410.75</v>
+        <v>2272.31</v>
       </c>
       <c r="D115" s="5" t="n">
-        <v>158043.54</v>
+        <v>160358.34</v>
       </c>
       <c r="E115" t="n">
         <v>1</v>
@@ -3767,13 +3671,13 @@
         <v>46134</v>
       </c>
       <c r="B116" s="5" t="n">
-        <v>158032.8</v>
+        <v>160341.03</v>
       </c>
       <c r="C116" s="5" t="n">
-        <v>1580.44</v>
+        <v>2522.44</v>
       </c>
       <c r="D116" s="5" t="n">
-        <v>156452.36</v>
+        <v>157818.59</v>
       </c>
       <c r="E116" t="n">
         <v>1</v>
@@ -3785,12 +3689,12 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini short (risk 1,580)</t>
+          <t>Dow_Futures_E_mini short (risk 2,522)</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures stop (-1,421)</t>
+          <t>NY_Copper_Futures stop (-2,290)</t>
         </is>
       </c>
     </row>
@@ -3799,13 +3703,13 @@
         <v>46135</v>
       </c>
       <c r="B117" s="5" t="n">
-        <v>165883.16</v>
+        <v>166564.42</v>
       </c>
       <c r="C117" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D117" s="5" t="n">
-        <v>165883.16</v>
+        <v>166564.42</v>
       </c>
       <c r="E117" t="n">
         <v>0</v>
@@ -3814,7 +3718,7 @@
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini target_r (+7,850)</t>
+          <t>Dow_Futures_E_mini target_r (+6,223)</t>
         </is>
       </c>
     </row>
@@ -3823,13 +3727,13 @@
         <v>46136</v>
       </c>
       <c r="B118" s="5" t="n">
-        <v>165883.16</v>
+        <v>166564.42</v>
       </c>
       <c r="C118" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D118" s="5" t="n">
-        <v>165883.16</v>
+        <v>166564.42</v>
       </c>
       <c r="E118" t="n">
         <v>0</v>
@@ -3843,13 +3747,13 @@
         <v>46139</v>
       </c>
       <c r="B119" s="5" t="n">
-        <v>165883.16</v>
+        <v>166564.42</v>
       </c>
       <c r="C119" s="5" t="n">
-        <v>1658.83</v>
+        <v>2620.06</v>
       </c>
       <c r="D119" s="5" t="n">
-        <v>164224.32</v>
+        <v>163944.36</v>
       </c>
       <c r="E119" t="n">
         <v>1</v>
@@ -3861,7 +3765,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME short (risk 1,659)</t>
+          <t>Bitcoin_Per_USD_CME short (risk 2,620)</t>
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
@@ -3871,13 +3775,13 @@
         <v>46140</v>
       </c>
       <c r="B120" s="5" t="n">
-        <v>174170.49</v>
+        <v>173103.78</v>
       </c>
       <c r="C120" s="5" t="n">
-        <v>1642.24</v>
+        <v>2578.84</v>
       </c>
       <c r="D120" s="5" t="n">
-        <v>172528.24</v>
+        <v>170524.93</v>
       </c>
       <c r="E120" t="n">
         <v>1</v>
@@ -3889,12 +3793,12 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini short (risk 1,642)</t>
+          <t>S_P_500_E_mini short (risk 2,579)</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME target_r (+8,287)</t>
+          <t>Bitcoin_Per_USD_CME target_r (+6,539)</t>
         </is>
       </c>
     </row>
@@ -3903,58 +3807,62 @@
         <v>46141</v>
       </c>
       <c r="B121" s="5" t="n">
-        <v>174170.49</v>
+        <v>179547.8</v>
       </c>
       <c r="C121" s="5" t="n">
-        <v>3367.53</v>
+        <v>2682.36</v>
       </c>
       <c r="D121" s="5" t="n">
-        <v>170802.96</v>
+        <v>176865.45</v>
       </c>
       <c r="E121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT, S_P_500_E_mini</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 1,725)</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr"/>
+          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 2,682)</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>S_P_500_E_mini target_r (+6,444)</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="4" t="n">
         <v>46142</v>
       </c>
       <c r="B122" s="5" t="n">
-        <v>172524.31</v>
+        <v>186193.42</v>
       </c>
       <c r="C122" s="5" t="n">
-        <v>3433.31</v>
+        <v>2782.09</v>
       </c>
       <c r="D122" s="5" t="n">
-        <v>169091</v>
+        <v>183411.33</v>
       </c>
       <c r="E122" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT, Corn_CBOT_Futures</t>
+          <t>Corn_CBOT_Futures</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures short (risk 1,708)</t>
+          <t>Corn_CBOT_Futures short (risk 2,782)</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini stop (-1,646)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT target_r (+6,646)</t>
         </is>
       </c>
     </row>
@@ -3963,30 +3871,30 @@
         <v>46143</v>
       </c>
       <c r="B123" s="5" t="n">
-        <v>170456.7</v>
+        <v>182825.62</v>
       </c>
       <c r="C123" s="5" t="n">
-        <v>6747.45</v>
+        <v>8519.75</v>
       </c>
       <c r="D123" s="5" t="n">
-        <v>163709.24</v>
+        <v>174305.87</v>
       </c>
       <c r="E123" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT, Japanese_Yen_Futures, Live_Cattle_Futures_CME, US_Dollar_Index_Futures</t>
+          <t>Japanese_Yen_Futures, Live_Cattle_Futures_CME, US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Japanese_Yen_Futures short (risk 1,691); Live_Cattle_Futures_CME short (risk 1,674); US_Dollar_Index_Futures long (risk 1,657)</t>
+          <t>Japanese_Yen_Futures short (risk 2,885); Live_Cattle_Futures_CME short (risk 2,840); US_Dollar_Index_Futures long (risk 2,795)</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures stop (-2,068)</t>
+          <t>Corn_CBOT_Futures unknown_pl (-3,368)</t>
         </is>
       </c>
     </row>
@@ -3995,58 +3903,62 @@
         <v>46146</v>
       </c>
       <c r="B124" s="5" t="n">
-        <v>170456.7</v>
+        <v>189879.38</v>
       </c>
       <c r="C124" s="5" t="n">
-        <v>8384.549999999999</v>
+        <v>8421.9</v>
       </c>
       <c r="D124" s="5" t="n">
-        <v>162072.15</v>
+        <v>181457.48</v>
       </c>
       <c r="E124" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT, Japanese_Yen_Futures, Live_Cattle_Futures_CME, Nasdaq_100_E_mini, US_Dollar_Index_Futures</t>
+          <t>Japanese_Yen_Futures, Nasdaq_100_E_mini, US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini short (risk 1,637)</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr"/>
+          <t>Nasdaq_100_E_mini short (risk 2,742)</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Live_Cattle_Futures_CME target_r (+7,054)</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="n">
         <v>46147</v>
       </c>
       <c r="B125" s="5" t="n">
-        <v>168818.49</v>
+        <v>194100.39</v>
       </c>
       <c r="C125" s="5" t="n">
-        <v>8368.18</v>
+        <v>5739.39</v>
       </c>
       <c r="D125" s="5" t="n">
-        <v>160450.31</v>
+        <v>188361.01</v>
       </c>
       <c r="E125" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT, Corn_CBOT_Futures, Japanese_Yen_Futures, Live_Cattle_Futures_CME, US_Dollar_Index_Futures</t>
+          <t>Corn_CBOT_Futures, Japanese_Yen_Futures</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures short (risk 1,621)</t>
+          <t>Corn_CBOT_Futures short (risk 2,854)</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini stop (-1,638)</t>
+          <t>Nasdaq_100_E_mini unknown_pl (-2,744); US_Dollar_Index_Futures target_r (+6,965)</t>
         </is>
       </c>
     </row>
@@ -4055,30 +3967,30 @@
         <v>46148</v>
       </c>
       <c r="B126" s="5" t="n">
-        <v>181657.03</v>
+        <v>197520.28</v>
       </c>
       <c r="C126" s="5" t="n">
-        <v>3278.5</v>
+        <v>5879.23</v>
       </c>
       <c r="D126" s="5" t="n">
-        <v>178378.53</v>
+        <v>191641.05</v>
       </c>
       <c r="E126" t="n">
         <v>2</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME, Live_Cattle_Futures_CME</t>
+          <t>Bitcoin_Per_USD_CME, US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME short (risk 1,605)</t>
+          <t>Bitcoin_Per_USD_CME short (risk 2,963); US_Dollar_Index_Futures long (risk 2,916)</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT target_r (+8,588); Corn_CBOT_Futures target_r (+7,809); Japanese_Yen_Futures stop (-1,874); US_Dollar_Index_Futures stop (-1,684)</t>
+          <t>Corn_CBOT_Futures target_r (+6,617); Japanese_Yen_Futures stop (-3,197)</t>
         </is>
       </c>
     </row>
@@ -4087,30 +3999,30 @@
         <v>46149</v>
       </c>
       <c r="B127" s="5" t="n">
-        <v>198016.99</v>
+        <v>204916.9</v>
       </c>
       <c r="C127" s="5" t="n">
-        <v>3549.73</v>
+        <v>8897.92</v>
       </c>
       <c r="D127" s="5" t="n">
-        <v>194467.26</v>
+        <v>196018.98</v>
       </c>
       <c r="E127" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>EURO_Futures, NY_Platinum_Futures</t>
+          <t>EURO_Futures, NY_Platinum_Futures, US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>EURO_Futures short (risk 1,784); NY_Platinum_Futures short (risk 1,766)</t>
+          <t>EURO_Futures short (risk 3,015); NY_Platinum_Futures short (risk 2,967)</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME target_r (+8,017); Live_Cattle_Futures_CME target_r (+8,343)</t>
+          <t>Bitcoin_Per_USD_CME target_r (+7,397)</t>
         </is>
       </c>
     </row>
@@ -4119,26 +4031,26 @@
         <v>46150</v>
       </c>
       <c r="B128" s="5" t="n">
-        <v>196187.46</v>
+        <v>201825.09</v>
       </c>
       <c r="C128" s="5" t="n">
-        <v>1765.95</v>
+        <v>5883.41</v>
       </c>
       <c r="D128" s="5" t="n">
-        <v>194421.52</v>
+        <v>195941.69</v>
       </c>
       <c r="E128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures</t>
+          <t>NY_Platinum_Futures, US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
-          <t>EURO_Futures stop (-1,830)</t>
+          <t>EURO_Futures unknown_pl (-3,092)</t>
         </is>
       </c>
     </row>
@@ -4147,30 +4059,30 @@
         <v>46153</v>
       </c>
       <c r="B129" s="5" t="n">
-        <v>194397.24</v>
+        <v>198817.21</v>
       </c>
       <c r="C129" s="5" t="n">
-        <v>1944.22</v>
+        <v>5998.47</v>
       </c>
       <c r="D129" s="5" t="n">
-        <v>192453.03</v>
+        <v>192818.74</v>
       </c>
       <c r="E129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX</t>
+          <t>Gold_Futures_COMEX, US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX short (risk 1,944)</t>
+          <t>Gold_Futures_COMEX short (risk 3,082)</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures stop (-1,790)</t>
+          <t>NY_Platinum_Futures stop (-3,008)</t>
         </is>
       </c>
     </row>
@@ -4179,13 +4091,13 @@
         <v>46154</v>
       </c>
       <c r="B130" s="5" t="n">
-        <v>192390.81</v>
+        <v>202903.39</v>
       </c>
       <c r="C130" s="5" t="n">
-        <v>1924.53</v>
+        <v>3033.04</v>
       </c>
       <c r="D130" s="5" t="n">
-        <v>190466.28</v>
+        <v>199870.36</v>
       </c>
       <c r="E130" t="n">
         <v>1</v>
@@ -4197,12 +4109,12 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX short (risk 1,925)</t>
+          <t>Silver_Futures_COMEX short (risk 3,033)</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX unknown_pl (-2,006)</t>
+          <t>Gold_Futures_COMEX unknown_pl (-3,181); US_Dollar_Index_Futures target_r (+7,267)</t>
         </is>
       </c>
     </row>
@@ -4211,13 +4123,13 @@
         <v>46155</v>
       </c>
       <c r="B131" s="5" t="n">
-        <v>190462.27</v>
+        <v>199864.04</v>
       </c>
       <c r="C131" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D131" s="5" t="n">
-        <v>190462.27</v>
+        <v>199864.04</v>
       </c>
       <c r="E131" t="n">
         <v>0</v>
@@ -4226,7 +4138,7 @@
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX stop (-1,929)</t>
+          <t>Silver_Futures_COMEX stop (-3,039)</t>
         </is>
       </c>
     </row>
@@ -4235,13 +4147,13 @@
         <v>46156</v>
       </c>
       <c r="B132" s="5" t="n">
-        <v>190462.27</v>
+        <v>199864.04</v>
       </c>
       <c r="C132" s="5" t="n">
-        <v>1904.62</v>
+        <v>3143.86</v>
       </c>
       <c r="D132" s="5" t="n">
-        <v>188557.65</v>
+        <v>196720.18</v>
       </c>
       <c r="E132" t="n">
         <v>1</v>
@@ -4253,7 +4165,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 1,905)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 3,144)</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
@@ -4263,13 +4175,13 @@
         <v>46157</v>
       </c>
       <c r="B133" s="5" t="n">
-        <v>199933.21</v>
+        <v>207637.56</v>
       </c>
       <c r="C133" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D133" s="5" t="n">
-        <v>199933.21</v>
+        <v>207637.56</v>
       </c>
       <c r="E133" t="n">
         <v>0</v>
@@ -4278,7 +4190,7 @@
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT target_r (+9,471)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT target_r (+7,774)</t>
         </is>
       </c>
     </row>
@@ -4287,13 +4199,13 @@
         <v>46160</v>
       </c>
       <c r="B134" s="5" t="n">
-        <v>199933.21</v>
+        <v>207637.56</v>
       </c>
       <c r="C134" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>199933.21</v>
+        <v>207637.56</v>
       </c>
       <c r="E134" t="n">
         <v>0</v>
@@ -4307,13 +4219,13 @@
         <v>46161</v>
       </c>
       <c r="B135" s="5" t="n">
-        <v>199933.21</v>
+        <v>207637.56</v>
       </c>
       <c r="C135" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>199933.21</v>
+        <v>207637.56</v>
       </c>
       <c r="E135" t="n">
         <v>0</v>
@@ -4327,13 +4239,13 @@
         <v>46162</v>
       </c>
       <c r="B136" s="5" t="n">
-        <v>199933.21</v>
+        <v>207637.56</v>
       </c>
       <c r="C136" s="5" t="n">
-        <v>1999.33</v>
+        <v>3266.14</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>197933.87</v>
+        <v>204371.42</v>
       </c>
       <c r="E136" t="n">
         <v>1</v>
@@ -4345,7 +4257,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures short (risk 1,999)</t>
+          <t>US_Dollar_Index_Futures short (risk 3,266)</t>
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
@@ -4355,13 +4267,13 @@
         <v>46163</v>
       </c>
       <c r="B137" s="5" t="n">
-        <v>199933.21</v>
+        <v>207637.56</v>
       </c>
       <c r="C137" s="5" t="n">
-        <v>3978.67</v>
+        <v>6480.9</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>195954.53</v>
+        <v>201156.66</v>
       </c>
       <c r="E137" t="n">
         <v>2</v>
@@ -4373,7 +4285,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures long (risk 1,979)</t>
+          <t>NY_Palladium_Futures long (risk 3,215)</t>
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
@@ -4383,70 +4295,70 @@
         <v>46164</v>
       </c>
       <c r="B138" s="5" t="n">
-        <v>199933.21</v>
+        <v>215636.64</v>
       </c>
       <c r="C138" s="5" t="n">
-        <v>3978.67</v>
+        <v>3266.14</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>195954.53</v>
+        <v>212370.5</v>
       </c>
       <c r="E138" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures, US_Dollar_Index_Futures</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="G138" t="inlineStr"/>
-      <c r="H138" t="inlineStr"/>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>NY_Palladium_Futures target_r (+7,999)</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="4" t="n">
         <v>46167</v>
       </c>
       <c r="B139" s="5" t="n">
-        <v>199933.21</v>
+        <v>223768.49</v>
       </c>
       <c r="C139" s="5" t="n">
-        <v>3978.67</v>
+        <v>-0</v>
       </c>
       <c r="D139" s="5" t="n">
-        <v>195954.53</v>
+        <v>223768.49</v>
       </c>
       <c r="E139" t="n">
-        <v>2</v>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>NY_Palladium_Futures, US_Dollar_Index_Futures</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr"/>
-      <c r="H139" t="inlineStr"/>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>US_Dollar_Index_Futures target_r (+8,132)</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="4" t="n">
         <v>46168</v>
       </c>
       <c r="B140" s="5" t="n">
-        <v>199933.21</v>
+        <v>223768.49</v>
       </c>
       <c r="C140" s="5" t="n">
-        <v>3978.67</v>
+        <v>-0</v>
       </c>
       <c r="D140" s="5" t="n">
-        <v>195954.53</v>
+        <v>223768.49</v>
       </c>
       <c r="E140" t="n">
-        <v>2</v>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>NY_Palladium_Futures, US_Dollar_Index_Futures</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr"/>
     </row>
@@ -4455,22 +4367,18 @@
         <v>46169</v>
       </c>
       <c r="B141" s="5" t="n">
-        <v>199933.21</v>
+        <v>223768.49</v>
       </c>
       <c r="C141" s="5" t="n">
-        <v>3978.67</v>
+        <v>-0</v>
       </c>
       <c r="D141" s="5" t="n">
-        <v>195954.53</v>
+        <v>223768.49</v>
       </c>
       <c r="E141" t="n">
-        <v>2</v>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>NY_Palladium_Futures, US_Dollar_Index_Futures</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr"/>
     </row>
@@ -4479,25 +4387,25 @@
         <v>46170</v>
       </c>
       <c r="B142" s="5" t="n">
-        <v>199933.21</v>
+        <v>223768.49</v>
       </c>
       <c r="C142" s="5" t="n">
-        <v>5938.22</v>
+        <v>6984.39</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>193994.99</v>
+        <v>216784.1</v>
       </c>
       <c r="E142" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures, Silver_Futures_COMEX, US_Dollar_Index_Futures</t>
+          <t>Silver_Futures_COMEX, US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX long (risk 1,960)</t>
+          <t>Silver_Futures_COMEX long (risk 3,520); US_Dollar_Index_Futures short (risk 3,465)</t>
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
@@ -4507,20 +4415,20 @@
         <v>46174</v>
       </c>
       <c r="B143" s="5" t="n">
-        <v>199933.21</v>
+        <v>223768.49</v>
       </c>
       <c r="C143" s="5" t="n">
-        <v>5938.22</v>
+        <v>6984.39</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>193994.99</v>
+        <v>216784.1</v>
       </c>
       <c r="E143" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures, Silver_Futures_COMEX, US_Dollar_Index_Futures</t>
+          <t>Silver_Futures_COMEX, US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="G143" t="inlineStr"/>
@@ -4531,20 +4439,20 @@
         <v>46175</v>
       </c>
       <c r="B144" s="5" t="n">
-        <v>199933.21</v>
+        <v>223768.49</v>
       </c>
       <c r="C144" s="5" t="n">
-        <v>5938.22</v>
+        <v>6984.39</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>193994.99</v>
+        <v>216784.1</v>
       </c>
       <c r="E144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures, Silver_Futures_COMEX, US_Dollar_Index_Futures</t>
+          <t>Silver_Futures_COMEX, US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="G144" t="inlineStr"/>
@@ -4555,26 +4463,26 @@
         <v>46176</v>
       </c>
       <c r="B145" s="5" t="n">
-        <v>197907.29</v>
+        <v>220249.63</v>
       </c>
       <c r="C145" s="5" t="n">
-        <v>3958.88</v>
+        <v>3519.88</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>193948.42</v>
+        <v>216729.76</v>
       </c>
       <c r="E145" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX, US_Dollar_Index_Futures</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures stop (-2,026)</t>
+          <t>US_Dollar_Index_Futures stop (-3,519)</t>
         </is>
       </c>
     </row>
@@ -4583,20 +4491,20 @@
         <v>46177</v>
       </c>
       <c r="B146" s="5" t="n">
-        <v>197907.29</v>
+        <v>220249.63</v>
       </c>
       <c r="C146" s="5" t="n">
-        <v>3958.88</v>
+        <v>3519.88</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>193948.42</v>
+        <v>216729.76</v>
       </c>
       <c r="E146" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX, US_Dollar_Index_Futures</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="G146" t="inlineStr"/>
@@ -4607,13 +4515,13 @@
         <v>46178</v>
       </c>
       <c r="B147" s="5" t="n">
-        <v>193903.16</v>
+        <v>216722.12</v>
       </c>
       <c r="C147" s="5" t="n">
-        <v>1939.48</v>
+        <v>3409.16</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>191963.67</v>
+        <v>213312.97</v>
       </c>
       <c r="E147" t="n">
         <v>1</v>
@@ -4625,12 +4533,12 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini short (risk 1,939)</t>
+          <t>Dow_Futures_E_mini short (risk 3,409)</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX stop (-1,964); US_Dollar_Index_Futures stop (-2,040)</t>
+          <t>Silver_Futures_COMEX stop (-3,528)</t>
         </is>
       </c>
     </row>
@@ -4639,13 +4547,13 @@
         <v>46181</v>
       </c>
       <c r="B148" s="5" t="n">
-        <v>203563.98</v>
+        <v>225180.7</v>
       </c>
       <c r="C148" s="5" t="n">
-        <v>3820.08</v>
+        <v>6658.05</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>199743.91</v>
+        <v>218522.65</v>
       </c>
       <c r="E148" t="n">
         <v>2</v>
@@ -4657,12 +4565,12 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX long (risk 1,920); US_Dollar_Index_Futures short (risk 1,900)</t>
+          <t>Gold_Futures_COMEX long (risk 3,355); US_Dollar_Index_Futures short (risk 3,303)</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini target_r (+9,661)</t>
+          <t>Dow_Futures_E_mini target_r (+8,459)</t>
         </is>
       </c>
     </row>
@@ -4671,26 +4579,22 @@
         <v>46182</v>
       </c>
       <c r="B149" s="5" t="n">
-        <v>201630.15</v>
+        <v>230008.13</v>
       </c>
       <c r="C149" s="5" t="n">
-        <v>1900.44</v>
+        <v>-0</v>
       </c>
       <c r="D149" s="5" t="n">
-        <v>199729.71</v>
+        <v>230008.13</v>
       </c>
       <c r="E149" t="n">
-        <v>1</v>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>US_Dollar_Index_Futures</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX stop (-1,934)</t>
+          <t>Gold_Futures_COMEX stop (-3,380); US_Dollar_Index_Futures target_r (+8,208)</t>
         </is>
       </c>
     </row>
@@ -4699,22 +4603,18 @@
         <v>46183</v>
       </c>
       <c r="B150" s="5" t="n">
-        <v>201630.15</v>
+        <v>230008.13</v>
       </c>
       <c r="C150" s="5" t="n">
-        <v>1900.44</v>
+        <v>-0</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>199729.71</v>
+        <v>230008.13</v>
       </c>
       <c r="E150" t="n">
-        <v>1</v>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>US_Dollar_Index_Futures</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr"/>
     </row>
@@ -4723,73 +4623,73 @@
         <v>46184</v>
       </c>
       <c r="B151" s="5" t="n">
-        <v>199673.4</v>
+        <v>230008.13</v>
       </c>
       <c r="C151" s="5" t="n">
-        <v>1997.3</v>
+        <v>7179.14</v>
       </c>
       <c r="D151" s="5" t="n">
-        <v>197676.11</v>
+        <v>222828.99</v>
       </c>
       <c r="E151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX</t>
+          <t>Gold_Futures_COMEX, US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX long (risk 1,997)</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>US_Dollar_Index_Futures stop (-1,957)</t>
-        </is>
-      </c>
+          <t>Gold_Futures_COMEX long (risk 3,618); US_Dollar_Index_Futures short (risk 3,561)</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="4" t="n">
         <v>46185</v>
       </c>
       <c r="B152" s="5" t="n">
-        <v>199673.4</v>
+        <v>247914.78</v>
       </c>
       <c r="C152" s="5" t="n">
-        <v>3974.06</v>
+        <v>3505.1</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>195699.35</v>
+        <v>244409.68</v>
       </c>
       <c r="E152" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures, Gold_Futures_COMEX</t>
+          <t>Corn_CBOT_Futures</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures long (risk 1,977)</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr"/>
+          <t>Corn_CBOT_Futures long (risk 3,505)</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX target_r (+9,032); US_Dollar_Index_Futures target_r (+8,874)</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="4" t="n">
         <v>46188</v>
       </c>
       <c r="B153" s="5" t="n">
-        <v>207383.25</v>
+        <v>243890.41</v>
       </c>
       <c r="C153" s="5" t="n">
-        <v>1956.99</v>
+        <v>3844.56</v>
       </c>
       <c r="D153" s="5" t="n">
-        <v>205426.26</v>
+        <v>240045.85</v>
       </c>
       <c r="E153" t="n">
         <v>1</v>
@@ -4801,12 +4701,12 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT long (risk 1,957)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT long (risk 3,845)</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures stop (-2,270); Gold_Futures_COMEX target_r (+9,979)</t>
+          <t>Corn_CBOT_Futures stop (-4,024)</t>
         </is>
       </c>
     </row>
@@ -4815,37 +4715,37 @@
         <v>46189</v>
       </c>
       <c r="B154" s="5" t="n">
-        <v>207383.25</v>
+        <v>253385.32</v>
       </c>
       <c r="C154" s="5" t="n">
-        <v>1956.99</v>
+        <v>-0</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>205426.26</v>
+        <v>253385.32</v>
       </c>
       <c r="E154" t="n">
-        <v>1</v>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr"/>
-      <c r="H154" t="inlineStr"/>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT target_r (+9,495)</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="n">
         <v>46190</v>
       </c>
       <c r="B155" s="5" t="n">
-        <v>216960.58</v>
+        <v>253385.32</v>
       </c>
       <c r="C155" s="5" t="n">
-        <v>2054.26</v>
+        <v>3985.75</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>214906.32</v>
+        <v>249399.57</v>
       </c>
       <c r="E155" t="n">
         <v>1</v>
@@ -4857,27 +4757,23 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures short (risk 2,054)</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT bullish_reversal (+9,577)</t>
-        </is>
-      </c>
+          <t>US_Dollar_Index_Futures short (risk 3,986)</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="4" t="n">
         <v>46191</v>
       </c>
       <c r="B156" s="5" t="n">
-        <v>214878.46</v>
+        <v>249345.52</v>
       </c>
       <c r="C156" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>214878.46</v>
+        <v>249345.52</v>
       </c>
       <c r="E156" t="n">
         <v>0</v>
@@ -4886,7 +4782,7 @@
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures stop (-2,082)</t>
+          <t>US_Dollar_Index_Futures stop (-4,040)</t>
         </is>
       </c>
     </row>
@@ -4895,13 +4791,13 @@
         <v>46192</v>
       </c>
       <c r="B157" s="5" t="n">
-        <v>214878.46</v>
+        <v>249345.52</v>
       </c>
       <c r="C157" s="5" t="n">
-        <v>2148.78</v>
+        <v>3922.21</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>212729.68</v>
+        <v>245423.32</v>
       </c>
       <c r="E157" t="n">
         <v>1</v>
@@ -4913,7 +4809,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures short (risk 2,149)</t>
+          <t>US_Dollar_Index_Futures short (risk 3,922)</t>
         </is>
       </c>
       <c r="H157" t="inlineStr"/>
@@ -4923,13 +4819,13 @@
         <v>46195</v>
       </c>
       <c r="B158" s="5" t="n">
-        <v>214878.46</v>
+        <v>249345.52</v>
       </c>
       <c r="C158" s="5" t="n">
-        <v>2148.78</v>
+        <v>3922.21</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>212729.68</v>
+        <v>245423.32</v>
       </c>
       <c r="E158" t="n">
         <v>1</v>
@@ -4947,13 +4843,13 @@
         <v>46196</v>
       </c>
       <c r="B159" s="5" t="n">
-        <v>212700.04</v>
+        <v>245369.22</v>
       </c>
       <c r="C159" s="5" t="n">
-        <v>2127.3</v>
+        <v>3860.51</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>210572.74</v>
+        <v>241508.71</v>
       </c>
       <c r="E159" t="n">
         <v>1</v>
@@ -4965,12 +4861,12 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures long (risk 2,127)</t>
+          <t>NY_Platinum_Futures long (risk 3,861)</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures stop (-2,178)</t>
+          <t>US_Dollar_Index_Futures stop (-3,976)</t>
         </is>
       </c>
     </row>
@@ -4979,13 +4875,13 @@
         <v>46197</v>
       </c>
       <c r="B160" s="5" t="n">
-        <v>210531.23</v>
+        <v>241433.38</v>
       </c>
       <c r="C160" s="5" t="n">
-        <v>2105.73</v>
+        <v>3798.93</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>208425.51</v>
+        <v>237634.45</v>
       </c>
       <c r="E160" t="n">
         <v>1</v>
@@ -4997,12 +4893,12 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>EURO_Futures long (risk 2,106)</t>
+          <t>EURO_Futures long (risk 3,799)</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures stop (-2,169)</t>
+          <t>NY_Platinum_Futures stop (-3,936)</t>
         </is>
       </c>
     </row>
@@ -5011,13 +4907,13 @@
         <v>46198</v>
       </c>
       <c r="B161" s="5" t="n">
-        <v>210531.23</v>
+        <v>241433.38</v>
       </c>
       <c r="C161" s="5" t="n">
-        <v>10318.52</v>
+        <v>18401.79</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>200212.71</v>
+        <v>223031.6</v>
       </c>
       <c r="E161" t="n">
         <v>5</v>
@@ -5029,7 +4925,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures short (risk 2,084); NY_Palladium_Futures long (risk 2,063); NY_Platinum_Futures long (risk 2,043); US_Dollar_Index_Futures short (risk 2,022)</t>
+          <t>NY_Natural_Gas_Futures short (risk 3,738); NY_Palladium_Futures long (risk 3,679); NY_Platinum_Futures long (risk 3,621); US_Dollar_Index_Futures short (risk 3,564)</t>
         </is>
       </c>
       <c r="H161" t="inlineStr"/>
@@ -5039,26 +4935,26 @@
         <v>46199</v>
       </c>
       <c r="B162" s="5" t="n">
-        <v>228616.18</v>
+        <v>264810.11</v>
       </c>
       <c r="C162" s="5" t="n">
-        <v>4148.51</v>
+        <v>3621.32</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>224467.67</v>
+        <v>261188.79</v>
       </c>
       <c r="E162" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>EURO_Futures, NY_Platinum_Futures</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures stop (-2,254); NY_Palladium_Futures target_r (+10,263); US_Dollar_Index_Futures target_r (+10,077)</t>
+          <t>EURO_Futures target_r (+9,470); NY_Natural_Gas_Futures stop (-4,043); NY_Palladium_Futures target_r (+9,101); US_Dollar_Index_Futures target_r (+8,849)</t>
         </is>
       </c>
     </row>
@@ -5067,20 +4963,20 @@
         <v>46202</v>
       </c>
       <c r="B163" s="5" t="n">
-        <v>228616.18</v>
+        <v>264810.11</v>
       </c>
       <c r="C163" s="5" t="n">
-        <v>4148.51</v>
+        <v>3621.32</v>
       </c>
       <c r="D163" s="5" t="n">
-        <v>224467.67</v>
+        <v>261188.79</v>
       </c>
       <c r="E163" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>EURO_Futures, NY_Platinum_Futures</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="G163" t="inlineStr"/>
@@ -5091,25 +4987,25 @@
         <v>46203</v>
       </c>
       <c r="B164" s="5" t="n">
-        <v>228616.18</v>
+        <v>264810.11</v>
       </c>
       <c r="C164" s="5" t="n">
-        <v>10815.42</v>
+        <v>15753.95</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>217800.76</v>
+        <v>249056.15</v>
       </c>
       <c r="E164" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT, EURO_Futures, German_Long_Bund, Gold_Futures_COMEX, NY_Platinum_Futures</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT, German_Long_Bund, Gold_Futures_COMEX, NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT long (risk 2,245); German_Long_Bund short (risk 2,222); Gold_Futures_COMEX long (risk 2,200)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT long (risk 4,108); German_Long_Bund short (risk 4,044); Gold_Futures_COMEX long (risk 3,980)</t>
         </is>
       </c>
       <c r="H164" t="inlineStr"/>
@@ -5119,30 +5015,30 @@
         <v>46204</v>
       </c>
       <c r="B165" s="5" t="n">
-        <v>248647.89</v>
+        <v>290897.86</v>
       </c>
       <c r="C165" s="5" t="n">
-        <v>8662.190000000001</v>
+        <v>7773.68</v>
       </c>
       <c r="D165" s="5" t="n">
-        <v>239985.7</v>
+        <v>283124.17</v>
       </c>
       <c r="E165" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini, EURO_Futures, German_Long_Bund, Sugar_World_CSCE_Futures</t>
+          <t>Dow_Futures_E_mini, Sugar_World_CSCE_Futures</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini short (risk 2,178); Sugar_World_CSCE_Futures short (risk 2,156)</t>
+          <t>Dow_Futures_E_mini short (risk 3,918); Sugar_World_CSCE_Futures short (risk 3,856)</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT target_r (+11,114); Gold_Futures_COMEX target_r (+10,985); NY_Platinum_Futures stop (-2,067)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT target_r (+10,071); German_Long_Bund target_r (+9,758); Gold_Futures_COMEX target_r (+9,923); NY_Platinum_Futures stop (-3,664)</t>
         </is>
       </c>
     </row>
@@ -5151,26 +5047,26 @@
         <v>46205</v>
       </c>
       <c r="B166" s="5" t="n">
-        <v>246446.46</v>
+        <v>286938.08</v>
       </c>
       <c r="C166" s="5" t="n">
-        <v>6484.18</v>
+        <v>3856.03</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>239962.28</v>
+        <v>283082.05</v>
       </c>
       <c r="E166" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>EURO_Futures, German_Long_Bund, Sugar_World_CSCE_Futures</t>
+          <t>Sugar_World_CSCE_Futures</t>
         </is>
       </c>
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini stop (-2,201)</t>
+          <t>Dow_Futures_E_mini stop (-3,960)</t>
         </is>
       </c>
     </row>
@@ -5179,20 +5075,20 @@
         <v>46206</v>
       </c>
       <c r="B167" s="5" t="n">
-        <v>246446.46</v>
+        <v>286938.08</v>
       </c>
       <c r="C167" s="5" t="n">
-        <v>6484.18</v>
+        <v>3856.03</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>239962.28</v>
+        <v>283082.05</v>
       </c>
       <c r="E167" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>EURO_Futures, German_Long_Bund, Sugar_World_CSCE_Futures</t>
+          <t>Sugar_World_CSCE_Futures</t>
         </is>
       </c>
       <c r="G167" t="inlineStr"/>
@@ -5203,26 +5099,22 @@
         <v>46210</v>
       </c>
       <c r="B168" s="5" t="n">
-        <v>254876.42</v>
+        <v>282488.81</v>
       </c>
       <c r="C168" s="5" t="n">
-        <v>2105.73</v>
+        <v>-0</v>
       </c>
       <c r="D168" s="5" t="n">
-        <v>252770.69</v>
+        <v>282488.81</v>
       </c>
       <c r="E168" t="n">
-        <v>1</v>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>EURO_Futures</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr">
         <is>
-          <t>German_Long_Bund target_r (+10,918); Sugar_World_CSCE_Futures stop (-2,488)</t>
+          <t>Sugar_World_CSCE_Futures stop (-4,449)</t>
         </is>
       </c>
     </row>
@@ -5231,25 +5123,25 @@
         <v>46211</v>
       </c>
       <c r="B169" s="5" t="n">
-        <v>254876.42</v>
+        <v>282488.81</v>
       </c>
       <c r="C169" s="5" t="n">
-        <v>7135.86</v>
+        <v>8817.200000000001</v>
       </c>
       <c r="D169" s="5" t="n">
-        <v>247740.56</v>
+        <v>273671.61</v>
       </c>
       <c r="E169" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>EURO_Futures, Live_Cattle_Futures_CME, NY_Natural_Gas_Futures</t>
+          <t>Live_Cattle_Futures_CME, NY_Natural_Gas_Futures</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME long (risk 2,528); NY_Natural_Gas_Futures short (risk 2,502)</t>
+          <t>Live_Cattle_Futures_CME long (risk 4,444); NY_Natural_Gas_Futures short (risk 4,374)</t>
         </is>
       </c>
       <c r="H169" t="inlineStr"/>
@@ -5259,26 +5151,22 @@
         <v>46212</v>
       </c>
       <c r="B170" s="5" t="n">
-        <v>263855.85</v>
+        <v>304254.5</v>
       </c>
       <c r="C170" s="5" t="n">
-        <v>4633.43</v>
+        <v>-0</v>
       </c>
       <c r="D170" s="5" t="n">
-        <v>259222.42</v>
+        <v>304254.5</v>
       </c>
       <c r="E170" t="n">
-        <v>2</v>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>EURO_Futures, Live_Cattle_Futures_CME</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F170" t="inlineStr"/>
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures bearish_reversal (+8,979)</t>
+          <t>Live_Cattle_Futures_CME target_r (+11,003); NY_Natural_Gas_Futures target_r (+10,763)</t>
         </is>
       </c>
     </row>
@@ -5287,53 +5175,45 @@
         <v>46213</v>
       </c>
       <c r="B171" s="5" t="n">
-        <v>261207.78</v>
+        <v>304254.5</v>
       </c>
       <c r="C171" s="5" t="n">
-        <v>2105.73</v>
+        <v>-0</v>
       </c>
       <c r="D171" s="5" t="n">
-        <v>259102.05</v>
+        <v>304254.5</v>
       </c>
       <c r="E171" t="n">
-        <v>1</v>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>EURO_Futures</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F171" t="inlineStr"/>
       <c r="G171" t="inlineStr"/>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>Live_Cattle_Futures_CME stop (-2,648)</t>
-        </is>
-      </c>
+      <c r="H171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="4" t="n">
         <v>46216</v>
       </c>
       <c r="B172" s="5" t="n">
-        <v>261207.78</v>
+        <v>304254.5</v>
       </c>
       <c r="C172" s="5" t="n">
-        <v>4696.75</v>
+        <v>4785.92</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>256511.03</v>
+        <v>299468.58</v>
       </c>
       <c r="E172" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT, EURO_Futures</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 2,591)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 4,786)</t>
         </is>
       </c>
       <c r="H172" t="inlineStr"/>
@@ -5343,20 +5223,20 @@
         <v>46217</v>
       </c>
       <c r="B173" s="5" t="n">
-        <v>261207.78</v>
+        <v>304254.5</v>
       </c>
       <c r="C173" s="5" t="n">
-        <v>4696.75</v>
+        <v>4785.92</v>
       </c>
       <c r="D173" s="5" t="n">
-        <v>256511.03</v>
+        <v>299468.58</v>
       </c>
       <c r="E173" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT, EURO_Futures</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT</t>
         </is>
       </c>
       <c r="G173" t="inlineStr"/>
@@ -5367,26 +5247,22 @@
         <v>46218</v>
       </c>
       <c r="B174" s="5" t="n">
-        <v>258488.81</v>
+        <v>299232.24</v>
       </c>
       <c r="C174" s="5" t="n">
-        <v>2105.73</v>
+        <v>-0</v>
       </c>
       <c r="D174" s="5" t="n">
-        <v>256383.08</v>
+        <v>299232.24</v>
       </c>
       <c r="E174" t="n">
-        <v>1</v>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>EURO_Futures</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F174" t="inlineStr"/>
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT stop (-2,719)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT stop (-5,022)</t>
         </is>
       </c>
     </row>
@@ -5395,22 +5271,18 @@
         <v>46219</v>
       </c>
       <c r="B175" s="5" t="n">
-        <v>258488.81</v>
+        <v>299232.24</v>
       </c>
       <c r="C175" s="5" t="n">
-        <v>2105.73</v>
+        <v>-0</v>
       </c>
       <c r="D175" s="5" t="n">
-        <v>256383.08</v>
+        <v>299232.24</v>
       </c>
       <c r="E175" t="n">
-        <v>1</v>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>EURO_Futures</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F175" t="inlineStr"/>
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr"/>
     </row>
@@ -5419,25 +5291,25 @@
         <v>46220</v>
       </c>
       <c r="B176" s="5" t="n">
-        <v>258488.81</v>
+        <v>299232.24</v>
       </c>
       <c r="C176" s="5" t="n">
-        <v>4669.56</v>
+        <v>4706.92</v>
       </c>
       <c r="D176" s="5" t="n">
-        <v>253819.25</v>
+        <v>294525.31</v>
       </c>
       <c r="E176" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>EURO_Futures, Gold_Futures_COMEX</t>
+          <t>Gold_Futures_COMEX</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX long (risk 2,564)</t>
+          <t>Gold_Futures_COMEX long (risk 4,707)</t>
         </is>
       </c>
       <c r="H176" t="inlineStr"/>
@@ -5447,74 +5319,62 @@
         <v>46223</v>
       </c>
       <c r="B177" s="5" t="n">
-        <v>258488.81</v>
+        <v>310954.93</v>
       </c>
       <c r="C177" s="5" t="n">
-        <v>4669.56</v>
+        <v>-0</v>
       </c>
       <c r="D177" s="5" t="n">
-        <v>253819.25</v>
+        <v>310954.93</v>
       </c>
       <c r="E177" t="n">
-        <v>2</v>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>EURO_Futures, Gold_Futures_COMEX</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F177" t="inlineStr"/>
       <c r="G177" t="inlineStr"/>
-      <c r="H177" t="inlineStr"/>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX target_r (+11,723)</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="4" t="n">
         <v>46224</v>
       </c>
       <c r="B178" s="5" t="n">
-        <v>271283.66</v>
+        <v>310954.93</v>
       </c>
       <c r="C178" s="5" t="n">
-        <v>2105.73</v>
+        <v>-0</v>
       </c>
       <c r="D178" s="5" t="n">
-        <v>269177.93</v>
+        <v>310954.93</v>
       </c>
       <c r="E178" t="n">
-        <v>1</v>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>EURO_Futures</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F178" t="inlineStr"/>
       <c r="G178" t="inlineStr"/>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Gold_Futures_COMEX target_r (+12,795)</t>
-        </is>
-      </c>
+      <c r="H178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="4" t="n">
         <v>46225</v>
       </c>
       <c r="B179" s="5" t="n">
-        <v>271283.66</v>
+        <v>310954.93</v>
       </c>
       <c r="C179" s="5" t="n">
-        <v>2105.73</v>
+        <v>-0</v>
       </c>
       <c r="D179" s="5" t="n">
-        <v>269177.93</v>
+        <v>310954.93</v>
       </c>
       <c r="E179" t="n">
-        <v>1</v>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>EURO_Futures</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F179" t="inlineStr"/>
       <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr"/>
     </row>
@@ -5523,22 +5383,18 @@
         <v>46226</v>
       </c>
       <c r="B180" s="5" t="n">
-        <v>271283.66</v>
+        <v>310954.93</v>
       </c>
       <c r="C180" s="5" t="n">
-        <v>2105.73</v>
+        <v>-0</v>
       </c>
       <c r="D180" s="5" t="n">
-        <v>269177.93</v>
+        <v>310954.93</v>
       </c>
       <c r="E180" t="n">
-        <v>1</v>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>EURO_Futures</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F180" t="inlineStr"/>
       <c r="G180" t="inlineStr"/>
       <c r="H180" t="inlineStr"/>
     </row>
@@ -5547,13 +5403,13 @@
         <v>46227</v>
       </c>
       <c r="B181" s="5" t="n">
-        <v>271158.62</v>
+        <v>310742.28</v>
       </c>
       <c r="C181" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D181" s="5" t="n">
-        <v>271158.62</v>
+        <v>310742.28</v>
       </c>
       <c r="E181" t="n">
         <v>0</v>
@@ -5561,12 +5417,12 @@
       <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 2,692); Corn_CBOT_Futures short (risk 2,665)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 4,891); Corn_CBOT_Futures short (risk 4,814)</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT open_at_end (open-&gt;closed 0); Corn_CBOT_Futures open_at_end (open-&gt;closed 0); EURO_Futures open_at_end (open-&gt;closed 0)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT open_at_end (open-&gt;closed 0); Corn_CBOT_Futures open_at_end (open-&gt;closed 0)</t>
         </is>
       </c>
     </row>
@@ -5582,7 +5438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M83"/>
+  <dimension ref="A1:M87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -5597,7 +5453,7 @@
     <col width="9" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5692,25 +5548,25 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G2" t="n">
         <v>0.012</v>
       </c>
       <c r="H2" t="n">
-        <v>4.988</v>
+        <v>2.488</v>
       </c>
       <c r="I2" s="5" t="n">
         <v>100000</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>1000</v>
+        <v>1573</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>4987.95</v>
+        <v>3913.55</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>104987.95</v>
+        <v>103913.55</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -5736,36 +5592,36 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>-1</v>
+        <v>2.5</v>
       </c>
       <c r="G3" t="n">
-        <v>0.014</v>
+        <v>0.007</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.014</v>
+        <v>2.493</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>104987.95</v>
+        <v>103913.55</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>1049.88</v>
-      </c>
-      <c r="K3" s="7" t="n">
-        <v>-1065.1</v>
+        <v>1634.56</v>
+      </c>
+      <c r="K3" s="6" t="n">
+        <v>4074.56</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>103922.86</v>
+        <v>107988.1</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
@@ -5803,16 +5659,16 @@
         <v>-1.008</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>103922.86</v>
+        <v>107988.1</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>1039.23</v>
+        <v>1698.65</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>-1047.44</v>
+        <v>-1712.08</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>102875.41</v>
+        <v>106276.02</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -5845,25 +5701,25 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G5" t="n">
         <v>0.002</v>
       </c>
       <c r="H5" t="n">
-        <v>4.998</v>
+        <v>2.498</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>102883.63</v>
+        <v>106289.45</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>1028.84</v>
+        <v>1671.93</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>5141.69</v>
+        <v>4175.79</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>108017.11</v>
+        <v>110451.81</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -5905,20 +5761,20 @@
         <v>-1.085</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>108017.11</v>
+        <v>110451.81</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>1080.17</v>
+        <v>1737.41</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>-1172.1</v>
+        <v>-1885.27</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>106845.01</v>
+        <v>108566.54</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>unknown_pl</t>
         </is>
       </c>
     </row>
@@ -5940,36 +5796,36 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-23</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>4.32</v>
+        <v>2.5</v>
       </c>
       <c r="G7" t="n">
         <v>0.006</v>
       </c>
       <c r="H7" t="n">
-        <v>4.314</v>
+        <v>2.494</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>106845.01</v>
+        <v>108566.54</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>1068.45</v>
+        <v>1707.75</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>4609.46</v>
+        <v>4259.06</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>111454.47</v>
+        <v>112825.6</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>bullish_reversal</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
@@ -6007,20 +5863,20 @@
         <v>-1.006</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>105776.56</v>
+        <v>112825.6</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>1057.77</v>
+        <v>1774.75</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>-1064.35</v>
+        <v>-1785.79</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>110390.12</v>
+        <v>111039.81</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>unknown_pl</t>
         </is>
       </c>
     </row>
@@ -6058,16 +5914,16 @@
         <v>-1.222</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>110396.7</v>
+        <v>111050.85</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>1103.97</v>
+        <v>1746.83</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>-1349.29</v>
+        <v>-2135.01</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>109040.83</v>
+        <v>108904.8</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -6109,16 +5965,16 @@
         <v>-1.069</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>109286.15</v>
+        <v>109292.98</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>1092.86</v>
+        <v>1719.18</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>-1168.23</v>
+        <v>-1837.74</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>107872.6</v>
+        <v>107067.06</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -6160,20 +6016,20 @@
         <v>-1.06</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>108193.29</v>
+        <v>107573.81</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>1081.93</v>
+        <v>1692.14</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>-1146.53</v>
+        <v>-1793.16</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>106726.07</v>
+        <v>105273.9</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>unknown_pl</t>
         </is>
       </c>
     </row>
@@ -6202,25 +6058,25 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G12" t="n">
         <v>0.002</v>
       </c>
       <c r="H12" t="n">
-        <v>4.998</v>
+        <v>2.498</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>107111.36</v>
+        <v>105881.67</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>1071.11</v>
+        <v>1665.52</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>5353.52</v>
+        <v>4160.61</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>112079.59</v>
+        <v>109434.51</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -6262,16 +6118,16 @@
         <v>-1.026</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>105794.92</v>
+        <v>103827.97</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>1057.95</v>
+        <v>1633.21</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>-1085.79</v>
+        <v>-1676.19</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>113135.24</v>
+        <v>111067.7</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -6313,16 +6169,16 @@
         <v>-1.002</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>111021.64</v>
+        <v>107801.29</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>1110.22</v>
+        <v>1695.71</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>-1112.57</v>
+        <v>-1699.3</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>110967.02</v>
+        <v>107735.2</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -6364,16 +6220,16 @@
         <v>-1.004</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>109911.42</v>
+        <v>106105.58</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>1099.11</v>
+        <v>1669.04</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>-1103.73</v>
+        <v>-1676.05</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>109863.3</v>
+        <v>106059.16</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -6406,25 +6262,25 @@
         <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G16" t="n">
         <v>0.001</v>
       </c>
       <c r="H16" t="n">
-        <v>4.999</v>
+        <v>2.499</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>108812.31</v>
+        <v>104436.54</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>1088.12</v>
+        <v>1642.79</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>5439.89</v>
+        <v>4105.87</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>115303.18</v>
+        <v>110165.03</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -6466,16 +6322,16 @@
         <v>-1.005</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>107717.22</v>
+        <v>102783.16</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>1077.17</v>
+        <v>1616.78</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>-1082.15</v>
+        <v>-1624.26</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>114221.03</v>
+        <v>108540.77</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -6501,36 +6357,36 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>2.373</v>
+        <v>2.5</v>
       </c>
       <c r="G18" t="n">
         <v>0.001</v>
       </c>
       <c r="H18" t="n">
-        <v>2.372</v>
+        <v>2.499</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>113168.06</v>
+        <v>106915.03</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>1131.68</v>
+        <v>1681.77</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>2684.82</v>
+        <v>4203.12</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>113838.98</v>
+        <v>112743.89</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>bullish_reversal</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
@@ -6552,36 +6408,36 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>-1</v>
+        <v>2.5</v>
       </c>
       <c r="G19" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.002</v>
+        <v>2.499</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>112031.4</v>
+        <v>111110.68</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>1120.31</v>
-      </c>
-      <c r="K19" s="7" t="n">
-        <v>-1122.8</v>
+        <v>1747.77</v>
+      </c>
+      <c r="K19" s="6" t="n">
+        <v>4367.49</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>110893.34</v>
+        <v>115435.19</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
@@ -6619,16 +6475,16 @@
         <v>-1.009</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>110911.09</v>
+        <v>109362.91</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>1109.11</v>
+        <v>1720.28</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>-1119.1</v>
+        <v>-1735.78</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>112016.14</v>
+        <v>113699.41</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -6670,16 +6526,16 @@
         <v>-1.138</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>109774.14</v>
+        <v>107599.65</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>1097.74</v>
+        <v>1692.54</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>-1249.15</v>
+        <v>-1926</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>109644.19</v>
+        <v>111773.42</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -6690,98 +6546,98 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures</t>
+          <t>EURO_STOXX_50_Index</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
           <t>2026-02-13</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>2026-02-17</t>
-        </is>
-      </c>
       <c r="E22" t="n">
         <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>-1</v>
+        <v>2.5</v>
       </c>
       <c r="G22" t="n">
-        <v>0.004</v>
+        <v>0.001</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.004</v>
+        <v>2.499</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>108512.51</v>
+        <v>112006.87</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>1085.13</v>
-      </c>
-      <c r="K22" s="7" t="n">
-        <v>-1089.74</v>
+        <v>1761.87</v>
+      </c>
+      <c r="K22" s="6" t="n">
+        <v>4403.76</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>108554.45</v>
+        <v>116177.18</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>NY_Copper_Futures</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
         <v>-1</v>
       </c>
       <c r="G23" t="n">
-        <v>0.286</v>
+        <v>0.004</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.286</v>
+        <v>-1.004</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>107422.77</v>
+        <v>110011.55</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>1074.23</v>
+        <v>1730.48</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>-1381.15</v>
+        <v>-1737.85</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>112326.72</v>
+        <v>114439.33</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -6792,58 +6648,58 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F24" t="n">
-        <v>-1</v>
+        <v>2.5</v>
       </c>
       <c r="G24" t="n">
-        <v>0.103</v>
+        <v>0.143</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.103</v>
+        <v>2.357</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>106348.54</v>
+        <v>114439.33</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>1063.49</v>
-      </c>
-      <c r="K24" s="7" t="n">
-        <v>-1172.56</v>
+        <v>1800.13</v>
+      </c>
+      <c r="K24" s="6" t="n">
+        <v>4243.17</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>111154.16</v>
+        <v>127197.46</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Ethereum_Per_USD_Binance</t>
+          <t>Cocoa_NYCSCE_Futures</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6865,25 +6721,25 @@
         <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G25" t="n">
-        <v>0.105</v>
+        <v>0.051</v>
       </c>
       <c r="H25" t="n">
-        <v>4.895</v>
+        <v>2.449</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>105285.05</v>
+        <v>112639.2</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>1052.85</v>
+        <v>1771.81</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>5153.43</v>
+        <v>4338.67</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>113707.87</v>
+        <v>118778.01</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -6894,58 +6750,58 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX</t>
+          <t>Ethereum_Per_USD_Binance</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>4.246</v>
+        <v>2.5</v>
       </c>
       <c r="G26" t="n">
-        <v>0.003</v>
+        <v>0.105</v>
       </c>
       <c r="H26" t="n">
-        <v>4.243</v>
+        <v>2.395</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>110022.48</v>
+        <v>110867.39</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>1100.22</v>
+        <v>1743.94</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>4668.33</v>
+        <v>4176.29</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>116065.86</v>
+        <v>122954.29</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>bearish_reversal</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Gold_Futures_COMEX</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -6955,63 +6811,63 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E27" t="n">
         <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>-1</v>
+        <v>2.5</v>
       </c>
       <c r="G27" t="n">
-        <v>0.174</v>
+        <v>0.003</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.174</v>
+        <v>2.497</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>112738.76</v>
+        <v>127197.46</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>1127.39</v>
-      </c>
-      <c r="K27" s="7" t="n">
-        <v>-1323.45</v>
+        <v>2000.82</v>
+      </c>
+      <c r="K27" s="6" t="n">
+        <v>4996.78</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>112515.53</v>
+        <v>132194.24</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
           <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -7021,22 +6877,22 @@
         <v>-1</v>
       </c>
       <c r="G28" t="n">
-        <v>0.002</v>
+        <v>0.174</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.002</v>
+        <v>-1.174</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>111611.37</v>
+        <v>132194.24</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>1116.11</v>
+        <v>2079.42</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>-1118</v>
+        <v>-2441.05</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>111397.52</v>
+        <v>129753.19</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -7047,22 +6903,22 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
           <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -7072,22 +6928,22 @@
         <v>-1</v>
       </c>
       <c r="G29" t="n">
-        <v>0.091</v>
+        <v>0.002</v>
       </c>
       <c r="H29" t="n">
-        <v>-1.091</v>
+        <v>-1.002</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>110299.19</v>
+        <v>130114.83</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>1102.99</v>
+        <v>2046.71</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>-1203.26</v>
+        <v>-2050.17</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>114862.59</v>
+        <v>127703.02</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -7098,7 +6954,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -7108,48 +6964,48 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E30" t="n">
         <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="G30" t="n">
-        <v>0.003</v>
+        <v>0.091</v>
       </c>
       <c r="H30" t="n">
-        <v>4.997</v>
+        <v>-1.091</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>114862.59</v>
+        <v>127706.48</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>1148.63</v>
-      </c>
-      <c r="K30" s="6" t="n">
-        <v>5739.66</v>
+        <v>2008.82</v>
+      </c>
+      <c r="K30" s="7" t="n">
+        <v>-2191.44</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>120602.26</v>
+        <v>125511.57</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP</t>
+          <t>Bitcoin_Per_USD_Binance</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -7159,37 +7015,37 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E31" t="n">
         <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G31" t="n">
-        <v>0.015</v>
+        <v>0.003</v>
       </c>
       <c r="H31" t="n">
-        <v>4.985</v>
+        <v>2.497</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>120602.26</v>
+        <v>125511.57</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>1206.02</v>
+        <v>1974.3</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>6011.7</v>
+        <v>4929.79</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>126613.96</v>
+        <v>130441.36</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -7200,47 +7056,47 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures</t>
+          <t>United_States_Oil_Fund_LP</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
           <t>2026-03-23</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>2026-03-31</t>
-        </is>
-      </c>
       <c r="E32" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G32" t="n">
-        <v>0.003</v>
+        <v>0.015</v>
       </c>
       <c r="H32" t="n">
-        <v>4.997</v>
+        <v>2.485</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>119396.23</v>
+        <v>130441.36</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>1193.96</v>
+        <v>2051.84</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>5966.27</v>
+        <v>5098.28</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>138842.52</v>
+        <v>135539.64</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -7251,7 +7107,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX</t>
+          <t>NY_Copper_Futures</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -7261,37 +7117,37 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
           <t>2026-03-24</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>2026-03-25</t>
-        </is>
-      </c>
       <c r="E33" t="n">
         <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G33" t="n">
-        <v>0.007</v>
+        <v>0.003</v>
       </c>
       <c r="H33" t="n">
-        <v>4.993</v>
+        <v>2.497</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>125420</v>
+        <v>128389.52</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>1254.2</v>
+        <v>2019.57</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>6262.29</v>
+        <v>5042.93</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>132876.25</v>
+        <v>140582.57</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -7302,47 +7158,47 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP</t>
+          <t>Gold_Futures_COMEX</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E34" t="n">
         <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G34" t="n">
-        <v>0.026</v>
+        <v>0.007</v>
       </c>
       <c r="H34" t="n">
-        <v>4.974</v>
+        <v>2.493</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>131682.29</v>
+        <v>133520.08</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>1316.82</v>
+        <v>2100.27</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>6550.35</v>
+        <v>5236.09</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>145392.87</v>
+        <v>145818.66</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -7353,7 +7209,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance</t>
+          <t>United_States_Oil_Fund_LP</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -7363,48 +7219,48 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>-1</v>
+        <v>2.5</v>
       </c>
       <c r="G35" t="n">
-        <v>0.004</v>
+        <v>0.026</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.004</v>
+        <v>2.474</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>145392.87</v>
+        <v>145818.66</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>1453.93</v>
-      </c>
-      <c r="K35" s="7" t="n">
-        <v>-1459.03</v>
+        <v>2293.73</v>
+      </c>
+      <c r="K35" s="6" t="n">
+        <v>5675.51</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>157989.47</v>
+        <v>151494.16</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Ethereum_Per_USD_Binance</t>
+          <t>Bitcoin_Per_USD_Binance</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -7414,48 +7270,48 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F36" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="G36" t="n">
-        <v>0.125</v>
+        <v>0.004</v>
       </c>
       <c r="H36" t="n">
-        <v>4.875</v>
+        <v>-1.004</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>143938.94</v>
+        <v>151494.16</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>1439.39</v>
-      </c>
-      <c r="K36" s="6" t="n">
-        <v>7017.02</v>
+        <v>2383</v>
+      </c>
+      <c r="K36" s="7" t="n">
+        <v>-2391.36</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>152409.89</v>
+        <v>160305.05</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME</t>
+          <t>Ethereum_Per_USD_Binance</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -7477,25 +7333,25 @@
         <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G37" t="n">
-        <v>0.061</v>
+        <v>0.125</v>
       </c>
       <c r="H37" t="n">
-        <v>4.939</v>
+        <v>2.375</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>142499.55</v>
+        <v>149111.16</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>1425</v>
+        <v>2345.52</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>7038.61</v>
+        <v>5570.61</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>159448.5</v>
+        <v>157064.77</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -7506,7 +7362,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures</t>
+          <t>Live_Cattle_Futures_CME</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7521,145 +7377,145 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>-1</v>
+        <v>2.5</v>
       </c>
       <c r="G38" t="n">
-        <v>0.008</v>
+        <v>0.061</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.008</v>
+        <v>2.439</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>141074.55</v>
+        <v>146765.64</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>1410.75</v>
-      </c>
-      <c r="K38" s="7" t="n">
-        <v>-1421.49</v>
+        <v>2308.62</v>
+      </c>
+      <c r="K38" s="6" t="n">
+        <v>5631.64</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>158032.8</v>
+        <v>162696.41</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>NY_Copper_Futures</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="G39" t="n">
-        <v>0.065</v>
+        <v>0.008</v>
       </c>
       <c r="H39" t="n">
-        <v>0.9350000000000001</v>
+        <v>-1.008</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>156583.83</v>
+        <v>144457.02</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>1565.84</v>
-      </c>
-      <c r="K39" s="6" t="n">
-        <v>1464.82</v>
+        <v>2272.31</v>
+      </c>
+      <c r="K39" s="7" t="n">
+        <v>-2289.62</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>159454.29</v>
+        <v>160341.03</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>data_end</t>
+          <t>stop</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>0.033</v>
+        <v>0.065</v>
       </c>
       <c r="H40" t="n">
-        <v>4.967</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>158043.54</v>
+        <v>158041.1</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>1580.44</v>
+        <v>2485.99</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>7850.36</v>
+        <v>2325.6</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>165883.16</v>
+        <v>162630.65</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>data_end</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME</t>
+          <t>Dow_Futures_E_mini</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -7669,37 +7525,37 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E41" t="n">
         <v>1</v>
       </c>
       <c r="F41" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G41" t="n">
-        <v>0.004</v>
+        <v>0.033</v>
       </c>
       <c r="H41" t="n">
-        <v>4.996</v>
+        <v>2.467</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>165883.16</v>
+        <v>160358.34</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>1658.83</v>
+        <v>2522.44</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>8287.33</v>
+        <v>6223.39</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>174170.49</v>
+        <v>166564.42</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -7710,7 +7566,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini</t>
+          <t>Bitcoin_Per_USD_CME</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -7720,48 +7576,48 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
+          <t>2026-04-27</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
       <c r="E42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F42" t="n">
-        <v>-1</v>
+        <v>2.5</v>
       </c>
       <c r="G42" t="n">
-        <v>0.002</v>
+        <v>0.004</v>
       </c>
       <c r="H42" t="n">
-        <v>-1.002</v>
+        <v>2.496</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>164224.32</v>
+        <v>166564.42</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>1642.24</v>
-      </c>
-      <c r="K42" s="7" t="n">
-        <v>-1646.17</v>
+        <v>2620.06</v>
+      </c>
+      <c r="K42" s="6" t="n">
+        <v>6539.36</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>172524.31</v>
+        <v>173103.78</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT</t>
+          <t>S_P_500_E_mini</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -7771,37 +7627,37 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
       <c r="E43" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G43" t="n">
-        <v>0.022</v>
+        <v>0.001</v>
       </c>
       <c r="H43" t="n">
-        <v>4.978</v>
+        <v>2.499</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>172528.24</v>
+        <v>163944.36</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>1725.28</v>
+        <v>2578.84</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>8587.639999999999</v>
+        <v>6444.03</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>177406.13</v>
+        <v>179547.8</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -7812,7 +7668,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -7822,48 +7678,48 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
       <c r="E44" t="n">
         <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>-1</v>
+        <v>2.5</v>
       </c>
       <c r="G44" t="n">
-        <v>0.211</v>
+        <v>0.022</v>
       </c>
       <c r="H44" t="n">
-        <v>-1.211</v>
+        <v>2.478</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>170802.96</v>
+        <v>170524.93</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>1708.03</v>
-      </c>
-      <c r="K44" s="7" t="n">
-        <v>-2067.61</v>
+        <v>2682.36</v>
+      </c>
+      <c r="K44" s="6" t="n">
+        <v>6645.62</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>170456.7</v>
+        <v>186193.42</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Japanese_Yen_Futures</t>
+          <t>Corn_CBOT_Futures</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -7873,48 +7729,48 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
       <c r="E45" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
         <v>-1</v>
       </c>
       <c r="G45" t="n">
-        <v>0.108</v>
+        <v>0.211</v>
       </c>
       <c r="H45" t="n">
-        <v>-1.108</v>
+        <v>-1.211</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>169091</v>
+        <v>176865.45</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>1690.91</v>
+        <v>2782.09</v>
       </c>
       <c r="K45" s="7" t="n">
-        <v>-1873.71</v>
+        <v>-3367.8</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>183341.35</v>
+        <v>182825.62</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>unknown_pl</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME</t>
+          <t>Japanese_Yen_Futures</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -7929,48 +7785,48 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F46" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="G46" t="n">
-        <v>0.016</v>
+        <v>0.108</v>
       </c>
       <c r="H46" t="n">
-        <v>4.984</v>
+        <v>-1.108</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>167400.09</v>
+        <v>183411.33</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>1674</v>
-      </c>
-      <c r="K46" s="6" t="n">
-        <v>8343.219999999999</v>
+        <v>2885.06</v>
+      </c>
+      <c r="K46" s="7" t="n">
+        <v>-3196.96</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>198016.99</v>
+        <v>197520.28</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>Live_Cattle_Futures_CME</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -7980,53 +7836,53 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>-1</v>
+        <v>2.5</v>
       </c>
       <c r="G47" t="n">
         <v>0.016</v>
       </c>
       <c r="H47" t="n">
-        <v>-1.016</v>
+        <v>2.484</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>165726.09</v>
+        <v>180526.27</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>1657.26</v>
-      </c>
-      <c r="K47" s="7" t="n">
-        <v>-1684.32</v>
+        <v>2839.68</v>
+      </c>
+      <c r="K47" s="6" t="n">
+        <v>7053.76</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>181657.03</v>
+        <v>189879.38</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -8035,39 +7891,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F48" t="n">
-        <v>-1</v>
+        <v>2.5</v>
       </c>
       <c r="G48" t="n">
-        <v>0.001</v>
+        <v>0.008</v>
       </c>
       <c r="H48" t="n">
-        <v>-1.001</v>
+        <v>2.492</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>163709.24</v>
+        <v>177686.59</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>1637.09</v>
-      </c>
-      <c r="K48" s="7" t="n">
-        <v>-1638.21</v>
+        <v>2795.01</v>
+      </c>
+      <c r="K48" s="6" t="n">
+        <v>6964.71</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>168818.49</v>
+        <v>194100.39</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -8077,48 +7933,48 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
       <c r="E49" t="n">
         <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="G49" t="n">
-        <v>0.182</v>
+        <v>0.001</v>
       </c>
       <c r="H49" t="n">
-        <v>4.818</v>
+        <v>-1.001</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>162072.15</v>
+        <v>174305.87</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>1620.72</v>
-      </c>
-      <c r="K49" s="6" t="n">
-        <v>7808.93</v>
+        <v>2741.83</v>
+      </c>
+      <c r="K49" s="7" t="n">
+        <v>-2743.7</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>185215.06</v>
+        <v>187135.69</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>unknown_pl</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME</t>
+          <t>Corn_CBOT_Futures</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -8128,37 +7984,37 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
       <c r="E50" t="n">
         <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G50" t="n">
-        <v>0.004</v>
+        <v>0.182</v>
       </c>
       <c r="H50" t="n">
-        <v>4.996</v>
+        <v>2.318</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>160450.31</v>
+        <v>181457.48</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>1604.5</v>
+        <v>2854.33</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>8016.73</v>
+        <v>6616.85</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>189673.77</v>
+        <v>200717.24</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
@@ -8169,7 +8025,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>EURO_Futures</t>
+          <t>Bitcoin_Per_USD_CME</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -8179,99 +8035,99 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
       <c r="E51" t="n">
         <v>1</v>
       </c>
       <c r="F51" t="n">
-        <v>-1</v>
+        <v>2.5</v>
       </c>
       <c r="G51" t="n">
-        <v>0.026</v>
+        <v>0.004</v>
       </c>
       <c r="H51" t="n">
-        <v>-1.026</v>
+        <v>2.496</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>178378.53</v>
+        <v>188361.01</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>1783.79</v>
-      </c>
-      <c r="K51" s="7" t="n">
-        <v>-1829.52</v>
+        <v>2962.92</v>
+      </c>
+      <c r="K51" s="6" t="n">
+        <v>7396.62</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>196187.46</v>
+        <v>204916.9</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F52" t="n">
-        <v>-1</v>
+        <v>2.5</v>
       </c>
       <c r="G52" t="n">
-        <v>0.014</v>
+        <v>0.008</v>
       </c>
       <c r="H52" t="n">
-        <v>-1.014</v>
+        <v>2.492</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>176594.74</v>
+        <v>185398.09</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>1765.95</v>
-      </c>
-      <c r="K52" s="7" t="n">
-        <v>-1790.22</v>
+        <v>2916.31</v>
+      </c>
+      <c r="K52" s="6" t="n">
+        <v>7266.97</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>194397.24</v>
+        <v>202903.39</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX</t>
+          <t>EURO_Futures</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -8281,12 +8137,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -8296,22 +8152,22 @@
         <v>-1</v>
       </c>
       <c r="G53" t="n">
-        <v>0.032</v>
+        <v>0.026</v>
       </c>
       <c r="H53" t="n">
-        <v>-1.032</v>
+        <v>-1.026</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>194421.52</v>
+        <v>191641.05</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>1944.22</v>
+        <v>3014.51</v>
       </c>
       <c r="K53" s="7" t="n">
-        <v>-2006.43</v>
+        <v>-3091.81</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>192390.81</v>
+        <v>201825.09</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -8322,7 +8178,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -8332,37 +8188,37 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F54" t="n">
         <v>-1</v>
       </c>
       <c r="G54" t="n">
-        <v>0.002</v>
+        <v>0.014</v>
       </c>
       <c r="H54" t="n">
-        <v>-1.002</v>
+        <v>-1.014</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>192453.03</v>
+        <v>188626.54</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>1924.53</v>
+        <v>2967.1</v>
       </c>
       <c r="K54" s="7" t="n">
-        <v>-1928.54</v>
+        <v>-3007.88</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>190462.27</v>
+        <v>198817.21</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -8373,7 +8229,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT</t>
+          <t>Gold_Futures_COMEX</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -8383,48 +8239,48 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E55" t="n">
         <v>1</v>
       </c>
       <c r="F55" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="G55" t="n">
-        <v>0.027</v>
+        <v>0.032</v>
       </c>
       <c r="H55" t="n">
-        <v>4.973</v>
+        <v>-1.032</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>190462.27</v>
+        <v>195941.69</v>
       </c>
       <c r="J55" s="5" t="n">
-        <v>1904.62</v>
-      </c>
-      <c r="K55" s="6" t="n">
-        <v>9470.93</v>
+        <v>3082.16</v>
+      </c>
+      <c r="K55" s="7" t="n">
+        <v>-3180.79</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>199933.21</v>
+        <v>195636.42</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>unknown_pl</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -8434,37 +8290,37 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F56" t="n">
         <v>-1</v>
       </c>
       <c r="G56" t="n">
-        <v>0.021</v>
+        <v>0.002</v>
       </c>
       <c r="H56" t="n">
-        <v>-1.021</v>
+        <v>-1.002</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>199933.21</v>
+        <v>192818.74</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>1999.33</v>
+        <v>3033.04</v>
       </c>
       <c r="K56" s="7" t="n">
-        <v>-2040.34</v>
+        <v>-3039.36</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>193903.16</v>
+        <v>199864.04</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -8475,149 +8331,149 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F57" t="n">
-        <v>-1</v>
+        <v>2.5</v>
       </c>
       <c r="G57" t="n">
-        <v>0.024</v>
+        <v>0.027</v>
       </c>
       <c r="H57" t="n">
-        <v>-1.024</v>
+        <v>2.473</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>197933.87</v>
+        <v>199864.04</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>1979.34</v>
-      </c>
-      <c r="K57" s="7" t="n">
-        <v>-2025.91</v>
+        <v>3143.86</v>
+      </c>
+      <c r="K57" s="6" t="n">
+        <v>7773.52</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>197907.29</v>
+        <v>207637.56</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F58" t="n">
-        <v>-1</v>
+        <v>2.5</v>
       </c>
       <c r="G58" t="n">
-        <v>0.002</v>
+        <v>0.01</v>
       </c>
       <c r="H58" t="n">
-        <v>-1.002</v>
+        <v>2.49</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>195954.53</v>
+        <v>207637.56</v>
       </c>
       <c r="J58" s="5" t="n">
-        <v>1959.55</v>
-      </c>
-      <c r="K58" s="7" t="n">
-        <v>-1963.79</v>
+        <v>3266.14</v>
+      </c>
+      <c r="K58" s="6" t="n">
+        <v>8131.85</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>195943.5</v>
+        <v>223768.49</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini</t>
+          <t>NY_Palladium_Futures</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E59" t="n">
         <v>1</v>
       </c>
       <c r="F59" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G59" t="n">
-        <v>0.019</v>
+        <v>0.012</v>
       </c>
       <c r="H59" t="n">
-        <v>4.981</v>
+        <v>2.488</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>193948.42</v>
+        <v>204371.42</v>
       </c>
       <c r="J59" s="5" t="n">
-        <v>1939.48</v>
+        <v>3214.76</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>9660.83</v>
+        <v>7999.09</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>203563.98</v>
+        <v>215636.64</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -8628,7 +8484,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -8638,37 +8494,37 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F60" t="n">
         <v>-1</v>
       </c>
       <c r="G60" t="n">
-        <v>0.007</v>
+        <v>0.002</v>
       </c>
       <c r="H60" t="n">
-        <v>-1.007</v>
+        <v>-1.002</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>191963.67</v>
+        <v>223768.49</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>1919.64</v>
+        <v>3519.88</v>
       </c>
       <c r="K60" s="7" t="n">
-        <v>-1933.83</v>
+        <v>-3527.51</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>201630.15</v>
+        <v>216722.12</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -8689,12 +8545,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -8704,22 +8560,22 @@
         <v>-1</v>
       </c>
       <c r="G61" t="n">
-        <v>0.03</v>
+        <v>0.016</v>
       </c>
       <c r="H61" t="n">
-        <v>-1.03</v>
+        <v>-1.016</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>190044.04</v>
+        <v>220248.61</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>1900.44</v>
+        <v>3464.51</v>
       </c>
       <c r="K61" s="7" t="n">
-        <v>-1956.75</v>
+        <v>-3518.86</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>199673.4</v>
+        <v>220249.63</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
@@ -8730,47 +8586,47 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX</t>
+          <t>Dow_Futures_E_mini</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F62" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G62" t="n">
-        <v>0.004</v>
+        <v>0.019</v>
       </c>
       <c r="H62" t="n">
-        <v>4.996</v>
+        <v>2.481</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>199729.71</v>
+        <v>216729.76</v>
       </c>
       <c r="J62" s="5" t="n">
-        <v>1997.3</v>
+        <v>3409.16</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>9979.469999999999</v>
+        <v>8458.57</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>207383.25</v>
+        <v>225180.7</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -8781,7 +8637,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures</t>
+          <t>Gold_Futures_COMEX</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -8791,12 +8647,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -8806,22 +8662,22 @@
         <v>-1</v>
       </c>
       <c r="G63" t="n">
-        <v>0.148</v>
+        <v>0.007</v>
       </c>
       <c r="H63" t="n">
-        <v>-1.148</v>
+        <v>-1.007</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>197676.11</v>
+        <v>213312.97</v>
       </c>
       <c r="J63" s="5" t="n">
-        <v>1976.76</v>
+        <v>3355.41</v>
       </c>
       <c r="K63" s="7" t="n">
-        <v>-2269.61</v>
+        <v>-3380.22</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>197403.79</v>
+        <v>221800.48</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -8832,102 +8688,102 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F64" t="n">
-        <v>4.924</v>
+        <v>2.5</v>
       </c>
       <c r="G64" t="n">
-        <v>0.03</v>
+        <v>0.015</v>
       </c>
       <c r="H64" t="n">
-        <v>4.894</v>
+        <v>2.485</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>195699.35</v>
+        <v>209957.55</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>1956.99</v>
+        <v>3302.63</v>
       </c>
       <c r="K64" s="6" t="n">
-        <v>9577.32</v>
+        <v>8207.65</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>216960.58</v>
+        <v>230008.13</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>bullish_reversal</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>Gold_Futures_COMEX</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E65" t="n">
         <v>1</v>
       </c>
       <c r="F65" t="n">
-        <v>-1</v>
+        <v>2.5</v>
       </c>
       <c r="G65" t="n">
-        <v>0.014</v>
+        <v>0.004</v>
       </c>
       <c r="H65" t="n">
-        <v>-1.014</v>
+        <v>2.496</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>205426.26</v>
+        <v>230008.13</v>
       </c>
       <c r="J65" s="5" t="n">
-        <v>2054.26</v>
-      </c>
-      <c r="K65" s="7" t="n">
-        <v>-2082.12</v>
+        <v>3618.03</v>
+      </c>
+      <c r="K65" s="6" t="n">
+        <v>9032.35</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>214878.46</v>
+        <v>239040.48</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
@@ -8944,48 +8800,48 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F66" t="n">
-        <v>-1</v>
+        <v>2.5</v>
       </c>
       <c r="G66" t="n">
-        <v>0.014</v>
+        <v>0.008</v>
       </c>
       <c r="H66" t="n">
-        <v>-1.014</v>
+        <v>2.492</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>214878.46</v>
+        <v>226390.1</v>
       </c>
       <c r="J66" s="5" t="n">
-        <v>2148.78</v>
-      </c>
-      <c r="K66" s="7" t="n">
-        <v>-2178.42</v>
+        <v>3561.12</v>
+      </c>
+      <c r="K66" s="6" t="n">
+        <v>8874.299999999999</v>
       </c>
       <c r="L66" s="5" t="n">
-        <v>212700.04</v>
+        <v>247914.78</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures</t>
+          <t>Corn_CBOT_Futures</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -8995,12 +8851,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -9010,22 +8866,22 @@
         <v>-1</v>
       </c>
       <c r="G67" t="n">
-        <v>0.02</v>
+        <v>0.148</v>
       </c>
       <c r="H67" t="n">
-        <v>-1.02</v>
+        <v>-1.148</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>212729.68</v>
+        <v>222828.99</v>
       </c>
       <c r="J67" s="5" t="n">
-        <v>2127.3</v>
+        <v>3505.1</v>
       </c>
       <c r="K67" s="7" t="n">
-        <v>-2168.8</v>
+        <v>-4024.37</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>210531.23</v>
+        <v>243890.41</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
@@ -9036,7 +8892,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>EURO_Futures</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -9046,40 +8902,48 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
-        </is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>1</v>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="G68" t="n">
-        <v>0.004</v>
+        <v>0.03</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.004</v>
+        <v>2.47</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>210572.74</v>
+        <v>244409.68</v>
       </c>
       <c r="J68" s="5" t="n">
-        <v>2105.73</v>
-      </c>
-      <c r="K68" s="7" t="n">
-        <v>-7.63</v>
+        <v>3844.56</v>
+      </c>
+      <c r="K68" s="6" t="n">
+        <v>9494.91</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>271158.62</v>
+        <v>253385.32</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>open_at_end</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -9089,12 +8953,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -9104,22 +8968,22 @@
         <v>-1</v>
       </c>
       <c r="G69" t="n">
-        <v>0.082</v>
+        <v>0.014</v>
       </c>
       <c r="H69" t="n">
-        <v>-1.082</v>
+        <v>-1.014</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>208425.51</v>
+        <v>253385.32</v>
       </c>
       <c r="J69" s="5" t="n">
-        <v>2084.26</v>
+        <v>3985.75</v>
       </c>
       <c r="K69" s="7" t="n">
-        <v>-2254.4</v>
+        <v>-4039.8</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>208276.83</v>
+        <v>249345.52</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
@@ -9130,51 +8994,51 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F70" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="G70" t="n">
-        <v>0.026</v>
+        <v>0.014</v>
       </c>
       <c r="H70" t="n">
-        <v>4.974</v>
+        <v>-1.014</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>206341.25</v>
+        <v>249345.52</v>
       </c>
       <c r="J70" s="5" t="n">
-        <v>2063.41</v>
-      </c>
-      <c r="K70" s="6" t="n">
-        <v>10262.76</v>
+        <v>3922.21</v>
+      </c>
+      <c r="K70" s="7" t="n">
+        <v>-3976.3</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>218539.6</v>
+        <v>245369.22</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
     </row>
@@ -9191,37 +9055,37 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F71" t="n">
         <v>-1</v>
       </c>
       <c r="G71" t="n">
-        <v>0.012</v>
+        <v>0.02</v>
       </c>
       <c r="H71" t="n">
-        <v>-1.012</v>
+        <v>-1.02</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>204277.84</v>
+        <v>245423.32</v>
       </c>
       <c r="J71" s="5" t="n">
-        <v>2042.78</v>
+        <v>3860.51</v>
       </c>
       <c r="K71" s="7" t="n">
-        <v>-2066.88</v>
+        <v>-3935.84</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>248647.89</v>
+        <v>241433.38</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
@@ -9232,17 +9096,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>EURO_Futures</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9251,28 +9115,28 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F72" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G72" t="n">
-        <v>0.017</v>
+        <v>0.007</v>
       </c>
       <c r="H72" t="n">
-        <v>4.983</v>
+        <v>2.493</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>202235.06</v>
+        <v>241508.71</v>
       </c>
       <c r="J72" s="5" t="n">
-        <v>2022.35</v>
+        <v>3798.93</v>
       </c>
       <c r="K72" s="6" t="n">
-        <v>10076.58</v>
+        <v>9469.799999999999</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>228616.18</v>
+        <v>250903.18</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
@@ -9283,98 +9147,98 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT</t>
+          <t>NY_Natural_Gas_Futures</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E73" t="n">
         <v>1</v>
       </c>
       <c r="F73" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="G73" t="n">
-        <v>0.049</v>
+        <v>0.082</v>
       </c>
       <c r="H73" t="n">
-        <v>4.951</v>
+        <v>-1.082</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>224467.67</v>
+        <v>237634.45</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>2244.68</v>
-      </c>
-      <c r="K73" s="6" t="n">
-        <v>11113.89</v>
+        <v>3737.99</v>
+      </c>
+      <c r="K73" s="7" t="n">
+        <v>-4043.13</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>239730.07</v>
+        <v>246860.05</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>German_Long_Bund</t>
+          <t>NY_Palladium_Futures</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F74" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G74" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.026</v>
       </c>
       <c r="H74" t="n">
-        <v>4.913</v>
+        <v>2.474</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>222223</v>
+        <v>233896.46</v>
       </c>
       <c r="J74" s="5" t="n">
-        <v>2222.23</v>
+        <v>3679.19</v>
       </c>
       <c r="K74" s="6" t="n">
-        <v>10917.91</v>
+        <v>9101.16</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>257364.38</v>
+        <v>255961.21</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
@@ -9385,7 +9249,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -9395,7 +9259,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -9404,39 +9268,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F75" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="G75" t="n">
-        <v>0.007</v>
+        <v>0.012</v>
       </c>
       <c r="H75" t="n">
-        <v>4.993</v>
+        <v>-1.012</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>220000.77</v>
+        <v>230217.27</v>
       </c>
       <c r="J75" s="5" t="n">
-        <v>2200.01</v>
-      </c>
-      <c r="K75" s="6" t="n">
-        <v>10984.71</v>
+        <v>3621.32</v>
+      </c>
+      <c r="K75" s="7" t="n">
+        <v>-3664.05</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>250714.77</v>
+        <v>290897.86</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -9446,201 +9310,201 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E76" t="n">
         <v>1</v>
       </c>
       <c r="F76" t="n">
-        <v>-1</v>
+        <v>2.5</v>
       </c>
       <c r="G76" t="n">
-        <v>0.011</v>
+        <v>0.017</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.011</v>
+        <v>2.483</v>
       </c>
       <c r="I76" s="5" t="n">
-        <v>217800.76</v>
+        <v>226595.95</v>
       </c>
       <c r="J76" s="5" t="n">
-        <v>2178.01</v>
-      </c>
-      <c r="K76" s="7" t="n">
-        <v>-2201.43</v>
+        <v>3564.35</v>
+      </c>
+      <c r="K76" s="6" t="n">
+        <v>8848.9</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>246446.46</v>
+        <v>264810.11</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sugar_World_CSCE_Futures</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
       <c r="E77" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F77" t="n">
-        <v>-1</v>
+        <v>2.5</v>
       </c>
       <c r="G77" t="n">
-        <v>0.154</v>
+        <v>0.049</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.154</v>
+        <v>2.451</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>215622.75</v>
+        <v>261188.79</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>2156.23</v>
-      </c>
-      <c r="K77" s="7" t="n">
-        <v>-2487.95</v>
+        <v>4108.5</v>
+      </c>
+      <c r="K77" s="6" t="n">
+        <v>10070.83</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>254876.42</v>
+        <v>274880.94</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME</t>
+          <t>German_Long_Bund</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F78" t="n">
-        <v>-1</v>
+        <v>2.5</v>
       </c>
       <c r="G78" t="n">
-        <v>0.048</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="H78" t="n">
-        <v>-1.048</v>
+        <v>2.413</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>252770.69</v>
+        <v>257080.29</v>
       </c>
       <c r="J78" s="5" t="n">
-        <v>2527.71</v>
-      </c>
-      <c r="K78" s="7" t="n">
-        <v>-2648.07</v>
+        <v>4043.87</v>
+      </c>
+      <c r="K78" s="6" t="n">
+        <v>9758.040000000001</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>261207.78</v>
+        <v>284638.98</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures</t>
+          <t>Gold_Futures_COMEX</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E79" t="n">
         <v>1</v>
       </c>
       <c r="F79" t="n">
-        <v>3.627</v>
+        <v>2.5</v>
       </c>
       <c r="G79" t="n">
-        <v>0.039</v>
+        <v>0.007</v>
       </c>
       <c r="H79" t="n">
-        <v>3.588</v>
+        <v>2.493</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>250242.99</v>
+        <v>253036.42</v>
       </c>
       <c r="J79" s="5" t="n">
-        <v>2502.43</v>
+        <v>3980.26</v>
       </c>
       <c r="K79" s="6" t="n">
-        <v>8979.43</v>
+        <v>9922.92</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>263855.85</v>
+        <v>294561.9</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>bearish_reversal</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT</t>
+          <t>Dow_Futures_E_mini</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -9650,37 +9514,37 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F80" t="n">
         <v>-1</v>
       </c>
       <c r="G80" t="n">
-        <v>0.049</v>
+        <v>0.011</v>
       </c>
       <c r="H80" t="n">
-        <v>-1.049</v>
+        <v>-1.011</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>259102.05</v>
+        <v>249056.15</v>
       </c>
       <c r="J80" s="5" t="n">
-        <v>2591.02</v>
+        <v>3917.65</v>
       </c>
       <c r="K80" s="7" t="n">
-        <v>-2718.97</v>
+        <v>-3959.78</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>258488.81</v>
+        <v>286938.08</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -9691,135 +9555,339 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX</t>
+          <t>Sugar_World_CSCE_Futures</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E81" t="n">
         <v>2</v>
       </c>
       <c r="F81" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="G81" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.154</v>
       </c>
       <c r="H81" t="n">
-        <v>4.991</v>
+        <v>-1.154</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>256383.08</v>
+        <v>245138.5</v>
       </c>
       <c r="J81" s="5" t="n">
-        <v>2563.83</v>
-      </c>
-      <c r="K81" s="6" t="n">
-        <v>12794.85</v>
+        <v>3856.03</v>
+      </c>
+      <c r="K81" s="7" t="n">
+        <v>-4449.26</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>271283.66</v>
+        <v>282488.81</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT</t>
+          <t>Live_Cattle_Futures_CME</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>1</v>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="G82" t="n">
-        <v>0.019</v>
+        <v>0.024</v>
       </c>
       <c r="H82" t="n">
-        <v>-0.019</v>
+        <v>2.476</v>
       </c>
       <c r="I82" s="5" t="n">
-        <v>269177.93</v>
+        <v>282488.81</v>
       </c>
       <c r="J82" s="5" t="n">
-        <v>2691.78</v>
-      </c>
-      <c r="K82" s="7" t="n">
-        <v>-50.79</v>
+        <v>4443.55</v>
+      </c>
+      <c r="K82" s="6" t="n">
+        <v>11003.07</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>271232.87</v>
+        <v>293491.89</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>open_at_end</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
+          <t>NY_Natural_Gas_Futures</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="H83" t="n">
+        <v>2.461</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>278045.26</v>
+      </c>
+      <c r="J83" s="5" t="n">
+        <v>4373.65</v>
+      </c>
+      <c r="K83" s="6" t="n">
+        <v>10762.61</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>304254.5</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>target_r</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>2</v>
+      </c>
+      <c r="F84" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="H84" t="n">
+        <v>-1.049</v>
+      </c>
+      <c r="I84" s="5" t="n">
+        <v>304254.5</v>
+      </c>
+      <c r="J84" s="5" t="n">
+        <v>4785.92</v>
+      </c>
+      <c r="K84" s="7" t="n">
+        <v>-5022.27</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>299232.24</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="H85" t="n">
+        <v>2.491</v>
+      </c>
+      <c r="I85" s="5" t="n">
+        <v>299232.24</v>
+      </c>
+      <c r="J85" s="5" t="n">
+        <v>4706.92</v>
+      </c>
+      <c r="K85" s="6" t="n">
+        <v>11722.69</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>310954.93</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>target_r</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="H86" t="n">
+        <v>-0.019</v>
+      </c>
+      <c r="I86" s="5" t="n">
+        <v>310954.93</v>
+      </c>
+      <c r="J86" s="5" t="n">
+        <v>4891.32</v>
+      </c>
+      <c r="K86" s="7" t="n">
+        <v>-92.29000000000001</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>310862.64</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
           <t>Corn_CBOT_Futures</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>short</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="F83" t="n">
+      <c r="F87" t="n">
         <v>0</v>
       </c>
-      <c r="G83" t="n">
+      <c r="G87" t="n">
         <v>0.025</v>
       </c>
-      <c r="H83" t="n">
+      <c r="H87" t="n">
         <v>-0.025</v>
       </c>
-      <c r="I83" s="5" t="n">
-        <v>266486.15</v>
-      </c>
-      <c r="J83" s="5" t="n">
-        <v>2664.86</v>
-      </c>
-      <c r="K83" s="7" t="n">
-        <v>-66.62</v>
-      </c>
-      <c r="L83" s="5" t="n">
-        <v>271166.25</v>
-      </c>
-      <c r="M83" t="inlineStr">
+      <c r="I87" s="5" t="n">
+        <v>306063.61</v>
+      </c>
+      <c r="J87" s="5" t="n">
+        <v>4814.38</v>
+      </c>
+      <c r="K87" s="7" t="n">
+        <v>-120.36</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>310742.28</v>
+      </c>
+      <c r="M87" t="inlineStr">
         <is>
           <t>open_at_end</t>
         </is>

--- a/output/quickfix_portfolio_daily.xlsx
+++ b/output/quickfix_portfolio_daily.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>310,742.28</t>
+          <t>390,832.54</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+210.74%</t>
+          <t>+290.83%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>325,673  (+225.67%)</t>
+          <t>404,600  (+304.60%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>8,611  (14.9 pts of return)</t>
+          <t>7,696  (13.8 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>35.1x</t>
+          <t>48.5x</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>59.5%</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>+2.44R  (best +2.50R)</t>
+          <t>+3.21R  (best +8.92R)</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6,696  (+3.84%)</t>
+          <t>7,646  (+3.77%)</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-2,804  (-1.65%)</t>
+          <t>-2,684  (-1.31%)</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>7.6% of live balance</t>
+          <t>5.7% of live balance</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.573% of liquid capital</t>
+          <t>1.175% of liquid capital (solved for a 6% max drawdown)</t>
         </is>
       </c>
     </row>
@@ -954,10 +954,10 @@
         <v>100000</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>1573</v>
+        <v>1175</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>98427</v>
+        <v>98825</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX short (risk 1,573)</t>
+          <t>Gold_Futures_COMEX short (risk 1,175)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -979,13 +979,13 @@
         <v>46010</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>103913.55</v>
+        <v>109506.16</v>
       </c>
       <c r="C3" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>103913.55</v>
+        <v>109506.16</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -994,7 +994,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX target_r (+3,914)</t>
+          <t>Gold_Futures_COMEX target_r (+9,506)</t>
         </is>
       </c>
     </row>
@@ -1003,13 +1003,13 @@
         <v>46011</v>
       </c>
       <c r="B4" s="5" t="n">
-        <v>103913.55</v>
+        <v>109506.16</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>103913.55</v>
+        <v>109506.16</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -1023,13 +1023,13 @@
         <v>46021</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>103913.55</v>
+        <v>109506.16</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1634.56</v>
+        <v>1286.7</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>102278.99</v>
+        <v>108219.47</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX short (risk 1,635)</t>
+          <t>Gold_Futures_COMEX short (risk 1,287)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -1051,13 +1051,13 @@
         <v>46023</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>103913.55</v>
+        <v>109506.16</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1634.56</v>
+        <v>1286.7</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>102278.99</v>
+        <v>108219.47</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -1075,13 +1075,13 @@
         <v>46024</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>107988.1</v>
+        <v>112713.58</v>
       </c>
       <c r="C7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>107988.1</v>
+        <v>112713.58</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -1090,7 +1090,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX target_r (+4,075)</t>
+          <t>Gold_Futures_COMEX target_r (+3,207)</t>
         </is>
       </c>
     </row>
@@ -1099,13 +1099,13 @@
         <v>46025</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>107988.1</v>
+        <v>112713.58</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>107988.1</v>
+        <v>112713.58</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -1119,13 +1119,13 @@
         <v>46026</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>107988.1</v>
+        <v>112713.58</v>
       </c>
       <c r="C9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>107988.1</v>
+        <v>112713.58</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1139,13 +1139,13 @@
         <v>46027</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>107988.1</v>
+        <v>112713.58</v>
       </c>
       <c r="C10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>107988.1</v>
+        <v>112713.58</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -1159,13 +1159,13 @@
         <v>46028</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>107988.1</v>
+        <v>112713.58</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>107988.1</v>
+        <v>112713.58</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -1179,13 +1179,13 @@
         <v>46029</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>107988.1</v>
+        <v>112713.58</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>3370.59</v>
+        <v>2633.21</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>104617.52</v>
+        <v>110080.38</v>
       </c>
       <c r="E12" t="n">
         <v>2</v>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Coffee_NYCSCE_Futures short (risk 1,699); S_P_500_Index short (risk 1,672)</t>
+          <t>Coffee_NYCSCE_Futures short (risk 1,324); S_P_500_Index short (risk 1,309)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -1207,13 +1207,13 @@
         <v>46030</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>110451.81</v>
+        <v>118231.44</v>
       </c>
       <c r="C13" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>110451.81</v>
+        <v>118231.44</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1222,7 +1222,7 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Coffee_NYCSCE_Futures stop (-1,712); S_P_500_Index target_r (+4,176)</t>
+          <t>Coffee_NYCSCE_Futures stop (-1,335); S_P_500_Index target_r (+6,853)</t>
         </is>
       </c>
     </row>
@@ -1231,13 +1231,13 @@
         <v>46031</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>110451.81</v>
+        <v>118231.44</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>110451.81</v>
+        <v>118231.44</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1251,13 +1251,13 @@
         <v>46032</v>
       </c>
       <c r="B15" s="5" t="n">
-        <v>110451.81</v>
+        <v>118231.44</v>
       </c>
       <c r="C15" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>110451.81</v>
+        <v>118231.44</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1271,13 +1271,13 @@
         <v>46033</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>110451.81</v>
+        <v>118231.44</v>
       </c>
       <c r="C16" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>110451.81</v>
+        <v>118231.44</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -1291,13 +1291,13 @@
         <v>46034</v>
       </c>
       <c r="B17" s="5" t="n">
-        <v>110451.81</v>
+        <v>118231.44</v>
       </c>
       <c r="C17" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>110451.81</v>
+        <v>118231.44</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -1311,13 +1311,13 @@
         <v>46035</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>110451.81</v>
+        <v>118231.44</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>1737.41</v>
+        <v>1389.22</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>108714.41</v>
+        <v>116842.22</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures long (risk 1,737)</t>
+          <t>Cocoa_NYCSCE_Futures long (risk 1,389)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -1339,13 +1339,13 @@
         <v>46036</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>108566.54</v>
+        <v>122783.28</v>
       </c>
       <c r="C19" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>108566.54</v>
+        <v>122783.28</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -1354,7 +1354,7 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures unknown_pl (-1,885)</t>
+          <t>Cocoa_NYCSCE_Futures target_r (+4,552)</t>
         </is>
       </c>
     </row>
@@ -1363,13 +1363,13 @@
         <v>46037</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>108566.54</v>
+        <v>122783.28</v>
       </c>
       <c r="C20" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>108566.54</v>
+        <v>122783.28</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -1383,13 +1383,13 @@
         <v>46038</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>108566.54</v>
+        <v>122783.28</v>
       </c>
       <c r="C21" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>108566.54</v>
+        <v>122783.28</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -1403,13 +1403,13 @@
         <v>46039</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>108566.54</v>
+        <v>122783.28</v>
       </c>
       <c r="C22" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>108566.54</v>
+        <v>122783.28</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>46040</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>108566.54</v>
+        <v>122783.28</v>
       </c>
       <c r="C23" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>108566.54</v>
+        <v>122783.28</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -1443,13 +1443,13 @@
         <v>46041</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>108566.54</v>
+        <v>122783.28</v>
       </c>
       <c r="C24" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>108566.54</v>
+        <v>122783.28</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -1463,13 +1463,13 @@
         <v>46042</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>108566.54</v>
+        <v>122783.28</v>
       </c>
       <c r="C25" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>108566.54</v>
+        <v>122783.28</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -1483,13 +1483,13 @@
         <v>46043</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>108566.54</v>
+        <v>122783.28</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>1707.75</v>
+        <v>1442.7</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>106858.79</v>
+        <v>121340.58</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Coffee_NYCSCE_Futures long (risk 1,708)</t>
+          <t>Coffee_NYCSCE_Futures long (risk 1,443)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -1511,13 +1511,13 @@
         <v>46044</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>108566.54</v>
+        <v>122783.28</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>1707.75</v>
+        <v>1442.7</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>106858.79</v>
+        <v>121340.58</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -1535,13 +1535,13 @@
         <v>46045</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>112825.6</v>
+        <v>126381.33</v>
       </c>
       <c r="C28" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>112825.6</v>
+        <v>126381.33</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -1550,7 +1550,7 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Coffee_NYCSCE_Futures target_r (+4,259)</t>
+          <t>Coffee_NYCSCE_Futures target_r (+3,598)</t>
         </is>
       </c>
     </row>
@@ -1559,13 +1559,13 @@
         <v>46046</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>112825.6</v>
+        <v>126381.33</v>
       </c>
       <c r="C29" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>112825.6</v>
+        <v>126381.33</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>46047</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>112825.6</v>
+        <v>126381.33</v>
       </c>
       <c r="C30" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>112825.6</v>
+        <v>126381.33</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -1599,13 +1599,13 @@
         <v>46048</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>112825.6</v>
+        <v>126381.33</v>
       </c>
       <c r="C31" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>112825.6</v>
+        <v>126381.33</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -1619,13 +1619,13 @@
         <v>46049</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>112825.6</v>
+        <v>126381.33</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>1774.75</v>
+        <v>1484.98</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>111050.85</v>
+        <v>124896.34</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>S_P_500_Index short (risk 1,775)</t>
+          <t>S_P_500_Index short (risk 1,485)</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -1647,13 +1647,13 @@
         <v>46050</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>111039.81</v>
+        <v>121845.57</v>
       </c>
       <c r="C33" s="5" t="n">
-        <v>1746.83</v>
+        <v>1467.53</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>109292.98</v>
+        <v>120378.04</v>
       </c>
       <c r="E33" t="n">
         <v>1</v>
@@ -1665,12 +1665,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Teucrium_Wheat_Fund short (risk 1,747)</t>
+          <t>Teucrium_Wheat_Fund short (risk 1,468)</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>S_P_500_Index unknown_pl (-1,786)</t>
+          <t>S_P_500_Index stop (-4,536)</t>
         </is>
       </c>
     </row>
@@ -1679,13 +1679,13 @@
         <v>46051</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>108904.8</v>
+        <v>119970.32</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>5076.83</v>
+        <v>4193.66</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>103827.97</v>
+        <v>115776.66</v>
       </c>
       <c r="E34" t="n">
         <v>3</v>
@@ -1697,12 +1697,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ethereum_Per_USD_Binance long (risk 1,719); Live_Cattle_Futures_CME short (risk 1,692); S_P_500_Index short (risk 1,666)</t>
+          <t>Ethereum_Per_USD_Binance long (risk 1,414); Live_Cattle_Futures_CME short (risk 1,398); S_P_500_Index short (risk 1,381)</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Teucrium_Wheat_Fund stop (-2,135)</t>
+          <t>Teucrium_Wheat_Fund stop (-1,875)</t>
         </is>
       </c>
     </row>
@@ -1711,13 +1711,13 @@
         <v>46052</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>109434.51</v>
+        <v>121618.26</v>
       </c>
       <c r="C35" s="5" t="n">
-        <v>1633.21</v>
+        <v>1360.38</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>107801.29</v>
+        <v>120257.89</v>
       </c>
       <c r="E35" t="n">
         <v>1</v>
@@ -1729,12 +1729,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures long (risk 1,633)</t>
+          <t>Cocoa_NYCSCE_Futures long (risk 1,360)</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Ethereum_Per_USD_Binance stop (-1,838); Live_Cattle_Futures_CME unknown_pl (-1,793); S_P_500_Index target_r (+4,161)</t>
+          <t>Ethereum_Per_USD_Binance stop (-1,512); Live_Cattle_Futures_CME unknown_pl (-1,481); S_P_500_Index target_r (+4,641)</t>
         </is>
       </c>
     </row>
@@ -1743,13 +1743,13 @@
         <v>46053</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>109434.51</v>
+        <v>121618.26</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>1633.21</v>
+        <v>1360.38</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>107801.29</v>
+        <v>120257.89</v>
       </c>
       <c r="E36" t="n">
         <v>1</v>
@@ -1767,13 +1767,13 @@
         <v>46054</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>109434.51</v>
+        <v>121618.26</v>
       </c>
       <c r="C37" s="5" t="n">
-        <v>1633.21</v>
+        <v>1360.38</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>107801.29</v>
+        <v>120257.89</v>
       </c>
       <c r="E37" t="n">
         <v>1</v>
@@ -1791,13 +1791,13 @@
         <v>46055</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>109434.51</v>
+        <v>121618.26</v>
       </c>
       <c r="C38" s="5" t="n">
-        <v>4997.97</v>
+        <v>4169.83</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>104436.54</v>
+        <v>117448.43</v>
       </c>
       <c r="E38" t="n">
         <v>3</v>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance long (risk 1,696); S_P_500_Index short (risk 1,669)</t>
+          <t>Bitcoin_Per_USD_Binance long (risk 1,413); S_P_500_Index short (risk 1,396)</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -1819,13 +1819,13 @@
         <v>46056</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>106059.16</v>
+        <v>118799.95</v>
       </c>
       <c r="C39" s="5" t="n">
-        <v>3276</v>
+        <v>2740.39</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>102783.16</v>
+        <v>116059.56</v>
       </c>
       <c r="E39" t="n">
         <v>2</v>
@@ -1837,12 +1837,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>EURO_STOXX_50_Index short (risk 1,643)</t>
+          <t>EURO_STOXX_50_Index short (risk 1,380)</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance stop (-1,699); S_P_500_Index unknown_pl (-1,676)</t>
+          <t>Bitcoin_Per_USD_Binance stop (-1,416); S_P_500_Index unknown_pl (-1,402)</t>
         </is>
       </c>
     </row>
@@ -1851,13 +1851,13 @@
         <v>46057</v>
       </c>
       <c r="B40" s="5" t="n">
-        <v>106059.16</v>
+        <v>118799.95</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>3276</v>
+        <v>2740.39</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>102783.16</v>
+        <v>116059.56</v>
       </c>
       <c r="E40" t="n">
         <v>2</v>
@@ -1875,13 +1875,13 @@
         <v>46058</v>
       </c>
       <c r="B41" s="5" t="n">
-        <v>110165.03</v>
+        <v>122249.08</v>
       </c>
       <c r="C41" s="5" t="n">
-        <v>3249.99</v>
+        <v>2724.08</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>106915.03</v>
+        <v>119525</v>
       </c>
       <c r="E41" t="n">
         <v>2</v>
@@ -1893,12 +1893,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures long (risk 1,617)</t>
+          <t>NY_Copper_Futures long (risk 1,364)</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>EURO_STOXX_50_Index target_r (+4,106)</t>
+          <t>EURO_STOXX_50_Index target_r (+3,449)</t>
         </is>
       </c>
     </row>
@@ -1907,13 +1907,13 @@
         <v>46059</v>
       </c>
       <c r="B42" s="5" t="n">
-        <v>108540.77</v>
+        <v>120879.07</v>
       </c>
       <c r="C42" s="5" t="n">
-        <v>3314.99</v>
+        <v>2764.79</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>105225.78</v>
+        <v>118114.28</v>
       </c>
       <c r="E42" t="n">
         <v>2</v>
@@ -1925,12 +1925,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance long (risk 1,682)</t>
+          <t>Bitcoin_Per_USD_Binance long (risk 1,404)</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures stop (-1,624)</t>
+          <t>NY_Copper_Futures stop (-1,370)</t>
         </is>
       </c>
     </row>
@@ -1939,13 +1939,13 @@
         <v>46060</v>
       </c>
       <c r="B43" s="5" t="n">
-        <v>112743.89</v>
+        <v>125246.7</v>
       </c>
       <c r="C43" s="5" t="n">
-        <v>1633.21</v>
+        <v>1360.38</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>111110.68</v>
+        <v>123886.32</v>
       </c>
       <c r="E43" t="n">
         <v>1</v>
@@ -1958,7 +1958,7 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance target_r (+4,203)</t>
+          <t>Bitcoin_Per_USD_Binance target_r (+4,368)</t>
         </is>
       </c>
     </row>
@@ -1967,13 +1967,13 @@
         <v>46061</v>
       </c>
       <c r="B44" s="5" t="n">
-        <v>112743.89</v>
+        <v>125246.7</v>
       </c>
       <c r="C44" s="5" t="n">
-        <v>1633.21</v>
+        <v>1360.38</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>111110.68</v>
+        <v>123886.32</v>
       </c>
       <c r="E44" t="n">
         <v>1</v>
@@ -1991,13 +1991,13 @@
         <v>46062</v>
       </c>
       <c r="B45" s="5" t="n">
-        <v>112743.89</v>
+        <v>125246.7</v>
       </c>
       <c r="C45" s="5" t="n">
-        <v>1633.21</v>
+        <v>1360.38</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>111110.68</v>
+        <v>123886.32</v>
       </c>
       <c r="E45" t="n">
         <v>1</v>
@@ -2015,13 +2015,13 @@
         <v>46063</v>
       </c>
       <c r="B46" s="5" t="n">
-        <v>111067.7</v>
+        <v>123850.52</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>3468.05</v>
+        <v>2894.22</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>107599.65</v>
+        <v>120956.3</v>
       </c>
       <c r="E46" t="n">
         <v>2</v>
@@ -2033,12 +2033,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>EURO_STOXX_50_Index short (risk 1,748); S_P_500_Index short (risk 1,720)</t>
+          <t>EURO_STOXX_50_Index short (risk 1,456); S_P_500_Index short (risk 1,439)</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures stop (-1,676)</t>
+          <t>Cocoa_NYCSCE_Futures stop (-1,396)</t>
         </is>
       </c>
     </row>
@@ -2047,13 +2047,13 @@
         <v>46064</v>
       </c>
       <c r="B47" s="5" t="n">
-        <v>113699.41</v>
+        <v>126036.55</v>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1692.54</v>
+        <v>1421.24</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>112006.87</v>
+        <v>124615.32</v>
       </c>
       <c r="E47" t="n">
         <v>1</v>
@@ -2065,12 +2065,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT short (risk 1,693)</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT short (risk 1,421)</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>EURO_STOXX_50_Index target_r (+4,367); S_P_500_Index unknown_pl (-1,736)</t>
+          <t>EURO_STOXX_50_Index target_r (+3,638); S_P_500_Index unknown_pl (-1,452)</t>
         </is>
       </c>
     </row>
@@ -2079,13 +2079,13 @@
         <v>46065</v>
       </c>
       <c r="B48" s="5" t="n">
-        <v>111773.42</v>
+        <v>124419.28</v>
       </c>
       <c r="C48" s="5" t="n">
-        <v>1761.87</v>
+        <v>1464.23</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>110011.55</v>
+        <v>122955.05</v>
       </c>
       <c r="E48" t="n">
         <v>1</v>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>EURO_STOXX_50_Index short (risk 1,762)</t>
+          <t>EURO_STOXX_50_Index short (risk 1,464)</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT stop (-1,926)</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT stop (-1,617)</t>
         </is>
       </c>
     </row>
@@ -2111,13 +2111,13 @@
         <v>46066</v>
       </c>
       <c r="B49" s="5" t="n">
-        <v>116177.18</v>
+        <v>128079.1</v>
       </c>
       <c r="C49" s="5" t="n">
-        <v>1730.48</v>
+        <v>1444.72</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>114446.7</v>
+        <v>126634.38</v>
       </c>
       <c r="E49" t="n">
         <v>1</v>
@@ -2129,12 +2129,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures long (risk 1,730)</t>
+          <t>NY_Copper_Futures long (risk 1,445)</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>EURO_STOXX_50_Index target_r (+4,404)</t>
+          <t>EURO_STOXX_50_Index target_r (+3,660)</t>
         </is>
       </c>
     </row>
@@ -2143,13 +2143,13 @@
         <v>46067</v>
       </c>
       <c r="B50" s="5" t="n">
-        <v>116177.18</v>
+        <v>128079.1</v>
       </c>
       <c r="C50" s="5" t="n">
-        <v>1730.48</v>
+        <v>1444.72</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>114446.7</v>
+        <v>126634.38</v>
       </c>
       <c r="E50" t="n">
         <v>1</v>
@@ -2167,13 +2167,13 @@
         <v>46068</v>
       </c>
       <c r="B51" s="5" t="n">
-        <v>116177.18</v>
+        <v>128079.1</v>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1730.48</v>
+        <v>1444.72</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>114446.7</v>
+        <v>126634.38</v>
       </c>
       <c r="E51" t="n">
         <v>1</v>
@@ -2191,13 +2191,13 @@
         <v>46069</v>
       </c>
       <c r="B52" s="5" t="n">
-        <v>116177.18</v>
+        <v>128079.1</v>
       </c>
       <c r="C52" s="5" t="n">
-        <v>1730.48</v>
+        <v>1444.72</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>114446.7</v>
+        <v>126634.38</v>
       </c>
       <c r="E52" t="n">
         <v>1</v>
@@ -2215,13 +2215,13 @@
         <v>46070</v>
       </c>
       <c r="B53" s="5" t="n">
-        <v>114439.33</v>
+        <v>126628.24</v>
       </c>
       <c r="C53" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>114439.33</v>
+        <v>126628.24</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
@@ -2230,7 +2230,7 @@
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures stop (-1,738)</t>
+          <t>NY_Copper_Futures stop (-1,451)</t>
         </is>
       </c>
     </row>
@@ -2239,13 +2239,13 @@
         <v>46071</v>
       </c>
       <c r="B54" s="5" t="n">
-        <v>114439.33</v>
+        <v>126628.24</v>
       </c>
       <c r="C54" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>114439.33</v>
+        <v>126628.24</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
@@ -2259,13 +2259,13 @@
         <v>46072</v>
       </c>
       <c r="B55" s="5" t="n">
-        <v>114439.33</v>
+        <v>126628.24</v>
       </c>
       <c r="C55" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>114439.33</v>
+        <v>126628.24</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
@@ -2279,13 +2279,13 @@
         <v>46073</v>
       </c>
       <c r="B56" s="5" t="n">
-        <v>114439.33</v>
+        <v>126628.24</v>
       </c>
       <c r="C56" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>114439.33</v>
+        <v>126628.24</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
@@ -2299,13 +2299,13 @@
         <v>46074</v>
       </c>
       <c r="B57" s="5" t="n">
-        <v>114439.33</v>
+        <v>126628.24</v>
       </c>
       <c r="C57" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>114439.33</v>
+        <v>126628.24</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
@@ -2319,13 +2319,13 @@
         <v>46075</v>
       </c>
       <c r="B58" s="5" t="n">
-        <v>114439.33</v>
+        <v>126628.24</v>
       </c>
       <c r="C58" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>114439.33</v>
+        <v>126628.24</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
@@ -2339,13 +2339,13 @@
         <v>46076</v>
       </c>
       <c r="B59" s="5" t="n">
-        <v>114439.33</v>
+        <v>126628.24</v>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1800.13</v>
+        <v>1487.88</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>112639.2</v>
+        <v>125140.35</v>
       </c>
       <c r="E59" t="n">
         <v>1</v>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT short (risk 1,800)</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT short (risk 1,488)</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
@@ -2367,13 +2367,13 @@
         <v>46077</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>114439.33</v>
+        <v>126628.24</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>5315.89</v>
+        <v>4411.4</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>109123.44</v>
+        <v>122216.83</v>
       </c>
       <c r="E60" t="n">
         <v>3</v>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures long (risk 1,772); Ethereum_Per_USD_Binance long (risk 1,744)</t>
+          <t>Cocoa_NYCSCE_Futures long (risk 1,470); Ethereum_Per_USD_Binance long (risk 1,453)</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
@@ -2395,13 +2395,13 @@
         <v>46078</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>127197.46</v>
+        <v>137272.43</v>
       </c>
       <c r="C61" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>127197.46</v>
+        <v>137272.43</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
@@ -2410,7 +2410,7 @@
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures target_r (+4,339); Ethereum_Per_USD_Binance target_r (+4,176); US_30_Year_T_Bond_Futures_CBOT target_r (+4,243)</t>
+          <t>Cocoa_NYCSCE_Futures target_r (+3,657); Ethereum_Per_USD_Binance target_r (+3,480); US_30_Year_T_Bond_Futures_CBOT target_r (+3,507)</t>
         </is>
       </c>
     </row>
@@ -2419,13 +2419,13 @@
         <v>46079</v>
       </c>
       <c r="B62" s="5" t="n">
-        <v>127197.46</v>
+        <v>137272.43</v>
       </c>
       <c r="C62" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>127197.46</v>
+        <v>137272.43</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
@@ -2439,13 +2439,13 @@
         <v>46080</v>
       </c>
       <c r="B63" s="5" t="n">
-        <v>127197.46</v>
+        <v>137272.43</v>
       </c>
       <c r="C63" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>127197.46</v>
+        <v>137272.43</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
@@ -2459,13 +2459,13 @@
         <v>46081</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>127197.46</v>
+        <v>137272.43</v>
       </c>
       <c r="C64" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>127197.46</v>
+        <v>137272.43</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
@@ -2479,13 +2479,13 @@
         <v>46082</v>
       </c>
       <c r="B65" s="5" t="n">
-        <v>127197.46</v>
+        <v>137272.43</v>
       </c>
       <c r="C65" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>127197.46</v>
+        <v>137272.43</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
@@ -2499,13 +2499,13 @@
         <v>46083</v>
       </c>
       <c r="B66" s="5" t="n">
-        <v>127197.46</v>
+        <v>137272.43</v>
       </c>
       <c r="C66" s="5" t="n">
-        <v>2000.82</v>
+        <v>1612.95</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>125196.64</v>
+        <v>135659.48</v>
       </c>
       <c r="E66" t="n">
         <v>1</v>
@@ -2517,7 +2517,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX short (risk 2,001)</t>
+          <t>Gold_Futures_COMEX short (risk 1,613)</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
@@ -2527,13 +2527,13 @@
         <v>46084</v>
       </c>
       <c r="B67" s="5" t="n">
-        <v>132194.24</v>
+        <v>141300.57</v>
       </c>
       <c r="C67" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>132194.24</v>
+        <v>141300.57</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
@@ -2542,7 +2542,7 @@
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX target_r (+4,997)</t>
+          <t>Gold_Futures_COMEX target_r (+4,028)</t>
         </is>
       </c>
     </row>
@@ -2551,13 +2551,13 @@
         <v>46085</v>
       </c>
       <c r="B68" s="5" t="n">
-        <v>132194.24</v>
+        <v>141300.57</v>
       </c>
       <c r="C68" s="5" t="n">
-        <v>2079.42</v>
+        <v>1660.28</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>130114.83</v>
+        <v>139640.29</v>
       </c>
       <c r="E68" t="n">
         <v>1</v>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate short (risk 2,079)</t>
+          <t>USD_EUR_Cross_Rate short (risk 1,660)</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
@@ -2579,13 +2579,13 @@
         <v>46086</v>
       </c>
       <c r="B69" s="5" t="n">
-        <v>129753.19</v>
+        <v>139351.55</v>
       </c>
       <c r="C69" s="5" t="n">
-        <v>2046.71</v>
+        <v>1640.77</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>127706.48</v>
+        <v>137710.77</v>
       </c>
       <c r="E69" t="n">
         <v>1</v>
@@ -2597,12 +2597,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>S_P_500_Index long (risk 2,047)</t>
+          <t>S_P_500_Index long (risk 1,641)</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate stop (-2,441)</t>
+          <t>USD_EUR_Cross_Rate stop (-1,949)</t>
         </is>
       </c>
     </row>
@@ -2611,13 +2611,13 @@
         <v>46087</v>
       </c>
       <c r="B70" s="5" t="n">
-        <v>127703.02</v>
+        <v>137587.23</v>
       </c>
       <c r="C70" s="5" t="n">
-        <v>2008.82</v>
+        <v>1618.1</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>125694.19</v>
+        <v>135969.13</v>
       </c>
       <c r="E70" t="n">
         <v>1</v>
@@ -2629,12 +2629,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate short (risk 2,009)</t>
+          <t>USD_EUR_Cross_Rate short (risk 1,618)</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>S_P_500_Index stop (-2,050)</t>
+          <t>S_P_500_Index stop (-1,764)</t>
         </is>
       </c>
     </row>
@@ -2643,13 +2643,13 @@
         <v>46088</v>
       </c>
       <c r="B71" s="5" t="n">
-        <v>127703.02</v>
+        <v>137587.23</v>
       </c>
       <c r="C71" s="5" t="n">
-        <v>2008.82</v>
+        <v>1618.1</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>125694.19</v>
+        <v>135969.13</v>
       </c>
       <c r="E71" t="n">
         <v>1</v>
@@ -2667,13 +2667,13 @@
         <v>46089</v>
       </c>
       <c r="B72" s="5" t="n">
-        <v>127703.02</v>
+        <v>137587.23</v>
       </c>
       <c r="C72" s="5" t="n">
-        <v>2008.82</v>
+        <v>1618.1</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>125694.19</v>
+        <v>135969.13</v>
       </c>
       <c r="E72" t="n">
         <v>1</v>
@@ -2691,13 +2691,13 @@
         <v>46090</v>
       </c>
       <c r="B73" s="5" t="n">
-        <v>125511.57</v>
+        <v>135822.03</v>
       </c>
       <c r="C73" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>125511.57</v>
+        <v>135822.03</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
@@ -2706,7 +2706,7 @@
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate stop (-2,191)</t>
+          <t>USD_EUR_Cross_Rate stop (-1,765)</t>
         </is>
       </c>
     </row>
@@ -2715,13 +2715,13 @@
         <v>46091</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>125511.57</v>
+        <v>135822.03</v>
       </c>
       <c r="C74" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>125511.57</v>
+        <v>135822.03</v>
       </c>
       <c r="E74" t="n">
         <v>0</v>
@@ -2735,13 +2735,13 @@
         <v>46092</v>
       </c>
       <c r="B75" s="5" t="n">
-        <v>125511.57</v>
+        <v>135822.03</v>
       </c>
       <c r="C75" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>125511.57</v>
+        <v>135822.03</v>
       </c>
       <c r="E75" t="n">
         <v>0</v>
@@ -2755,13 +2755,13 @@
         <v>46093</v>
       </c>
       <c r="B76" s="5" t="n">
-        <v>125511.57</v>
+        <v>135822.03</v>
       </c>
       <c r="C76" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>125511.57</v>
+        <v>135822.03</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
@@ -2775,13 +2775,13 @@
         <v>46094</v>
       </c>
       <c r="B77" s="5" t="n">
-        <v>125511.57</v>
+        <v>135822.03</v>
       </c>
       <c r="C77" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>125511.57</v>
+        <v>135822.03</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
@@ -2795,13 +2795,13 @@
         <v>46095</v>
       </c>
       <c r="B78" s="5" t="n">
-        <v>125511.57</v>
+        <v>135822.03</v>
       </c>
       <c r="C78" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>125511.57</v>
+        <v>135822.03</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
@@ -2815,13 +2815,13 @@
         <v>46096</v>
       </c>
       <c r="B79" s="5" t="n">
-        <v>125511.57</v>
+        <v>135822.03</v>
       </c>
       <c r="C79" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>125511.57</v>
+        <v>135822.03</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
@@ -2835,13 +2835,13 @@
         <v>46097</v>
       </c>
       <c r="B80" s="5" t="n">
-        <v>125511.57</v>
+        <v>135822.03</v>
       </c>
       <c r="C80" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>125511.57</v>
+        <v>135822.03</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
@@ -2855,13 +2855,13 @@
         <v>46098</v>
       </c>
       <c r="B81" s="5" t="n">
-        <v>125511.57</v>
+        <v>135822.03</v>
       </c>
       <c r="C81" s="5" t="n">
-        <v>1974.3</v>
+        <v>1595.91</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>123537.28</v>
+        <v>134226.12</v>
       </c>
       <c r="E81" t="n">
         <v>1</v>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance short (risk 1,974)</t>
+          <t>Bitcoin_Per_USD_Binance short (risk 1,596)</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
@@ -2883,13 +2883,13 @@
         <v>46099</v>
       </c>
       <c r="B82" s="5" t="n">
-        <v>130441.36</v>
+        <v>139806.99</v>
       </c>
       <c r="C82" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>130441.36</v>
+        <v>139806.99</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
@@ -2898,7 +2898,7 @@
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance target_r (+4,930)</t>
+          <t>Bitcoin_Per_USD_Binance target_r (+3,985)</t>
         </is>
       </c>
     </row>
@@ -2907,13 +2907,13 @@
         <v>46100</v>
       </c>
       <c r="B83" s="5" t="n">
-        <v>130441.36</v>
+        <v>139806.99</v>
       </c>
       <c r="C83" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>130441.36</v>
+        <v>139806.99</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
@@ -2927,13 +2927,13 @@
         <v>46101</v>
       </c>
       <c r="B84" s="5" t="n">
-        <v>130441.36</v>
+        <v>139806.99</v>
       </c>
       <c r="C84" s="5" t="n">
-        <v>2051.84</v>
+        <v>1642.73</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>128389.52</v>
+        <v>138164.26</v>
       </c>
       <c r="E84" t="n">
         <v>1</v>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP short (risk 2,052)</t>
+          <t>United_States_Oil_Fund_LP short (risk 1,643)</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
@@ -2955,13 +2955,13 @@
         <v>46102</v>
       </c>
       <c r="B85" s="5" t="n">
-        <v>130441.36</v>
+        <v>139806.99</v>
       </c>
       <c r="C85" s="5" t="n">
-        <v>2051.84</v>
+        <v>1642.73</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>128389.52</v>
+        <v>138164.26</v>
       </c>
       <c r="E85" t="n">
         <v>1</v>
@@ -2979,13 +2979,13 @@
         <v>46103</v>
       </c>
       <c r="B86" s="5" t="n">
-        <v>130441.36</v>
+        <v>139806.99</v>
       </c>
       <c r="C86" s="5" t="n">
-        <v>2051.84</v>
+        <v>1642.73</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>128389.52</v>
+        <v>138164.26</v>
       </c>
       <c r="E86" t="n">
         <v>1</v>
@@ -3003,13 +3003,13 @@
         <v>46104</v>
       </c>
       <c r="B87" s="5" t="n">
-        <v>135539.64</v>
+        <v>150353.06</v>
       </c>
       <c r="C87" s="5" t="n">
-        <v>2019.57</v>
+        <v>1623.43</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>133520.08</v>
+        <v>148729.63</v>
       </c>
       <c r="E87" t="n">
         <v>1</v>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures long (risk 2,020)</t>
+          <t>NY_Copper_Futures long (risk 1,623)</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP target_r (+5,098)</t>
+          <t>United_States_Oil_Fund_LP target_r (+10,546)</t>
         </is>
       </c>
     </row>
@@ -3035,13 +3035,13 @@
         <v>46105</v>
       </c>
       <c r="B88" s="5" t="n">
-        <v>140582.57</v>
+        <v>154483.93</v>
       </c>
       <c r="C88" s="5" t="n">
-        <v>2100.27</v>
+        <v>1747.57</v>
       </c>
       <c r="D88" s="5" t="n">
-        <v>138482.3</v>
+        <v>152736.35</v>
       </c>
       <c r="E88" t="n">
         <v>1</v>
@@ -3053,12 +3053,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX long (risk 2,100)</t>
+          <t>Gold_Futures_COMEX long (risk 1,748)</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures target_r (+5,043)</t>
+          <t>NY_Copper_Futures target_r (+4,131)</t>
         </is>
       </c>
     </row>
@@ -3067,13 +3067,13 @@
         <v>46106</v>
       </c>
       <c r="B89" s="5" t="n">
-        <v>145818.66</v>
+        <v>162875.87</v>
       </c>
       <c r="C89" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D89" s="5" t="n">
-        <v>145818.66</v>
+        <v>162875.87</v>
       </c>
       <c r="E89" t="n">
         <v>0</v>
@@ -3082,7 +3082,7 @@
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX target_r (+5,236)</t>
+          <t>Gold_Futures_COMEX target_r (+8,392)</t>
         </is>
       </c>
     </row>
@@ -3091,13 +3091,13 @@
         <v>46107</v>
       </c>
       <c r="B90" s="5" t="n">
-        <v>145818.66</v>
+        <v>162875.87</v>
       </c>
       <c r="C90" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>145818.66</v>
+        <v>162875.87</v>
       </c>
       <c r="E90" t="n">
         <v>0</v>
@@ -3111,13 +3111,13 @@
         <v>46108</v>
       </c>
       <c r="B91" s="5" t="n">
-        <v>145818.66</v>
+        <v>162875.87</v>
       </c>
       <c r="C91" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>145818.66</v>
+        <v>162875.87</v>
       </c>
       <c r="E91" t="n">
         <v>0</v>
@@ -3131,13 +3131,13 @@
         <v>46109</v>
       </c>
       <c r="B92" s="5" t="n">
-        <v>145818.66</v>
+        <v>162875.87</v>
       </c>
       <c r="C92" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>145818.66</v>
+        <v>162875.87</v>
       </c>
       <c r="E92" t="n">
         <v>0</v>
@@ -3151,13 +3151,13 @@
         <v>46110</v>
       </c>
       <c r="B93" s="5" t="n">
-        <v>145818.66</v>
+        <v>162875.87</v>
       </c>
       <c r="C93" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>145818.66</v>
+        <v>162875.87</v>
       </c>
       <c r="E93" t="n">
         <v>0</v>
@@ -3171,13 +3171,13 @@
         <v>46111</v>
       </c>
       <c r="B94" s="5" t="n">
-        <v>145818.66</v>
+        <v>162875.87</v>
       </c>
       <c r="C94" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>145818.66</v>
+        <v>162875.87</v>
       </c>
       <c r="E94" t="n">
         <v>0</v>
@@ -3191,13 +3191,13 @@
         <v>46112</v>
       </c>
       <c r="B95" s="5" t="n">
-        <v>145818.66</v>
+        <v>162875.87</v>
       </c>
       <c r="C95" s="5" t="n">
-        <v>2293.73</v>
+        <v>1913.79</v>
       </c>
       <c r="D95" s="5" t="n">
-        <v>143524.93</v>
+        <v>160962.08</v>
       </c>
       <c r="E95" t="n">
         <v>1</v>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP short (risk 2,294)</t>
+          <t>United_States_Oil_Fund_LP short (risk 1,914)</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
@@ -3219,13 +3219,13 @@
         <v>46113</v>
       </c>
       <c r="B96" s="5" t="n">
-        <v>151494.16</v>
+        <v>175830.82</v>
       </c>
       <c r="C96" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D96" s="5" t="n">
-        <v>151494.16</v>
+        <v>175830.82</v>
       </c>
       <c r="E96" t="n">
         <v>0</v>
@@ -3234,7 +3234,7 @@
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP target_r (+5,676)</t>
+          <t>United_States_Oil_Fund_LP target_r (+12,955)</t>
         </is>
       </c>
     </row>
@@ -3243,13 +3243,13 @@
         <v>46114</v>
       </c>
       <c r="B97" s="5" t="n">
-        <v>151494.16</v>
+        <v>175830.82</v>
       </c>
       <c r="C97" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D97" s="5" t="n">
-        <v>151494.16</v>
+        <v>175830.82</v>
       </c>
       <c r="E97" t="n">
         <v>0</v>
@@ -3263,13 +3263,13 @@
         <v>46115</v>
       </c>
       <c r="B98" s="5" t="n">
-        <v>151494.16</v>
+        <v>175830.82</v>
       </c>
       <c r="C98" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D98" s="5" t="n">
-        <v>151494.16</v>
+        <v>175830.82</v>
       </c>
       <c r="E98" t="n">
         <v>0</v>
@@ -3283,13 +3283,13 @@
         <v>46116</v>
       </c>
       <c r="B99" s="5" t="n">
-        <v>151494.16</v>
+        <v>175830.82</v>
       </c>
       <c r="C99" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D99" s="5" t="n">
-        <v>151494.16</v>
+        <v>175830.82</v>
       </c>
       <c r="E99" t="n">
         <v>0</v>
@@ -3303,13 +3303,13 @@
         <v>46117</v>
       </c>
       <c r="B100" s="5" t="n">
-        <v>151494.16</v>
+        <v>175830.82</v>
       </c>
       <c r="C100" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>151494.16</v>
+        <v>175830.82</v>
       </c>
       <c r="E100" t="n">
         <v>0</v>
@@ -3323,13 +3323,13 @@
         <v>46118</v>
       </c>
       <c r="B101" s="5" t="n">
-        <v>151494.16</v>
+        <v>175830.82</v>
       </c>
       <c r="C101" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>151494.16</v>
+        <v>175830.82</v>
       </c>
       <c r="E101" t="n">
         <v>0</v>
@@ -3343,13 +3343,13 @@
         <v>46119</v>
       </c>
       <c r="B102" s="5" t="n">
-        <v>151494.16</v>
+        <v>175830.82</v>
       </c>
       <c r="C102" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D102" s="5" t="n">
-        <v>151494.16</v>
+        <v>175830.82</v>
       </c>
       <c r="E102" t="n">
         <v>0</v>
@@ -3363,13 +3363,13 @@
         <v>46120</v>
       </c>
       <c r="B103" s="5" t="n">
-        <v>151494.16</v>
+        <v>175830.82</v>
       </c>
       <c r="C103" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D103" s="5" t="n">
-        <v>151494.16</v>
+        <v>175830.82</v>
       </c>
       <c r="E103" t="n">
         <v>0</v>
@@ -3383,13 +3383,13 @@
         <v>46121</v>
       </c>
       <c r="B104" s="5" t="n">
-        <v>151494.16</v>
+        <v>175830.82</v>
       </c>
       <c r="C104" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D104" s="5" t="n">
-        <v>151494.16</v>
+        <v>175830.82</v>
       </c>
       <c r="E104" t="n">
         <v>0</v>
@@ -3403,13 +3403,13 @@
         <v>46122</v>
       </c>
       <c r="B105" s="5" t="n">
-        <v>151494.16</v>
+        <v>175830.82</v>
       </c>
       <c r="C105" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D105" s="5" t="n">
-        <v>151494.16</v>
+        <v>175830.82</v>
       </c>
       <c r="E105" t="n">
         <v>0</v>
@@ -3423,13 +3423,13 @@
         <v>46123</v>
       </c>
       <c r="B106" s="5" t="n">
-        <v>151494.16</v>
+        <v>175830.82</v>
       </c>
       <c r="C106" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D106" s="5" t="n">
-        <v>151494.16</v>
+        <v>175830.82</v>
       </c>
       <c r="E106" t="n">
         <v>0</v>
@@ -3443,13 +3443,13 @@
         <v>46124</v>
       </c>
       <c r="B107" s="5" t="n">
-        <v>151494.16</v>
+        <v>175830.82</v>
       </c>
       <c r="C107" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D107" s="5" t="n">
-        <v>151494.16</v>
+        <v>175830.82</v>
       </c>
       <c r="E107" t="n">
         <v>0</v>
@@ -3463,13 +3463,13 @@
         <v>46125</v>
       </c>
       <c r="B108" s="5" t="n">
-        <v>151494.16</v>
+        <v>175830.82</v>
       </c>
       <c r="C108" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>151494.16</v>
+        <v>175830.82</v>
       </c>
       <c r="E108" t="n">
         <v>0</v>
@@ -3483,13 +3483,13 @@
         <v>46126</v>
       </c>
       <c r="B109" s="5" t="n">
-        <v>151494.16</v>
+        <v>175830.82</v>
       </c>
       <c r="C109" s="5" t="n">
-        <v>2383</v>
+        <v>2066.01</v>
       </c>
       <c r="D109" s="5" t="n">
-        <v>149111.16</v>
+        <v>173764.81</v>
       </c>
       <c r="E109" t="n">
         <v>1</v>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance short (risk 2,383)</t>
+          <t>Bitcoin_Per_USD_Binance short (risk 2,066)</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
@@ -3511,13 +3511,13 @@
         <v>46127</v>
       </c>
       <c r="B110" s="5" t="n">
-        <v>151494.16</v>
+        <v>175830.82</v>
       </c>
       <c r="C110" s="5" t="n">
-        <v>9309.450000000001</v>
+        <v>8119.53</v>
       </c>
       <c r="D110" s="5" t="n">
-        <v>142184.71</v>
+        <v>167711.29</v>
       </c>
       <c r="E110" t="n">
         <v>4</v>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Ethereum_Per_USD_Binance short (risk 2,346); Live_Cattle_Futures_CME short (risk 2,309); NY_Copper_Futures short (risk 2,272)</t>
+          <t>Ethereum_Per_USD_Binance short (risk 2,042); Live_Cattle_Futures_CME short (risk 2,018); NY_Copper_Futures short (risk 1,994)</t>
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
@@ -3539,13 +3539,13 @@
         <v>46128</v>
       </c>
       <c r="B111" s="5" t="n">
-        <v>162696.41</v>
+        <v>185602.02</v>
       </c>
       <c r="C111" s="5" t="n">
-        <v>4655.31</v>
+        <v>4060.05</v>
       </c>
       <c r="D111" s="5" t="n">
-        <v>158041.1</v>
+        <v>181541.97</v>
       </c>
       <c r="E111" t="n">
         <v>2</v>
@@ -3558,7 +3558,7 @@
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Ethereum_Per_USD_Binance target_r (+5,571); Live_Cattle_Futures_CME target_r (+5,632)</t>
+          <t>Ethereum_Per_USD_Binance target_r (+4,849); Live_Cattle_Futures_CME target_r (+4,922)</t>
         </is>
       </c>
     </row>
@@ -3567,13 +3567,13 @@
         <v>46129</v>
       </c>
       <c r="B112" s="5" t="n">
-        <v>162630.65</v>
+        <v>185524.26</v>
       </c>
       <c r="C112" s="5" t="n">
-        <v>2272.31</v>
+        <v>1994.04</v>
       </c>
       <c r="D112" s="5" t="n">
-        <v>160358.34</v>
+        <v>183530.22</v>
       </c>
       <c r="E112" t="n">
         <v>1</v>
@@ -3585,12 +3585,12 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate long (risk 2,486)</t>
+          <t>USD_EUR_Cross_Rate long (risk 2,133)</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance stop (-2,391); USD_EUR_Cross_Rate data_end (+2,326)</t>
+          <t>Bitcoin_Per_USD_Binance stop (-2,073); USD_EUR_Cross_Rate data_end (+1,995)</t>
         </is>
       </c>
     </row>
@@ -3599,13 +3599,13 @@
         <v>46130</v>
       </c>
       <c r="B113" s="5" t="n">
-        <v>162630.65</v>
+        <v>185524.26</v>
       </c>
       <c r="C113" s="5" t="n">
-        <v>2272.31</v>
+        <v>1994.04</v>
       </c>
       <c r="D113" s="5" t="n">
-        <v>160358.34</v>
+        <v>183530.22</v>
       </c>
       <c r="E113" t="n">
         <v>1</v>
@@ -3623,13 +3623,13 @@
         <v>46132</v>
       </c>
       <c r="B114" s="5" t="n">
-        <v>162630.65</v>
+        <v>185524.26</v>
       </c>
       <c r="C114" s="5" t="n">
-        <v>2272.31</v>
+        <v>1994.04</v>
       </c>
       <c r="D114" s="5" t="n">
-        <v>160358.34</v>
+        <v>183530.22</v>
       </c>
       <c r="E114" t="n">
         <v>1</v>
@@ -3647,13 +3647,13 @@
         <v>46133</v>
       </c>
       <c r="B115" s="5" t="n">
-        <v>162630.65</v>
+        <v>185524.26</v>
       </c>
       <c r="C115" s="5" t="n">
-        <v>2272.31</v>
+        <v>1994.04</v>
       </c>
       <c r="D115" s="5" t="n">
-        <v>160358.34</v>
+        <v>183530.22</v>
       </c>
       <c r="E115" t="n">
         <v>1</v>
@@ -3671,13 +3671,13 @@
         <v>46134</v>
       </c>
       <c r="B116" s="5" t="n">
-        <v>160341.03</v>
+        <v>183515.03</v>
       </c>
       <c r="C116" s="5" t="n">
-        <v>2522.44</v>
+        <v>2156.48</v>
       </c>
       <c r="D116" s="5" t="n">
-        <v>157818.59</v>
+        <v>181358.55</v>
       </c>
       <c r="E116" t="n">
         <v>1</v>
@@ -3689,12 +3689,12 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini short (risk 2,522)</t>
+          <t>Dow_Futures_E_mini short (risk 2,156)</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures stop (-2,290)</t>
+          <t>NY_Copper_Futures stop (-2,009)</t>
         </is>
       </c>
     </row>
@@ -3703,13 +3703,13 @@
         <v>46135</v>
       </c>
       <c r="B117" s="5" t="n">
-        <v>166564.42</v>
+        <v>192459.06</v>
       </c>
       <c r="C117" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D117" s="5" t="n">
-        <v>166564.42</v>
+        <v>192459.06</v>
       </c>
       <c r="E117" t="n">
         <v>0</v>
@@ -3718,7 +3718,7 @@
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini target_r (+6,223)</t>
+          <t>Dow_Futures_E_mini target_r (+8,944)</t>
         </is>
       </c>
     </row>
@@ -3727,13 +3727,13 @@
         <v>46136</v>
       </c>
       <c r="B118" s="5" t="n">
-        <v>166564.42</v>
+        <v>192459.06</v>
       </c>
       <c r="C118" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D118" s="5" t="n">
-        <v>166564.42</v>
+        <v>192459.06</v>
       </c>
       <c r="E118" t="n">
         <v>0</v>
@@ -3747,13 +3747,13 @@
         <v>46139</v>
       </c>
       <c r="B119" s="5" t="n">
-        <v>166564.42</v>
+        <v>192459.06</v>
       </c>
       <c r="C119" s="5" t="n">
-        <v>2620.06</v>
+        <v>2261.39</v>
       </c>
       <c r="D119" s="5" t="n">
-        <v>163944.36</v>
+        <v>190197.66</v>
       </c>
       <c r="E119" t="n">
         <v>1</v>
@@ -3765,7 +3765,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME short (risk 2,620)</t>
+          <t>Bitcoin_Per_USD_CME short (risk 2,261)</t>
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
@@ -3775,13 +3775,13 @@
         <v>46140</v>
       </c>
       <c r="B120" s="5" t="n">
-        <v>173103.78</v>
+        <v>203151.8</v>
       </c>
       <c r="C120" s="5" t="n">
-        <v>2578.84</v>
+        <v>2234.82</v>
       </c>
       <c r="D120" s="5" t="n">
-        <v>170524.93</v>
+        <v>200916.97</v>
       </c>
       <c r="E120" t="n">
         <v>1</v>
@@ -3793,12 +3793,12 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini short (risk 2,579)</t>
+          <t>S_P_500_E_mini short (risk 2,235)</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME target_r (+6,539)</t>
+          <t>Bitcoin_Per_USD_CME target_r (+10,693)</t>
         </is>
       </c>
     </row>
@@ -3807,13 +3807,13 @@
         <v>46141</v>
       </c>
       <c r="B121" s="5" t="n">
-        <v>179547.8</v>
+        <v>208736.18</v>
       </c>
       <c r="C121" s="5" t="n">
-        <v>2682.36</v>
+        <v>2360.77</v>
       </c>
       <c r="D121" s="5" t="n">
-        <v>176865.45</v>
+        <v>206375.4</v>
       </c>
       <c r="E121" t="n">
         <v>1</v>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 2,682)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 2,361)</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini target_r (+6,444)</t>
+          <t>S_P_500_E_mini target_r (+5,584)</t>
         </is>
       </c>
     </row>
@@ -3839,13 +3839,13 @@
         <v>46142</v>
       </c>
       <c r="B122" s="5" t="n">
-        <v>186193.42</v>
+        <v>214585.06</v>
       </c>
       <c r="C122" s="5" t="n">
-        <v>2782.09</v>
+        <v>2424.91</v>
       </c>
       <c r="D122" s="5" t="n">
-        <v>183411.33</v>
+        <v>212160.15</v>
       </c>
       <c r="E122" t="n">
         <v>1</v>
@@ -3857,12 +3857,12 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures short (risk 2,782)</t>
+          <t>Corn_CBOT_Futures short (risk 2,425)</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT target_r (+6,646)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT target_r (+5,849)</t>
         </is>
       </c>
     </row>
@@ -3871,13 +3871,13 @@
         <v>46143</v>
       </c>
       <c r="B123" s="5" t="n">
-        <v>182825.62</v>
+        <v>211649.64</v>
       </c>
       <c r="C123" s="5" t="n">
-        <v>8519.75</v>
+        <v>7391.12</v>
       </c>
       <c r="D123" s="5" t="n">
-        <v>174305.87</v>
+        <v>204258.53</v>
       </c>
       <c r="E123" t="n">
         <v>3</v>
@@ -3889,12 +3889,12 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Japanese_Yen_Futures short (risk 2,885); Live_Cattle_Futures_CME short (risk 2,840); US_Dollar_Index_Futures long (risk 2,795)</t>
+          <t>Japanese_Yen_Futures short (risk 2,493); Live_Cattle_Futures_CME short (risk 2,464); US_Dollar_Index_Futures long (risk 2,435)</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures unknown_pl (-3,368)</t>
+          <t>Corn_CBOT_Futures unknown_pl (-2,935)</t>
         </is>
       </c>
     </row>
@@ -3903,13 +3903,13 @@
         <v>46146</v>
       </c>
       <c r="B124" s="5" t="n">
-        <v>189879.38</v>
+        <v>217769.2</v>
       </c>
       <c r="C124" s="5" t="n">
-        <v>8421.9</v>
+        <v>7327.56</v>
       </c>
       <c r="D124" s="5" t="n">
-        <v>181457.48</v>
+        <v>210441.64</v>
       </c>
       <c r="E124" t="n">
         <v>3</v>
@@ -3921,12 +3921,12 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini short (risk 2,742)</t>
+          <t>Nasdaq_100_E_mini short (risk 2,400)</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME target_r (+7,054)</t>
+          <t>Live_Cattle_Futures_CME target_r (+6,120)</t>
         </is>
       </c>
     </row>
@@ -3935,13 +3935,13 @@
         <v>46147</v>
       </c>
       <c r="B125" s="5" t="n">
-        <v>194100.39</v>
+        <v>229839.29</v>
       </c>
       <c r="C125" s="5" t="n">
-        <v>5739.39</v>
+        <v>4965.57</v>
       </c>
       <c r="D125" s="5" t="n">
-        <v>188361.01</v>
+        <v>224873.72</v>
       </c>
       <c r="E125" t="n">
         <v>2</v>
@@ -3953,12 +3953,12 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures short (risk 2,854)</t>
+          <t>Corn_CBOT_Futures short (risk 2,473)</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini unknown_pl (-2,744); US_Dollar_Index_Futures target_r (+6,965)</t>
+          <t>Nasdaq_100_E_mini target_r (+6,003); US_Dollar_Index_Futures target_r (+6,067)</t>
         </is>
       </c>
     </row>
@@ -3967,13 +3967,13 @@
         <v>46148</v>
       </c>
       <c r="B126" s="5" t="n">
-        <v>197520.28</v>
+        <v>245059.99</v>
       </c>
       <c r="C126" s="5" t="n">
-        <v>5879.23</v>
+        <v>5253.49</v>
       </c>
       <c r="D126" s="5" t="n">
-        <v>191641.05</v>
+        <v>239806.51</v>
       </c>
       <c r="E126" t="n">
         <v>2</v>
@@ -3985,12 +3985,12 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME short (risk 2,963); US_Dollar_Index_Futures long (risk 2,916)</t>
+          <t>Bitcoin_Per_USD_CME short (risk 2,642); US_Dollar_Index_Futures long (risk 2,611)</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures target_r (+6,617); Japanese_Yen_Futures stop (-3,197)</t>
+          <t>Corn_CBOT_Futures target_r (+17,983); Japanese_Yen_Futures stop (-2,762)</t>
         </is>
       </c>
     </row>
@@ -3999,13 +3999,13 @@
         <v>46149</v>
       </c>
       <c r="B127" s="5" t="n">
-        <v>204916.9</v>
+        <v>251656.14</v>
       </c>
       <c r="C127" s="5" t="n">
-        <v>8897.92</v>
+        <v>8213.559999999999</v>
       </c>
       <c r="D127" s="5" t="n">
-        <v>196018.98</v>
+        <v>243442.57</v>
       </c>
       <c r="E127" t="n">
         <v>3</v>
@@ -4017,12 +4017,12 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>EURO_Futures short (risk 3,015); NY_Platinum_Futures short (risk 2,967)</t>
+          <t>EURO_Futures short (risk 2,818); NY_Platinum_Futures short (risk 2,785)</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME target_r (+7,397)</t>
+          <t>Bitcoin_Per_USD_CME target_r (+6,596)</t>
         </is>
       </c>
     </row>
@@ -4031,13 +4031,13 @@
         <v>46150</v>
       </c>
       <c r="B128" s="5" t="n">
-        <v>201825.09</v>
+        <v>258754.78</v>
       </c>
       <c r="C128" s="5" t="n">
-        <v>5883.41</v>
+        <v>5395.84</v>
       </c>
       <c r="D128" s="5" t="n">
-        <v>195941.69</v>
+        <v>253358.94</v>
       </c>
       <c r="E128" t="n">
         <v>2</v>
@@ -4050,7 +4050,7 @@
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
-          <t>EURO_Futures unknown_pl (-3,092)</t>
+          <t>EURO_Futures target_r (+7,099)</t>
         </is>
       </c>
     </row>
@@ -4059,13 +4059,13 @@
         <v>46153</v>
       </c>
       <c r="B129" s="5" t="n">
-        <v>198817.21</v>
+        <v>255931.88</v>
       </c>
       <c r="C129" s="5" t="n">
-        <v>5998.47</v>
+        <v>5588.19</v>
       </c>
       <c r="D129" s="5" t="n">
-        <v>192818.74</v>
+        <v>250343.7</v>
       </c>
       <c r="E129" t="n">
         <v>2</v>
@@ -4077,12 +4077,12 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX short (risk 3,082)</t>
+          <t>Gold_Futures_COMEX short (risk 2,977)</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures stop (-3,008)</t>
+          <t>NY_Platinum_Futures stop (-2,823)</t>
         </is>
       </c>
     </row>
@@ -4091,13 +4091,13 @@
         <v>46154</v>
       </c>
       <c r="B130" s="5" t="n">
-        <v>202903.39</v>
+        <v>259366.39</v>
       </c>
       <c r="C130" s="5" t="n">
-        <v>3033.04</v>
+        <v>2941.54</v>
       </c>
       <c r="D130" s="5" t="n">
-        <v>199870.36</v>
+        <v>256424.85</v>
       </c>
       <c r="E130" t="n">
         <v>1</v>
@@ -4109,12 +4109,12 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX short (risk 3,033)</t>
+          <t>Silver_Futures_COMEX short (risk 2,942)</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX unknown_pl (-3,181); US_Dollar_Index_Futures target_r (+7,267)</t>
+          <t>Gold_Futures_COMEX unknown_pl (-3,072); US_Dollar_Index_Futures target_r (+6,507)</t>
         </is>
       </c>
     </row>
@@ -4123,13 +4123,13 @@
         <v>46155</v>
       </c>
       <c r="B131" s="5" t="n">
-        <v>199864.04</v>
+        <v>256418.72</v>
       </c>
       <c r="C131" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D131" s="5" t="n">
-        <v>199864.04</v>
+        <v>256418.72</v>
       </c>
       <c r="E131" t="n">
         <v>0</v>
@@ -4138,7 +4138,7 @@
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX stop (-3,039)</t>
+          <t>Silver_Futures_COMEX stop (-2,948)</t>
         </is>
       </c>
     </row>
@@ -4147,13 +4147,13 @@
         <v>46156</v>
       </c>
       <c r="B132" s="5" t="n">
-        <v>199864.04</v>
+        <v>256418.72</v>
       </c>
       <c r="C132" s="5" t="n">
-        <v>3143.86</v>
+        <v>3012.92</v>
       </c>
       <c r="D132" s="5" t="n">
-        <v>196720.18</v>
+        <v>253405.8</v>
       </c>
       <c r="E132" t="n">
         <v>1</v>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 3,144)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 3,013)</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
@@ -4175,13 +4175,13 @@
         <v>46157</v>
       </c>
       <c r="B133" s="5" t="n">
-        <v>207637.56</v>
+        <v>265746.43</v>
       </c>
       <c r="C133" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D133" s="5" t="n">
-        <v>207637.56</v>
+        <v>265746.43</v>
       </c>
       <c r="E133" t="n">
         <v>0</v>
@@ -4190,7 +4190,7 @@
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT target_r (+7,774)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT target_r (+9,328)</t>
         </is>
       </c>
     </row>
@@ -4199,13 +4199,13 @@
         <v>46160</v>
       </c>
       <c r="B134" s="5" t="n">
-        <v>207637.56</v>
+        <v>265746.43</v>
       </c>
       <c r="C134" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>207637.56</v>
+        <v>265746.43</v>
       </c>
       <c r="E134" t="n">
         <v>0</v>
@@ -4219,13 +4219,13 @@
         <v>46161</v>
       </c>
       <c r="B135" s="5" t="n">
-        <v>207637.56</v>
+        <v>265746.43</v>
       </c>
       <c r="C135" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>207637.56</v>
+        <v>265746.43</v>
       </c>
       <c r="E135" t="n">
         <v>0</v>
@@ -4239,13 +4239,13 @@
         <v>46162</v>
       </c>
       <c r="B136" s="5" t="n">
-        <v>207637.56</v>
+        <v>265746.43</v>
       </c>
       <c r="C136" s="5" t="n">
-        <v>3266.14</v>
+        <v>3122.52</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>204371.42</v>
+        <v>262623.91</v>
       </c>
       <c r="E136" t="n">
         <v>1</v>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures short (risk 3,266)</t>
+          <t>US_Dollar_Index_Futures short (risk 3,123)</t>
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
@@ -4267,13 +4267,13 @@
         <v>46163</v>
       </c>
       <c r="B137" s="5" t="n">
-        <v>207637.56</v>
+        <v>265746.43</v>
       </c>
       <c r="C137" s="5" t="n">
-        <v>6480.9</v>
+        <v>6208.35</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>201156.66</v>
+        <v>259538.08</v>
       </c>
       <c r="E137" t="n">
         <v>2</v>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures long (risk 3,215)</t>
+          <t>NY_Palladium_Futures long (risk 3,086)</t>
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
@@ -4295,13 +4295,13 @@
         <v>46164</v>
       </c>
       <c r="B138" s="5" t="n">
-        <v>215636.64</v>
+        <v>273442.91</v>
       </c>
       <c r="C138" s="5" t="n">
-        <v>3266.14</v>
+        <v>3122.52</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>212370.5</v>
+        <v>270320.39</v>
       </c>
       <c r="E138" t="n">
         <v>1</v>
@@ -4314,7 +4314,7 @@
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures target_r (+7,999)</t>
+          <t>NY_Palladium_Futures target_r (+7,696)</t>
         </is>
       </c>
     </row>
@@ -4323,13 +4323,13 @@
         <v>46167</v>
       </c>
       <c r="B139" s="5" t="n">
-        <v>223768.49</v>
+        <v>281217.18</v>
       </c>
       <c r="C139" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D139" s="5" t="n">
-        <v>223768.49</v>
+        <v>281217.18</v>
       </c>
       <c r="E139" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures target_r (+8,132)</t>
+          <t>US_Dollar_Index_Futures target_r (+7,774)</t>
         </is>
       </c>
     </row>
@@ -4347,13 +4347,13 @@
         <v>46168</v>
       </c>
       <c r="B140" s="5" t="n">
-        <v>223768.49</v>
+        <v>281217.18</v>
       </c>
       <c r="C140" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D140" s="5" t="n">
-        <v>223768.49</v>
+        <v>281217.18</v>
       </c>
       <c r="E140" t="n">
         <v>0</v>
@@ -4367,13 +4367,13 @@
         <v>46169</v>
       </c>
       <c r="B141" s="5" t="n">
-        <v>223768.49</v>
+        <v>281217.18</v>
       </c>
       <c r="C141" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D141" s="5" t="n">
-        <v>223768.49</v>
+        <v>281217.18</v>
       </c>
       <c r="E141" t="n">
         <v>0</v>
@@ -4387,13 +4387,13 @@
         <v>46170</v>
       </c>
       <c r="B142" s="5" t="n">
-        <v>223768.49</v>
+        <v>281217.18</v>
       </c>
       <c r="C142" s="5" t="n">
-        <v>6984.39</v>
+        <v>6569.78</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>216784.1</v>
+        <v>274647.4</v>
       </c>
       <c r="E142" t="n">
         <v>2</v>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX long (risk 3,520); US_Dollar_Index_Futures short (risk 3,465)</t>
+          <t>Silver_Futures_COMEX long (risk 3,304); US_Dollar_Index_Futures short (risk 3,265)</t>
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
@@ -4415,13 +4415,13 @@
         <v>46174</v>
       </c>
       <c r="B143" s="5" t="n">
-        <v>223768.49</v>
+        <v>281217.18</v>
       </c>
       <c r="C143" s="5" t="n">
-        <v>6984.39</v>
+        <v>6569.78</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>216784.1</v>
+        <v>274647.4</v>
       </c>
       <c r="E143" t="n">
         <v>2</v>
@@ -4439,13 +4439,13 @@
         <v>46175</v>
       </c>
       <c r="B144" s="5" t="n">
-        <v>223768.49</v>
+        <v>281217.18</v>
       </c>
       <c r="C144" s="5" t="n">
-        <v>6984.39</v>
+        <v>6569.78</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>216784.1</v>
+        <v>274647.4</v>
       </c>
       <c r="E144" t="n">
         <v>2</v>
@@ -4463,13 +4463,13 @@
         <v>46176</v>
       </c>
       <c r="B145" s="5" t="n">
-        <v>220249.63</v>
+        <v>277900.48</v>
       </c>
       <c r="C145" s="5" t="n">
-        <v>3519.88</v>
+        <v>3304.3</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>216729.76</v>
+        <v>274596.18</v>
       </c>
       <c r="E145" t="n">
         <v>1</v>
@@ -4482,7 +4482,7 @@
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures stop (-3,519)</t>
+          <t>US_Dollar_Index_Futures stop (-3,317)</t>
         </is>
       </c>
     </row>
@@ -4491,13 +4491,13 @@
         <v>46177</v>
       </c>
       <c r="B146" s="5" t="n">
-        <v>220249.63</v>
+        <v>277900.48</v>
       </c>
       <c r="C146" s="5" t="n">
-        <v>3519.88</v>
+        <v>3304.3</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>216729.76</v>
+        <v>274596.18</v>
       </c>
       <c r="E146" t="n">
         <v>1</v>
@@ -4515,13 +4515,13 @@
         <v>46178</v>
       </c>
       <c r="B147" s="5" t="n">
-        <v>216722.12</v>
+        <v>274589.02</v>
       </c>
       <c r="C147" s="5" t="n">
-        <v>3409.16</v>
+        <v>3226.51</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>213312.97</v>
+        <v>271362.51</v>
       </c>
       <c r="E147" t="n">
         <v>1</v>
@@ -4533,12 +4533,12 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini short (risk 3,409)</t>
+          <t>Dow_Futures_E_mini short (risk 3,227)</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX stop (-3,528)</t>
+          <t>Silver_Futures_COMEX stop (-3,311)</t>
         </is>
       </c>
     </row>
@@ -4547,13 +4547,13 @@
         <v>46181</v>
       </c>
       <c r="B148" s="5" t="n">
-        <v>225180.7</v>
+        <v>303384.07</v>
       </c>
       <c r="C148" s="5" t="n">
-        <v>6658.05</v>
+        <v>6339.55</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>218522.65</v>
+        <v>297044.51</v>
       </c>
       <c r="E148" t="n">
         <v>2</v>
@@ -4565,12 +4565,12 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX long (risk 3,355); US_Dollar_Index_Futures short (risk 3,303)</t>
+          <t>Gold_Futures_COMEX long (risk 3,189); US_Dollar_Index_Futures short (risk 3,151)</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini target_r (+8,459)</t>
+          <t>Dow_Futures_E_mini target_r (+28,795)</t>
         </is>
       </c>
     </row>
@@ -4579,13 +4579,13 @@
         <v>46182</v>
       </c>
       <c r="B149" s="5" t="n">
-        <v>230008.13</v>
+        <v>308002.91</v>
       </c>
       <c r="C149" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D149" s="5" t="n">
-        <v>230008.13</v>
+        <v>308002.91</v>
       </c>
       <c r="E149" t="n">
         <v>0</v>
@@ -4594,7 +4594,7 @@
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX stop (-3,380); US_Dollar_Index_Futures target_r (+8,208)</t>
+          <t>Gold_Futures_COMEX stop (-3,212); US_Dollar_Index_Futures target_r (+7,831)</t>
         </is>
       </c>
     </row>
@@ -4603,13 +4603,13 @@
         <v>46183</v>
       </c>
       <c r="B150" s="5" t="n">
-        <v>230008.13</v>
+        <v>308002.91</v>
       </c>
       <c r="C150" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>230008.13</v>
+        <v>308002.91</v>
       </c>
       <c r="E150" t="n">
         <v>0</v>
@@ -4623,13 +4623,13 @@
         <v>46184</v>
       </c>
       <c r="B151" s="5" t="n">
-        <v>230008.13</v>
+        <v>308002.91</v>
       </c>
       <c r="C151" s="5" t="n">
-        <v>7179.14</v>
+        <v>7195.54</v>
       </c>
       <c r="D151" s="5" t="n">
-        <v>222828.99</v>
+        <v>300807.37</v>
       </c>
       <c r="E151" t="n">
         <v>2</v>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX long (risk 3,618); US_Dollar_Index_Futures short (risk 3,561)</t>
+          <t>Gold_Futures_COMEX long (risk 3,619); US_Dollar_Index_Futures short (risk 3,577)</t>
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
@@ -4651,13 +4651,13 @@
         <v>46185</v>
       </c>
       <c r="B152" s="5" t="n">
-        <v>247914.78</v>
+        <v>325950.44</v>
       </c>
       <c r="C152" s="5" t="n">
-        <v>3505.1</v>
+        <v>3534.49</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>244409.68</v>
+        <v>322415.95</v>
       </c>
       <c r="E152" t="n">
         <v>1</v>
@@ -4669,12 +4669,12 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures long (risk 3,505)</t>
+          <t>Corn_CBOT_Futures long (risk 3,534)</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX target_r (+9,032); US_Dollar_Index_Futures target_r (+8,874)</t>
+          <t>Gold_Futures_COMEX target_r (+9,035); US_Dollar_Index_Futures target_r (+8,913)</t>
         </is>
       </c>
     </row>
@@ -4683,13 +4683,13 @@
         <v>46188</v>
       </c>
       <c r="B153" s="5" t="n">
-        <v>243890.41</v>
+        <v>321892.32</v>
       </c>
       <c r="C153" s="5" t="n">
-        <v>3844.56</v>
+        <v>3788.39</v>
       </c>
       <c r="D153" s="5" t="n">
-        <v>240045.85</v>
+        <v>318103.94</v>
       </c>
       <c r="E153" t="n">
         <v>1</v>
@@ -4701,12 +4701,12 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT long (risk 3,845)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT long (risk 3,788)</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures stop (-4,024)</t>
+          <t>Corn_CBOT_Futures stop (-4,058)</t>
         </is>
       </c>
     </row>
@@ -4715,13 +4715,13 @@
         <v>46189</v>
       </c>
       <c r="B154" s="5" t="n">
-        <v>253385.32</v>
+        <v>331248.49</v>
       </c>
       <c r="C154" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>253385.32</v>
+        <v>331248.49</v>
       </c>
       <c r="E154" t="n">
         <v>0</v>
@@ -4730,7 +4730,7 @@
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT target_r (+9,495)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT target_r (+9,356)</t>
         </is>
       </c>
     </row>
@@ -4739,13 +4739,13 @@
         <v>46190</v>
       </c>
       <c r="B155" s="5" t="n">
-        <v>253385.32</v>
+        <v>331248.49</v>
       </c>
       <c r="C155" s="5" t="n">
-        <v>3985.75</v>
+        <v>3892.17</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>249399.57</v>
+        <v>327356.32</v>
       </c>
       <c r="E155" t="n">
         <v>1</v>
@@ -4757,7 +4757,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures short (risk 3,986)</t>
+          <t>US_Dollar_Index_Futures short (risk 3,892)</t>
         </is>
       </c>
       <c r="H155" t="inlineStr"/>
@@ -4767,13 +4767,13 @@
         <v>46191</v>
       </c>
       <c r="B156" s="5" t="n">
-        <v>249345.52</v>
+        <v>327303.55</v>
       </c>
       <c r="C156" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>249345.52</v>
+        <v>327303.55</v>
       </c>
       <c r="E156" t="n">
         <v>0</v>
@@ -4782,7 +4782,7 @@
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures stop (-4,040)</t>
+          <t>US_Dollar_Index_Futures stop (-3,945)</t>
         </is>
       </c>
     </row>
@@ -4791,13 +4791,13 @@
         <v>46192</v>
       </c>
       <c r="B157" s="5" t="n">
-        <v>249345.52</v>
+        <v>327303.55</v>
       </c>
       <c r="C157" s="5" t="n">
-        <v>3922.21</v>
+        <v>3845.82</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>245423.32</v>
+        <v>323457.73</v>
       </c>
       <c r="E157" t="n">
         <v>1</v>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures short (risk 3,922)</t>
+          <t>US_Dollar_Index_Futures short (risk 3,846)</t>
         </is>
       </c>
       <c r="H157" t="inlineStr"/>
@@ -4819,13 +4819,13 @@
         <v>46195</v>
       </c>
       <c r="B158" s="5" t="n">
-        <v>249345.52</v>
+        <v>327303.55</v>
       </c>
       <c r="C158" s="5" t="n">
-        <v>3922.21</v>
+        <v>3845.82</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>245423.32</v>
+        <v>323457.73</v>
       </c>
       <c r="E158" t="n">
         <v>1</v>
@@ -4843,13 +4843,13 @@
         <v>46196</v>
       </c>
       <c r="B159" s="5" t="n">
-        <v>245369.22</v>
+        <v>323404.69</v>
       </c>
       <c r="C159" s="5" t="n">
-        <v>3860.51</v>
+        <v>3800.63</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>241508.71</v>
+        <v>319604.06</v>
       </c>
       <c r="E159" t="n">
         <v>1</v>
@@ -4861,12 +4861,12 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures long (risk 3,861)</t>
+          <t>NY_Platinum_Futures long (risk 3,801)</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures stop (-3,976)</t>
+          <t>US_Dollar_Index_Futures stop (-3,899)</t>
         </is>
       </c>
     </row>
@@ -4875,13 +4875,13 @@
         <v>46197</v>
       </c>
       <c r="B160" s="5" t="n">
-        <v>241433.38</v>
+        <v>319529.9</v>
       </c>
       <c r="C160" s="5" t="n">
-        <v>3798.93</v>
+        <v>3755.35</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>237634.45</v>
+        <v>315774.55</v>
       </c>
       <c r="E160" t="n">
         <v>1</v>
@@ -4893,12 +4893,12 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>EURO_Futures long (risk 3,799)</t>
+          <t>EURO_Futures long (risk 3,755)</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures stop (-3,936)</t>
+          <t>NY_Platinum_Futures stop (-3,875)</t>
         </is>
       </c>
     </row>
@@ -4907,13 +4907,13 @@
         <v>46198</v>
       </c>
       <c r="B161" s="5" t="n">
-        <v>241433.38</v>
+        <v>319529.9</v>
       </c>
       <c r="C161" s="5" t="n">
-        <v>18401.79</v>
+        <v>18337.21</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>223031.6</v>
+        <v>301192.68</v>
       </c>
       <c r="E161" t="n">
         <v>5</v>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures short (risk 3,738); NY_Palladium_Futures long (risk 3,679); NY_Platinum_Futures long (risk 3,621); US_Dollar_Index_Futures short (risk 3,564)</t>
+          <t>NY_Natural_Gas_Futures short (risk 3,710); NY_Palladium_Futures long (risk 3,667); NY_Platinum_Futures long (risk 3,624); US_Dollar_Index_Futures short (risk 3,581)</t>
         </is>
       </c>
       <c r="H161" t="inlineStr"/>
@@ -4935,13 +4935,13 @@
         <v>46199</v>
       </c>
       <c r="B162" s="5" t="n">
-        <v>264810.11</v>
+        <v>342838.66</v>
       </c>
       <c r="C162" s="5" t="n">
-        <v>3621.32</v>
+        <v>3623.67</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>261188.79</v>
+        <v>339214.99</v>
       </c>
       <c r="E162" t="n">
         <v>1</v>
@@ -4954,7 +4954,7 @@
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr">
         <is>
-          <t>EURO_Futures target_r (+9,470); NY_Natural_Gas_Futures stop (-4,043); NY_Palladium_Futures target_r (+9,101); US_Dollar_Index_Futures target_r (+8,849)</t>
+          <t>EURO_Futures target_r (+9,361); NY_Natural_Gas_Futures stop (-4,013); NY_Palladium_Futures target_r (+9,070); US_Dollar_Index_Futures target_r (+8,890)</t>
         </is>
       </c>
     </row>
@@ -4963,13 +4963,13 @@
         <v>46202</v>
       </c>
       <c r="B163" s="5" t="n">
-        <v>264810.11</v>
+        <v>342838.66</v>
       </c>
       <c r="C163" s="5" t="n">
-        <v>3621.32</v>
+        <v>3623.67</v>
       </c>
       <c r="D163" s="5" t="n">
-        <v>261188.79</v>
+        <v>339214.99</v>
       </c>
       <c r="E163" t="n">
         <v>1</v>
@@ -4987,13 +4987,13 @@
         <v>46203</v>
       </c>
       <c r="B164" s="5" t="n">
-        <v>264810.11</v>
+        <v>342838.66</v>
       </c>
       <c r="C164" s="5" t="n">
-        <v>15753.95</v>
+        <v>15441.05</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>249056.15</v>
+        <v>327397.61</v>
       </c>
       <c r="E164" t="n">
         <v>4</v>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT long (risk 4,108); German_Long_Bund short (risk 4,044); Gold_Futures_COMEX long (risk 3,980)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT long (risk 3,986); German_Long_Bund short (risk 3,939); Gold_Futures_COMEX long (risk 3,893)</t>
         </is>
       </c>
       <c r="H164" t="inlineStr"/>
@@ -5015,13 +5015,13 @@
         <v>46204</v>
       </c>
       <c r="B165" s="5" t="n">
-        <v>290897.86</v>
+        <v>368151.61</v>
       </c>
       <c r="C165" s="5" t="n">
-        <v>7773.68</v>
+        <v>7648.64</v>
       </c>
       <c r="D165" s="5" t="n">
-        <v>283124.17</v>
+        <v>360502.97</v>
       </c>
       <c r="E165" t="n">
         <v>2</v>
@@ -5033,12 +5033,12 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini short (risk 3,918); Sugar_World_CSCE_Futures short (risk 3,856)</t>
+          <t>Dow_Futures_E_mini short (risk 3,847); Sugar_World_CSCE_Futures short (risk 3,802)</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT target_r (+10,071); German_Long_Bund target_r (+9,758); Gold_Futures_COMEX target_r (+9,923); NY_Platinum_Futures stop (-3,664)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT target_r (+9,770); German_Long_Bund target_r (+9,505); Gold_Futures_COMEX target_r (+9,705); NY_Platinum_Futures stop (-3,666)</t>
         </is>
       </c>
     </row>
@@ -5047,13 +5047,13 @@
         <v>46205</v>
       </c>
       <c r="B166" s="5" t="n">
-        <v>286938.08</v>
+        <v>364263.33</v>
       </c>
       <c r="C166" s="5" t="n">
-        <v>3856.03</v>
+        <v>3801.72</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>283082.05</v>
+        <v>360461.61</v>
       </c>
       <c r="E166" t="n">
         <v>1</v>
@@ -5066,7 +5066,7 @@
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini stop (-3,960)</t>
+          <t>Dow_Futures_E_mini stop (-3,888)</t>
         </is>
       </c>
     </row>
@@ -5075,13 +5075,13 @@
         <v>46206</v>
       </c>
       <c r="B167" s="5" t="n">
-        <v>286938.08</v>
+        <v>364263.33</v>
       </c>
       <c r="C167" s="5" t="n">
-        <v>3856.03</v>
+        <v>3801.72</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>283082.05</v>
+        <v>360461.61</v>
       </c>
       <c r="E167" t="n">
         <v>1</v>
@@ -5099,13 +5099,13 @@
         <v>46210</v>
       </c>
       <c r="B168" s="5" t="n">
-        <v>282488.81</v>
+        <v>359876.73</v>
       </c>
       <c r="C168" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D168" s="5" t="n">
-        <v>282488.81</v>
+        <v>359876.73</v>
       </c>
       <c r="E168" t="n">
         <v>0</v>
@@ -5114,7 +5114,7 @@
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Sugar_World_CSCE_Futures stop (-4,449)</t>
+          <t>Sugar_World_CSCE_Futures stop (-4,387)</t>
         </is>
       </c>
     </row>
@@ -5123,13 +5123,13 @@
         <v>46211</v>
       </c>
       <c r="B169" s="5" t="n">
-        <v>282488.81</v>
+        <v>359876.73</v>
       </c>
       <c r="C169" s="5" t="n">
-        <v>8817.200000000001</v>
+        <v>8407.42</v>
       </c>
       <c r="D169" s="5" t="n">
-        <v>273671.61</v>
+        <v>351469.31</v>
       </c>
       <c r="E169" t="n">
         <v>2</v>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME long (risk 4,444); NY_Natural_Gas_Futures short (risk 4,374)</t>
+          <t>Live_Cattle_Futures_CME long (risk 4,229); NY_Natural_Gas_Futures short (risk 4,179)</t>
         </is>
       </c>
       <c r="H169" t="inlineStr"/>
@@ -5151,13 +5151,13 @@
         <v>46212</v>
       </c>
       <c r="B170" s="5" t="n">
-        <v>304254.5</v>
+        <v>384657.99</v>
       </c>
       <c r="C170" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D170" s="5" t="n">
-        <v>304254.5</v>
+        <v>384657.99</v>
       </c>
       <c r="E170" t="n">
         <v>0</v>
@@ -5166,7 +5166,7 @@
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME target_r (+11,003); NY_Natural_Gas_Futures target_r (+10,763)</t>
+          <t>Live_Cattle_Futures_CME target_r (+14,498); NY_Natural_Gas_Futures target_r (+10,283)</t>
         </is>
       </c>
     </row>
@@ -5175,13 +5175,13 @@
         <v>46213</v>
       </c>
       <c r="B171" s="5" t="n">
-        <v>304254.5</v>
+        <v>384657.99</v>
       </c>
       <c r="C171" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D171" s="5" t="n">
-        <v>304254.5</v>
+        <v>384657.99</v>
       </c>
       <c r="E171" t="n">
         <v>0</v>
@@ -5195,13 +5195,13 @@
         <v>46216</v>
       </c>
       <c r="B172" s="5" t="n">
-        <v>304254.5</v>
+        <v>384657.99</v>
       </c>
       <c r="C172" s="5" t="n">
-        <v>4785.92</v>
+        <v>4519.73</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>299468.58</v>
+        <v>380138.25</v>
       </c>
       <c r="E172" t="n">
         <v>1</v>
@@ -5213,7 +5213,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 4,786)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 4,520)</t>
         </is>
       </c>
       <c r="H172" t="inlineStr"/>
@@ -5223,13 +5223,13 @@
         <v>46217</v>
       </c>
       <c r="B173" s="5" t="n">
-        <v>304254.5</v>
+        <v>384657.99</v>
       </c>
       <c r="C173" s="5" t="n">
-        <v>4785.92</v>
+        <v>4519.73</v>
       </c>
       <c r="D173" s="5" t="n">
-        <v>299468.58</v>
+        <v>380138.25</v>
       </c>
       <c r="E173" t="n">
         <v>1</v>
@@ -5247,13 +5247,13 @@
         <v>46218</v>
       </c>
       <c r="B174" s="5" t="n">
-        <v>299232.24</v>
+        <v>379915.06</v>
       </c>
       <c r="C174" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D174" s="5" t="n">
-        <v>299232.24</v>
+        <v>379915.06</v>
       </c>
       <c r="E174" t="n">
         <v>0</v>
@@ -5262,7 +5262,7 @@
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT stop (-5,022)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT stop (-4,743)</t>
         </is>
       </c>
     </row>
@@ -5271,13 +5271,13 @@
         <v>46219</v>
       </c>
       <c r="B175" s="5" t="n">
-        <v>299232.24</v>
+        <v>379915.06</v>
       </c>
       <c r="C175" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D175" s="5" t="n">
-        <v>299232.24</v>
+        <v>379915.06</v>
       </c>
       <c r="E175" t="n">
         <v>0</v>
@@ -5291,13 +5291,13 @@
         <v>46220</v>
       </c>
       <c r="B176" s="5" t="n">
-        <v>299232.24</v>
+        <v>379915.06</v>
       </c>
       <c r="C176" s="5" t="n">
-        <v>4706.92</v>
+        <v>4464</v>
       </c>
       <c r="D176" s="5" t="n">
-        <v>294525.31</v>
+        <v>375451.06</v>
       </c>
       <c r="E176" t="n">
         <v>1</v>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX long (risk 4,707)</t>
+          <t>Gold_Futures_COMEX long (risk 4,464)</t>
         </is>
       </c>
       <c r="H176" t="inlineStr"/>
@@ -5319,13 +5319,13 @@
         <v>46223</v>
       </c>
       <c r="B177" s="5" t="n">
-        <v>310954.93</v>
+        <v>391032.75</v>
       </c>
       <c r="C177" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D177" s="5" t="n">
-        <v>310954.93</v>
+        <v>391032.75</v>
       </c>
       <c r="E177" t="n">
         <v>0</v>
@@ -5334,7 +5334,7 @@
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX target_r (+11,723)</t>
+          <t>Gold_Futures_COMEX target_r (+11,118)</t>
         </is>
       </c>
     </row>
@@ -5343,13 +5343,13 @@
         <v>46224</v>
       </c>
       <c r="B178" s="5" t="n">
-        <v>310954.93</v>
+        <v>391032.75</v>
       </c>
       <c r="C178" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D178" s="5" t="n">
-        <v>310954.93</v>
+        <v>391032.75</v>
       </c>
       <c r="E178" t="n">
         <v>0</v>
@@ -5363,13 +5363,13 @@
         <v>46225</v>
       </c>
       <c r="B179" s="5" t="n">
-        <v>310954.93</v>
+        <v>391032.75</v>
       </c>
       <c r="C179" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D179" s="5" t="n">
-        <v>310954.93</v>
+        <v>391032.75</v>
       </c>
       <c r="E179" t="n">
         <v>0</v>
@@ -5383,13 +5383,13 @@
         <v>46226</v>
       </c>
       <c r="B180" s="5" t="n">
-        <v>310954.93</v>
+        <v>391032.75</v>
       </c>
       <c r="C180" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D180" s="5" t="n">
-        <v>310954.93</v>
+        <v>391032.75</v>
       </c>
       <c r="E180" t="n">
         <v>0</v>
@@ -5403,13 +5403,13 @@
         <v>46227</v>
       </c>
       <c r="B181" s="5" t="n">
-        <v>310742.28</v>
+        <v>390832.54</v>
       </c>
       <c r="C181" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D181" s="5" t="n">
-        <v>310742.28</v>
+        <v>390832.54</v>
       </c>
       <c r="E181" t="n">
         <v>0</v>
@@ -5417,7 +5417,7 @@
       <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 4,891); Corn_CBOT_Futures short (risk 4,814)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 4,595); Corn_CBOT_Futures short (risk 4,541)</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -5548,25 +5548,25 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>2.5</v>
+        <v>8.102</v>
       </c>
       <c r="G2" t="n">
         <v>0.012</v>
       </c>
       <c r="H2" t="n">
-        <v>2.488</v>
+        <v>8.09</v>
       </c>
       <c r="I2" s="5" t="n">
         <v>100000</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>1573</v>
+        <v>1175</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>3913.55</v>
+        <v>9506.16</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>103913.55</v>
+        <v>109506.16</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -5608,16 +5608,16 @@
         <v>2.493</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>103913.55</v>
+        <v>109506.16</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>1634.56</v>
+        <v>1286.7</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>4074.56</v>
+        <v>3207.42</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>107988.1</v>
+        <v>112713.58</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -5659,16 +5659,16 @@
         <v>-1.008</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>107988.1</v>
+        <v>112713.58</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>1698.65</v>
+        <v>1324.38</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>-1712.08</v>
+        <v>-1334.85</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>106276.02</v>
+        <v>111378.73</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -5701,25 +5701,25 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5</v>
+        <v>5.238</v>
       </c>
       <c r="G5" t="n">
         <v>0.002</v>
       </c>
       <c r="H5" t="n">
-        <v>2.498</v>
+        <v>5.236</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>106289.45</v>
+        <v>111389.2</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>1671.93</v>
+        <v>1308.82</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>4175.79</v>
+        <v>6852.71</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>110451.81</v>
+        <v>118231.44</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -5752,29 +5752,29 @@
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>-1</v>
+        <v>3.319</v>
       </c>
       <c r="G6" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.043</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.085</v>
+        <v>3.277</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>110451.81</v>
+        <v>118231.44</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>1737.41</v>
-      </c>
-      <c r="K6" s="7" t="n">
-        <v>-1885.27</v>
+        <v>1389.22</v>
+      </c>
+      <c r="K6" s="6" t="n">
+        <v>4551.84</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>108566.54</v>
+        <v>122783.28</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>unknown_pl</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
@@ -5812,16 +5812,16 @@
         <v>2.494</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>108566.54</v>
+        <v>122783.28</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>1707.75</v>
+        <v>1442.7</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>4259.06</v>
+        <v>3598.04</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>112825.6</v>
+        <v>126381.33</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -5854,29 +5854,29 @@
         <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>-1</v>
+        <v>-3.048</v>
       </c>
       <c r="G8" t="n">
         <v>0.006</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.006</v>
+        <v>-3.054</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>112825.6</v>
+        <v>126381.33</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>1774.75</v>
+        <v>1484.98</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>-1785.79</v>
+        <v>-4535.76</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>111039.81</v>
+        <v>121845.57</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>unknown_pl</t>
+          <t>stop</t>
         </is>
       </c>
     </row>
@@ -5905,25 +5905,25 @@
         <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>-1</v>
+        <v>-1.056</v>
       </c>
       <c r="G9" t="n">
         <v>0.222</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.222</v>
+        <v>-1.278</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>111050.85</v>
+        <v>124896.34</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>1746.83</v>
+        <v>1467.53</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>-2135.01</v>
+        <v>-1875.25</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>108904.8</v>
+        <v>119970.32</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -5965,16 +5965,16 @@
         <v>-1.069</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>109292.98</v>
+        <v>120378.04</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>1719.18</v>
+        <v>1414.44</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>-1837.74</v>
+        <v>-1511.99</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>107067.06</v>
+        <v>118458.33</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -6016,16 +6016,16 @@
         <v>-1.06</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>107573.81</v>
+        <v>118963.6</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>1692.14</v>
+        <v>1397.82</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>-1793.16</v>
+        <v>-1481.27</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>105273.9</v>
+        <v>116977.06</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -6058,25 +6058,25 @@
         <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>2.5</v>
+        <v>3.362</v>
       </c>
       <c r="G12" t="n">
         <v>0.002</v>
       </c>
       <c r="H12" t="n">
-        <v>2.498</v>
+        <v>3.36</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>105881.67</v>
+        <v>117565.77</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>1665.52</v>
+        <v>1381.4</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>4160.61</v>
+        <v>4641.2</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>109434.51</v>
+        <v>121618.26</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -6118,16 +6118,16 @@
         <v>-1.026</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>103827.97</v>
+        <v>115776.66</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>1633.21</v>
+        <v>1360.38</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>-1676.19</v>
+        <v>-1396.18</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>111067.7</v>
+        <v>123850.52</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -6169,16 +6169,16 @@
         <v>-1.002</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>107801.29</v>
+        <v>120257.89</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>1695.71</v>
+        <v>1413.03</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>-1699.3</v>
+        <v>-1416.02</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>107735.2</v>
+        <v>120202.24</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -6220,16 +6220,16 @@
         <v>-1.004</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>106105.58</v>
+        <v>118844.86</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>1669.04</v>
+        <v>1396.43</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>-1676.05</v>
+        <v>-1402.29</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>106059.16</v>
+        <v>118799.95</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -6271,16 +6271,16 @@
         <v>2.499</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>104436.54</v>
+        <v>117448.43</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>1642.79</v>
+        <v>1380.02</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>4105.87</v>
+        <v>3449.13</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>110165.03</v>
+        <v>122249.08</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -6322,16 +6322,16 @@
         <v>-1.005</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>102783.16</v>
+        <v>116059.56</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>1616.78</v>
+        <v>1363.7</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>-1624.26</v>
+        <v>-1370.01</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>108540.77</v>
+        <v>120879.07</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -6364,25 +6364,25 @@
         <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>2.5</v>
+        <v>3.111</v>
       </c>
       <c r="G18" t="n">
         <v>0.001</v>
       </c>
       <c r="H18" t="n">
-        <v>2.499</v>
+        <v>3.11</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>106915.03</v>
+        <v>119525</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>1681.77</v>
+        <v>1404.42</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>4203.12</v>
+        <v>4367.63</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>112743.89</v>
+        <v>125246.7</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -6424,16 +6424,16 @@
         <v>2.499</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>111110.68</v>
+        <v>123886.32</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>1747.77</v>
+        <v>1455.66</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>4367.49</v>
+        <v>3637.55</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>115435.19</v>
+        <v>127488.07</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -6475,16 +6475,16 @@
         <v>-1.009</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>109362.91</v>
+        <v>122430.66</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>1720.28</v>
+        <v>1438.56</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>-1735.78</v>
+        <v>-1451.52</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>113699.41</v>
+        <v>126036.55</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -6526,16 +6526,16 @@
         <v>-1.138</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>107599.65</v>
+        <v>120956.3</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>1692.54</v>
+        <v>1421.24</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>-1926</v>
+        <v>-1617.27</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>111773.42</v>
+        <v>124419.28</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -6577,16 +6577,16 @@
         <v>2.499</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>112006.87</v>
+        <v>124615.32</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>1761.87</v>
+        <v>1464.23</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>4403.76</v>
+        <v>3659.82</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>116177.18</v>
+        <v>128079.1</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -6628,16 +6628,16 @@
         <v>-1.004</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>110011.55</v>
+        <v>122955.05</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>1730.48</v>
+        <v>1444.72</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>-1737.85</v>
+        <v>-1450.87</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>114439.33</v>
+        <v>126628.24</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -6679,16 +6679,16 @@
         <v>2.357</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>114439.33</v>
+        <v>126628.24</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>1800.13</v>
+        <v>1487.88</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>4243.17</v>
+        <v>3507.15</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>127197.46</v>
+        <v>137272.43</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -6721,25 +6721,25 @@
         <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>2.5</v>
+        <v>2.538</v>
       </c>
       <c r="G25" t="n">
         <v>0.051</v>
       </c>
       <c r="H25" t="n">
-        <v>2.449</v>
+        <v>2.487</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>112639.2</v>
+        <v>125140.35</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>1771.81</v>
+        <v>1470.4</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>4338.67</v>
+        <v>3657.2</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>118778.01</v>
+        <v>130285.44</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -6781,16 +6781,16 @@
         <v>2.395</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>110867.39</v>
+        <v>123669.95</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>1743.94</v>
+        <v>1453.12</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>4176.29</v>
+        <v>3479.84</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>122954.29</v>
+        <v>133765.28</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -6832,16 +6832,16 @@
         <v>2.497</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>127197.46</v>
+        <v>137272.43</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>2000.82</v>
+        <v>1612.95</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>4996.78</v>
+        <v>4028.14</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>132194.24</v>
+        <v>141300.57</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -6883,16 +6883,16 @@
         <v>-1.174</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>132194.24</v>
+        <v>141300.57</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>2079.42</v>
+        <v>1660.28</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>-2441.05</v>
+        <v>-1949.03</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>129753.19</v>
+        <v>139351.55</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -6925,25 +6925,25 @@
         <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>-1</v>
+        <v>-1.074</v>
       </c>
       <c r="G29" t="n">
         <v>0.002</v>
       </c>
       <c r="H29" t="n">
-        <v>-1.002</v>
+        <v>-1.075</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>130114.83</v>
+        <v>139640.29</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>2046.71</v>
+        <v>1640.77</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>-2050.17</v>
+        <v>-1764.31</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>127703.02</v>
+        <v>137587.23</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -6985,16 +6985,16 @@
         <v>-1.091</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>127706.48</v>
+        <v>137710.77</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>2008.82</v>
+        <v>1618.1</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>-2191.44</v>
+        <v>-1765.2</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>125511.57</v>
+        <v>135822.03</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -7036,16 +7036,16 @@
         <v>2.497</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>125511.57</v>
+        <v>135822.03</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>1974.3</v>
+        <v>1595.91</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>4929.79</v>
+        <v>3984.96</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>130441.36</v>
+        <v>139806.99</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -7078,25 +7078,25 @@
         <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>2.5</v>
+        <v>6.435</v>
       </c>
       <c r="G32" t="n">
         <v>0.015</v>
       </c>
       <c r="H32" t="n">
-        <v>2.485</v>
+        <v>6.42</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>130441.36</v>
+        <v>139806.99</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>2051.84</v>
+        <v>1642.73</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>5098.28</v>
+        <v>10546.07</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>135539.64</v>
+        <v>150353.06</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -7129,25 +7129,25 @@
         <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>2.5</v>
+        <v>2.547</v>
       </c>
       <c r="G33" t="n">
         <v>0.003</v>
       </c>
       <c r="H33" t="n">
-        <v>2.497</v>
+        <v>2.545</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>128389.52</v>
+        <v>138164.26</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>2019.57</v>
+        <v>1623.43</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>5042.93</v>
+        <v>4130.87</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>140582.57</v>
+        <v>154483.93</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -7180,25 +7180,25 @@
         <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>2.5</v>
+        <v>4.809</v>
       </c>
       <c r="G34" t="n">
         <v>0.007</v>
       </c>
       <c r="H34" t="n">
-        <v>2.493</v>
+        <v>4.802</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>133520.08</v>
+        <v>148729.63</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>2100.27</v>
+        <v>1747.57</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>5236.09</v>
+        <v>8391.940000000001</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>145818.66</v>
+        <v>162875.87</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -7231,25 +7231,25 @@
         <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>2.5</v>
+        <v>6.795</v>
       </c>
       <c r="G35" t="n">
         <v>0.026</v>
       </c>
       <c r="H35" t="n">
-        <v>2.474</v>
+        <v>6.769</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>145818.66</v>
+        <v>162875.87</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>2293.73</v>
+        <v>1913.79</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>5675.51</v>
+        <v>12954.95</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>151494.16</v>
+        <v>175830.82</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -7291,16 +7291,16 @@
         <v>-1.004</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>151494.16</v>
+        <v>175830.82</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>2383</v>
+        <v>2066.01</v>
       </c>
       <c r="K36" s="7" t="n">
-        <v>-2391.36</v>
+        <v>-2073.26</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>160305.05</v>
+        <v>183528.76</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -7342,16 +7342,16 @@
         <v>2.375</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>149111.16</v>
+        <v>173764.81</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>2345.52</v>
+        <v>2041.74</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>5570.61</v>
+        <v>4849.12</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>157064.77</v>
+        <v>180679.94</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -7393,16 +7393,16 @@
         <v>2.439</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>146765.64</v>
+        <v>171723.07</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>2308.62</v>
+        <v>2017.75</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>5631.64</v>
+        <v>4922.08</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>162696.41</v>
+        <v>185602.02</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -7444,16 +7444,16 @@
         <v>-1.008</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>144457.02</v>
+        <v>169705.32</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>2272.31</v>
+        <v>1994.04</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>-2289.62</v>
+        <v>-2009.23</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>160341.03</v>
+        <v>183515.03</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -7495,16 +7495,16 @@
         <v>0.9350000000000001</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>158041.1</v>
+        <v>181541.97</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>2485.99</v>
+        <v>2133.12</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>2325.6</v>
+        <v>1995.5</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>162630.65</v>
+        <v>185524.26</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -7537,25 +7537,25 @@
         <v>1</v>
       </c>
       <c r="F41" t="n">
-        <v>2.5</v>
+        <v>4.18</v>
       </c>
       <c r="G41" t="n">
         <v>0.033</v>
       </c>
       <c r="H41" t="n">
-        <v>2.467</v>
+        <v>4.148</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>160358.34</v>
+        <v>183530.22</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>2522.44</v>
+        <v>2156.48</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>6223.39</v>
+        <v>8944.030000000001</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>166564.42</v>
+        <v>192459.06</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -7588,25 +7588,25 @@
         <v>1</v>
       </c>
       <c r="F42" t="n">
-        <v>2.5</v>
+        <v>4.732</v>
       </c>
       <c r="G42" t="n">
         <v>0.004</v>
       </c>
       <c r="H42" t="n">
-        <v>2.496</v>
+        <v>4.728</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>166564.42</v>
+        <v>192459.06</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>2620.06</v>
+        <v>2261.39</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>6539.36</v>
+        <v>10692.74</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>173103.78</v>
+        <v>203151.8</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -7648,16 +7648,16 @@
         <v>2.499</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>163944.36</v>
+        <v>190197.66</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>2578.84</v>
+        <v>2234.82</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>6444.03</v>
+        <v>5584.38</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>179547.8</v>
+        <v>208736.18</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -7699,16 +7699,16 @@
         <v>2.478</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>170524.93</v>
+        <v>200916.97</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>2682.36</v>
+        <v>2360.77</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>6645.62</v>
+        <v>5848.89</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>186193.42</v>
+        <v>214585.06</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -7750,16 +7750,16 @@
         <v>-1.211</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>176865.45</v>
+        <v>206375.4</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>2782.09</v>
+        <v>2424.91</v>
       </c>
       <c r="K45" s="7" t="n">
-        <v>-3367.8</v>
+        <v>-2935.42</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>182825.62</v>
+        <v>211649.64</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -7801,16 +7801,16 @@
         <v>-1.108</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>183411.33</v>
+        <v>212160.15</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>2885.06</v>
+        <v>2492.88</v>
       </c>
       <c r="K46" s="7" t="n">
-        <v>-3196.96</v>
+        <v>-2762.38</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>197520.28</v>
+        <v>245059.99</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -7852,16 +7852,16 @@
         <v>2.484</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>180526.27</v>
+        <v>209667.27</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>2839.68</v>
+        <v>2463.59</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>7053.76</v>
+        <v>6119.56</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>189879.38</v>
+        <v>217769.2</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -7903,16 +7903,16 @@
         <v>2.492</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>177686.59</v>
+        <v>207203.68</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>2795.01</v>
+        <v>2434.64</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>6964.71</v>
+        <v>6066.73</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>194100.39</v>
+        <v>229839.29</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -7945,29 +7945,29 @@
         <v>1</v>
       </c>
       <c r="F49" t="n">
-        <v>-1</v>
+        <v>2.502</v>
       </c>
       <c r="G49" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>-1.001</v>
+        <v>2.501</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>174305.87</v>
+        <v>204258.53</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>2741.83</v>
-      </c>
-      <c r="K49" s="7" t="n">
-        <v>-2743.7</v>
+        <v>2400.04</v>
+      </c>
+      <c r="K49" s="6" t="n">
+        <v>6003.36</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>187135.69</v>
+        <v>223772.56</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>unknown_pl</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
@@ -7996,25 +7996,25 @@
         <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>2.5</v>
+        <v>7.455</v>
       </c>
       <c r="G50" t="n">
         <v>0.182</v>
       </c>
       <c r="H50" t="n">
-        <v>2.318</v>
+        <v>7.273</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>181457.48</v>
+        <v>210441.64</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>2854.33</v>
+        <v>2472.69</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>6616.85</v>
+        <v>17983.08</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>200717.24</v>
+        <v>247822.38</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
@@ -8056,16 +8056,16 @@
         <v>2.496</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>188361.01</v>
+        <v>224873.72</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>2962.92</v>
+        <v>2642.27</v>
       </c>
       <c r="K51" s="6" t="n">
-        <v>7396.62</v>
+        <v>6596.14</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>204916.9</v>
+        <v>251656.14</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -8107,16 +8107,16 @@
         <v>2.492</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>185398.09</v>
+        <v>222231.46</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>2916.31</v>
+        <v>2611.22</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>7266.97</v>
+        <v>6506.73</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>202903.39</v>
+        <v>259366.39</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -8149,29 +8149,29 @@
         <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>-1</v>
+        <v>2.532</v>
       </c>
       <c r="G53" t="n">
-        <v>0.026</v>
+        <v>0.013</v>
       </c>
       <c r="H53" t="n">
-        <v>-1.026</v>
+        <v>2.519</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>191641.05</v>
+        <v>239806.51</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>3014.51</v>
-      </c>
-      <c r="K53" s="7" t="n">
-        <v>-3091.81</v>
+        <v>2817.73</v>
+      </c>
+      <c r="K53" s="6" t="n">
+        <v>7098.64</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>201825.09</v>
+        <v>258754.78</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>unknown_pl</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
@@ -8209,16 +8209,16 @@
         <v>-1.014</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>188626.54</v>
+        <v>236988.78</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>2967.1</v>
+        <v>2784.62</v>
       </c>
       <c r="K54" s="7" t="n">
-        <v>-3007.88</v>
+        <v>-2822.89</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>198817.21</v>
+        <v>255931.88</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -8260,16 +8260,16 @@
         <v>-1.032</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>195941.69</v>
+        <v>253358.94</v>
       </c>
       <c r="J55" s="5" t="n">
-        <v>3082.16</v>
+        <v>2976.97</v>
       </c>
       <c r="K55" s="7" t="n">
-        <v>-3180.79</v>
+        <v>-3072.23</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>195636.42</v>
+        <v>252859.65</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
@@ -8311,16 +8311,16 @@
         <v>-1.002</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>192818.74</v>
+        <v>250343.7</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>3033.04</v>
+        <v>2941.54</v>
       </c>
       <c r="K56" s="7" t="n">
-        <v>-3039.36</v>
+        <v>-2947.67</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>199864.04</v>
+        <v>256418.72</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -8353,25 +8353,25 @@
         <v>1</v>
       </c>
       <c r="F57" t="n">
-        <v>2.5</v>
+        <v>3.123</v>
       </c>
       <c r="G57" t="n">
         <v>0.027</v>
       </c>
       <c r="H57" t="n">
-        <v>2.473</v>
+        <v>3.096</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>199864.04</v>
+        <v>256418.72</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>3143.86</v>
+        <v>3012.92</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>7773.52</v>
+        <v>9327.709999999999</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>207637.56</v>
+        <v>265746.43</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -8413,16 +8413,16 @@
         <v>2.49</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>207637.56</v>
+        <v>265746.43</v>
       </c>
       <c r="J58" s="5" t="n">
-        <v>3266.14</v>
+        <v>3122.52</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>8131.85</v>
+        <v>7774.28</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>223768.49</v>
+        <v>281217.18</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -8455,25 +8455,25 @@
         <v>1</v>
       </c>
       <c r="F59" t="n">
-        <v>2.5</v>
+        <v>2.506</v>
       </c>
       <c r="G59" t="n">
         <v>0.012</v>
       </c>
       <c r="H59" t="n">
-        <v>2.488</v>
+        <v>2.494</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>204371.42</v>
+        <v>262623.91</v>
       </c>
       <c r="J59" s="5" t="n">
-        <v>3214.76</v>
+        <v>3085.83</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>7999.09</v>
+        <v>7696.48</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>215636.64</v>
+        <v>273442.91</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -8515,16 +8515,16 @@
         <v>-1.002</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>223768.49</v>
+        <v>281217.18</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>3519.88</v>
+        <v>3304.3</v>
       </c>
       <c r="K60" s="7" t="n">
-        <v>-3527.51</v>
+        <v>-3311.47</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>216722.12</v>
+        <v>274589.02</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -8566,16 +8566,16 @@
         <v>-1.016</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>220248.61</v>
+        <v>277912.88</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>3464.51</v>
+        <v>3265.48</v>
       </c>
       <c r="K61" s="7" t="n">
-        <v>-3518.86</v>
+        <v>-3316.7</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>220249.63</v>
+        <v>277900.48</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
@@ -8608,25 +8608,25 @@
         <v>1</v>
       </c>
       <c r="F62" t="n">
-        <v>2.5</v>
+        <v>8.943</v>
       </c>
       <c r="G62" t="n">
         <v>0.019</v>
       </c>
       <c r="H62" t="n">
-        <v>2.481</v>
+        <v>8.925000000000001</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>216729.76</v>
+        <v>274596.18</v>
       </c>
       <c r="J62" s="5" t="n">
-        <v>3409.16</v>
+        <v>3226.51</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>8458.57</v>
+        <v>28795.05</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>225180.7</v>
+        <v>303384.07</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -8668,16 +8668,16 @@
         <v>-1.007</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>213312.97</v>
+        <v>271362.51</v>
       </c>
       <c r="J63" s="5" t="n">
-        <v>3355.41</v>
+        <v>3188.51</v>
       </c>
       <c r="K63" s="7" t="n">
-        <v>-3380.22</v>
+        <v>-3212.08</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>221800.48</v>
+        <v>300171.98</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -8719,16 +8719,16 @@
         <v>2.485</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>209957.55</v>
+        <v>268174</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>3302.63</v>
+        <v>3151.04</v>
       </c>
       <c r="K64" s="6" t="n">
-        <v>8207.65</v>
+        <v>7830.93</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>230008.13</v>
+        <v>308002.91</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
@@ -8770,16 +8770,16 @@
         <v>2.496</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>230008.13</v>
+        <v>308002.91</v>
       </c>
       <c r="J65" s="5" t="n">
-        <v>3618.03</v>
+        <v>3619.03</v>
       </c>
       <c r="K65" s="6" t="n">
-        <v>9032.35</v>
+        <v>9034.860000000001</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>239040.48</v>
+        <v>317037.77</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
@@ -8821,16 +8821,16 @@
         <v>2.492</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>226390.1</v>
+        <v>304383.88</v>
       </c>
       <c r="J66" s="5" t="n">
-        <v>3561.12</v>
+        <v>3576.51</v>
       </c>
       <c r="K66" s="6" t="n">
-        <v>8874.299999999999</v>
+        <v>8912.66</v>
       </c>
       <c r="L66" s="5" t="n">
-        <v>247914.78</v>
+        <v>325950.44</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
@@ -8872,16 +8872,16 @@
         <v>-1.148</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>222828.99</v>
+        <v>300807.37</v>
       </c>
       <c r="J67" s="5" t="n">
-        <v>3505.1</v>
+        <v>3534.49</v>
       </c>
       <c r="K67" s="7" t="n">
-        <v>-4024.37</v>
+        <v>-4058.11</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>243890.41</v>
+        <v>321892.32</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
@@ -8923,16 +8923,16 @@
         <v>2.47</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>244409.68</v>
+        <v>322415.95</v>
       </c>
       <c r="J68" s="5" t="n">
-        <v>3844.56</v>
+        <v>3788.39</v>
       </c>
       <c r="K68" s="6" t="n">
-        <v>9494.91</v>
+        <v>9356.17</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>253385.32</v>
+        <v>331248.49</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
@@ -8974,16 +8974,16 @@
         <v>-1.014</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>253385.32</v>
+        <v>331248.49</v>
       </c>
       <c r="J69" s="5" t="n">
-        <v>3985.75</v>
+        <v>3892.17</v>
       </c>
       <c r="K69" s="7" t="n">
-        <v>-4039.8</v>
+        <v>-3944.94</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>249345.52</v>
+        <v>327303.55</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
@@ -9025,16 +9025,16 @@
         <v>-1.014</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>249345.52</v>
+        <v>327303.55</v>
       </c>
       <c r="J70" s="5" t="n">
-        <v>3922.21</v>
+        <v>3845.82</v>
       </c>
       <c r="K70" s="7" t="n">
-        <v>-3976.3</v>
+        <v>-3898.86</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>245369.22</v>
+        <v>323404.69</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
@@ -9076,16 +9076,16 @@
         <v>-1.02</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>245423.32</v>
+        <v>323457.73</v>
       </c>
       <c r="J71" s="5" t="n">
-        <v>3860.51</v>
+        <v>3800.63</v>
       </c>
       <c r="K71" s="7" t="n">
-        <v>-3935.84</v>
+        <v>-3874.79</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>241433.38</v>
+        <v>319529.9</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
@@ -9127,16 +9127,16 @@
         <v>2.493</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>241508.71</v>
+        <v>319604.06</v>
       </c>
       <c r="J72" s="5" t="n">
-        <v>3798.93</v>
+        <v>3755.35</v>
       </c>
       <c r="K72" s="6" t="n">
-        <v>9469.799999999999</v>
+        <v>9361.16</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>250903.18</v>
+        <v>328891.06</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
@@ -9178,16 +9178,16 @@
         <v>-1.082</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>237634.45</v>
+        <v>315774.55</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>3737.99</v>
+        <v>3710.35</v>
       </c>
       <c r="K73" s="7" t="n">
-        <v>-4043.13</v>
+        <v>-4013.24</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>246860.05</v>
+        <v>324877.82</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -9229,16 +9229,16 @@
         <v>2.474</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>233896.46</v>
+        <v>312064.2</v>
       </c>
       <c r="J74" s="5" t="n">
-        <v>3679.19</v>
+        <v>3666.75</v>
       </c>
       <c r="K74" s="6" t="n">
-        <v>9101.16</v>
+        <v>9070.389999999999</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>255961.21</v>
+        <v>333948.21</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
@@ -9280,16 +9280,16 @@
         <v>-1.012</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>230217.27</v>
+        <v>308397.45</v>
       </c>
       <c r="J75" s="5" t="n">
-        <v>3621.32</v>
+        <v>3623.67</v>
       </c>
       <c r="K75" s="7" t="n">
-        <v>-3664.05</v>
+        <v>-3666.43</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>290897.86</v>
+        <v>368151.61</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
@@ -9331,16 +9331,16 @@
         <v>2.483</v>
       </c>
       <c r="I76" s="5" t="n">
-        <v>226595.95</v>
+        <v>304773.78</v>
       </c>
       <c r="J76" s="5" t="n">
-        <v>3564.35</v>
+        <v>3581.09</v>
       </c>
       <c r="K76" s="6" t="n">
-        <v>8848.9</v>
+        <v>8890.450000000001</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>264810.11</v>
+        <v>342838.66</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
@@ -9382,16 +9382,16 @@
         <v>2.451</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>261188.79</v>
+        <v>339214.99</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>4108.5</v>
+        <v>3985.78</v>
       </c>
       <c r="K77" s="6" t="n">
-        <v>10070.83</v>
+        <v>9770.01</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>274880.94</v>
+        <v>352608.67</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
@@ -9433,16 +9433,16 @@
         <v>2.413</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>257080.29</v>
+        <v>335229.22</v>
       </c>
       <c r="J78" s="5" t="n">
-        <v>4043.87</v>
+        <v>3938.94</v>
       </c>
       <c r="K78" s="6" t="n">
-        <v>9758.040000000001</v>
+        <v>9504.84</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>284638.98</v>
+        <v>362113.52</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -9484,16 +9484,16 @@
         <v>2.493</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>253036.42</v>
+        <v>331290.27</v>
       </c>
       <c r="J79" s="5" t="n">
-        <v>3980.26</v>
+        <v>3892.66</v>
       </c>
       <c r="K79" s="6" t="n">
-        <v>9922.92</v>
+        <v>9704.530000000001</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>294561.9</v>
+        <v>371818.04</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
@@ -9535,16 +9535,16 @@
         <v>-1.011</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>249056.15</v>
+        <v>327397.61</v>
       </c>
       <c r="J80" s="5" t="n">
-        <v>3917.65</v>
+        <v>3846.92</v>
       </c>
       <c r="K80" s="7" t="n">
-        <v>-3959.78</v>
+        <v>-3888.29</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>286938.08</v>
+        <v>364263.33</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -9586,16 +9586,16 @@
         <v>-1.154</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>245138.5</v>
+        <v>323550.69</v>
       </c>
       <c r="J81" s="5" t="n">
-        <v>3856.03</v>
+        <v>3801.72</v>
       </c>
       <c r="K81" s="7" t="n">
-        <v>-4449.26</v>
+        <v>-4386.6</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>282488.81</v>
+        <v>359876.73</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -9628,25 +9628,25 @@
         <v>1</v>
       </c>
       <c r="F82" t="n">
-        <v>2.5</v>
+        <v>3.452</v>
       </c>
       <c r="G82" t="n">
         <v>0.024</v>
       </c>
       <c r="H82" t="n">
-        <v>2.476</v>
+        <v>3.429</v>
       </c>
       <c r="I82" s="5" t="n">
-        <v>282488.81</v>
+        <v>359876.73</v>
       </c>
       <c r="J82" s="5" t="n">
-        <v>4443.55</v>
+        <v>4228.55</v>
       </c>
       <c r="K82" s="6" t="n">
-        <v>11003.07</v>
+        <v>14497.97</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>293491.89</v>
+        <v>374374.7</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
@@ -9688,16 +9688,16 @@
         <v>2.461</v>
       </c>
       <c r="I83" s="5" t="n">
-        <v>278045.26</v>
+        <v>355648.17</v>
       </c>
       <c r="J83" s="5" t="n">
-        <v>4373.65</v>
+        <v>4178.87</v>
       </c>
       <c r="K83" s="6" t="n">
-        <v>10762.61</v>
+        <v>10283.29</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>304254.5</v>
+        <v>384657.99</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
@@ -9739,16 +9739,16 @@
         <v>-1.049</v>
       </c>
       <c r="I84" s="5" t="n">
-        <v>304254.5</v>
+        <v>384657.99</v>
       </c>
       <c r="J84" s="5" t="n">
-        <v>4785.92</v>
+        <v>4519.73</v>
       </c>
       <c r="K84" s="7" t="n">
-        <v>-5022.27</v>
+        <v>-4742.93</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>299232.24</v>
+        <v>379915.06</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
@@ -9790,16 +9790,16 @@
         <v>2.491</v>
       </c>
       <c r="I85" s="5" t="n">
-        <v>299232.24</v>
+        <v>379915.06</v>
       </c>
       <c r="J85" s="5" t="n">
-        <v>4706.92</v>
+        <v>4464</v>
       </c>
       <c r="K85" s="6" t="n">
-        <v>11722.69</v>
+        <v>11117.69</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>310954.93</v>
+        <v>391032.75</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
@@ -9833,16 +9833,16 @@
         <v>-0.019</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>310954.93</v>
+        <v>391032.75</v>
       </c>
       <c r="J86" s="5" t="n">
-        <v>4891.32</v>
+        <v>4594.63</v>
       </c>
       <c r="K86" s="7" t="n">
-        <v>-92.29000000000001</v>
+        <v>-86.69</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>310862.64</v>
+        <v>390946.06</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
@@ -9876,16 +9876,16 @@
         <v>-0.025</v>
       </c>
       <c r="I87" s="5" t="n">
-        <v>306063.61</v>
+        <v>386438.11</v>
       </c>
       <c r="J87" s="5" t="n">
-        <v>4814.38</v>
+        <v>4540.65</v>
       </c>
       <c r="K87" s="7" t="n">
-        <v>-120.36</v>
+        <v>-113.52</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>310742.28</v>
+        <v>390832.54</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>

--- a/output/quickfix_portfolio_daily.xlsx
+++ b/output/quickfix_portfolio_daily.xlsx
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>390,832.54</t>
+          <t>290,445.81</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+290.83%</t>
+          <t>+190.45%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>404,600  (+304.60%)</t>
+          <t>300,899  (+200.90%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7,696  (13.8 pts of return)</t>
+          <t>6,394  (10.5 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>48.5x</t>
+          <t>31.7x</t>
         </is>
       </c>
     </row>
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>58.3%</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>+3.21R  (best +8.92R)</t>
+          <t>+2.74R  (best +8.09R)</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>7,646  (+3.77%)</t>
+          <t>5,453  (+3.22%)</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-2,684  (-1.31%)</t>
+          <t>-2,189  (-1.31%)</t>
         </is>
       </c>
     </row>
@@ -1207,13 +1207,13 @@
         <v>46030</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>118231.44</v>
+        <v>114647.62</v>
       </c>
       <c r="C13" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>118231.44</v>
+        <v>114647.62</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1222,7 +1222,7 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Coffee_NYCSCE_Futures stop (-1,335); S_P_500_Index target_r (+6,853)</t>
+          <t>Coffee_NYCSCE_Futures stop (-1,335); S_P_500_Index target_r (+3,269)</t>
         </is>
       </c>
     </row>
@@ -1231,13 +1231,13 @@
         <v>46031</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>118231.44</v>
+        <v>114647.62</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>118231.44</v>
+        <v>114647.62</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1251,13 +1251,13 @@
         <v>46032</v>
       </c>
       <c r="B15" s="5" t="n">
-        <v>118231.44</v>
+        <v>114647.62</v>
       </c>
       <c r="C15" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>118231.44</v>
+        <v>114647.62</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1271,13 +1271,13 @@
         <v>46033</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>118231.44</v>
+        <v>114647.62</v>
       </c>
       <c r="C16" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>118231.44</v>
+        <v>114647.62</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -1291,13 +1291,13 @@
         <v>46034</v>
       </c>
       <c r="B17" s="5" t="n">
-        <v>118231.44</v>
+        <v>114647.62</v>
       </c>
       <c r="C17" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>118231.44</v>
+        <v>114647.62</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -1311,13 +1311,13 @@
         <v>46035</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>118231.44</v>
+        <v>114647.62</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>1389.22</v>
+        <v>1347.11</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>116842.22</v>
+        <v>113300.51</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures long (risk 1,389)</t>
+          <t>Cocoa_NYCSCE_Futures long (risk 1,347)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -1339,13 +1339,13 @@
         <v>46036</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>122783.28</v>
+        <v>113185.86</v>
       </c>
       <c r="C19" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>122783.28</v>
+        <v>113185.86</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -1354,7 +1354,7 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures target_r (+4,552)</t>
+          <t>Cocoa_NYCSCE_Futures unknown_pl (-1,462)</t>
         </is>
       </c>
     </row>
@@ -1363,13 +1363,13 @@
         <v>46037</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>122783.28</v>
+        <v>113185.86</v>
       </c>
       <c r="C20" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>122783.28</v>
+        <v>113185.86</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -1383,13 +1383,13 @@
         <v>46038</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>122783.28</v>
+        <v>113185.86</v>
       </c>
       <c r="C21" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>122783.28</v>
+        <v>113185.86</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -1403,13 +1403,13 @@
         <v>46039</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>122783.28</v>
+        <v>113185.86</v>
       </c>
       <c r="C22" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>122783.28</v>
+        <v>113185.86</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>46040</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>122783.28</v>
+        <v>113185.86</v>
       </c>
       <c r="C23" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>122783.28</v>
+        <v>113185.86</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -1443,13 +1443,13 @@
         <v>46041</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>122783.28</v>
+        <v>113185.86</v>
       </c>
       <c r="C24" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>122783.28</v>
+        <v>113185.86</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -1463,13 +1463,13 @@
         <v>46042</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>122783.28</v>
+        <v>113185.86</v>
       </c>
       <c r="C25" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>122783.28</v>
+        <v>113185.86</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -1483,13 +1483,13 @@
         <v>46043</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>122783.28</v>
+        <v>113185.86</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>1442.7</v>
+        <v>1329.93</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>121340.58</v>
+        <v>111855.93</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Coffee_NYCSCE_Futures long (risk 1,443)</t>
+          <t>Coffee_NYCSCE_Futures long (risk 1,330)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -1511,13 +1511,13 @@
         <v>46044</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>122783.28</v>
+        <v>113185.86</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>1442.7</v>
+        <v>1329.93</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>121340.58</v>
+        <v>111855.93</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -1535,13 +1535,13 @@
         <v>46045</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>126381.33</v>
+        <v>116502.66</v>
       </c>
       <c r="C28" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>126381.33</v>
+        <v>116502.66</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -1550,7 +1550,7 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Coffee_NYCSCE_Futures target_r (+3,598)</t>
+          <t>Coffee_NYCSCE_Futures target_r (+3,317)</t>
         </is>
       </c>
     </row>
@@ -1559,13 +1559,13 @@
         <v>46046</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>126381.33</v>
+        <v>116502.66</v>
       </c>
       <c r="C29" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>126381.33</v>
+        <v>116502.66</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>46047</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>126381.33</v>
+        <v>116502.66</v>
       </c>
       <c r="C30" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>126381.33</v>
+        <v>116502.66</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -1599,13 +1599,13 @@
         <v>46048</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>126381.33</v>
+        <v>116502.66</v>
       </c>
       <c r="C31" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>126381.33</v>
+        <v>116502.66</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -1619,13 +1619,13 @@
         <v>46049</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>126381.33</v>
+        <v>116502.66</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>1484.98</v>
+        <v>1368.91</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>124896.34</v>
+        <v>115133.76</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>S_P_500_Index short (risk 1,485)</t>
+          <t>S_P_500_Index short (risk 1,369)</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -1647,13 +1647,13 @@
         <v>46050</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>121845.57</v>
+        <v>112321.45</v>
       </c>
       <c r="C33" s="5" t="n">
-        <v>1467.53</v>
+        <v>1352.82</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>120378.04</v>
+        <v>110968.63</v>
       </c>
       <c r="E33" t="n">
         <v>1</v>
@@ -1665,12 +1665,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Teucrium_Wheat_Fund short (risk 1,468)</t>
+          <t>Teucrium_Wheat_Fund short (risk 1,353)</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>S_P_500_Index stop (-4,536)</t>
+          <t>S_P_500_Index stop (-4,181)</t>
         </is>
       </c>
     </row>
@@ -1679,13 +1679,13 @@
         <v>46051</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>119970.32</v>
+        <v>110592.78</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>4193.66</v>
+        <v>3865.86</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>115776.66</v>
+        <v>106726.92</v>
       </c>
       <c r="E34" t="n">
         <v>3</v>
@@ -1697,12 +1697,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ethereum_Per_USD_Binance long (risk 1,414); Live_Cattle_Futures_CME short (risk 1,398); S_P_500_Index short (risk 1,381)</t>
+          <t>Ethereum_Per_USD_Binance long (risk 1,304); Live_Cattle_Futures_CME short (risk 1,289); S_P_500_Index short (risk 1,273)</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Teucrium_Wheat_Fund stop (-1,875)</t>
+          <t>Teucrium_Wheat_Fund stop (-1,729)</t>
         </is>
       </c>
     </row>
@@ -1711,13 +1711,13 @@
         <v>46052</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>121618.26</v>
+        <v>112111.91</v>
       </c>
       <c r="C35" s="5" t="n">
-        <v>1360.38</v>
+        <v>1254.04</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>120257.89</v>
+        <v>110857.87</v>
       </c>
       <c r="E35" t="n">
         <v>1</v>
@@ -1729,12 +1729,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures long (risk 1,360)</t>
+          <t>Cocoa_NYCSCE_Futures long (risk 1,254)</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Ethereum_Per_USD_Binance stop (-1,512); Live_Cattle_Futures_CME unknown_pl (-1,481); S_P_500_Index target_r (+4,641)</t>
+          <t>Ethereum_Per_USD_Binance stop (-1,394); Live_Cattle_Futures_CME unknown_pl (-1,365); S_P_500_Index target_r (+4,278)</t>
         </is>
       </c>
     </row>
@@ -1743,13 +1743,13 @@
         <v>46053</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>121618.26</v>
+        <v>112111.91</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>1360.38</v>
+        <v>1254.04</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>120257.89</v>
+        <v>110857.87</v>
       </c>
       <c r="E36" t="n">
         <v>1</v>
@@ -1767,13 +1767,13 @@
         <v>46054</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>121618.26</v>
+        <v>112111.91</v>
       </c>
       <c r="C37" s="5" t="n">
-        <v>1360.38</v>
+        <v>1254.04</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>120257.89</v>
+        <v>110857.87</v>
       </c>
       <c r="E37" t="n">
         <v>1</v>
@@ -1791,13 +1791,13 @@
         <v>46055</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>121618.26</v>
+        <v>112111.91</v>
       </c>
       <c r="C38" s="5" t="n">
-        <v>4169.83</v>
+        <v>3843.9</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>117448.43</v>
+        <v>108268.01</v>
       </c>
       <c r="E38" t="n">
         <v>3</v>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance long (risk 1,413); S_P_500_Index short (risk 1,396)</t>
+          <t>Bitcoin_Per_USD_Binance long (risk 1,303); S_P_500_Index short (risk 1,287)</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -1819,13 +1819,13 @@
         <v>46056</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>118799.95</v>
+        <v>109513.89</v>
       </c>
       <c r="C39" s="5" t="n">
-        <v>2740.39</v>
+        <v>2526.19</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>116059.56</v>
+        <v>106987.7</v>
       </c>
       <c r="E39" t="n">
         <v>2</v>
@@ -1837,12 +1837,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>EURO_STOXX_50_Index short (risk 1,380)</t>
+          <t>EURO_STOXX_50_Index short (risk 1,272)</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance stop (-1,416); S_P_500_Index unknown_pl (-1,402)</t>
+          <t>Bitcoin_Per_USD_Binance stop (-1,305); S_P_500_Index unknown_pl (-1,293)</t>
         </is>
       </c>
     </row>
@@ -1851,13 +1851,13 @@
         <v>46057</v>
       </c>
       <c r="B40" s="5" t="n">
-        <v>118799.95</v>
+        <v>109513.89</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>2740.39</v>
+        <v>2526.19</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>116059.56</v>
+        <v>106987.7</v>
       </c>
       <c r="E40" t="n">
         <v>2</v>
@@ -1875,13 +1875,13 @@
         <v>46058</v>
       </c>
       <c r="B41" s="5" t="n">
-        <v>122249.08</v>
+        <v>112693.42</v>
       </c>
       <c r="C41" s="5" t="n">
-        <v>2724.08</v>
+        <v>2511.15</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>119525</v>
+        <v>110182.27</v>
       </c>
       <c r="E41" t="n">
         <v>2</v>
@@ -1893,12 +1893,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures long (risk 1,364)</t>
+          <t>NY_Copper_Futures long (risk 1,257)</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>EURO_STOXX_50_Index target_r (+3,449)</t>
+          <t>EURO_STOXX_50_Index target_r (+3,180)</t>
         </is>
       </c>
     </row>
@@ -1907,13 +1907,13 @@
         <v>46059</v>
       </c>
       <c r="B42" s="5" t="n">
-        <v>120879.07</v>
+        <v>111430.5</v>
       </c>
       <c r="C42" s="5" t="n">
-        <v>2764.79</v>
+        <v>2548.68</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>118114.28</v>
+        <v>108881.81</v>
       </c>
       <c r="E42" t="n">
         <v>2</v>
@@ -1925,12 +1925,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance long (risk 1,404)</t>
+          <t>Bitcoin_Per_USD_Binance long (risk 1,295)</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures stop (-1,370)</t>
+          <t>NY_Copper_Futures stop (-1,263)</t>
         </is>
       </c>
     </row>
@@ -1939,13 +1939,13 @@
         <v>46060</v>
       </c>
       <c r="B43" s="5" t="n">
-        <v>125246.7</v>
+        <v>114666.09</v>
       </c>
       <c r="C43" s="5" t="n">
-        <v>1360.38</v>
+        <v>1254.04</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>123886.32</v>
+        <v>113412.05</v>
       </c>
       <c r="E43" t="n">
         <v>1</v>
@@ -1958,7 +1958,7 @@
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance target_r (+4,368)</t>
+          <t>Bitcoin_Per_USD_Binance target_r (+3,236)</t>
         </is>
       </c>
     </row>
@@ -1967,13 +1967,13 @@
         <v>46061</v>
       </c>
       <c r="B44" s="5" t="n">
-        <v>125246.7</v>
+        <v>114666.09</v>
       </c>
       <c r="C44" s="5" t="n">
-        <v>1360.38</v>
+        <v>1254.04</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>123886.32</v>
+        <v>113412.05</v>
       </c>
       <c r="E44" t="n">
         <v>1</v>
@@ -1991,13 +1991,13 @@
         <v>46062</v>
       </c>
       <c r="B45" s="5" t="n">
-        <v>125246.7</v>
+        <v>114666.09</v>
       </c>
       <c r="C45" s="5" t="n">
-        <v>1360.38</v>
+        <v>1254.04</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>123886.32</v>
+        <v>113412.05</v>
       </c>
       <c r="E45" t="n">
         <v>1</v>
@@ -2015,13 +2015,13 @@
         <v>46063</v>
       </c>
       <c r="B46" s="5" t="n">
-        <v>123850.52</v>
+        <v>113379.05</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>2894.22</v>
+        <v>2649.53</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>120956.3</v>
+        <v>110729.52</v>
       </c>
       <c r="E46" t="n">
         <v>2</v>
@@ -2033,12 +2033,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>EURO_STOXX_50_Index short (risk 1,456); S_P_500_Index short (risk 1,439)</t>
+          <t>EURO_STOXX_50_Index short (risk 1,333); S_P_500_Index short (risk 1,317)</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures stop (-1,396)</t>
+          <t>Cocoa_NYCSCE_Futures stop (-1,287)</t>
         </is>
       </c>
     </row>
@@ -2047,13 +2047,13 @@
         <v>46064</v>
       </c>
       <c r="B47" s="5" t="n">
-        <v>126036.55</v>
+        <v>115380.25</v>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1421.24</v>
+        <v>1301.07</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>124615.32</v>
+        <v>114079.18</v>
       </c>
       <c r="E47" t="n">
         <v>1</v>
@@ -2065,12 +2065,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT short (risk 1,421)</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT short (risk 1,301)</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>EURO_STOXX_50_Index target_r (+3,638); S_P_500_Index unknown_pl (-1,452)</t>
+          <t>EURO_STOXX_50_Index target_r (+3,330); S_P_500_Index unknown_pl (-1,329)</t>
         </is>
       </c>
     </row>
@@ -2079,13 +2079,13 @@
         <v>46065</v>
       </c>
       <c r="B48" s="5" t="n">
-        <v>124419.28</v>
+        <v>113899.72</v>
       </c>
       <c r="C48" s="5" t="n">
-        <v>1464.23</v>
+        <v>1340.43</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>122955.05</v>
+        <v>112559.29</v>
       </c>
       <c r="E48" t="n">
         <v>1</v>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>EURO_STOXX_50_Index short (risk 1,464)</t>
+          <t>EURO_STOXX_50_Index short (risk 1,340)</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT stop (-1,617)</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT stop (-1,481)</t>
         </is>
       </c>
     </row>
@@ -2111,13 +2111,13 @@
         <v>46066</v>
       </c>
       <c r="B49" s="5" t="n">
-        <v>128079.1</v>
+        <v>117250.11</v>
       </c>
       <c r="C49" s="5" t="n">
-        <v>1444.72</v>
+        <v>1322.57</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>126634.38</v>
+        <v>115927.54</v>
       </c>
       <c r="E49" t="n">
         <v>1</v>
@@ -2129,12 +2129,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures long (risk 1,445)</t>
+          <t>NY_Copper_Futures long (risk 1,323)</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>EURO_STOXX_50_Index target_r (+3,660)</t>
+          <t>EURO_STOXX_50_Index target_r (+3,350)</t>
         </is>
       </c>
     </row>
@@ -2143,13 +2143,13 @@
         <v>46067</v>
       </c>
       <c r="B50" s="5" t="n">
-        <v>128079.1</v>
+        <v>117250.11</v>
       </c>
       <c r="C50" s="5" t="n">
-        <v>1444.72</v>
+        <v>1322.57</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>126634.38</v>
+        <v>115927.54</v>
       </c>
       <c r="E50" t="n">
         <v>1</v>
@@ -2167,13 +2167,13 @@
         <v>46068</v>
       </c>
       <c r="B51" s="5" t="n">
-        <v>128079.1</v>
+        <v>117250.11</v>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1444.72</v>
+        <v>1322.57</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>126634.38</v>
+        <v>115927.54</v>
       </c>
       <c r="E51" t="n">
         <v>1</v>
@@ -2191,13 +2191,13 @@
         <v>46069</v>
       </c>
       <c r="B52" s="5" t="n">
-        <v>128079.1</v>
+        <v>117250.11</v>
       </c>
       <c r="C52" s="5" t="n">
-        <v>1444.72</v>
+        <v>1322.57</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>126634.38</v>
+        <v>115927.54</v>
       </c>
       <c r="E52" t="n">
         <v>1</v>
@@ -2215,13 +2215,13 @@
         <v>46070</v>
       </c>
       <c r="B53" s="5" t="n">
-        <v>126628.24</v>
+        <v>115921.91</v>
       </c>
       <c r="C53" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>126628.24</v>
+        <v>115921.91</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
@@ -2230,7 +2230,7 @@
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures stop (-1,451)</t>
+          <t>NY_Copper_Futures stop (-1,328)</t>
         </is>
       </c>
     </row>
@@ -2239,13 +2239,13 @@
         <v>46071</v>
       </c>
       <c r="B54" s="5" t="n">
-        <v>126628.24</v>
+        <v>115921.91</v>
       </c>
       <c r="C54" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>126628.24</v>
+        <v>115921.91</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
@@ -2259,13 +2259,13 @@
         <v>46072</v>
       </c>
       <c r="B55" s="5" t="n">
-        <v>126628.24</v>
+        <v>115921.91</v>
       </c>
       <c r="C55" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>126628.24</v>
+        <v>115921.91</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
@@ -2279,13 +2279,13 @@
         <v>46073</v>
       </c>
       <c r="B56" s="5" t="n">
-        <v>126628.24</v>
+        <v>115921.91</v>
       </c>
       <c r="C56" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>126628.24</v>
+        <v>115921.91</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
@@ -2299,13 +2299,13 @@
         <v>46074</v>
       </c>
       <c r="B57" s="5" t="n">
-        <v>126628.24</v>
+        <v>115921.91</v>
       </c>
       <c r="C57" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>126628.24</v>
+        <v>115921.91</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
@@ -2319,13 +2319,13 @@
         <v>46075</v>
       </c>
       <c r="B58" s="5" t="n">
-        <v>126628.24</v>
+        <v>115921.91</v>
       </c>
       <c r="C58" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>126628.24</v>
+        <v>115921.91</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
@@ -2339,13 +2339,13 @@
         <v>46076</v>
       </c>
       <c r="B59" s="5" t="n">
-        <v>126628.24</v>
+        <v>115921.91</v>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1487.88</v>
+        <v>1362.08</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>125140.35</v>
+        <v>114559.83</v>
       </c>
       <c r="E59" t="n">
         <v>1</v>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT short (risk 1,488)</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT short (risk 1,362)</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
@@ -2367,13 +2367,13 @@
         <v>46077</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>126628.24</v>
+        <v>115921.91</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>4411.4</v>
+        <v>4038.42</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>122216.83</v>
+        <v>111883.49</v>
       </c>
       <c r="E60" t="n">
         <v>3</v>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures long (risk 1,470); Ethereum_Per_USD_Binance long (risk 1,453)</t>
+          <t>Cocoa_NYCSCE_Futures long (risk 1,346); Ethereum_Per_USD_Binance long (risk 1,330)</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
@@ -2395,13 +2395,13 @@
         <v>46078</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>137272.43</v>
+        <v>125666.15</v>
       </c>
       <c r="C61" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>137272.43</v>
+        <v>125666.15</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
@@ -2410,7 +2410,7 @@
       <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures target_r (+3,657); Ethereum_Per_USD_Binance target_r (+3,480); US_30_Year_T_Bond_Futures_CBOT target_r (+3,507)</t>
+          <t>Cocoa_NYCSCE_Futures target_r (+3,348); Ethereum_Per_USD_Binance target_r (+3,186); US_30_Year_T_Bond_Futures_CBOT target_r (+3,211)</t>
         </is>
       </c>
     </row>
@@ -2419,13 +2419,13 @@
         <v>46079</v>
       </c>
       <c r="B62" s="5" t="n">
-        <v>137272.43</v>
+        <v>125666.15</v>
       </c>
       <c r="C62" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>137272.43</v>
+        <v>125666.15</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
@@ -2439,13 +2439,13 @@
         <v>46080</v>
       </c>
       <c r="B63" s="5" t="n">
-        <v>137272.43</v>
+        <v>125666.15</v>
       </c>
       <c r="C63" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>137272.43</v>
+        <v>125666.15</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
@@ -2459,13 +2459,13 @@
         <v>46081</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>137272.43</v>
+        <v>125666.15</v>
       </c>
       <c r="C64" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>137272.43</v>
+        <v>125666.15</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
@@ -2479,13 +2479,13 @@
         <v>46082</v>
       </c>
       <c r="B65" s="5" t="n">
-        <v>137272.43</v>
+        <v>125666.15</v>
       </c>
       <c r="C65" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>137272.43</v>
+        <v>125666.15</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
@@ -2499,13 +2499,13 @@
         <v>46083</v>
       </c>
       <c r="B66" s="5" t="n">
-        <v>137272.43</v>
+        <v>125666.15</v>
       </c>
       <c r="C66" s="5" t="n">
-        <v>1612.95</v>
+        <v>1476.58</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>135659.48</v>
+        <v>124189.57</v>
       </c>
       <c r="E66" t="n">
         <v>1</v>
@@ -2517,7 +2517,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX short (risk 1,613)</t>
+          <t>Gold_Futures_COMEX short (risk 1,477)</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
@@ -2527,13 +2527,13 @@
         <v>46084</v>
       </c>
       <c r="B67" s="5" t="n">
-        <v>141300.57</v>
+        <v>129353.71</v>
       </c>
       <c r="C67" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>141300.57</v>
+        <v>129353.71</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
@@ -2542,7 +2542,7 @@
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX target_r (+4,028)</t>
+          <t>Gold_Futures_COMEX target_r (+3,688)</t>
         </is>
       </c>
     </row>
@@ -2551,13 +2551,13 @@
         <v>46085</v>
       </c>
       <c r="B68" s="5" t="n">
-        <v>141300.57</v>
+        <v>129353.71</v>
       </c>
       <c r="C68" s="5" t="n">
-        <v>1660.28</v>
+        <v>1519.91</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>139640.29</v>
+        <v>127833.8</v>
       </c>
       <c r="E68" t="n">
         <v>1</v>
@@ -2569,7 +2569,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate short (risk 1,660)</t>
+          <t>USD_EUR_Cross_Rate short (risk 1,520)</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
@@ -2579,13 +2579,13 @@
         <v>46086</v>
       </c>
       <c r="B69" s="5" t="n">
-        <v>139351.55</v>
+        <v>127569.47</v>
       </c>
       <c r="C69" s="5" t="n">
-        <v>1640.77</v>
+        <v>1502.05</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>137710.77</v>
+        <v>126067.42</v>
       </c>
       <c r="E69" t="n">
         <v>1</v>
@@ -2597,12 +2597,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>S_P_500_Index long (risk 1,641)</t>
+          <t>S_P_500_Index long (risk 1,502)</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate stop (-1,949)</t>
+          <t>USD_EUR_Cross_Rate stop (-1,784)</t>
         </is>
       </c>
     </row>
@@ -2611,13 +2611,13 @@
         <v>46087</v>
       </c>
       <c r="B70" s="5" t="n">
-        <v>137587.23</v>
+        <v>125954.33</v>
       </c>
       <c r="C70" s="5" t="n">
-        <v>1618.1</v>
+        <v>1481.29</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>135969.13</v>
+        <v>124473.04</v>
       </c>
       <c r="E70" t="n">
         <v>1</v>
@@ -2629,12 +2629,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate short (risk 1,618)</t>
+          <t>USD_EUR_Cross_Rate short (risk 1,481)</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>S_P_500_Index stop (-1,764)</t>
+          <t>S_P_500_Index stop (-1,615)</t>
         </is>
       </c>
     </row>
@@ -2643,13 +2643,13 @@
         <v>46088</v>
       </c>
       <c r="B71" s="5" t="n">
-        <v>137587.23</v>
+        <v>125954.33</v>
       </c>
       <c r="C71" s="5" t="n">
-        <v>1618.1</v>
+        <v>1481.29</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>135969.13</v>
+        <v>124473.04</v>
       </c>
       <c r="E71" t="n">
         <v>1</v>
@@ -2667,13 +2667,13 @@
         <v>46089</v>
       </c>
       <c r="B72" s="5" t="n">
-        <v>137587.23</v>
+        <v>125954.33</v>
       </c>
       <c r="C72" s="5" t="n">
-        <v>1618.1</v>
+        <v>1481.29</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>135969.13</v>
+        <v>124473.04</v>
       </c>
       <c r="E72" t="n">
         <v>1</v>
@@ -2691,13 +2691,13 @@
         <v>46090</v>
       </c>
       <c r="B73" s="5" t="n">
-        <v>135822.03</v>
+        <v>124338.38</v>
       </c>
       <c r="C73" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>135822.03</v>
+        <v>124338.38</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
@@ -2706,7 +2706,7 @@
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate stop (-1,765)</t>
+          <t>USD_EUR_Cross_Rate stop (-1,616)</t>
         </is>
       </c>
     </row>
@@ -2715,13 +2715,13 @@
         <v>46091</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>135822.03</v>
+        <v>124338.38</v>
       </c>
       <c r="C74" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>135822.03</v>
+        <v>124338.38</v>
       </c>
       <c r="E74" t="n">
         <v>0</v>
@@ -2735,13 +2735,13 @@
         <v>46092</v>
       </c>
       <c r="B75" s="5" t="n">
-        <v>135822.03</v>
+        <v>124338.38</v>
       </c>
       <c r="C75" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>135822.03</v>
+        <v>124338.38</v>
       </c>
       <c r="E75" t="n">
         <v>0</v>
@@ -2755,13 +2755,13 @@
         <v>46093</v>
       </c>
       <c r="B76" s="5" t="n">
-        <v>135822.03</v>
+        <v>124338.38</v>
       </c>
       <c r="C76" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>135822.03</v>
+        <v>124338.38</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
@@ -2775,13 +2775,13 @@
         <v>46094</v>
       </c>
       <c r="B77" s="5" t="n">
-        <v>135822.03</v>
+        <v>124338.38</v>
       </c>
       <c r="C77" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>135822.03</v>
+        <v>124338.38</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
@@ -2795,13 +2795,13 @@
         <v>46095</v>
       </c>
       <c r="B78" s="5" t="n">
-        <v>135822.03</v>
+        <v>124338.38</v>
       </c>
       <c r="C78" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>135822.03</v>
+        <v>124338.38</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
@@ -2815,13 +2815,13 @@
         <v>46096</v>
       </c>
       <c r="B79" s="5" t="n">
-        <v>135822.03</v>
+        <v>124338.38</v>
       </c>
       <c r="C79" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>135822.03</v>
+        <v>124338.38</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
@@ -2835,13 +2835,13 @@
         <v>46097</v>
       </c>
       <c r="B80" s="5" t="n">
-        <v>135822.03</v>
+        <v>124338.38</v>
       </c>
       <c r="C80" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>135822.03</v>
+        <v>124338.38</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
@@ -2855,13 +2855,13 @@
         <v>46098</v>
       </c>
       <c r="B81" s="5" t="n">
-        <v>135822.03</v>
+        <v>124338.38</v>
       </c>
       <c r="C81" s="5" t="n">
-        <v>1595.91</v>
+        <v>1460.98</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>134226.12</v>
+        <v>122877.4</v>
       </c>
       <c r="E81" t="n">
         <v>1</v>
@@ -2873,7 +2873,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance short (risk 1,596)</t>
+          <t>Bitcoin_Per_USD_Binance short (risk 1,461)</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
@@ -2883,13 +2883,13 @@
         <v>46099</v>
       </c>
       <c r="B82" s="5" t="n">
-        <v>139806.99</v>
+        <v>127986.41</v>
       </c>
       <c r="C82" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>139806.99</v>
+        <v>127986.41</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
@@ -2898,7 +2898,7 @@
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance target_r (+3,985)</t>
+          <t>Bitcoin_Per_USD_Binance target_r (+3,648)</t>
         </is>
       </c>
     </row>
@@ -2907,13 +2907,13 @@
         <v>46100</v>
       </c>
       <c r="B83" s="5" t="n">
-        <v>139806.99</v>
+        <v>127986.41</v>
       </c>
       <c r="C83" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>139806.99</v>
+        <v>127986.41</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
@@ -2927,13 +2927,13 @@
         <v>46101</v>
       </c>
       <c r="B84" s="5" t="n">
-        <v>139806.99</v>
+        <v>127986.41</v>
       </c>
       <c r="C84" s="5" t="n">
-        <v>1642.73</v>
+        <v>1503.84</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>138164.26</v>
+        <v>126482.57</v>
       </c>
       <c r="E84" t="n">
         <v>1</v>
@@ -2945,7 +2945,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP short (risk 1,643)</t>
+          <t>United_States_Oil_Fund_LP short (risk 1,504)</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
@@ -2955,13 +2955,13 @@
         <v>46102</v>
       </c>
       <c r="B85" s="5" t="n">
-        <v>139806.99</v>
+        <v>127986.41</v>
       </c>
       <c r="C85" s="5" t="n">
-        <v>1642.73</v>
+        <v>1503.84</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>138164.26</v>
+        <v>126482.57</v>
       </c>
       <c r="E85" t="n">
         <v>1</v>
@@ -2979,13 +2979,13 @@
         <v>46103</v>
       </c>
       <c r="B86" s="5" t="n">
-        <v>139806.99</v>
+        <v>127986.41</v>
       </c>
       <c r="C86" s="5" t="n">
-        <v>1642.73</v>
+        <v>1503.84</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>138164.26</v>
+        <v>126482.57</v>
       </c>
       <c r="E86" t="n">
         <v>1</v>
@@ -3003,13 +3003,13 @@
         <v>46104</v>
       </c>
       <c r="B87" s="5" t="n">
-        <v>150353.06</v>
+        <v>137640.81</v>
       </c>
       <c r="C87" s="5" t="n">
-        <v>1623.43</v>
+        <v>1486.17</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>148729.63</v>
+        <v>136154.64</v>
       </c>
       <c r="E87" t="n">
         <v>1</v>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures long (risk 1,623)</t>
+          <t>NY_Copper_Futures long (risk 1,486)</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP target_r (+10,546)</t>
+          <t>United_States_Oil_Fund_LP target_r (+9,654)</t>
         </is>
       </c>
     </row>
@@ -3035,13 +3035,13 @@
         <v>46105</v>
       </c>
       <c r="B88" s="5" t="n">
-        <v>154483.93</v>
+        <v>141422.42</v>
       </c>
       <c r="C88" s="5" t="n">
-        <v>1747.57</v>
+        <v>1599.82</v>
       </c>
       <c r="D88" s="5" t="n">
-        <v>152736.35</v>
+        <v>139822.6</v>
       </c>
       <c r="E88" t="n">
         <v>1</v>
@@ -3053,12 +3053,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX long (risk 1,748)</t>
+          <t>Gold_Futures_COMEX long (risk 1,600)</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures target_r (+4,131)</t>
+          <t>NY_Copper_Futures target_r (+3,782)</t>
         </is>
       </c>
     </row>
@@ -3067,13 +3067,13 @@
         <v>46106</v>
       </c>
       <c r="B89" s="5" t="n">
-        <v>162875.87</v>
+        <v>149104.83</v>
       </c>
       <c r="C89" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D89" s="5" t="n">
-        <v>162875.87</v>
+        <v>149104.83</v>
       </c>
       <c r="E89" t="n">
         <v>0</v>
@@ -3082,7 +3082,7 @@
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX target_r (+8,392)</t>
+          <t>Gold_Futures_COMEX target_r (+7,682)</t>
         </is>
       </c>
     </row>
@@ -3091,13 +3091,13 @@
         <v>46107</v>
       </c>
       <c r="B90" s="5" t="n">
-        <v>162875.87</v>
+        <v>149104.83</v>
       </c>
       <c r="C90" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>162875.87</v>
+        <v>149104.83</v>
       </c>
       <c r="E90" t="n">
         <v>0</v>
@@ -3111,13 +3111,13 @@
         <v>46108</v>
       </c>
       <c r="B91" s="5" t="n">
-        <v>162875.87</v>
+        <v>149104.83</v>
       </c>
       <c r="C91" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>162875.87</v>
+        <v>149104.83</v>
       </c>
       <c r="E91" t="n">
         <v>0</v>
@@ -3131,13 +3131,13 @@
         <v>46109</v>
       </c>
       <c r="B92" s="5" t="n">
-        <v>162875.87</v>
+        <v>149104.83</v>
       </c>
       <c r="C92" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>162875.87</v>
+        <v>149104.83</v>
       </c>
       <c r="E92" t="n">
         <v>0</v>
@@ -3151,13 +3151,13 @@
         <v>46110</v>
       </c>
       <c r="B93" s="5" t="n">
-        <v>162875.87</v>
+        <v>149104.83</v>
       </c>
       <c r="C93" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>162875.87</v>
+        <v>149104.83</v>
       </c>
       <c r="E93" t="n">
         <v>0</v>
@@ -3171,13 +3171,13 @@
         <v>46111</v>
       </c>
       <c r="B94" s="5" t="n">
-        <v>162875.87</v>
+        <v>149104.83</v>
       </c>
       <c r="C94" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>162875.87</v>
+        <v>149104.83</v>
       </c>
       <c r="E94" t="n">
         <v>0</v>
@@ -3191,13 +3191,13 @@
         <v>46112</v>
       </c>
       <c r="B95" s="5" t="n">
-        <v>162875.87</v>
+        <v>149104.83</v>
       </c>
       <c r="C95" s="5" t="n">
-        <v>1913.79</v>
+        <v>1751.98</v>
       </c>
       <c r="D95" s="5" t="n">
-        <v>160962.08</v>
+        <v>147352.85</v>
       </c>
       <c r="E95" t="n">
         <v>1</v>
@@ -3209,7 +3209,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP short (risk 1,914)</t>
+          <t>United_States_Oil_Fund_LP short (risk 1,752)</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
@@ -3219,13 +3219,13 @@
         <v>46113</v>
       </c>
       <c r="B96" s="5" t="n">
-        <v>175830.82</v>
+        <v>153439.86</v>
       </c>
       <c r="C96" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D96" s="5" t="n">
-        <v>175830.82</v>
+        <v>153439.86</v>
       </c>
       <c r="E96" t="n">
         <v>0</v>
@@ -3234,7 +3234,7 @@
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP target_r (+12,955)</t>
+          <t>United_States_Oil_Fund_LP target_r (+4,335)</t>
         </is>
       </c>
     </row>
@@ -3243,13 +3243,13 @@
         <v>46114</v>
       </c>
       <c r="B97" s="5" t="n">
-        <v>175830.82</v>
+        <v>153439.86</v>
       </c>
       <c r="C97" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D97" s="5" t="n">
-        <v>175830.82</v>
+        <v>153439.86</v>
       </c>
       <c r="E97" t="n">
         <v>0</v>
@@ -3263,13 +3263,13 @@
         <v>46115</v>
       </c>
       <c r="B98" s="5" t="n">
-        <v>175830.82</v>
+        <v>153439.86</v>
       </c>
       <c r="C98" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D98" s="5" t="n">
-        <v>175830.82</v>
+        <v>153439.86</v>
       </c>
       <c r="E98" t="n">
         <v>0</v>
@@ -3283,13 +3283,13 @@
         <v>46116</v>
       </c>
       <c r="B99" s="5" t="n">
-        <v>175830.82</v>
+        <v>153439.86</v>
       </c>
       <c r="C99" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D99" s="5" t="n">
-        <v>175830.82</v>
+        <v>153439.86</v>
       </c>
       <c r="E99" t="n">
         <v>0</v>
@@ -3303,13 +3303,13 @@
         <v>46117</v>
       </c>
       <c r="B100" s="5" t="n">
-        <v>175830.82</v>
+        <v>153439.86</v>
       </c>
       <c r="C100" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>175830.82</v>
+        <v>153439.86</v>
       </c>
       <c r="E100" t="n">
         <v>0</v>
@@ -3323,13 +3323,13 @@
         <v>46118</v>
       </c>
       <c r="B101" s="5" t="n">
-        <v>175830.82</v>
+        <v>153439.86</v>
       </c>
       <c r="C101" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>175830.82</v>
+        <v>153439.86</v>
       </c>
       <c r="E101" t="n">
         <v>0</v>
@@ -3343,13 +3343,13 @@
         <v>46119</v>
       </c>
       <c r="B102" s="5" t="n">
-        <v>175830.82</v>
+        <v>153439.86</v>
       </c>
       <c r="C102" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D102" s="5" t="n">
-        <v>175830.82</v>
+        <v>153439.86</v>
       </c>
       <c r="E102" t="n">
         <v>0</v>
@@ -3363,13 +3363,13 @@
         <v>46120</v>
       </c>
       <c r="B103" s="5" t="n">
-        <v>175830.82</v>
+        <v>153439.86</v>
       </c>
       <c r="C103" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D103" s="5" t="n">
-        <v>175830.82</v>
+        <v>153439.86</v>
       </c>
       <c r="E103" t="n">
         <v>0</v>
@@ -3383,13 +3383,13 @@
         <v>46121</v>
       </c>
       <c r="B104" s="5" t="n">
-        <v>175830.82</v>
+        <v>153439.86</v>
       </c>
       <c r="C104" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D104" s="5" t="n">
-        <v>175830.82</v>
+        <v>153439.86</v>
       </c>
       <c r="E104" t="n">
         <v>0</v>
@@ -3403,13 +3403,13 @@
         <v>46122</v>
       </c>
       <c r="B105" s="5" t="n">
-        <v>175830.82</v>
+        <v>153439.86</v>
       </c>
       <c r="C105" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D105" s="5" t="n">
-        <v>175830.82</v>
+        <v>153439.86</v>
       </c>
       <c r="E105" t="n">
         <v>0</v>
@@ -3423,13 +3423,13 @@
         <v>46123</v>
       </c>
       <c r="B106" s="5" t="n">
-        <v>175830.82</v>
+        <v>153439.86</v>
       </c>
       <c r="C106" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D106" s="5" t="n">
-        <v>175830.82</v>
+        <v>153439.86</v>
       </c>
       <c r="E106" t="n">
         <v>0</v>
@@ -3443,13 +3443,13 @@
         <v>46124</v>
       </c>
       <c r="B107" s="5" t="n">
-        <v>175830.82</v>
+        <v>153439.86</v>
       </c>
       <c r="C107" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D107" s="5" t="n">
-        <v>175830.82</v>
+        <v>153439.86</v>
       </c>
       <c r="E107" t="n">
         <v>0</v>
@@ -3463,13 +3463,13 @@
         <v>46125</v>
       </c>
       <c r="B108" s="5" t="n">
-        <v>175830.82</v>
+        <v>153439.86</v>
       </c>
       <c r="C108" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>175830.82</v>
+        <v>153439.86</v>
       </c>
       <c r="E108" t="n">
         <v>0</v>
@@ -3483,13 +3483,13 @@
         <v>46126</v>
       </c>
       <c r="B109" s="5" t="n">
-        <v>175830.82</v>
+        <v>153439.86</v>
       </c>
       <c r="C109" s="5" t="n">
-        <v>2066.01</v>
+        <v>1802.92</v>
       </c>
       <c r="D109" s="5" t="n">
-        <v>173764.81</v>
+        <v>151636.94</v>
       </c>
       <c r="E109" t="n">
         <v>1</v>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance short (risk 2,066)</t>
+          <t>Bitcoin_Per_USD_Binance short (risk 1,803)</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
@@ -3511,13 +3511,13 @@
         <v>46127</v>
       </c>
       <c r="B110" s="5" t="n">
-        <v>175830.82</v>
+        <v>153439.86</v>
       </c>
       <c r="C110" s="5" t="n">
-        <v>8119.53</v>
+        <v>7085.56</v>
       </c>
       <c r="D110" s="5" t="n">
-        <v>167711.29</v>
+        <v>146354.3</v>
       </c>
       <c r="E110" t="n">
         <v>4</v>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Ethereum_Per_USD_Binance short (risk 2,042); Live_Cattle_Futures_CME short (risk 2,018); NY_Copper_Futures short (risk 1,994)</t>
+          <t>Ethereum_Per_USD_Binance short (risk 1,782); Live_Cattle_Futures_CME short (risk 1,761); NY_Copper_Futures short (risk 1,740)</t>
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
@@ -3539,13 +3539,13 @@
         <v>46128</v>
       </c>
       <c r="B111" s="5" t="n">
-        <v>185602.02</v>
+        <v>161966.76</v>
       </c>
       <c r="C111" s="5" t="n">
-        <v>4060.05</v>
+        <v>3543.03</v>
       </c>
       <c r="D111" s="5" t="n">
-        <v>181541.97</v>
+        <v>158423.73</v>
       </c>
       <c r="E111" t="n">
         <v>2</v>
@@ -3558,7 +3558,7 @@
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Ethereum_Per_USD_Binance target_r (+4,849); Live_Cattle_Futures_CME target_r (+4,922)</t>
+          <t>Ethereum_Per_USD_Binance target_r (+4,232); Live_Cattle_Futures_CME target_r (+4,295)</t>
         </is>
       </c>
     </row>
@@ -3567,13 +3567,13 @@
         <v>46129</v>
       </c>
       <c r="B112" s="5" t="n">
-        <v>185524.26</v>
+        <v>161898.9</v>
       </c>
       <c r="C112" s="5" t="n">
-        <v>1994.04</v>
+        <v>1740.11</v>
       </c>
       <c r="D112" s="5" t="n">
-        <v>183530.22</v>
+        <v>160158.79</v>
       </c>
       <c r="E112" t="n">
         <v>1</v>
@@ -3585,12 +3585,12 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate long (risk 2,133)</t>
+          <t>USD_EUR_Cross_Rate long (risk 1,861)</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance stop (-2,073); USD_EUR_Cross_Rate data_end (+1,995)</t>
+          <t>Bitcoin_Per_USD_Binance stop (-1,809); USD_EUR_Cross_Rate data_end (+1,741)</t>
         </is>
       </c>
     </row>
@@ -3599,13 +3599,13 @@
         <v>46130</v>
       </c>
       <c r="B113" s="5" t="n">
-        <v>185524.26</v>
+        <v>161898.9</v>
       </c>
       <c r="C113" s="5" t="n">
-        <v>1994.04</v>
+        <v>1740.11</v>
       </c>
       <c r="D113" s="5" t="n">
-        <v>183530.22</v>
+        <v>160158.79</v>
       </c>
       <c r="E113" t="n">
         <v>1</v>
@@ -3623,13 +3623,13 @@
         <v>46132</v>
       </c>
       <c r="B114" s="5" t="n">
-        <v>185524.26</v>
+        <v>161898.9</v>
       </c>
       <c r="C114" s="5" t="n">
-        <v>1994.04</v>
+        <v>1740.11</v>
       </c>
       <c r="D114" s="5" t="n">
-        <v>183530.22</v>
+        <v>160158.79</v>
       </c>
       <c r="E114" t="n">
         <v>1</v>
@@ -3647,13 +3647,13 @@
         <v>46133</v>
       </c>
       <c r="B115" s="5" t="n">
-        <v>185524.26</v>
+        <v>161898.9</v>
       </c>
       <c r="C115" s="5" t="n">
-        <v>1994.04</v>
+        <v>1740.11</v>
       </c>
       <c r="D115" s="5" t="n">
-        <v>183530.22</v>
+        <v>160158.79</v>
       </c>
       <c r="E115" t="n">
         <v>1</v>
@@ -3671,13 +3671,13 @@
         <v>46134</v>
       </c>
       <c r="B116" s="5" t="n">
-        <v>183515.03</v>
+        <v>160145.53</v>
       </c>
       <c r="C116" s="5" t="n">
-        <v>2156.48</v>
+        <v>1881.87</v>
       </c>
       <c r="D116" s="5" t="n">
-        <v>181358.55</v>
+        <v>158263.67</v>
       </c>
       <c r="E116" t="n">
         <v>1</v>
@@ -3689,12 +3689,12 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini short (risk 2,156)</t>
+          <t>Dow_Futures_E_mini short (risk 1,882)</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures stop (-2,009)</t>
+          <t>NY_Copper_Futures stop (-1,753)</t>
         </is>
       </c>
     </row>
@@ -3703,13 +3703,13 @@
         <v>46135</v>
       </c>
       <c r="B117" s="5" t="n">
-        <v>192459.06</v>
+        <v>167950.6</v>
       </c>
       <c r="C117" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D117" s="5" t="n">
-        <v>192459.06</v>
+        <v>167950.6</v>
       </c>
       <c r="E117" t="n">
         <v>0</v>
@@ -3718,7 +3718,7 @@
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini target_r (+8,944)</t>
+          <t>Dow_Futures_E_mini target_r (+7,805)</t>
         </is>
       </c>
     </row>
@@ -3727,13 +3727,13 @@
         <v>46136</v>
       </c>
       <c r="B118" s="5" t="n">
-        <v>192459.06</v>
+        <v>167950.6</v>
       </c>
       <c r="C118" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D118" s="5" t="n">
-        <v>192459.06</v>
+        <v>167950.6</v>
       </c>
       <c r="E118" t="n">
         <v>0</v>
@@ -3747,13 +3747,13 @@
         <v>46139</v>
       </c>
       <c r="B119" s="5" t="n">
-        <v>192459.06</v>
+        <v>167950.6</v>
       </c>
       <c r="C119" s="5" t="n">
-        <v>2261.39</v>
+        <v>1973.42</v>
       </c>
       <c r="D119" s="5" t="n">
-        <v>190197.66</v>
+        <v>165977.18</v>
       </c>
       <c r="E119" t="n">
         <v>1</v>
@@ -3765,7 +3765,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME short (risk 2,261)</t>
+          <t>Bitcoin_Per_USD_CME short (risk 1,973)</t>
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
@@ -3775,13 +3775,13 @@
         <v>46140</v>
       </c>
       <c r="B120" s="5" t="n">
-        <v>203151.8</v>
+        <v>172876.02</v>
       </c>
       <c r="C120" s="5" t="n">
-        <v>2234.82</v>
+        <v>1950.23</v>
       </c>
       <c r="D120" s="5" t="n">
-        <v>200916.97</v>
+        <v>170925.79</v>
       </c>
       <c r="E120" t="n">
         <v>1</v>
@@ -3793,12 +3793,12 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini short (risk 2,235)</t>
+          <t>S_P_500_E_mini short (risk 1,950)</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME target_r (+10,693)</t>
+          <t>Bitcoin_Per_USD_CME target_r (+4,925)</t>
         </is>
       </c>
     </row>
@@ -3807,13 +3807,13 @@
         <v>46141</v>
       </c>
       <c r="B121" s="5" t="n">
-        <v>208736.18</v>
+        <v>177749.27</v>
       </c>
       <c r="C121" s="5" t="n">
-        <v>2360.77</v>
+        <v>2008.38</v>
       </c>
       <c r="D121" s="5" t="n">
-        <v>206375.4</v>
+        <v>175740.89</v>
       </c>
       <c r="E121" t="n">
         <v>1</v>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 2,361)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 2,008)</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini target_r (+5,584)</t>
+          <t>S_P_500_E_mini target_r (+4,873)</t>
         </is>
       </c>
     </row>
@@ -3839,13 +3839,13 @@
         <v>46142</v>
       </c>
       <c r="B122" s="5" t="n">
-        <v>214585.06</v>
+        <v>182725.08</v>
       </c>
       <c r="C122" s="5" t="n">
-        <v>2424.91</v>
+        <v>2064.96</v>
       </c>
       <c r="D122" s="5" t="n">
-        <v>212160.15</v>
+        <v>180660.13</v>
       </c>
       <c r="E122" t="n">
         <v>1</v>
@@ -3857,12 +3857,12 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures short (risk 2,425)</t>
+          <t>Corn_CBOT_Futures short (risk 2,065)</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT target_r (+5,849)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT target_r (+4,976)</t>
         </is>
       </c>
     </row>
@@ -3871,13 +3871,13 @@
         <v>46143</v>
       </c>
       <c r="B123" s="5" t="n">
-        <v>211649.64</v>
+        <v>180225.4</v>
       </c>
       <c r="C123" s="5" t="n">
-        <v>7391.12</v>
+        <v>6293.74</v>
       </c>
       <c r="D123" s="5" t="n">
-        <v>204258.53</v>
+        <v>173931.66</v>
       </c>
       <c r="E123" t="n">
         <v>3</v>
@@ -3889,12 +3889,12 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Japanese_Yen_Futures short (risk 2,493); Live_Cattle_Futures_CME short (risk 2,464); US_Dollar_Index_Futures long (risk 2,435)</t>
+          <t>Japanese_Yen_Futures short (risk 2,123); Live_Cattle_Futures_CME short (risk 2,098); US_Dollar_Index_Futures long (risk 2,073)</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures unknown_pl (-2,935)</t>
+          <t>Corn_CBOT_Futures unknown_pl (-2,500)</t>
         </is>
       </c>
     </row>
@@ -3903,13 +3903,13 @@
         <v>46146</v>
       </c>
       <c r="B124" s="5" t="n">
-        <v>217769.2</v>
+        <v>185436.37</v>
       </c>
       <c r="C124" s="5" t="n">
-        <v>7327.56</v>
+        <v>6239.62</v>
       </c>
       <c r="D124" s="5" t="n">
-        <v>210441.64</v>
+        <v>179196.75</v>
       </c>
       <c r="E124" t="n">
         <v>3</v>
@@ -3921,12 +3921,12 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini short (risk 2,400)</t>
+          <t>Nasdaq_100_E_mini short (risk 2,044)</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME target_r (+6,120)</t>
+          <t>Live_Cattle_Futures_CME target_r (+5,211)</t>
         </is>
       </c>
     </row>
@@ -3935,13 +3935,13 @@
         <v>46147</v>
       </c>
       <c r="B125" s="5" t="n">
-        <v>229839.29</v>
+        <v>195714.38</v>
       </c>
       <c r="C125" s="5" t="n">
-        <v>4965.57</v>
+        <v>4228.32</v>
       </c>
       <c r="D125" s="5" t="n">
-        <v>224873.72</v>
+        <v>191486.06</v>
       </c>
       <c r="E125" t="n">
         <v>2</v>
@@ -3953,12 +3953,12 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures short (risk 2,473)</t>
+          <t>Corn_CBOT_Futures short (risk 2,106)</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini target_r (+6,003); US_Dollar_Index_Futures target_r (+6,067)</t>
+          <t>Nasdaq_100_E_mini target_r (+5,112); US_Dollar_Index_Futures target_r (+5,166)</t>
         </is>
       </c>
     </row>
@@ -3967,13 +3967,13 @@
         <v>46148</v>
       </c>
       <c r="B126" s="5" t="n">
-        <v>245059.99</v>
+        <v>198243.21</v>
       </c>
       <c r="C126" s="5" t="n">
-        <v>5253.49</v>
+        <v>4473.49</v>
       </c>
       <c r="D126" s="5" t="n">
-        <v>239806.51</v>
+        <v>193769.73</v>
       </c>
       <c r="E126" t="n">
         <v>2</v>
@@ -3985,12 +3985,12 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME short (risk 2,642); US_Dollar_Index_Futures long (risk 2,611)</t>
+          <t>Bitcoin_Per_USD_CME short (risk 2,250); US_Dollar_Index_Futures long (risk 2,224)</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures target_r (+17,983); Japanese_Yen_Futures stop (-2,762)</t>
+          <t>Corn_CBOT_Futures target_r (+4,881); Japanese_Yen_Futures stop (-2,352)</t>
         </is>
       </c>
     </row>
@@ -3999,13 +3999,13 @@
         <v>46149</v>
       </c>
       <c r="B127" s="5" t="n">
-        <v>251656.14</v>
+        <v>203860.01</v>
       </c>
       <c r="C127" s="5" t="n">
-        <v>8213.559999999999</v>
+        <v>6750.36</v>
       </c>
       <c r="D127" s="5" t="n">
-        <v>243442.57</v>
+        <v>197109.65</v>
       </c>
       <c r="E127" t="n">
         <v>3</v>
@@ -4017,12 +4017,12 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>EURO_Futures short (risk 2,818); NY_Platinum_Futures short (risk 2,785)</t>
+          <t>EURO_Futures short (risk 2,277); NY_Platinum_Futures short (risk 2,250)</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME target_r (+6,596)</t>
+          <t>Bitcoin_Per_USD_CME target_r (+5,617)</t>
         </is>
       </c>
     </row>
@@ -4031,13 +4031,13 @@
         <v>46150</v>
       </c>
       <c r="B128" s="5" t="n">
-        <v>258754.78</v>
+        <v>209595.89</v>
       </c>
       <c r="C128" s="5" t="n">
-        <v>5395.84</v>
+        <v>4473.57</v>
       </c>
       <c r="D128" s="5" t="n">
-        <v>253358.94</v>
+        <v>205122.32</v>
       </c>
       <c r="E128" t="n">
         <v>2</v>
@@ -4050,7 +4050,7 @@
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
-          <t>EURO_Futures target_r (+7,099)</t>
+          <t>EURO_Futures target_r (+5,736)</t>
         </is>
       </c>
     </row>
@@ -4059,13 +4059,13 @@
         <v>46153</v>
       </c>
       <c r="B129" s="5" t="n">
-        <v>255931.88</v>
+        <v>207314.92</v>
       </c>
       <c r="C129" s="5" t="n">
-        <v>5588.19</v>
+        <v>4633.71</v>
       </c>
       <c r="D129" s="5" t="n">
-        <v>250343.7</v>
+        <v>202681.21</v>
       </c>
       <c r="E129" t="n">
         <v>2</v>
@@ -4077,12 +4077,12 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX short (risk 2,977)</t>
+          <t>Gold_Futures_COMEX short (risk 2,410)</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures stop (-2,823)</t>
+          <t>NY_Platinum_Futures stop (-2,281)</t>
         </is>
       </c>
     </row>
@@ -4091,13 +4091,13 @@
         <v>46154</v>
       </c>
       <c r="B130" s="5" t="n">
-        <v>259366.39</v>
+        <v>210368.26</v>
       </c>
       <c r="C130" s="5" t="n">
-        <v>2941.54</v>
+        <v>2381.5</v>
       </c>
       <c r="D130" s="5" t="n">
-        <v>256424.85</v>
+        <v>207986.76</v>
       </c>
       <c r="E130" t="n">
         <v>1</v>
@@ -4109,12 +4109,12 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX short (risk 2,942)</t>
+          <t>Silver_Futures_COMEX short (risk 2,382)</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX unknown_pl (-3,072); US_Dollar_Index_Futures target_r (+6,507)</t>
+          <t>Gold_Futures_COMEX unknown_pl (-2,487); US_Dollar_Index_Futures target_r (+5,541)</t>
         </is>
       </c>
     </row>
@@ -4123,13 +4123,13 @@
         <v>46155</v>
       </c>
       <c r="B131" s="5" t="n">
-        <v>256418.72</v>
+        <v>207981.8</v>
       </c>
       <c r="C131" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D131" s="5" t="n">
-        <v>256418.72</v>
+        <v>207981.8</v>
       </c>
       <c r="E131" t="n">
         <v>0</v>
@@ -4138,7 +4138,7 @@
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX stop (-2,948)</t>
+          <t>Silver_Futures_COMEX stop (-2,386)</t>
         </is>
       </c>
     </row>
@@ -4147,13 +4147,13 @@
         <v>46156</v>
       </c>
       <c r="B132" s="5" t="n">
-        <v>256418.72</v>
+        <v>207981.8</v>
       </c>
       <c r="C132" s="5" t="n">
-        <v>3012.92</v>
+        <v>2443.79</v>
       </c>
       <c r="D132" s="5" t="n">
-        <v>253405.8</v>
+        <v>205538.01</v>
       </c>
       <c r="E132" t="n">
         <v>1</v>
@@ -4165,7 +4165,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 3,013)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 2,444)</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
@@ -4175,13 +4175,13 @@
         <v>46157</v>
       </c>
       <c r="B133" s="5" t="n">
-        <v>265746.43</v>
+        <v>214024.31</v>
       </c>
       <c r="C133" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D133" s="5" t="n">
-        <v>265746.43</v>
+        <v>214024.31</v>
       </c>
       <c r="E133" t="n">
         <v>0</v>
@@ -4190,7 +4190,7 @@
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT target_r (+9,328)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT target_r (+6,043)</t>
         </is>
       </c>
     </row>
@@ -4199,13 +4199,13 @@
         <v>46160</v>
       </c>
       <c r="B134" s="5" t="n">
-        <v>265746.43</v>
+        <v>214024.31</v>
       </c>
       <c r="C134" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>265746.43</v>
+        <v>214024.31</v>
       </c>
       <c r="E134" t="n">
         <v>0</v>
@@ -4219,13 +4219,13 @@
         <v>46161</v>
       </c>
       <c r="B135" s="5" t="n">
-        <v>265746.43</v>
+        <v>214024.31</v>
       </c>
       <c r="C135" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>265746.43</v>
+        <v>214024.31</v>
       </c>
       <c r="E135" t="n">
         <v>0</v>
@@ -4239,13 +4239,13 @@
         <v>46162</v>
       </c>
       <c r="B136" s="5" t="n">
-        <v>265746.43</v>
+        <v>214024.31</v>
       </c>
       <c r="C136" s="5" t="n">
-        <v>3122.52</v>
+        <v>2514.79</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>262623.91</v>
+        <v>211509.52</v>
       </c>
       <c r="E136" t="n">
         <v>1</v>
@@ -4257,7 +4257,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures short (risk 3,123)</t>
+          <t>US_Dollar_Index_Futures short (risk 2,515)</t>
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
@@ -4267,13 +4267,13 @@
         <v>46163</v>
       </c>
       <c r="B137" s="5" t="n">
-        <v>265746.43</v>
+        <v>214024.31</v>
       </c>
       <c r="C137" s="5" t="n">
-        <v>6208.35</v>
+        <v>5000.02</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>259538.08</v>
+        <v>209024.29</v>
       </c>
       <c r="E137" t="n">
         <v>2</v>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures long (risk 3,086)</t>
+          <t>NY_Palladium_Futures long (risk 2,485)</t>
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
@@ -4295,13 +4295,13 @@
         <v>46164</v>
       </c>
       <c r="B138" s="5" t="n">
-        <v>273442.91</v>
+        <v>220222.83</v>
       </c>
       <c r="C138" s="5" t="n">
-        <v>3122.52</v>
+        <v>2514.79</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>270320.39</v>
+        <v>217708.04</v>
       </c>
       <c r="E138" t="n">
         <v>1</v>
@@ -4314,7 +4314,7 @@
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures target_r (+7,696)</t>
+          <t>NY_Palladium_Futures target_r (+6,199)</t>
         </is>
       </c>
     </row>
@@ -4323,13 +4323,13 @@
         <v>46167</v>
       </c>
       <c r="B139" s="5" t="n">
-        <v>281217.18</v>
+        <v>226484</v>
       </c>
       <c r="C139" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D139" s="5" t="n">
-        <v>281217.18</v>
+        <v>226484</v>
       </c>
       <c r="E139" t="n">
         <v>0</v>
@@ -4338,7 +4338,7 @@
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures target_r (+7,774)</t>
+          <t>US_Dollar_Index_Futures target_r (+6,261)</t>
         </is>
       </c>
     </row>
@@ -4347,13 +4347,13 @@
         <v>46168</v>
       </c>
       <c r="B140" s="5" t="n">
-        <v>281217.18</v>
+        <v>226484</v>
       </c>
       <c r="C140" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D140" s="5" t="n">
-        <v>281217.18</v>
+        <v>226484</v>
       </c>
       <c r="E140" t="n">
         <v>0</v>
@@ -4367,13 +4367,13 @@
         <v>46169</v>
       </c>
       <c r="B141" s="5" t="n">
-        <v>281217.18</v>
+        <v>226484</v>
       </c>
       <c r="C141" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D141" s="5" t="n">
-        <v>281217.18</v>
+        <v>226484</v>
       </c>
       <c r="E141" t="n">
         <v>0</v>
@@ -4387,13 +4387,13 @@
         <v>46170</v>
       </c>
       <c r="B142" s="5" t="n">
-        <v>281217.18</v>
+        <v>226484</v>
       </c>
       <c r="C142" s="5" t="n">
-        <v>6569.78</v>
+        <v>5291.11</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>274647.4</v>
+        <v>221192.89</v>
       </c>
       <c r="E142" t="n">
         <v>2</v>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX long (risk 3,304); US_Dollar_Index_Futures short (risk 3,265)</t>
+          <t>Silver_Futures_COMEX long (risk 2,661); US_Dollar_Index_Futures short (risk 2,630)</t>
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
@@ -4415,13 +4415,13 @@
         <v>46174</v>
       </c>
       <c r="B143" s="5" t="n">
-        <v>281217.18</v>
+        <v>226484</v>
       </c>
       <c r="C143" s="5" t="n">
-        <v>6569.78</v>
+        <v>5291.11</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>274647.4</v>
+        <v>221192.89</v>
       </c>
       <c r="E143" t="n">
         <v>2</v>
@@ -4439,13 +4439,13 @@
         <v>46175</v>
       </c>
       <c r="B144" s="5" t="n">
-        <v>281217.18</v>
+        <v>226484</v>
       </c>
       <c r="C144" s="5" t="n">
-        <v>6569.78</v>
+        <v>5291.11</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>274647.4</v>
+        <v>221192.89</v>
       </c>
       <c r="E144" t="n">
         <v>2</v>
@@ -4463,13 +4463,13 @@
         <v>46176</v>
       </c>
       <c r="B145" s="5" t="n">
-        <v>277900.48</v>
+        <v>223812.83</v>
       </c>
       <c r="C145" s="5" t="n">
-        <v>3304.3</v>
+        <v>2661.19</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>274596.18</v>
+        <v>221151.64</v>
       </c>
       <c r="E145" t="n">
         <v>1</v>
@@ -4482,7 +4482,7 @@
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures stop (-3,317)</t>
+          <t>US_Dollar_Index_Futures stop (-2,671)</t>
         </is>
       </c>
     </row>
@@ -4491,13 +4491,13 @@
         <v>46177</v>
       </c>
       <c r="B146" s="5" t="n">
-        <v>277900.48</v>
+        <v>223812.83</v>
       </c>
       <c r="C146" s="5" t="n">
-        <v>3304.3</v>
+        <v>2661.19</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>274596.18</v>
+        <v>221151.64</v>
       </c>
       <c r="E146" t="n">
         <v>1</v>
@@ -4515,13 +4515,13 @@
         <v>46178</v>
       </c>
       <c r="B147" s="5" t="n">
-        <v>274589.02</v>
+        <v>221145.87</v>
       </c>
       <c r="C147" s="5" t="n">
-        <v>3226.51</v>
+        <v>2598.53</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>271362.51</v>
+        <v>218547.34</v>
       </c>
       <c r="E147" t="n">
         <v>1</v>
@@ -4533,12 +4533,12 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini short (risk 3,227)</t>
+          <t>Dow_Futures_E_mini short (risk 2,599)</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX stop (-3,311)</t>
+          <t>Silver_Futures_COMEX stop (-2,667)</t>
         </is>
       </c>
     </row>
@@ -4547,13 +4547,13 @@
         <v>46181</v>
       </c>
       <c r="B148" s="5" t="n">
-        <v>303384.07</v>
+        <v>227593.17</v>
       </c>
       <c r="C148" s="5" t="n">
-        <v>6339.55</v>
+        <v>5105.69</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>297044.51</v>
+        <v>222487.48</v>
       </c>
       <c r="E148" t="n">
         <v>2</v>
@@ -4565,12 +4565,12 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX long (risk 3,189); US_Dollar_Index_Futures short (risk 3,151)</t>
+          <t>Gold_Futures_COMEX long (risk 2,568); US_Dollar_Index_Futures short (risk 2,538)</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini target_r (+28,795)</t>
+          <t>Dow_Futures_E_mini target_r (+6,447)</t>
         </is>
       </c>
     </row>
@@ -4579,13 +4579,13 @@
         <v>46182</v>
       </c>
       <c r="B149" s="5" t="n">
-        <v>308002.91</v>
+        <v>231313.05</v>
       </c>
       <c r="C149" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D149" s="5" t="n">
-        <v>308002.91</v>
+        <v>231313.05</v>
       </c>
       <c r="E149" t="n">
         <v>0</v>
@@ -4594,7 +4594,7 @@
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX stop (-3,212); US_Dollar_Index_Futures target_r (+7,831)</t>
+          <t>Gold_Futures_COMEX stop (-2,587); US_Dollar_Index_Futures target_r (+6,307)</t>
         </is>
       </c>
     </row>
@@ -4603,13 +4603,13 @@
         <v>46183</v>
       </c>
       <c r="B150" s="5" t="n">
-        <v>308002.91</v>
+        <v>231313.05</v>
       </c>
       <c r="C150" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>308002.91</v>
+        <v>231313.05</v>
       </c>
       <c r="E150" t="n">
         <v>0</v>
@@ -4623,13 +4623,13 @@
         <v>46184</v>
       </c>
       <c r="B151" s="5" t="n">
-        <v>308002.91</v>
+        <v>231313.05</v>
       </c>
       <c r="C151" s="5" t="n">
-        <v>7195.54</v>
+        <v>5403.92</v>
       </c>
       <c r="D151" s="5" t="n">
-        <v>300807.37</v>
+        <v>225909.13</v>
       </c>
       <c r="E151" t="n">
         <v>2</v>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX long (risk 3,619); US_Dollar_Index_Futures short (risk 3,577)</t>
+          <t>Gold_Futures_COMEX long (risk 2,718); US_Dollar_Index_Futures short (risk 2,686)</t>
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
@@ -4651,13 +4651,13 @@
         <v>46185</v>
       </c>
       <c r="B152" s="5" t="n">
-        <v>325950.44</v>
+        <v>244791.81</v>
       </c>
       <c r="C152" s="5" t="n">
-        <v>3534.49</v>
+        <v>2654.43</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>322415.95</v>
+        <v>242137.38</v>
       </c>
       <c r="E152" t="n">
         <v>1</v>
@@ -4669,12 +4669,12 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures long (risk 3,534)</t>
+          <t>Corn_CBOT_Futures long (risk 2,654)</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX target_r (+9,035); US_Dollar_Index_Futures target_r (+8,913)</t>
+          <t>Gold_Futures_COMEX target_r (+6,785); US_Dollar_Index_Futures target_r (+6,693)</t>
         </is>
       </c>
     </row>
@@ -4683,13 +4683,13 @@
         <v>46188</v>
       </c>
       <c r="B153" s="5" t="n">
-        <v>321892.32</v>
+        <v>241744.13</v>
       </c>
       <c r="C153" s="5" t="n">
-        <v>3788.39</v>
+        <v>2845.11</v>
       </c>
       <c r="D153" s="5" t="n">
-        <v>318103.94</v>
+        <v>238899.02</v>
       </c>
       <c r="E153" t="n">
         <v>1</v>
@@ -4701,12 +4701,12 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT long (risk 3,788)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT long (risk 2,845)</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures stop (-4,058)</t>
+          <t>Corn_CBOT_Futures stop (-3,048)</t>
         </is>
       </c>
     </row>
@@ -4715,13 +4715,13 @@
         <v>46189</v>
       </c>
       <c r="B154" s="5" t="n">
-        <v>331248.49</v>
+        <v>248770.7</v>
       </c>
       <c r="C154" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>331248.49</v>
+        <v>248770.7</v>
       </c>
       <c r="E154" t="n">
         <v>0</v>
@@ -4730,7 +4730,7 @@
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT target_r (+9,356)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT target_r (+7,027)</t>
         </is>
       </c>
     </row>
@@ -4739,13 +4739,13 @@
         <v>46190</v>
       </c>
       <c r="B155" s="5" t="n">
-        <v>331248.49</v>
+        <v>248770.7</v>
       </c>
       <c r="C155" s="5" t="n">
-        <v>3892.17</v>
+        <v>2923.06</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>327356.32</v>
+        <v>245847.65</v>
       </c>
       <c r="E155" t="n">
         <v>1</v>
@@ -4757,7 +4757,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures short (risk 3,892)</t>
+          <t>US_Dollar_Index_Futures short (risk 2,923)</t>
         </is>
       </c>
       <c r="H155" t="inlineStr"/>
@@ -4767,13 +4767,13 @@
         <v>46191</v>
       </c>
       <c r="B156" s="5" t="n">
-        <v>327303.55</v>
+        <v>245808.01</v>
       </c>
       <c r="C156" s="5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>327303.55</v>
+        <v>245808.01</v>
       </c>
       <c r="E156" t="n">
         <v>0</v>
@@ -4782,7 +4782,7 @@
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures stop (-3,945)</t>
+          <t>US_Dollar_Index_Futures stop (-2,963)</t>
         </is>
       </c>
     </row>
@@ -4791,13 +4791,13 @@
         <v>46192</v>
       </c>
       <c r="B157" s="5" t="n">
-        <v>327303.55</v>
+        <v>245808.01</v>
       </c>
       <c r="C157" s="5" t="n">
-        <v>3845.82</v>
+        <v>2888.24</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>323457.73</v>
+        <v>242919.77</v>
       </c>
       <c r="E157" t="n">
         <v>1</v>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures short (risk 3,846)</t>
+          <t>US_Dollar_Index_Futures short (risk 2,888)</t>
         </is>
       </c>
       <c r="H157" t="inlineStr"/>
@@ -4819,13 +4819,13 @@
         <v>46195</v>
       </c>
       <c r="B158" s="5" t="n">
-        <v>327303.55</v>
+        <v>245808.01</v>
       </c>
       <c r="C158" s="5" t="n">
-        <v>3845.82</v>
+        <v>2888.24</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>323457.73</v>
+        <v>242919.77</v>
       </c>
       <c r="E158" t="n">
         <v>1</v>
@@ -4843,13 +4843,13 @@
         <v>46196</v>
       </c>
       <c r="B159" s="5" t="n">
-        <v>323404.69</v>
+        <v>242879.93</v>
       </c>
       <c r="C159" s="5" t="n">
-        <v>3800.63</v>
+        <v>2854.31</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>319604.06</v>
+        <v>240025.62</v>
       </c>
       <c r="E159" t="n">
         <v>1</v>
@@ -4861,12 +4861,12 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures long (risk 3,801)</t>
+          <t>NY_Platinum_Futures long (risk 2,854)</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures stop (-3,899)</t>
+          <t>US_Dollar_Index_Futures stop (-2,928)</t>
         </is>
       </c>
     </row>
@@ -4875,13 +4875,13 @@
         <v>46197</v>
       </c>
       <c r="B160" s="5" t="n">
-        <v>319529.9</v>
+        <v>239969.93</v>
       </c>
       <c r="C160" s="5" t="n">
-        <v>3755.35</v>
+        <v>2820.3</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>315774.55</v>
+        <v>237149.63</v>
       </c>
       <c r="E160" t="n">
         <v>1</v>
@@ -4893,12 +4893,12 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>EURO_Futures long (risk 3,755)</t>
+          <t>EURO_Futures long (risk 2,820)</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures stop (-3,875)</t>
+          <t>NY_Platinum_Futures stop (-2,910)</t>
         </is>
       </c>
     </row>
@@ -4907,13 +4907,13 @@
         <v>46198</v>
       </c>
       <c r="B161" s="5" t="n">
-        <v>319529.9</v>
+        <v>239969.93</v>
       </c>
       <c r="C161" s="5" t="n">
-        <v>18337.21</v>
+        <v>13771.42</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>301192.68</v>
+        <v>226198.51</v>
       </c>
       <c r="E161" t="n">
         <v>5</v>
@@ -4925,7 +4925,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures short (risk 3,710); NY_Palladium_Futures long (risk 3,667); NY_Platinum_Futures long (risk 3,624); US_Dollar_Index_Futures short (risk 3,581)</t>
+          <t>NY_Natural_Gas_Futures short (risk 2,787); NY_Palladium_Futures long (risk 2,754); NY_Platinum_Futures long (risk 2,721); US_Dollar_Index_Futures short (risk 2,689)</t>
         </is>
       </c>
       <c r="H161" t="inlineStr"/>
@@ -4935,13 +4935,13 @@
         <v>46199</v>
       </c>
       <c r="B162" s="5" t="n">
-        <v>342838.66</v>
+        <v>257475.02</v>
       </c>
       <c r="C162" s="5" t="n">
-        <v>3623.67</v>
+        <v>2721.41</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>339214.99</v>
+        <v>254753.61</v>
       </c>
       <c r="E162" t="n">
         <v>1</v>
@@ -4954,7 +4954,7 @@
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr">
         <is>
-          <t>EURO_Futures target_r (+9,361); NY_Natural_Gas_Futures stop (-4,013); NY_Palladium_Futures target_r (+9,070); US_Dollar_Index_Futures target_r (+8,890)</t>
+          <t>EURO_Futures target_r (+7,030); NY_Natural_Gas_Futures stop (-3,014); NY_Palladium_Futures target_r (+6,812); US_Dollar_Index_Futures target_r (+6,677)</t>
         </is>
       </c>
     </row>
@@ -4963,13 +4963,13 @@
         <v>46202</v>
       </c>
       <c r="B163" s="5" t="n">
-        <v>342838.66</v>
+        <v>257475.02</v>
       </c>
       <c r="C163" s="5" t="n">
-        <v>3623.67</v>
+        <v>2721.41</v>
       </c>
       <c r="D163" s="5" t="n">
-        <v>339214.99</v>
+        <v>254753.61</v>
       </c>
       <c r="E163" t="n">
         <v>1</v>
@@ -4987,13 +4987,13 @@
         <v>46203</v>
       </c>
       <c r="B164" s="5" t="n">
-        <v>342838.66</v>
+        <v>257475.02</v>
       </c>
       <c r="C164" s="5" t="n">
-        <v>15441.05</v>
+        <v>11596.37</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>327397.61</v>
+        <v>245878.65</v>
       </c>
       <c r="E164" t="n">
         <v>4</v>
@@ -5005,7 +5005,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT long (risk 3,986); German_Long_Bund short (risk 3,939); Gold_Futures_COMEX long (risk 3,893)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT long (risk 2,993); German_Long_Bund short (risk 2,958); Gold_Futures_COMEX long (risk 2,923)</t>
         </is>
       </c>
       <c r="H164" t="inlineStr"/>
@@ -5015,13 +5015,13 @@
         <v>46204</v>
       </c>
       <c r="B165" s="5" t="n">
-        <v>368151.61</v>
+        <v>276485.29</v>
       </c>
       <c r="C165" s="5" t="n">
-        <v>7648.64</v>
+        <v>5744.2</v>
       </c>
       <c r="D165" s="5" t="n">
-        <v>360502.97</v>
+        <v>270741.09</v>
       </c>
       <c r="E165" t="n">
         <v>2</v>
@@ -5033,12 +5033,12 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini short (risk 3,847); Sugar_World_CSCE_Futures short (risk 3,802)</t>
+          <t>Dow_Futures_E_mini short (risk 2,889); Sugar_World_CSCE_Futures short (risk 2,855)</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT target_r (+9,770); German_Long_Bund target_r (+9,505); Gold_Futures_COMEX target_r (+9,705); NY_Platinum_Futures stop (-3,666)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT target_r (+7,337); German_Long_Bund target_r (+7,138); Gold_Futures_COMEX target_r (+7,288); NY_Platinum_Futures stop (-2,754)</t>
         </is>
       </c>
     </row>
@@ -5047,13 +5047,13 @@
         <v>46205</v>
       </c>
       <c r="B166" s="5" t="n">
-        <v>364263.33</v>
+        <v>273565.15</v>
       </c>
       <c r="C166" s="5" t="n">
-        <v>3801.72</v>
+        <v>2855.13</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>360461.61</v>
+        <v>270710.02</v>
       </c>
       <c r="E166" t="n">
         <v>1</v>
@@ -5066,7 +5066,7 @@
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini stop (-3,888)</t>
+          <t>Dow_Futures_E_mini stop (-2,920)</t>
         </is>
       </c>
     </row>
@@ -5075,13 +5075,13 @@
         <v>46206</v>
       </c>
       <c r="B167" s="5" t="n">
-        <v>364263.33</v>
+        <v>273565.15</v>
       </c>
       <c r="C167" s="5" t="n">
-        <v>3801.72</v>
+        <v>2855.13</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>360461.61</v>
+        <v>270710.02</v>
       </c>
       <c r="E167" t="n">
         <v>1</v>
@@ -5099,13 +5099,13 @@
         <v>46210</v>
       </c>
       <c r="B168" s="5" t="n">
-        <v>359876.73</v>
+        <v>270270.77</v>
       </c>
       <c r="C168" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D168" s="5" t="n">
-        <v>359876.73</v>
+        <v>270270.77</v>
       </c>
       <c r="E168" t="n">
         <v>0</v>
@@ -5114,7 +5114,7 @@
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Sugar_World_CSCE_Futures stop (-4,387)</t>
+          <t>Sugar_World_CSCE_Futures stop (-3,294)</t>
         </is>
       </c>
     </row>
@@ -5123,13 +5123,13 @@
         <v>46211</v>
       </c>
       <c r="B169" s="5" t="n">
-        <v>359876.73</v>
+        <v>270270.77</v>
       </c>
       <c r="C169" s="5" t="n">
-        <v>8407.42</v>
+        <v>6314.05</v>
       </c>
       <c r="D169" s="5" t="n">
-        <v>351469.31</v>
+        <v>263956.72</v>
       </c>
       <c r="E169" t="n">
         <v>2</v>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME long (risk 4,229); NY_Natural_Gas_Futures short (risk 4,179)</t>
+          <t>Live_Cattle_Futures_CME long (risk 3,176); NY_Natural_Gas_Futures short (risk 3,138)</t>
         </is>
       </c>
       <c r="H169" t="inlineStr"/>
@@ -5151,13 +5151,13 @@
         <v>46212</v>
       </c>
       <c r="B170" s="5" t="n">
-        <v>384657.99</v>
+        <v>285857.21</v>
       </c>
       <c r="C170" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D170" s="5" t="n">
-        <v>384657.99</v>
+        <v>285857.21</v>
       </c>
       <c r="E170" t="n">
         <v>0</v>
@@ -5166,7 +5166,7 @@
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME target_r (+14,498); NY_Natural_Gas_Futures target_r (+10,283)</t>
+          <t>Live_Cattle_Futures_CME target_r (+7,864); NY_Natural_Gas_Futures target_r (+7,723)</t>
         </is>
       </c>
     </row>
@@ -5175,13 +5175,13 @@
         <v>46213</v>
       </c>
       <c r="B171" s="5" t="n">
-        <v>384657.99</v>
+        <v>285857.21</v>
       </c>
       <c r="C171" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D171" s="5" t="n">
-        <v>384657.99</v>
+        <v>285857.21</v>
       </c>
       <c r="E171" t="n">
         <v>0</v>
@@ -5195,13 +5195,13 @@
         <v>46216</v>
       </c>
       <c r="B172" s="5" t="n">
-        <v>384657.99</v>
+        <v>285857.21</v>
       </c>
       <c r="C172" s="5" t="n">
-        <v>4519.73</v>
+        <v>3358.82</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>380138.25</v>
+        <v>282498.38</v>
       </c>
       <c r="E172" t="n">
         <v>1</v>
@@ -5213,7 +5213,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 4,520)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 3,359)</t>
         </is>
       </c>
       <c r="H172" t="inlineStr"/>
@@ -5223,13 +5223,13 @@
         <v>46217</v>
       </c>
       <c r="B173" s="5" t="n">
-        <v>384657.99</v>
+        <v>285857.21</v>
       </c>
       <c r="C173" s="5" t="n">
-        <v>4519.73</v>
+        <v>3358.82</v>
       </c>
       <c r="D173" s="5" t="n">
-        <v>380138.25</v>
+        <v>282498.38</v>
       </c>
       <c r="E173" t="n">
         <v>1</v>
@@ -5247,13 +5247,13 @@
         <v>46218</v>
       </c>
       <c r="B174" s="5" t="n">
-        <v>379915.06</v>
+        <v>282332.52</v>
       </c>
       <c r="C174" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D174" s="5" t="n">
-        <v>379915.06</v>
+        <v>282332.52</v>
       </c>
       <c r="E174" t="n">
         <v>0</v>
@@ -5262,7 +5262,7 @@
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT stop (-4,743)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT stop (-3,525)</t>
         </is>
       </c>
     </row>
@@ -5271,13 +5271,13 @@
         <v>46219</v>
       </c>
       <c r="B175" s="5" t="n">
-        <v>379915.06</v>
+        <v>282332.52</v>
       </c>
       <c r="C175" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D175" s="5" t="n">
-        <v>379915.06</v>
+        <v>282332.52</v>
       </c>
       <c r="E175" t="n">
         <v>0</v>
@@ -5291,13 +5291,13 @@
         <v>46220</v>
       </c>
       <c r="B176" s="5" t="n">
-        <v>379915.06</v>
+        <v>282332.52</v>
       </c>
       <c r="C176" s="5" t="n">
-        <v>4464</v>
+        <v>3317.41</v>
       </c>
       <c r="D176" s="5" t="n">
-        <v>375451.06</v>
+        <v>279015.11</v>
       </c>
       <c r="E176" t="n">
         <v>1</v>
@@ -5309,7 +5309,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX long (risk 4,464)</t>
+          <t>Gold_Futures_COMEX long (risk 3,317)</t>
         </is>
       </c>
       <c r="H176" t="inlineStr"/>
@@ -5319,13 +5319,13 @@
         <v>46223</v>
       </c>
       <c r="B177" s="5" t="n">
-        <v>391032.75</v>
+        <v>290594.59</v>
       </c>
       <c r="C177" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D177" s="5" t="n">
-        <v>391032.75</v>
+        <v>290594.59</v>
       </c>
       <c r="E177" t="n">
         <v>0</v>
@@ -5334,7 +5334,7 @@
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX target_r (+11,118)</t>
+          <t>Gold_Futures_COMEX target_r (+8,262)</t>
         </is>
       </c>
     </row>
@@ -5343,13 +5343,13 @@
         <v>46224</v>
       </c>
       <c r="B178" s="5" t="n">
-        <v>391032.75</v>
+        <v>290594.59</v>
       </c>
       <c r="C178" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D178" s="5" t="n">
-        <v>391032.75</v>
+        <v>290594.59</v>
       </c>
       <c r="E178" t="n">
         <v>0</v>
@@ -5363,13 +5363,13 @@
         <v>46225</v>
       </c>
       <c r="B179" s="5" t="n">
-        <v>391032.75</v>
+        <v>290594.59</v>
       </c>
       <c r="C179" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D179" s="5" t="n">
-        <v>391032.75</v>
+        <v>290594.59</v>
       </c>
       <c r="E179" t="n">
         <v>0</v>
@@ -5383,13 +5383,13 @@
         <v>46226</v>
       </c>
       <c r="B180" s="5" t="n">
-        <v>391032.75</v>
+        <v>290594.59</v>
       </c>
       <c r="C180" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D180" s="5" t="n">
-        <v>391032.75</v>
+        <v>290594.59</v>
       </c>
       <c r="E180" t="n">
         <v>0</v>
@@ -5403,13 +5403,13 @@
         <v>46227</v>
       </c>
       <c r="B181" s="5" t="n">
-        <v>390832.54</v>
+        <v>290445.81</v>
       </c>
       <c r="C181" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D181" s="5" t="n">
-        <v>390832.54</v>
+        <v>290445.81</v>
       </c>
       <c r="E181" t="n">
         <v>0</v>
@@ -5417,7 +5417,7 @@
       <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 4,595); Corn_CBOT_Futures short (risk 4,541)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 3,414); Corn_CBOT_Futures short (risk 3,374)</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -5701,13 +5701,13 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>5.238</v>
+        <v>2.5</v>
       </c>
       <c r="G5" t="n">
         <v>0.002</v>
       </c>
       <c r="H5" t="n">
-        <v>5.236</v>
+        <v>2.498</v>
       </c>
       <c r="I5" s="5" t="n">
         <v>111389.2</v>
@@ -5716,10 +5716,10 @@
         <v>1308.82</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>6852.71</v>
+        <v>3268.89</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>118231.44</v>
+        <v>114647.62</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -5752,29 +5752,29 @@
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>3.319</v>
+        <v>-1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.043</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>3.277</v>
+        <v>-1.085</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>118231.44</v>
+        <v>114647.62</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>1389.22</v>
-      </c>
-      <c r="K6" s="6" t="n">
-        <v>4551.84</v>
+        <v>1347.11</v>
+      </c>
+      <c r="K6" s="7" t="n">
+        <v>-1461.76</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>122783.28</v>
+        <v>113185.86</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>unknown_pl</t>
         </is>
       </c>
     </row>
@@ -5812,16 +5812,16 @@
         <v>2.494</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>122783.28</v>
+        <v>113185.86</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>1442.7</v>
+        <v>1329.93</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>3598.04</v>
+        <v>3316.8</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>126381.33</v>
+        <v>116502.66</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -5863,16 +5863,16 @@
         <v>-3.054</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>126381.33</v>
+        <v>116502.66</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>1484.98</v>
+        <v>1368.91</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>-4535.76</v>
+        <v>-4181.22</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>121845.57</v>
+        <v>112321.45</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -5914,16 +5914,16 @@
         <v>-1.278</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>124896.34</v>
+        <v>115133.76</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>1467.53</v>
+        <v>1352.82</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>-1875.25</v>
+        <v>-1728.67</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>119970.32</v>
+        <v>110592.78</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -5965,16 +5965,16 @@
         <v>-1.069</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>120378.04</v>
+        <v>110968.63</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>1414.44</v>
+        <v>1303.88</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>-1511.99</v>
+        <v>-1393.8</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>118458.33</v>
+        <v>109198.98</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -6016,16 +6016,16 @@
         <v>-1.06</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>118963.6</v>
+        <v>109664.74</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>1397.82</v>
+        <v>1288.56</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>-1481.27</v>
+        <v>-1365.49</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>116977.06</v>
+        <v>107833.49</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -6067,16 +6067,16 @@
         <v>3.36</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>117565.77</v>
+        <v>108376.18</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>1381.4</v>
+        <v>1273.42</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>4641.2</v>
+        <v>4278.42</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>121618.26</v>
+        <v>112111.91</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -6118,16 +6118,16 @@
         <v>-1.026</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>115776.66</v>
+        <v>106726.92</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>1360.38</v>
+        <v>1254.04</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>-1396.18</v>
+        <v>-1287.04</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>123850.52</v>
+        <v>113379.05</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -6169,16 +6169,16 @@
         <v>-1.002</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>120257.89</v>
+        <v>110857.87</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>1413.03</v>
+        <v>1302.58</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>-1416.02</v>
+        <v>-1305.34</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>120202.24</v>
+        <v>110806.57</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -6220,16 +6220,16 @@
         <v>-1.004</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>118844.86</v>
+        <v>109555.29</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>1396.43</v>
+        <v>1287.27</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>-1402.29</v>
+        <v>-1292.68</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>118799.95</v>
+        <v>109513.89</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -6271,16 +6271,16 @@
         <v>2.499</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>117448.43</v>
+        <v>108268.01</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>1380.02</v>
+        <v>1272.15</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>3449.13</v>
+        <v>3179.52</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>122249.08</v>
+        <v>112693.42</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -6322,16 +6322,16 @@
         <v>-1.005</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>116059.56</v>
+        <v>106987.7</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>1363.7</v>
+        <v>1257.11</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>-1370.01</v>
+        <v>-1262.92</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>120879.07</v>
+        <v>111430.5</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -6364,25 +6364,25 @@
         <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>3.111</v>
+        <v>2.5</v>
       </c>
       <c r="G18" t="n">
         <v>0.001</v>
       </c>
       <c r="H18" t="n">
-        <v>3.11</v>
+        <v>2.499</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>119525</v>
+        <v>110182.27</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>1404.42</v>
+        <v>1294.64</v>
       </c>
       <c r="K18" s="6" t="n">
-        <v>4367.63</v>
+        <v>3235.59</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>125246.7</v>
+        <v>114666.09</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -6424,16 +6424,16 @@
         <v>2.499</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>123886.32</v>
+        <v>113412.05</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>1455.66</v>
+        <v>1332.59</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>3637.55</v>
+        <v>3330</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>127488.07</v>
+        <v>116709.05</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -6475,16 +6475,16 @@
         <v>-1.009</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>122430.66</v>
+        <v>112079.46</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>1438.56</v>
+        <v>1316.93</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>-1451.52</v>
+        <v>-1328.8</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>126036.55</v>
+        <v>115380.25</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -6526,16 +6526,16 @@
         <v>-1.138</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>120956.3</v>
+        <v>110729.52</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>1421.24</v>
+        <v>1301.07</v>
       </c>
       <c r="K21" s="7" t="n">
-        <v>-1617.27</v>
+        <v>-1480.53</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>124419.28</v>
+        <v>113899.72</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
@@ -6577,16 +6577,16 @@
         <v>2.499</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>124615.32</v>
+        <v>114079.18</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>1464.23</v>
+        <v>1340.43</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>3659.82</v>
+        <v>3350.39</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>128079.1</v>
+        <v>117250.11</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
@@ -6628,16 +6628,16 @@
         <v>-1.004</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>122955.05</v>
+        <v>112559.29</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>1444.72</v>
+        <v>1322.57</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>-1450.87</v>
+        <v>-1328.2</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>126628.24</v>
+        <v>115921.91</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -6679,16 +6679,16 @@
         <v>2.357</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>126628.24</v>
+        <v>115921.91</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>1487.88</v>
+        <v>1362.08</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>3507.15</v>
+        <v>3210.62</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>137272.43</v>
+        <v>125666.15</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -6730,16 +6730,16 @@
         <v>2.487</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>125140.35</v>
+        <v>114559.83</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>1470.4</v>
+        <v>1346.08</v>
       </c>
       <c r="K25" s="6" t="n">
-        <v>3657.2</v>
+        <v>3347.99</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>130285.44</v>
+        <v>119269.9</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
@@ -6781,16 +6781,16 @@
         <v>2.395</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>123669.95</v>
+        <v>113213.75</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>1453.12</v>
+        <v>1330.26</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>3479.84</v>
+        <v>3185.63</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>133765.28</v>
+        <v>122455.52</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -6832,16 +6832,16 @@
         <v>2.497</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>137272.43</v>
+        <v>125666.15</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>1612.95</v>
+        <v>1476.58</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>4028.14</v>
+        <v>3687.56</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>141300.57</v>
+        <v>129353.71</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -6883,16 +6883,16 @@
         <v>-1.174</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>141300.57</v>
+        <v>129353.71</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>1660.28</v>
+        <v>1519.91</v>
       </c>
       <c r="K28" s="7" t="n">
-        <v>-1949.03</v>
+        <v>-1784.24</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>139351.55</v>
+        <v>127569.47</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
@@ -6934,16 +6934,16 @@
         <v>-1.075</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>139640.29</v>
+        <v>127833.8</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>1640.77</v>
+        <v>1502.05</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>-1764.31</v>
+        <v>-1615.14</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>137587.23</v>
+        <v>125954.33</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
@@ -6985,16 +6985,16 @@
         <v>-1.091</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>137710.77</v>
+        <v>126067.42</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>1618.1</v>
+        <v>1481.29</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>-1765.2</v>
+        <v>-1615.96</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>135822.03</v>
+        <v>124338.38</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
@@ -7036,16 +7036,16 @@
         <v>2.497</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>135822.03</v>
+        <v>124338.38</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>1595.91</v>
+        <v>1460.98</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>3984.96</v>
+        <v>3648.03</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>139806.99</v>
+        <v>127986.41</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
@@ -7087,16 +7087,16 @@
         <v>6.42</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>139806.99</v>
+        <v>127986.41</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>1642.73</v>
+        <v>1503.84</v>
       </c>
       <c r="K32" s="6" t="n">
-        <v>10546.07</v>
+        <v>9654.4</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>150353.06</v>
+        <v>137640.81</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
@@ -7138,16 +7138,16 @@
         <v>2.545</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>138164.26</v>
+        <v>126482.57</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>1623.43</v>
+        <v>1486.17</v>
       </c>
       <c r="K33" s="6" t="n">
-        <v>4130.87</v>
+        <v>3781.61</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>154483.93</v>
+        <v>141422.42</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
@@ -7189,16 +7189,16 @@
         <v>4.802</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>148729.63</v>
+        <v>136154.64</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>1747.57</v>
+        <v>1599.82</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>8391.940000000001</v>
+        <v>7682.41</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>162875.87</v>
+        <v>149104.83</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -7231,25 +7231,25 @@
         <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>6.795</v>
+        <v>2.5</v>
       </c>
       <c r="G35" t="n">
         <v>0.026</v>
       </c>
       <c r="H35" t="n">
-        <v>6.769</v>
+        <v>2.474</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>162875.87</v>
+        <v>149104.83</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>1913.79</v>
+        <v>1751.98</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>12954.95</v>
+        <v>4335.03</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>175830.82</v>
+        <v>153439.86</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -7291,16 +7291,16 @@
         <v>-1.004</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>175830.82</v>
+        <v>153439.86</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>2066.01</v>
+        <v>1802.92</v>
       </c>
       <c r="K36" s="7" t="n">
-        <v>-2073.26</v>
+        <v>-1809.24</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>183528.76</v>
+        <v>160157.52</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -7342,16 +7342,16 @@
         <v>2.375</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>173764.81</v>
+        <v>151636.94</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>2041.74</v>
+        <v>1781.73</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>4849.12</v>
+        <v>4231.62</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>180679.94</v>
+        <v>157671.48</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -7393,16 +7393,16 @@
         <v>2.439</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>171723.07</v>
+        <v>149855.21</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>2017.75</v>
+        <v>1760.8</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>4922.08</v>
+        <v>4295.28</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>185602.02</v>
+        <v>161966.76</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -7444,16 +7444,16 @@
         <v>-1.008</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>169705.32</v>
+        <v>148094.41</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>1994.04</v>
+        <v>1740.11</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>-2009.23</v>
+        <v>-1753.37</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>183515.03</v>
+        <v>160145.53</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -7495,16 +7495,16 @@
         <v>0.9350000000000001</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>181541.97</v>
+        <v>158423.73</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>2133.12</v>
+        <v>1861.48</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>1995.5</v>
+        <v>1741.38</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>185524.26</v>
+        <v>161898.9</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
@@ -7546,16 +7546,16 @@
         <v>4.148</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>183530.22</v>
+        <v>160158.79</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>2156.48</v>
+        <v>1881.87</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>8944.030000000001</v>
+        <v>7805.06</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>192459.06</v>
+        <v>167950.6</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -7588,25 +7588,25 @@
         <v>1</v>
       </c>
       <c r="F42" t="n">
-        <v>4.732</v>
+        <v>2.5</v>
       </c>
       <c r="G42" t="n">
         <v>0.004</v>
       </c>
       <c r="H42" t="n">
-        <v>4.728</v>
+        <v>2.496</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>192459.06</v>
+        <v>167950.6</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>2261.39</v>
+        <v>1973.42</v>
       </c>
       <c r="K42" s="6" t="n">
-        <v>10692.74</v>
+        <v>4925.43</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>203151.8</v>
+        <v>172876.02</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
@@ -7648,16 +7648,16 @@
         <v>2.499</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>190197.66</v>
+        <v>165977.18</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>2234.82</v>
+        <v>1950.23</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>5584.38</v>
+        <v>4873.25</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>208736.18</v>
+        <v>177749.27</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
@@ -7699,16 +7699,16 @@
         <v>2.478</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>200916.97</v>
+        <v>170925.79</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>2360.77</v>
+        <v>2008.38</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>5848.89</v>
+        <v>4975.81</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>214585.06</v>
+        <v>182725.08</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -7750,16 +7750,16 @@
         <v>-1.211</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>206375.4</v>
+        <v>175740.89</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>2424.91</v>
+        <v>2064.96</v>
       </c>
       <c r="K45" s="7" t="n">
-        <v>-2935.42</v>
+        <v>-2499.68</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>211649.64</v>
+        <v>180225.4</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
@@ -7801,16 +7801,16 @@
         <v>-1.108</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>212160.15</v>
+        <v>180660.13</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>2492.88</v>
+        <v>2122.76</v>
       </c>
       <c r="K46" s="7" t="n">
-        <v>-2762.38</v>
+        <v>-2352.24</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>245059.99</v>
+        <v>198243.21</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
@@ -7852,16 +7852,16 @@
         <v>2.484</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>209667.27</v>
+        <v>178537.37</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>2463.59</v>
+        <v>2097.81</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>6119.56</v>
+        <v>5210.97</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>217769.2</v>
+        <v>185436.37</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -7903,16 +7903,16 @@
         <v>2.492</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>207203.68</v>
+        <v>176439.56</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>2434.64</v>
+        <v>2073.16</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>6066.73</v>
+        <v>5165.99</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>229839.29</v>
+        <v>195714.38</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -7954,16 +7954,16 @@
         <v>2.501</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>204258.53</v>
+        <v>173931.66</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>2400.04</v>
+        <v>2043.7</v>
       </c>
       <c r="K49" s="6" t="n">
-        <v>6003.36</v>
+        <v>5112.02</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>223772.56</v>
+        <v>190548.39</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
@@ -7996,25 +7996,25 @@
         <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>7.455</v>
+        <v>2.5</v>
       </c>
       <c r="G50" t="n">
         <v>0.182</v>
       </c>
       <c r="H50" t="n">
-        <v>7.273</v>
+        <v>2.318</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>210441.64</v>
+        <v>179196.75</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>2472.69</v>
+        <v>2105.56</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>17983.08</v>
+        <v>4881.08</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>247822.38</v>
+        <v>200595.45</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
@@ -8056,16 +8056,16 @@
         <v>2.496</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>224873.72</v>
+        <v>191486.06</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>2642.27</v>
+        <v>2249.96</v>
       </c>
       <c r="K51" s="6" t="n">
-        <v>6596.14</v>
+        <v>5616.8</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>251656.14</v>
+        <v>203860.01</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -8107,16 +8107,16 @@
         <v>2.492</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>222231.46</v>
+        <v>189236.1</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>2611.22</v>
+        <v>2223.52</v>
       </c>
       <c r="K52" s="6" t="n">
-        <v>6506.73</v>
+        <v>5540.66</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>259366.39</v>
+        <v>210368.26</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
@@ -8158,16 +8158,16 @@
         <v>2.519</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>239806.51</v>
+        <v>193769.73</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>2817.73</v>
+        <v>2276.79</v>
       </c>
       <c r="K53" s="6" t="n">
-        <v>7098.64</v>
+        <v>5735.88</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>258754.78</v>
+        <v>209595.89</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -8209,16 +8209,16 @@
         <v>-1.014</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>236988.78</v>
+        <v>191492.93</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>2784.62</v>
+        <v>2250.04</v>
       </c>
       <c r="K54" s="7" t="n">
-        <v>-2822.89</v>
+        <v>-2280.97</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>255931.88</v>
+        <v>207314.92</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
@@ -8260,16 +8260,16 @@
         <v>-1.032</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>253358.94</v>
+        <v>205122.32</v>
       </c>
       <c r="J55" s="5" t="n">
-        <v>2976.97</v>
+        <v>2410.19</v>
       </c>
       <c r="K55" s="7" t="n">
-        <v>-3072.23</v>
+        <v>-2487.31</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>252859.65</v>
+        <v>204827.6</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
@@ -8311,16 +8311,16 @@
         <v>-1.002</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>250343.7</v>
+        <v>202681.21</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>2941.54</v>
+        <v>2381.5</v>
       </c>
       <c r="K56" s="7" t="n">
-        <v>-2947.67</v>
+        <v>-2386.47</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>256418.72</v>
+        <v>207981.8</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
@@ -8353,25 +8353,25 @@
         <v>1</v>
       </c>
       <c r="F57" t="n">
-        <v>3.123</v>
+        <v>2.5</v>
       </c>
       <c r="G57" t="n">
         <v>0.027</v>
       </c>
       <c r="H57" t="n">
-        <v>3.096</v>
+        <v>2.473</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>256418.72</v>
+        <v>207981.8</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>3012.92</v>
+        <v>2443.79</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>9327.709999999999</v>
+        <v>6042.51</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>265746.43</v>
+        <v>214024.31</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -8413,16 +8413,16 @@
         <v>2.49</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>265746.43</v>
+        <v>214024.31</v>
       </c>
       <c r="J58" s="5" t="n">
-        <v>3122.52</v>
+        <v>2514.79</v>
       </c>
       <c r="K58" s="6" t="n">
-        <v>7774.28</v>
+        <v>6261.17</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>281217.18</v>
+        <v>226484</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
@@ -8464,16 +8464,16 @@
         <v>2.494</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>262623.91</v>
+        <v>211509.52</v>
       </c>
       <c r="J59" s="5" t="n">
-        <v>3085.83</v>
+        <v>2485.24</v>
       </c>
       <c r="K59" s="6" t="n">
-        <v>7696.48</v>
+        <v>6198.52</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>273442.91</v>
+        <v>220222.83</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
@@ -8515,16 +8515,16 @@
         <v>-1.002</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>281217.18</v>
+        <v>226484</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>3304.3</v>
+        <v>2661.19</v>
       </c>
       <c r="K60" s="7" t="n">
-        <v>-3311.47</v>
+        <v>-2666.96</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>274589.02</v>
+        <v>221145.87</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
@@ -8566,16 +8566,16 @@
         <v>-1.016</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>277912.88</v>
+        <v>223822.81</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>3265.48</v>
+        <v>2629.92</v>
       </c>
       <c r="K61" s="7" t="n">
-        <v>-3316.7</v>
+        <v>-2671.17</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>277900.48</v>
+        <v>223812.83</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
@@ -8608,25 +8608,25 @@
         <v>1</v>
       </c>
       <c r="F62" t="n">
-        <v>8.943</v>
+        <v>2.5</v>
       </c>
       <c r="G62" t="n">
         <v>0.019</v>
       </c>
       <c r="H62" t="n">
-        <v>8.925000000000001</v>
+        <v>2.481</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>274596.18</v>
+        <v>221151.64</v>
       </c>
       <c r="J62" s="5" t="n">
-        <v>3226.51</v>
+        <v>2598.53</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>28795.05</v>
+        <v>6447.3</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>303384.07</v>
+        <v>227593.17</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -8668,16 +8668,16 @@
         <v>-1.007</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>271362.51</v>
+        <v>218547.34</v>
       </c>
       <c r="J63" s="5" t="n">
-        <v>3188.51</v>
+        <v>2567.93</v>
       </c>
       <c r="K63" s="7" t="n">
-        <v>-3212.08</v>
+        <v>-2586.92</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>300171.98</v>
+        <v>225006.25</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
@@ -8719,16 +8719,16 @@
         <v>2.485</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>268174</v>
+        <v>215979.41</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>3151.04</v>
+        <v>2537.76</v>
       </c>
       <c r="K64" s="6" t="n">
-        <v>7830.93</v>
+        <v>6306.8</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>308002.91</v>
+        <v>231313.05</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
@@ -8770,16 +8770,16 @@
         <v>2.496</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>308002.91</v>
+        <v>231313.05</v>
       </c>
       <c r="J65" s="5" t="n">
-        <v>3619.03</v>
+        <v>2717.93</v>
       </c>
       <c r="K65" s="6" t="n">
-        <v>9034.860000000001</v>
+        <v>6785.27</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>317037.77</v>
+        <v>238098.32</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
@@ -8821,16 +8821,16 @@
         <v>2.492</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>304383.88</v>
+        <v>228595.12</v>
       </c>
       <c r="J66" s="5" t="n">
-        <v>3576.51</v>
+        <v>2685.99</v>
       </c>
       <c r="K66" s="6" t="n">
-        <v>8912.66</v>
+        <v>6693.49</v>
       </c>
       <c r="L66" s="5" t="n">
-        <v>325950.44</v>
+        <v>244791.81</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
@@ -8872,16 +8872,16 @@
         <v>-1.148</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>300807.37</v>
+        <v>225909.13</v>
       </c>
       <c r="J67" s="5" t="n">
-        <v>3534.49</v>
+        <v>2654.43</v>
       </c>
       <c r="K67" s="7" t="n">
-        <v>-4058.11</v>
+        <v>-3047.68</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>321892.32</v>
+        <v>241744.13</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
@@ -8923,16 +8923,16 @@
         <v>2.47</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>322415.95</v>
+        <v>242137.38</v>
       </c>
       <c r="J68" s="5" t="n">
-        <v>3788.39</v>
+        <v>2845.11</v>
       </c>
       <c r="K68" s="6" t="n">
-        <v>9356.17</v>
+        <v>7026.57</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>331248.49</v>
+        <v>248770.7</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
@@ -8974,16 +8974,16 @@
         <v>-1.014</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>331248.49</v>
+        <v>248770.7</v>
       </c>
       <c r="J69" s="5" t="n">
-        <v>3892.17</v>
+        <v>2923.06</v>
       </c>
       <c r="K69" s="7" t="n">
-        <v>-3944.94</v>
+        <v>-2962.69</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>327303.55</v>
+        <v>245808.01</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
@@ -9025,16 +9025,16 @@
         <v>-1.014</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>327303.55</v>
+        <v>245808.01</v>
       </c>
       <c r="J70" s="5" t="n">
-        <v>3845.82</v>
+        <v>2888.24</v>
       </c>
       <c r="K70" s="7" t="n">
-        <v>-3898.86</v>
+        <v>-2928.08</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>323404.69</v>
+        <v>242879.93</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
@@ -9076,16 +9076,16 @@
         <v>-1.02</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>323457.73</v>
+        <v>242919.77</v>
       </c>
       <c r="J71" s="5" t="n">
-        <v>3800.63</v>
+        <v>2854.31</v>
       </c>
       <c r="K71" s="7" t="n">
-        <v>-3874.79</v>
+        <v>-2910</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>319529.9</v>
+        <v>239969.93</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
@@ -9127,16 +9127,16 @@
         <v>2.493</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>319604.06</v>
+        <v>240025.62</v>
       </c>
       <c r="J72" s="5" t="n">
-        <v>3755.35</v>
+        <v>2820.3</v>
       </c>
       <c r="K72" s="6" t="n">
-        <v>9361.16</v>
+        <v>7030.32</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>328891.06</v>
+        <v>247000.24</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
@@ -9178,16 +9178,16 @@
         <v>-1.082</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>315774.55</v>
+        <v>237149.63</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>3710.35</v>
+        <v>2786.51</v>
       </c>
       <c r="K73" s="7" t="n">
-        <v>-4013.24</v>
+        <v>-3013.98</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>324877.82</v>
+        <v>243986.26</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -9229,16 +9229,16 @@
         <v>2.474</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>312064.2</v>
+        <v>234363.12</v>
       </c>
       <c r="J74" s="5" t="n">
-        <v>3666.75</v>
+        <v>2753.77</v>
       </c>
       <c r="K74" s="6" t="n">
-        <v>9070.389999999999</v>
+        <v>6811.95</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>333948.21</v>
+        <v>250798.21</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
@@ -9280,16 +9280,16 @@
         <v>-1.012</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>308397.45</v>
+        <v>231609.35</v>
       </c>
       <c r="J75" s="5" t="n">
-        <v>3623.67</v>
+        <v>2721.41</v>
       </c>
       <c r="K75" s="7" t="n">
-        <v>-3666.43</v>
+        <v>-2753.52</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>368151.61</v>
+        <v>276485.29</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
@@ -9331,16 +9331,16 @@
         <v>2.483</v>
       </c>
       <c r="I76" s="5" t="n">
-        <v>304773.78</v>
+        <v>228887.94</v>
       </c>
       <c r="J76" s="5" t="n">
-        <v>3581.09</v>
+        <v>2689.43</v>
       </c>
       <c r="K76" s="6" t="n">
-        <v>8890.450000000001</v>
+        <v>6676.81</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>342838.66</v>
+        <v>257475.02</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
@@ -9382,16 +9382,16 @@
         <v>2.451</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>339214.99</v>
+        <v>254753.61</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>3985.78</v>
+        <v>2993.35</v>
       </c>
       <c r="K77" s="6" t="n">
-        <v>9770.01</v>
+        <v>7337.37</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>352608.67</v>
+        <v>264812.39</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
@@ -9433,16 +9433,16 @@
         <v>2.413</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>335229.22</v>
+        <v>251760.26</v>
       </c>
       <c r="J78" s="5" t="n">
-        <v>3938.94</v>
+        <v>2958.18</v>
       </c>
       <c r="K78" s="6" t="n">
-        <v>9504.84</v>
+        <v>7138.22</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>362113.52</v>
+        <v>271950.62</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -9484,16 +9484,16 @@
         <v>2.493</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>331290.27</v>
+        <v>248802.08</v>
       </c>
       <c r="J79" s="5" t="n">
-        <v>3892.66</v>
+        <v>2923.42</v>
       </c>
       <c r="K79" s="6" t="n">
-        <v>9704.530000000001</v>
+        <v>7288.19</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>371818.04</v>
+        <v>279238.81</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
@@ -9535,16 +9535,16 @@
         <v>-1.011</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>327397.61</v>
+        <v>245878.65</v>
       </c>
       <c r="J80" s="5" t="n">
-        <v>3846.92</v>
+        <v>2889.07</v>
       </c>
       <c r="K80" s="7" t="n">
-        <v>-3888.29</v>
+        <v>-2920.14</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>364263.33</v>
+        <v>273565.15</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -9586,16 +9586,16 @@
         <v>-1.154</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>323550.69</v>
+        <v>242989.58</v>
       </c>
       <c r="J81" s="5" t="n">
-        <v>3801.72</v>
+        <v>2855.13</v>
       </c>
       <c r="K81" s="7" t="n">
-        <v>-4386.6</v>
+        <v>-3294.38</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>359876.73</v>
+        <v>270270.77</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
@@ -9628,25 +9628,25 @@
         <v>1</v>
       </c>
       <c r="F82" t="n">
-        <v>3.452</v>
+        <v>2.5</v>
       </c>
       <c r="G82" t="n">
         <v>0.024</v>
       </c>
       <c r="H82" t="n">
-        <v>3.429</v>
+        <v>2.476</v>
       </c>
       <c r="I82" s="5" t="n">
-        <v>359876.73</v>
+        <v>270270.77</v>
       </c>
       <c r="J82" s="5" t="n">
-        <v>4228.55</v>
+        <v>3175.68</v>
       </c>
       <c r="K82" s="6" t="n">
-        <v>14497.97</v>
+        <v>7863.59</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>374374.7</v>
+        <v>278134.36</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
@@ -9688,16 +9688,16 @@
         <v>2.461</v>
       </c>
       <c r="I83" s="5" t="n">
-        <v>355648.17</v>
+        <v>267095.09</v>
       </c>
       <c r="J83" s="5" t="n">
-        <v>4178.87</v>
+        <v>3138.37</v>
       </c>
       <c r="K83" s="6" t="n">
-        <v>10283.29</v>
+        <v>7722.84</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>384657.99</v>
+        <v>285857.21</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
@@ -9739,16 +9739,16 @@
         <v>-1.049</v>
       </c>
       <c r="I84" s="5" t="n">
-        <v>384657.99</v>
+        <v>285857.21</v>
       </c>
       <c r="J84" s="5" t="n">
-        <v>4519.73</v>
+        <v>3358.82</v>
       </c>
       <c r="K84" s="7" t="n">
-        <v>-4742.93</v>
+        <v>-3524.69</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>379915.06</v>
+        <v>282332.52</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
@@ -9790,16 +9790,16 @@
         <v>2.491</v>
       </c>
       <c r="I85" s="5" t="n">
-        <v>379915.06</v>
+        <v>282332.52</v>
       </c>
       <c r="J85" s="5" t="n">
-        <v>4464</v>
+        <v>3317.41</v>
       </c>
       <c r="K85" s="6" t="n">
-        <v>11117.69</v>
+        <v>8262.07</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>391032.75</v>
+        <v>290594.59</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
@@ -9833,16 +9833,16 @@
         <v>-0.019</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>391032.75</v>
+        <v>290594.59</v>
       </c>
       <c r="J86" s="5" t="n">
-        <v>4594.63</v>
+        <v>3414.49</v>
       </c>
       <c r="K86" s="7" t="n">
-        <v>-86.69</v>
+        <v>-64.42</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>390946.06</v>
+        <v>290530.17</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
@@ -9876,16 +9876,16 @@
         <v>-0.025</v>
       </c>
       <c r="I87" s="5" t="n">
-        <v>386438.11</v>
+        <v>287180.1</v>
       </c>
       <c r="J87" s="5" t="n">
-        <v>4540.65</v>
+        <v>3374.37</v>
       </c>
       <c r="K87" s="7" t="n">
-        <v>-113.52</v>
+        <v>-84.36</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>390832.54</v>
+        <v>290445.81</v>
       </c>
       <c r="M87" t="inlineStr">
         <is>

--- a/output/quickfix_portfolio_daily.xlsx
+++ b/output/quickfix_portfolio_daily.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>target = 2.5R, or an opposite reversal nearer than 2.5R</t>
+          <t>target = 1.9R, or an opposite reversal nearer than 1.9R</t>
         </is>
       </c>
     </row>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>290,445.81</t>
+          <t>306,160.32</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+190.45%</t>
+          <t>+206.16%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>300,899  (+200.90%)</t>
+          <t>321,399  (+221.40%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6,394  (10.5 pts of return)</t>
+          <t>8,177  (15.2 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>31.7x</t>
+          <t>34.4x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>63.6%</t>
         </is>
       </c>
     </row>
@@ -730,7 +730,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.4 bars</t>
+          <t>1.2 bars</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>+2.74R  (best +8.09R)</t>
+          <t>+2.16R  (best +8.09R)</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5,453  (+3.22%)</t>
+          <t>5,092  (+3.01%)</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-2,189  (-1.31%)</t>
+          <t>-2,463  (-1.58%)</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>52% of trading days</t>
+          <t>48% of trading days</t>
         </is>
       </c>
     </row>
@@ -840,7 +840,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5.7% of live balance</t>
+          <t>6.8% of live balance</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1.175% of liquid capital (solved for a 6% max drawdown)</t>
+          <t>1.39% of liquid capital (solved for a 6% max drawdown)</t>
         </is>
       </c>
     </row>
@@ -954,10 +954,10 @@
         <v>100000</v>
       </c>
       <c r="C2" s="5" t="n">
-        <v>1175</v>
+        <v>1390</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>98825</v>
+        <v>98610</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -969,7 +969,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX short (risk 1,175)</t>
+          <t>Gold_Futures_COMEX short (risk 1,390)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -979,13 +979,13 @@
         <v>46010</v>
       </c>
       <c r="B3" s="5" t="n">
-        <v>109506.16</v>
+        <v>111245.59</v>
       </c>
       <c r="C3" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>109506.16</v>
+        <v>111245.59</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -994,7 +994,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX target_r (+9,506)</t>
+          <t>Gold_Futures_COMEX target_r (+11,246)</t>
         </is>
       </c>
     </row>
@@ -1003,13 +1003,13 @@
         <v>46011</v>
       </c>
       <c r="B4" s="5" t="n">
-        <v>109506.16</v>
+        <v>111245.59</v>
       </c>
       <c r="C4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>109506.16</v>
+        <v>111245.59</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -1023,13 +1023,13 @@
         <v>46021</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>109506.16</v>
+        <v>111245.59</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1286.7</v>
+        <v>1546.31</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>108219.47</v>
+        <v>109699.28</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX short (risk 1,287)</t>
+          <t>Gold_Futures_COMEX short (risk 1,546)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -1051,13 +1051,13 @@
         <v>46023</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>109506.16</v>
+        <v>111245.59</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1286.7</v>
+        <v>1546.31</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>108219.47</v>
+        <v>109699.28</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
@@ -1075,13 +1075,13 @@
         <v>46024</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>112713.58</v>
+        <v>114203.77</v>
       </c>
       <c r="C7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>112713.58</v>
+        <v>114203.77</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -1090,7 +1090,7 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX target_r (+3,207)</t>
+          <t>Gold_Futures_COMEX target_r (+2,958)</t>
         </is>
       </c>
     </row>
@@ -1099,13 +1099,13 @@
         <v>46025</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>112713.58</v>
+        <v>114203.77</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>112713.58</v>
+        <v>114203.77</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -1119,13 +1119,13 @@
         <v>46026</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>112713.58</v>
+        <v>114203.77</v>
       </c>
       <c r="C9" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>112713.58</v>
+        <v>114203.77</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1139,13 +1139,13 @@
         <v>46027</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>112713.58</v>
+        <v>114203.77</v>
       </c>
       <c r="C10" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>112713.58</v>
+        <v>114203.77</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -1159,13 +1159,13 @@
         <v>46028</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>112713.58</v>
+        <v>114203.77</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>112713.58</v>
+        <v>114203.77</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -1179,13 +1179,13 @@
         <v>46029</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>112713.58</v>
+        <v>114203.77</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>2633.21</v>
+        <v>3152.8</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>110080.38</v>
+        <v>111050.97</v>
       </c>
       <c r="E12" t="n">
         <v>2</v>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Coffee_NYCSCE_Futures short (risk 1,324); S_P_500_Index short (risk 1,309)</t>
+          <t>Coffee_NYCSCE_Futures short (risk 1,587); S_P_500_Index short (risk 1,565)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -1207,13 +1207,13 @@
         <v>46030</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>114647.62</v>
+        <v>115574.2</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>114647.62</v>
+        <v>115574.2</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1222,7 +1222,7 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Coffee_NYCSCE_Futures stop (-1,335); S_P_500_Index target_r (+3,269)</t>
+          <t>Coffee_NYCSCE_Futures stop (-1,600); S_P_500_Index target_r (+2,970)</t>
         </is>
       </c>
     </row>
@@ -1231,13 +1231,13 @@
         <v>46031</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>114647.62</v>
+        <v>115574.2</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>114647.62</v>
+        <v>115574.2</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -1251,13 +1251,13 @@
         <v>46032</v>
       </c>
       <c r="B15" s="5" t="n">
-        <v>114647.62</v>
+        <v>115574.2</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>114647.62</v>
+        <v>115574.2</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -1271,13 +1271,13 @@
         <v>46033</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>114647.62</v>
+        <v>115574.2</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>114647.62</v>
+        <v>115574.2</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -1291,13 +1291,13 @@
         <v>46034</v>
       </c>
       <c r="B17" s="5" t="n">
-        <v>114647.62</v>
+        <v>115574.2</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>114647.62</v>
+        <v>115574.2</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -1311,13 +1311,13 @@
         <v>46035</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>114647.62</v>
+        <v>115574.2</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>1347.11</v>
+        <v>1606.48</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>113300.51</v>
+        <v>113967.72</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures long (risk 1,347)</t>
+          <t>Cocoa_NYCSCE_Futures long (risk 1,606)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
@@ -1339,13 +1339,13 @@
         <v>46036</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>113185.86</v>
+        <v>113831</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>113185.86</v>
+        <v>113831</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
@@ -1354,7 +1354,7 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures unknown_pl (-1,462)</t>
+          <t>Cocoa_NYCSCE_Futures unknown_pl (-1,743)</t>
         </is>
       </c>
     </row>
@@ -1363,13 +1363,13 @@
         <v>46037</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>113185.86</v>
+        <v>113831</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>113185.86</v>
+        <v>113831</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -1383,13 +1383,13 @@
         <v>46038</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>113185.86</v>
+        <v>113831</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>113185.86</v>
+        <v>113831</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
@@ -1403,13 +1403,13 @@
         <v>46039</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>113185.86</v>
+        <v>113831</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>113185.86</v>
+        <v>113831</v>
       </c>
       <c r="E22" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>46040</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>113185.86</v>
+        <v>113831</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>113185.86</v>
+        <v>113831</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
@@ -1443,13 +1443,13 @@
         <v>46041</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>113185.86</v>
+        <v>113831</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>113185.86</v>
+        <v>113831</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
@@ -1463,13 +1463,13 @@
         <v>46042</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>113185.86</v>
+        <v>113831</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>113185.86</v>
+        <v>113831</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -1483,13 +1483,13 @@
         <v>46043</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>113185.86</v>
+        <v>113831</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>1329.93</v>
+        <v>1582.25</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>111855.93</v>
+        <v>112248.75</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Coffee_NYCSCE_Futures long (risk 1,330)</t>
+          <t>Coffee_NYCSCE_Futures long (risk 1,582)</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -1511,13 +1511,13 @@
         <v>46044</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>113185.86</v>
+        <v>113831</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>1329.93</v>
+        <v>1582.25</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>111855.93</v>
+        <v>112248.75</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -1535,13 +1535,13 @@
         <v>46045</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>116502.66</v>
+        <v>116827.71</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>116502.66</v>
+        <v>116827.71</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
@@ -1550,7 +1550,7 @@
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Coffee_NYCSCE_Futures target_r (+3,317)</t>
+          <t>Coffee_NYCSCE_Futures target_r (+2,997)</t>
         </is>
       </c>
     </row>
@@ -1559,13 +1559,13 @@
         <v>46046</v>
       </c>
       <c r="B29" s="5" t="n">
-        <v>116502.66</v>
+        <v>116827.71</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>116502.66</v>
+        <v>116827.71</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>46047</v>
       </c>
       <c r="B30" s="5" t="n">
-        <v>116502.66</v>
+        <v>116827.71</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D30" s="5" t="n">
-        <v>116502.66</v>
+        <v>116827.71</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
@@ -1599,13 +1599,13 @@
         <v>46048</v>
       </c>
       <c r="B31" s="5" t="n">
-        <v>116502.66</v>
+        <v>116827.71</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D31" s="5" t="n">
-        <v>116502.66</v>
+        <v>116827.71</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
@@ -1619,13 +1619,13 @@
         <v>46049</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>116502.66</v>
+        <v>116827.71</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>1368.91</v>
+        <v>1623.91</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>115133.76</v>
+        <v>115203.81</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>S_P_500_Index short (risk 1,369)</t>
+          <t>S_P_500_Index short (risk 1,624)</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -1647,13 +1647,13 @@
         <v>46050</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>112321.45</v>
+        <v>111867.62</v>
       </c>
       <c r="C33" s="5" t="n">
-        <v>1352.82</v>
+        <v>1601.33</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>110968.63</v>
+        <v>110266.29</v>
       </c>
       <c r="E33" t="n">
         <v>1</v>
@@ -1665,12 +1665,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Teucrium_Wheat_Fund short (risk 1,353)</t>
+          <t>Teucrium_Wheat_Fund short (risk 1,601)</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>S_P_500_Index stop (-4,181)</t>
+          <t>S_P_500_Index stop (-4,960)</t>
         </is>
       </c>
     </row>
@@ -1679,13 +1679,13 @@
         <v>46051</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>110592.78</v>
+        <v>109821.4</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>3865.86</v>
+        <v>4534.49</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>106726.92</v>
+        <v>105286.92</v>
       </c>
       <c r="E34" t="n">
         <v>3</v>
@@ -1697,12 +1697,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ethereum_Per_USD_Binance long (risk 1,304); Live_Cattle_Futures_CME short (risk 1,289); S_P_500_Index short (risk 1,273)</t>
+          <t>Ethereum_Per_USD_Binance long (risk 1,533); Live_Cattle_Futures_CME short (risk 1,511); S_P_500_Index short (risk 1,490)</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Teucrium_Wheat_Fund stop (-1,729)</t>
+          <t>Teucrium_Wheat_Fund stop (-2,046)</t>
         </is>
       </c>
     </row>
@@ -1711,13 +1711,13 @@
         <v>46052</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>112111.91</v>
+        <v>111588.76</v>
       </c>
       <c r="C35" s="5" t="n">
-        <v>1254.04</v>
+        <v>1463.49</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>110857.87</v>
+        <v>110125.27</v>
       </c>
       <c r="E35" t="n">
         <v>1</v>
@@ -1729,12 +1729,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures long (risk 1,254)</t>
+          <t>Cocoa_NYCSCE_Futures long (risk 1,463)</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Ethereum_Per_USD_Binance stop (-1,394); Live_Cattle_Futures_CME unknown_pl (-1,365); S_P_500_Index target_r (+4,278)</t>
+          <t>Ethereum_Per_USD_Binance stop (-1,638); Live_Cattle_Futures_CME unknown_pl (-1,602); S_P_500_Index target_r (+5,007)</t>
         </is>
       </c>
     </row>
@@ -1743,13 +1743,13 @@
         <v>46053</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>112111.91</v>
+        <v>111588.76</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>1254.04</v>
+        <v>1463.49</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>110857.87</v>
+        <v>110125.27</v>
       </c>
       <c r="E36" t="n">
         <v>1</v>
@@ -1767,13 +1767,13 @@
         <v>46054</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>112111.91</v>
+        <v>111588.76</v>
       </c>
       <c r="C37" s="5" t="n">
-        <v>1254.04</v>
+        <v>1463.49</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>110857.87</v>
+        <v>110125.27</v>
       </c>
       <c r="E37" t="n">
         <v>1</v>
@@ -1791,13 +1791,13 @@
         <v>46055</v>
       </c>
       <c r="B38" s="5" t="n">
-        <v>112111.91</v>
+        <v>111588.76</v>
       </c>
       <c r="C38" s="5" t="n">
-        <v>3843.9</v>
+        <v>4503.69</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>108268.01</v>
+        <v>107085.06</v>
       </c>
       <c r="E38" t="n">
         <v>3</v>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance long (risk 1,303); S_P_500_Index short (risk 1,287)</t>
+          <t>Bitcoin_Per_USD_Binance long (risk 1,531); S_P_500_Index short (risk 1,509)</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
@@ -1819,30 +1819,30 @@
         <v>46056</v>
       </c>
       <c r="B39" s="5" t="n">
-        <v>109513.89</v>
+        <v>111300.35</v>
       </c>
       <c r="C39" s="5" t="n">
-        <v>2526.19</v>
+        <v>1488.48</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>106987.7</v>
+        <v>109811.87</v>
       </c>
       <c r="E39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures, EURO_STOXX_50_Index</t>
+          <t>EURO_STOXX_50_Index</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>EURO_STOXX_50_Index short (risk 1,272)</t>
+          <t>EURO_STOXX_50_Index short (risk 1,488)</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance stop (-1,305); S_P_500_Index unknown_pl (-1,293)</t>
+          <t>Bitcoin_Per_USD_Binance stop (-1,534); Cocoa_NYCSCE_Futures target_r (+2,761); S_P_500_Index unknown_pl (-1,516)</t>
         </is>
       </c>
     </row>
@@ -1851,54 +1851,62 @@
         <v>46057</v>
       </c>
       <c r="B40" s="5" t="n">
-        <v>109513.89</v>
+        <v>114127.47</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>2526.19</v>
+        <v>1526.38</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>106987.7</v>
+        <v>112601.09</v>
       </c>
       <c r="E40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures, EURO_STOXX_50_Index</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+          <t>Cocoa_NYCSCE_Futures</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Cocoa_NYCSCE_Futures long (risk 1,526)</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>EURO_STOXX_50_Index target_r (+2,827)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
         <v>46058</v>
       </c>
       <c r="B41" s="5" t="n">
-        <v>112693.42</v>
+        <v>116981.35</v>
       </c>
       <c r="C41" s="5" t="n">
-        <v>2511.15</v>
+        <v>1565.16</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>110182.27</v>
+        <v>115416.19</v>
       </c>
       <c r="E41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures, NY_Copper_Futures</t>
+          <t>NY_Copper_Futures</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures long (risk 1,257)</t>
+          <t>NY_Copper_Futures long (risk 1,565)</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>EURO_STOXX_50_Index target_r (+3,180)</t>
+          <t>Cocoa_NYCSCE_Futures target_r (+2,854)</t>
         </is>
       </c>
     </row>
@@ -1907,30 +1915,30 @@
         <v>46059</v>
       </c>
       <c r="B42" s="5" t="n">
-        <v>111430.5</v>
+        <v>115408.95</v>
       </c>
       <c r="C42" s="5" t="n">
-        <v>2548.68</v>
+        <v>1604.29</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>108881.81</v>
+        <v>113804.67</v>
       </c>
       <c r="E42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance, Cocoa_NYCSCE_Futures</t>
+          <t>Bitcoin_Per_USD_Binance</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance long (risk 1,295)</t>
+          <t>Bitcoin_Per_USD_Binance long (risk 1,604)</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures stop (-1,263)</t>
+          <t>NY_Copper_Futures stop (-1,572)</t>
         </is>
       </c>
     </row>
@@ -1939,26 +1947,22 @@
         <v>46060</v>
       </c>
       <c r="B43" s="5" t="n">
-        <v>114666.09</v>
+        <v>118455.84</v>
       </c>
       <c r="C43" s="5" t="n">
-        <v>1254.04</v>
+        <v>0</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>113412.05</v>
+        <v>118455.84</v>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Cocoa_NYCSCE_Futures</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance target_r (+3,236)</t>
+          <t>Bitcoin_Per_USD_Binance target_r (+3,047)</t>
         </is>
       </c>
     </row>
@@ -1967,22 +1971,18 @@
         <v>46061</v>
       </c>
       <c r="B44" s="5" t="n">
-        <v>114666.09</v>
+        <v>118455.84</v>
       </c>
       <c r="C44" s="5" t="n">
-        <v>1254.04</v>
+        <v>0</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>113412.05</v>
+        <v>118455.84</v>
       </c>
       <c r="E44" t="n">
-        <v>1</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Cocoa_NYCSCE_Futures</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1991,13 +1991,13 @@
         <v>46062</v>
       </c>
       <c r="B45" s="5" t="n">
-        <v>114666.09</v>
+        <v>118455.84</v>
       </c>
       <c r="C45" s="5" t="n">
-        <v>1254.04</v>
+        <v>1646.54</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>113412.05</v>
+        <v>116809.3</v>
       </c>
       <c r="E45" t="n">
         <v>1</v>
@@ -2007,7 +2007,11 @@
           <t>Cocoa_NYCSCE_Futures</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Cocoa_NYCSCE_Futures long (risk 1,647)</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
@@ -2015,13 +2019,13 @@
         <v>46063</v>
       </c>
       <c r="B46" s="5" t="n">
-        <v>113379.05</v>
+        <v>116609.72</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>2649.53</v>
+        <v>3224.73</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>110729.52</v>
+        <v>113384.99</v>
       </c>
       <c r="E46" t="n">
         <v>2</v>
@@ -2033,12 +2037,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>EURO_STOXX_50_Index short (risk 1,333); S_P_500_Index short (risk 1,317)</t>
+          <t>EURO_STOXX_50_Index short (risk 1,624); S_P_500_Index short (risk 1,601)</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures stop (-1,287)</t>
+          <t>Cocoa_NYCSCE_Futures unknown_pl (-1,846)</t>
         </is>
       </c>
     </row>
@@ -2047,13 +2051,13 @@
         <v>46064</v>
       </c>
       <c r="B47" s="5" t="n">
-        <v>115380.25</v>
+        <v>118077.36</v>
       </c>
       <c r="C47" s="5" t="n">
-        <v>1301.07</v>
+        <v>1576.05</v>
       </c>
       <c r="D47" s="5" t="n">
-        <v>114079.18</v>
+        <v>116501.3</v>
       </c>
       <c r="E47" t="n">
         <v>1</v>
@@ -2065,12 +2069,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT short (risk 1,301)</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT short (risk 1,576)</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>EURO_STOXX_50_Index target_r (+3,330); S_P_500_Index unknown_pl (-1,329)</t>
+          <t>EURO_STOXX_50_Index target_r (+3,083); S_P_500_Index unknown_pl (-1,616)</t>
         </is>
       </c>
     </row>
@@ -2079,13 +2083,13 @@
         <v>46065</v>
       </c>
       <c r="B48" s="5" t="n">
-        <v>113899.72</v>
+        <v>116283.92</v>
       </c>
       <c r="C48" s="5" t="n">
-        <v>1340.43</v>
+        <v>1619.37</v>
       </c>
       <c r="D48" s="5" t="n">
-        <v>112559.29</v>
+        <v>114664.55</v>
       </c>
       <c r="E48" t="n">
         <v>1</v>
@@ -2097,12 +2101,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>EURO_STOXX_50_Index short (risk 1,340)</t>
+          <t>EURO_STOXX_50_Index short (risk 1,619)</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT stop (-1,481)</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT stop (-1,793)</t>
         </is>
       </c>
     </row>
@@ -2111,13 +2115,13 @@
         <v>46066</v>
       </c>
       <c r="B49" s="5" t="n">
-        <v>117250.11</v>
+        <v>119359.88</v>
       </c>
       <c r="C49" s="5" t="n">
-        <v>1322.57</v>
+        <v>1593.84</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>115927.54</v>
+        <v>117766.05</v>
       </c>
       <c r="E49" t="n">
         <v>1</v>
@@ -2129,12 +2133,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures long (risk 1,323)</t>
+          <t>NY_Copper_Futures long (risk 1,594)</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>EURO_STOXX_50_Index target_r (+3,350)</t>
+          <t>EURO_STOXX_50_Index target_r (+3,076)</t>
         </is>
       </c>
     </row>
@@ -2143,13 +2147,13 @@
         <v>46067</v>
       </c>
       <c r="B50" s="5" t="n">
-        <v>117250.11</v>
+        <v>119359.88</v>
       </c>
       <c r="C50" s="5" t="n">
-        <v>1322.57</v>
+        <v>1593.84</v>
       </c>
       <c r="D50" s="5" t="n">
-        <v>115927.54</v>
+        <v>117766.05</v>
       </c>
       <c r="E50" t="n">
         <v>1</v>
@@ -2167,13 +2171,13 @@
         <v>46068</v>
       </c>
       <c r="B51" s="5" t="n">
-        <v>117250.11</v>
+        <v>119359.88</v>
       </c>
       <c r="C51" s="5" t="n">
-        <v>1322.57</v>
+        <v>1593.84</v>
       </c>
       <c r="D51" s="5" t="n">
-        <v>115927.54</v>
+        <v>117766.05</v>
       </c>
       <c r="E51" t="n">
         <v>1</v>
@@ -2191,13 +2195,13 @@
         <v>46069</v>
       </c>
       <c r="B52" s="5" t="n">
-        <v>117250.11</v>
+        <v>119359.88</v>
       </c>
       <c r="C52" s="5" t="n">
-        <v>1322.57</v>
+        <v>1593.84</v>
       </c>
       <c r="D52" s="5" t="n">
-        <v>115927.54</v>
+        <v>117766.05</v>
       </c>
       <c r="E52" t="n">
         <v>1</v>
@@ -2215,13 +2219,13 @@
         <v>46070</v>
       </c>
       <c r="B53" s="5" t="n">
-        <v>115921.91</v>
+        <v>117759.26</v>
       </c>
       <c r="C53" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D53" s="5" t="n">
-        <v>115921.91</v>
+        <v>117759.26</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
@@ -2230,7 +2234,7 @@
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures stop (-1,328)</t>
+          <t>NY_Copper_Futures stop (-1,601)</t>
         </is>
       </c>
     </row>
@@ -2239,13 +2243,13 @@
         <v>46071</v>
       </c>
       <c r="B54" s="5" t="n">
-        <v>115921.91</v>
+        <v>117759.26</v>
       </c>
       <c r="C54" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D54" s="5" t="n">
-        <v>115921.91</v>
+        <v>117759.26</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
@@ -2259,13 +2263,13 @@
         <v>46072</v>
       </c>
       <c r="B55" s="5" t="n">
-        <v>115921.91</v>
+        <v>117759.26</v>
       </c>
       <c r="C55" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D55" s="5" t="n">
-        <v>115921.91</v>
+        <v>117759.26</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
@@ -2279,13 +2283,13 @@
         <v>46073</v>
       </c>
       <c r="B56" s="5" t="n">
-        <v>115921.91</v>
+        <v>117759.26</v>
       </c>
       <c r="C56" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D56" s="5" t="n">
-        <v>115921.91</v>
+        <v>117759.26</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
@@ -2299,13 +2303,13 @@
         <v>46074</v>
       </c>
       <c r="B57" s="5" t="n">
-        <v>115921.91</v>
+        <v>117759.26</v>
       </c>
       <c r="C57" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D57" s="5" t="n">
-        <v>115921.91</v>
+        <v>117759.26</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
@@ -2319,13 +2323,13 @@
         <v>46075</v>
       </c>
       <c r="B58" s="5" t="n">
-        <v>115921.91</v>
+        <v>117759.26</v>
       </c>
       <c r="C58" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D58" s="5" t="n">
-        <v>115921.91</v>
+        <v>117759.26</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
@@ -2339,13 +2343,13 @@
         <v>46076</v>
       </c>
       <c r="B59" s="5" t="n">
-        <v>115921.91</v>
+        <v>117759.26</v>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1362.08</v>
+        <v>1636.85</v>
       </c>
       <c r="D59" s="5" t="n">
-        <v>114559.83</v>
+        <v>116122.41</v>
       </c>
       <c r="E59" t="n">
         <v>1</v>
@@ -2357,7 +2361,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT short (risk 1,362)</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT short (risk 1,637)</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
@@ -2367,50 +2371,62 @@
         <v>46077</v>
       </c>
       <c r="B60" s="5" t="n">
-        <v>115921.91</v>
+        <v>120635.45</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>4038.42</v>
+        <v>3205.77</v>
       </c>
       <c r="D60" s="5" t="n">
-        <v>111883.49</v>
+        <v>117429.68</v>
       </c>
       <c r="E60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures, Ethereum_Per_USD_Binance, US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>Cocoa_NYCSCE_Futures, Ethereum_Per_USD_Binance</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures long (risk 1,346); Ethereum_Per_USD_Binance long (risk 1,330)</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>Cocoa_NYCSCE_Futures long (risk 1,614); Ethereum_Per_USD_Binance long (risk 1,592)</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>US_30_Year_T_Bond_Futures_CBOT target_r (+2,876)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="n">
         <v>46078</v>
       </c>
       <c r="B61" s="5" t="n">
-        <v>125666.15</v>
+        <v>126476.09</v>
       </c>
       <c r="C61" s="5" t="n">
-        <v>-0</v>
+        <v>1632.27</v>
       </c>
       <c r="D61" s="5" t="n">
-        <v>125666.15</v>
+        <v>124843.82</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>US_30_Year_T_Bond_Futures_CBOT short (risk 1,632)</t>
+        </is>
+      </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures target_r (+3,348); Ethereum_Per_USD_Binance target_r (+3,186); US_30_Year_T_Bond_Futures_CBOT target_r (+3,211)</t>
+          <t>Cocoa_NYCSCE_Futures target_r (+2,984); Ethereum_Per_USD_Binance target_r (+2,857)</t>
         </is>
       </c>
     </row>
@@ -2419,33 +2435,37 @@
         <v>46079</v>
       </c>
       <c r="B62" s="5" t="n">
-        <v>125666.15</v>
+        <v>124027.68</v>
       </c>
       <c r="C62" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D62" s="5" t="n">
-        <v>125666.15</v>
+        <v>124027.68</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
       </c>
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>US_30_Year_T_Bond_Futures_CBOT unknown_pl (-2,448)</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
         <v>46080</v>
       </c>
       <c r="B63" s="5" t="n">
-        <v>125666.15</v>
+        <v>124027.68</v>
       </c>
       <c r="C63" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D63" s="5" t="n">
-        <v>125666.15</v>
+        <v>124027.68</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
@@ -2459,13 +2479,13 @@
         <v>46081</v>
       </c>
       <c r="B64" s="5" t="n">
-        <v>125666.15</v>
+        <v>124027.68</v>
       </c>
       <c r="C64" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D64" s="5" t="n">
-        <v>125666.15</v>
+        <v>124027.68</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
@@ -2479,13 +2499,13 @@
         <v>46082</v>
       </c>
       <c r="B65" s="5" t="n">
-        <v>125666.15</v>
+        <v>124027.68</v>
       </c>
       <c r="C65" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D65" s="5" t="n">
-        <v>125666.15</v>
+        <v>124027.68</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
@@ -2499,13 +2519,13 @@
         <v>46083</v>
       </c>
       <c r="B66" s="5" t="n">
-        <v>125666.15</v>
+        <v>124027.68</v>
       </c>
       <c r="C66" s="5" t="n">
-        <v>1476.58</v>
+        <v>1723.98</v>
       </c>
       <c r="D66" s="5" t="n">
-        <v>124189.57</v>
+        <v>122303.7</v>
       </c>
       <c r="E66" t="n">
         <v>1</v>
@@ -2517,7 +2537,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX short (risk 1,477)</t>
+          <t>Gold_Futures_COMEX short (risk 1,724)</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
@@ -2527,13 +2547,13 @@
         <v>46084</v>
       </c>
       <c r="B67" s="5" t="n">
-        <v>129353.71</v>
+        <v>127298.72</v>
       </c>
       <c r="C67" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D67" s="5" t="n">
-        <v>129353.71</v>
+        <v>127298.72</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
@@ -2542,7 +2562,7 @@
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX target_r (+3,688)</t>
+          <t>Gold_Futures_COMEX target_r (+3,271)</t>
         </is>
       </c>
     </row>
@@ -2551,13 +2571,13 @@
         <v>46085</v>
       </c>
       <c r="B68" s="5" t="n">
-        <v>129353.71</v>
+        <v>127298.72</v>
       </c>
       <c r="C68" s="5" t="n">
-        <v>1519.91</v>
+        <v>1769.45</v>
       </c>
       <c r="D68" s="5" t="n">
-        <v>127833.8</v>
+        <v>125529.27</v>
       </c>
       <c r="E68" t="n">
         <v>1</v>
@@ -2569,7 +2589,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate short (risk 1,520)</t>
+          <t>USD_EUR_Cross_Rate short (risk 1,769)</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
@@ -2579,13 +2599,13 @@
         <v>46086</v>
       </c>
       <c r="B69" s="5" t="n">
-        <v>127569.47</v>
+        <v>125221.54</v>
       </c>
       <c r="C69" s="5" t="n">
-        <v>1502.05</v>
+        <v>1744.86</v>
       </c>
       <c r="D69" s="5" t="n">
-        <v>126067.42</v>
+        <v>123476.68</v>
       </c>
       <c r="E69" t="n">
         <v>1</v>
@@ -2597,12 +2617,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>S_P_500_Index long (risk 1,502)</t>
+          <t>S_P_500_Index long (risk 1,745)</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate stop (-1,784)</t>
+          <t>USD_EUR_Cross_Rate stop (-2,077)</t>
         </is>
       </c>
     </row>
@@ -2611,13 +2631,13 @@
         <v>46087</v>
       </c>
       <c r="B70" s="5" t="n">
-        <v>125954.33</v>
+        <v>123345.31</v>
       </c>
       <c r="C70" s="5" t="n">
-        <v>1481.29</v>
+        <v>1716.33</v>
       </c>
       <c r="D70" s="5" t="n">
-        <v>124473.04</v>
+        <v>121628.98</v>
       </c>
       <c r="E70" t="n">
         <v>1</v>
@@ -2629,12 +2649,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate short (risk 1,481)</t>
+          <t>USD_EUR_Cross_Rate short (risk 1,716)</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>S_P_500_Index stop (-1,615)</t>
+          <t>S_P_500_Index stop (-1,876)</t>
         </is>
       </c>
     </row>
@@ -2643,13 +2663,13 @@
         <v>46088</v>
       </c>
       <c r="B71" s="5" t="n">
-        <v>125954.33</v>
+        <v>123345.31</v>
       </c>
       <c r="C71" s="5" t="n">
-        <v>1481.29</v>
+        <v>1716.33</v>
       </c>
       <c r="D71" s="5" t="n">
-        <v>124473.04</v>
+        <v>121628.98</v>
       </c>
       <c r="E71" t="n">
         <v>1</v>
@@ -2667,13 +2687,13 @@
         <v>46089</v>
       </c>
       <c r="B72" s="5" t="n">
-        <v>125954.33</v>
+        <v>123345.31</v>
       </c>
       <c r="C72" s="5" t="n">
-        <v>1481.29</v>
+        <v>1716.33</v>
       </c>
       <c r="D72" s="5" t="n">
-        <v>124473.04</v>
+        <v>121628.98</v>
       </c>
       <c r="E72" t="n">
         <v>1</v>
@@ -2691,13 +2711,13 @@
         <v>46090</v>
       </c>
       <c r="B73" s="5" t="n">
-        <v>124338.38</v>
+        <v>121472.95</v>
       </c>
       <c r="C73" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D73" s="5" t="n">
-        <v>124338.38</v>
+        <v>121472.95</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
@@ -2706,7 +2726,7 @@
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate stop (-1,616)</t>
+          <t>USD_EUR_Cross_Rate stop (-1,872)</t>
         </is>
       </c>
     </row>
@@ -2715,13 +2735,13 @@
         <v>46091</v>
       </c>
       <c r="B74" s="5" t="n">
-        <v>124338.38</v>
+        <v>121472.95</v>
       </c>
       <c r="C74" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D74" s="5" t="n">
-        <v>124338.38</v>
+        <v>121472.95</v>
       </c>
       <c r="E74" t="n">
         <v>0</v>
@@ -2735,13 +2755,13 @@
         <v>46092</v>
       </c>
       <c r="B75" s="5" t="n">
-        <v>124338.38</v>
+        <v>121472.95</v>
       </c>
       <c r="C75" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D75" s="5" t="n">
-        <v>124338.38</v>
+        <v>121472.95</v>
       </c>
       <c r="E75" t="n">
         <v>0</v>
@@ -2755,13 +2775,13 @@
         <v>46093</v>
       </c>
       <c r="B76" s="5" t="n">
-        <v>124338.38</v>
+        <v>121472.95</v>
       </c>
       <c r="C76" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D76" s="5" t="n">
-        <v>124338.38</v>
+        <v>121472.95</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
@@ -2775,13 +2795,13 @@
         <v>46094</v>
       </c>
       <c r="B77" s="5" t="n">
-        <v>124338.38</v>
+        <v>121472.95</v>
       </c>
       <c r="C77" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D77" s="5" t="n">
-        <v>124338.38</v>
+        <v>121472.95</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
@@ -2795,13 +2815,13 @@
         <v>46095</v>
       </c>
       <c r="B78" s="5" t="n">
-        <v>124338.38</v>
+        <v>121472.95</v>
       </c>
       <c r="C78" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D78" s="5" t="n">
-        <v>124338.38</v>
+        <v>121472.95</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
@@ -2815,13 +2835,13 @@
         <v>46096</v>
       </c>
       <c r="B79" s="5" t="n">
-        <v>124338.38</v>
+        <v>121472.95</v>
       </c>
       <c r="C79" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D79" s="5" t="n">
-        <v>124338.38</v>
+        <v>121472.95</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
@@ -2835,13 +2855,13 @@
         <v>46097</v>
       </c>
       <c r="B80" s="5" t="n">
-        <v>124338.38</v>
+        <v>121472.95</v>
       </c>
       <c r="C80" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D80" s="5" t="n">
-        <v>124338.38</v>
+        <v>121472.95</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
@@ -2855,13 +2875,13 @@
         <v>46098</v>
       </c>
       <c r="B81" s="5" t="n">
-        <v>124338.38</v>
+        <v>121472.95</v>
       </c>
       <c r="C81" s="5" t="n">
-        <v>1460.98</v>
+        <v>1688.47</v>
       </c>
       <c r="D81" s="5" t="n">
-        <v>122877.4</v>
+        <v>119784.48</v>
       </c>
       <c r="E81" t="n">
         <v>1</v>
@@ -2873,7 +2893,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance short (risk 1,461)</t>
+          <t>Bitcoin_Per_USD_Binance short (risk 1,688)</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
@@ -2883,13 +2903,13 @@
         <v>46099</v>
       </c>
       <c r="B82" s="5" t="n">
-        <v>127986.41</v>
+        <v>124675.96</v>
       </c>
       <c r="C82" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D82" s="5" t="n">
-        <v>127986.41</v>
+        <v>124675.96</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
@@ -2898,7 +2918,7 @@
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance target_r (+3,648)</t>
+          <t>Bitcoin_Per_USD_Binance target_r (+3,203)</t>
         </is>
       </c>
     </row>
@@ -2907,13 +2927,13 @@
         <v>46100</v>
       </c>
       <c r="B83" s="5" t="n">
-        <v>127986.41</v>
+        <v>124675.96</v>
       </c>
       <c r="C83" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D83" s="5" t="n">
-        <v>127986.41</v>
+        <v>124675.96</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
@@ -2927,13 +2947,13 @@
         <v>46101</v>
       </c>
       <c r="B84" s="5" t="n">
-        <v>127986.41</v>
+        <v>124675.96</v>
       </c>
       <c r="C84" s="5" t="n">
-        <v>1503.84</v>
+        <v>1733</v>
       </c>
       <c r="D84" s="5" t="n">
-        <v>126482.57</v>
+        <v>122942.96</v>
       </c>
       <c r="E84" t="n">
         <v>1</v>
@@ -2945,7 +2965,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP short (risk 1,504)</t>
+          <t>United_States_Oil_Fund_LP short (risk 1,733)</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
@@ -2955,13 +2975,13 @@
         <v>46102</v>
       </c>
       <c r="B85" s="5" t="n">
-        <v>127986.41</v>
+        <v>124675.96</v>
       </c>
       <c r="C85" s="5" t="n">
-        <v>1503.84</v>
+        <v>1733</v>
       </c>
       <c r="D85" s="5" t="n">
-        <v>126482.57</v>
+        <v>122942.96</v>
       </c>
       <c r="E85" t="n">
         <v>1</v>
@@ -2979,13 +2999,13 @@
         <v>46103</v>
       </c>
       <c r="B86" s="5" t="n">
-        <v>127986.41</v>
+        <v>124675.96</v>
       </c>
       <c r="C86" s="5" t="n">
-        <v>1503.84</v>
+        <v>1733</v>
       </c>
       <c r="D86" s="5" t="n">
-        <v>126482.57</v>
+        <v>122942.96</v>
       </c>
       <c r="E86" t="n">
         <v>1</v>
@@ -3003,13 +3023,13 @@
         <v>46104</v>
       </c>
       <c r="B87" s="5" t="n">
-        <v>137640.81</v>
+        <v>135801.5</v>
       </c>
       <c r="C87" s="5" t="n">
-        <v>1486.17</v>
+        <v>1708.91</v>
       </c>
       <c r="D87" s="5" t="n">
-        <v>136154.64</v>
+        <v>134092.59</v>
       </c>
       <c r="E87" t="n">
         <v>1</v>
@@ -3021,12 +3041,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures long (risk 1,486)</t>
+          <t>NY_Copper_Futures long (risk 1,709)</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP target_r (+9,654)</t>
+          <t>United_States_Oil_Fund_LP target_r (+11,126)</t>
         </is>
       </c>
     </row>
@@ -3035,13 +3055,13 @@
         <v>46105</v>
       </c>
       <c r="B88" s="5" t="n">
-        <v>141422.42</v>
+        <v>139043.35</v>
       </c>
       <c r="C88" s="5" t="n">
-        <v>1599.82</v>
+        <v>1863.89</v>
       </c>
       <c r="D88" s="5" t="n">
-        <v>139822.6</v>
+        <v>137179.47</v>
       </c>
       <c r="E88" t="n">
         <v>1</v>
@@ -3053,12 +3073,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX long (risk 1,600)</t>
+          <t>Gold_Futures_COMEX long (risk 1,864)</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures target_r (+3,782)</t>
+          <t>NY_Copper_Futures target_r (+3,242)</t>
         </is>
       </c>
     </row>
@@ -3067,13 +3087,13 @@
         <v>46106</v>
       </c>
       <c r="B89" s="5" t="n">
-        <v>149104.83</v>
+        <v>142571.79</v>
       </c>
       <c r="C89" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D89" s="5" t="n">
-        <v>149104.83</v>
+        <v>142571.79</v>
       </c>
       <c r="E89" t="n">
         <v>0</v>
@@ -3082,7 +3102,7 @@
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX target_r (+7,682)</t>
+          <t>Gold_Futures_COMEX target_r (+3,528)</t>
         </is>
       </c>
     </row>
@@ -3091,13 +3111,13 @@
         <v>46107</v>
       </c>
       <c r="B90" s="5" t="n">
-        <v>149104.83</v>
+        <v>142571.79</v>
       </c>
       <c r="C90" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D90" s="5" t="n">
-        <v>149104.83</v>
+        <v>142571.79</v>
       </c>
       <c r="E90" t="n">
         <v>0</v>
@@ -3111,13 +3131,13 @@
         <v>46108</v>
       </c>
       <c r="B91" s="5" t="n">
-        <v>149104.83</v>
+        <v>142571.79</v>
       </c>
       <c r="C91" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D91" s="5" t="n">
-        <v>149104.83</v>
+        <v>142571.79</v>
       </c>
       <c r="E91" t="n">
         <v>0</v>
@@ -3131,13 +3151,13 @@
         <v>46109</v>
       </c>
       <c r="B92" s="5" t="n">
-        <v>149104.83</v>
+        <v>142571.79</v>
       </c>
       <c r="C92" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D92" s="5" t="n">
-        <v>149104.83</v>
+        <v>142571.79</v>
       </c>
       <c r="E92" t="n">
         <v>0</v>
@@ -3151,13 +3171,13 @@
         <v>46110</v>
       </c>
       <c r="B93" s="5" t="n">
-        <v>149104.83</v>
+        <v>142571.79</v>
       </c>
       <c r="C93" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D93" s="5" t="n">
-        <v>149104.83</v>
+        <v>142571.79</v>
       </c>
       <c r="E93" t="n">
         <v>0</v>
@@ -3171,13 +3191,13 @@
         <v>46111</v>
       </c>
       <c r="B94" s="5" t="n">
-        <v>149104.83</v>
+        <v>142571.79</v>
       </c>
       <c r="C94" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D94" s="5" t="n">
-        <v>149104.83</v>
+        <v>142571.79</v>
       </c>
       <c r="E94" t="n">
         <v>0</v>
@@ -3191,13 +3211,13 @@
         <v>46112</v>
       </c>
       <c r="B95" s="5" t="n">
-        <v>149104.83</v>
+        <v>142571.79</v>
       </c>
       <c r="C95" s="5" t="n">
-        <v>1751.98</v>
+        <v>1981.75</v>
       </c>
       <c r="D95" s="5" t="n">
-        <v>147352.85</v>
+        <v>140590.05</v>
       </c>
       <c r="E95" t="n">
         <v>1</v>
@@ -3209,7 +3229,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP short (risk 1,752)</t>
+          <t>United_States_Oil_Fund_LP short (risk 1,982)</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
@@ -3219,13 +3239,13 @@
         <v>46113</v>
       </c>
       <c r="B96" s="5" t="n">
-        <v>153439.86</v>
+        <v>146286.3</v>
       </c>
       <c r="C96" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D96" s="5" t="n">
-        <v>153439.86</v>
+        <v>146286.3</v>
       </c>
       <c r="E96" t="n">
         <v>0</v>
@@ -3234,7 +3254,7 @@
       <c r="G96" t="inlineStr"/>
       <c r="H96" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP target_r (+4,335)</t>
+          <t>United_States_Oil_Fund_LP target_r (+3,715)</t>
         </is>
       </c>
     </row>
@@ -3243,13 +3263,13 @@
         <v>46114</v>
       </c>
       <c r="B97" s="5" t="n">
-        <v>153439.86</v>
+        <v>146286.3</v>
       </c>
       <c r="C97" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D97" s="5" t="n">
-        <v>153439.86</v>
+        <v>146286.3</v>
       </c>
       <c r="E97" t="n">
         <v>0</v>
@@ -3263,13 +3283,13 @@
         <v>46115</v>
       </c>
       <c r="B98" s="5" t="n">
-        <v>153439.86</v>
+        <v>146286.3</v>
       </c>
       <c r="C98" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D98" s="5" t="n">
-        <v>153439.86</v>
+        <v>146286.3</v>
       </c>
       <c r="E98" t="n">
         <v>0</v>
@@ -3283,13 +3303,13 @@
         <v>46116</v>
       </c>
       <c r="B99" s="5" t="n">
-        <v>153439.86</v>
+        <v>146286.3</v>
       </c>
       <c r="C99" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D99" s="5" t="n">
-        <v>153439.86</v>
+        <v>146286.3</v>
       </c>
       <c r="E99" t="n">
         <v>0</v>
@@ -3303,13 +3323,13 @@
         <v>46117</v>
       </c>
       <c r="B100" s="5" t="n">
-        <v>153439.86</v>
+        <v>146286.3</v>
       </c>
       <c r="C100" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D100" s="5" t="n">
-        <v>153439.86</v>
+        <v>146286.3</v>
       </c>
       <c r="E100" t="n">
         <v>0</v>
@@ -3323,13 +3343,13 @@
         <v>46118</v>
       </c>
       <c r="B101" s="5" t="n">
-        <v>153439.86</v>
+        <v>146286.3</v>
       </c>
       <c r="C101" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D101" s="5" t="n">
-        <v>153439.86</v>
+        <v>146286.3</v>
       </c>
       <c r="E101" t="n">
         <v>0</v>
@@ -3343,13 +3363,13 @@
         <v>46119</v>
       </c>
       <c r="B102" s="5" t="n">
-        <v>153439.86</v>
+        <v>146286.3</v>
       </c>
       <c r="C102" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D102" s="5" t="n">
-        <v>153439.86</v>
+        <v>146286.3</v>
       </c>
       <c r="E102" t="n">
         <v>0</v>
@@ -3363,13 +3383,13 @@
         <v>46120</v>
       </c>
       <c r="B103" s="5" t="n">
-        <v>153439.86</v>
+        <v>146286.3</v>
       </c>
       <c r="C103" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D103" s="5" t="n">
-        <v>153439.86</v>
+        <v>146286.3</v>
       </c>
       <c r="E103" t="n">
         <v>0</v>
@@ -3383,13 +3403,13 @@
         <v>46121</v>
       </c>
       <c r="B104" s="5" t="n">
-        <v>153439.86</v>
+        <v>146286.3</v>
       </c>
       <c r="C104" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D104" s="5" t="n">
-        <v>153439.86</v>
+        <v>146286.3</v>
       </c>
       <c r="E104" t="n">
         <v>0</v>
@@ -3403,13 +3423,13 @@
         <v>46122</v>
       </c>
       <c r="B105" s="5" t="n">
-        <v>153439.86</v>
+        <v>146286.3</v>
       </c>
       <c r="C105" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D105" s="5" t="n">
-        <v>153439.86</v>
+        <v>146286.3</v>
       </c>
       <c r="E105" t="n">
         <v>0</v>
@@ -3423,13 +3443,13 @@
         <v>46123</v>
       </c>
       <c r="B106" s="5" t="n">
-        <v>153439.86</v>
+        <v>146286.3</v>
       </c>
       <c r="C106" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D106" s="5" t="n">
-        <v>153439.86</v>
+        <v>146286.3</v>
       </c>
       <c r="E106" t="n">
         <v>0</v>
@@ -3443,13 +3463,13 @@
         <v>46124</v>
       </c>
       <c r="B107" s="5" t="n">
-        <v>153439.86</v>
+        <v>146286.3</v>
       </c>
       <c r="C107" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D107" s="5" t="n">
-        <v>153439.86</v>
+        <v>146286.3</v>
       </c>
       <c r="E107" t="n">
         <v>0</v>
@@ -3463,13 +3483,13 @@
         <v>46125</v>
       </c>
       <c r="B108" s="5" t="n">
-        <v>153439.86</v>
+        <v>146286.3</v>
       </c>
       <c r="C108" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D108" s="5" t="n">
-        <v>153439.86</v>
+        <v>146286.3</v>
       </c>
       <c r="E108" t="n">
         <v>0</v>
@@ -3483,13 +3503,13 @@
         <v>46126</v>
       </c>
       <c r="B109" s="5" t="n">
-        <v>153439.86</v>
+        <v>146286.3</v>
       </c>
       <c r="C109" s="5" t="n">
-        <v>1802.92</v>
+        <v>2033.38</v>
       </c>
       <c r="D109" s="5" t="n">
-        <v>151636.94</v>
+        <v>144252.92</v>
       </c>
       <c r="E109" t="n">
         <v>1</v>
@@ -3501,7 +3521,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance short (risk 1,803)</t>
+          <t>Bitcoin_Per_USD_Binance short (risk 2,033)</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
@@ -3511,13 +3531,13 @@
         <v>46127</v>
       </c>
       <c r="B110" s="5" t="n">
-        <v>153439.86</v>
+        <v>146286.3</v>
       </c>
       <c r="C110" s="5" t="n">
-        <v>7085.56</v>
+        <v>7965.5</v>
       </c>
       <c r="D110" s="5" t="n">
-        <v>146354.3</v>
+        <v>138320.8</v>
       </c>
       <c r="E110" t="n">
         <v>4</v>
@@ -3529,7 +3549,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Ethereum_Per_USD_Binance short (risk 1,782); Live_Cattle_Futures_CME short (risk 1,761); NY_Copper_Futures short (risk 1,740)</t>
+          <t>Ethereum_Per_USD_Binance short (risk 2,005); Live_Cattle_Futures_CME short (risk 1,977); NY_Copper_Futures short (risk 1,950)</t>
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
@@ -3539,13 +3559,13 @@
         <v>46128</v>
       </c>
       <c r="B111" s="5" t="n">
-        <v>161966.76</v>
+        <v>153482.31</v>
       </c>
       <c r="C111" s="5" t="n">
-        <v>3543.03</v>
+        <v>3983.14</v>
       </c>
       <c r="D111" s="5" t="n">
-        <v>158423.73</v>
+        <v>149499.17</v>
       </c>
       <c r="E111" t="n">
         <v>2</v>
@@ -3558,7 +3578,7 @@
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Ethereum_Per_USD_Binance target_r (+4,232); Live_Cattle_Futures_CME target_r (+4,295)</t>
+          <t>Ethereum_Per_USD_Binance target_r (+3,559); Live_Cattle_Futures_CME target_r (+3,637)</t>
         </is>
       </c>
     </row>
@@ -3567,13 +3587,13 @@
         <v>46129</v>
       </c>
       <c r="B112" s="5" t="n">
-        <v>161898.9</v>
+        <v>153385.77</v>
       </c>
       <c r="C112" s="5" t="n">
-        <v>1740.11</v>
+        <v>1949.76</v>
       </c>
       <c r="D112" s="5" t="n">
-        <v>160158.79</v>
+        <v>151436.01</v>
       </c>
       <c r="E112" t="n">
         <v>1</v>
@@ -3585,12 +3605,12 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate long (risk 1,861)</t>
+          <t>USD_EUR_Cross_Rate long (risk 2,078)</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance stop (-1,809); USD_EUR_Cross_Rate data_end (+1,741)</t>
+          <t>Bitcoin_Per_USD_Binance stop (-2,041); USD_EUR_Cross_Rate data_end (+1,944)</t>
         </is>
       </c>
     </row>
@@ -3599,13 +3619,13 @@
         <v>46130</v>
       </c>
       <c r="B113" s="5" t="n">
-        <v>161898.9</v>
+        <v>153385.77</v>
       </c>
       <c r="C113" s="5" t="n">
-        <v>1740.11</v>
+        <v>1949.76</v>
       </c>
       <c r="D113" s="5" t="n">
-        <v>160158.79</v>
+        <v>151436.01</v>
       </c>
       <c r="E113" t="n">
         <v>1</v>
@@ -3623,13 +3643,13 @@
         <v>46132</v>
       </c>
       <c r="B114" s="5" t="n">
-        <v>161898.9</v>
+        <v>153385.77</v>
       </c>
       <c r="C114" s="5" t="n">
-        <v>1740.11</v>
+        <v>1949.76</v>
       </c>
       <c r="D114" s="5" t="n">
-        <v>160158.79</v>
+        <v>151436.01</v>
       </c>
       <c r="E114" t="n">
         <v>1</v>
@@ -3647,13 +3667,13 @@
         <v>46133</v>
       </c>
       <c r="B115" s="5" t="n">
-        <v>161898.9</v>
+        <v>153385.77</v>
       </c>
       <c r="C115" s="5" t="n">
-        <v>1740.11</v>
+        <v>1949.76</v>
       </c>
       <c r="D115" s="5" t="n">
-        <v>160158.79</v>
+        <v>151436.01</v>
       </c>
       <c r="E115" t="n">
         <v>1</v>
@@ -3671,13 +3691,13 @@
         <v>46134</v>
       </c>
       <c r="B116" s="5" t="n">
-        <v>160145.53</v>
+        <v>151421.15</v>
       </c>
       <c r="C116" s="5" t="n">
-        <v>1881.87</v>
+        <v>2104.96</v>
       </c>
       <c r="D116" s="5" t="n">
-        <v>158263.67</v>
+        <v>149316.19</v>
       </c>
       <c r="E116" t="n">
         <v>1</v>
@@ -3689,12 +3709,12 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini short (risk 1,882)</t>
+          <t>Dow_Futures_E_mini short (risk 2,105)</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures stop (-1,753)</t>
+          <t>NY_Copper_Futures stop (-1,965)</t>
         </is>
       </c>
     </row>
@@ -3703,13 +3723,13 @@
         <v>46135</v>
       </c>
       <c r="B117" s="5" t="n">
-        <v>167950.6</v>
+        <v>160151.51</v>
       </c>
       <c r="C117" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D117" s="5" t="n">
-        <v>167950.6</v>
+        <v>160151.51</v>
       </c>
       <c r="E117" t="n">
         <v>0</v>
@@ -3718,7 +3738,7 @@
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini target_r (+7,805)</t>
+          <t>Dow_Futures_E_mini target_r (+8,730)</t>
         </is>
       </c>
     </row>
@@ -3727,13 +3747,13 @@
         <v>46136</v>
       </c>
       <c r="B118" s="5" t="n">
-        <v>167950.6</v>
+        <v>160151.51</v>
       </c>
       <c r="C118" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D118" s="5" t="n">
-        <v>167950.6</v>
+        <v>160151.51</v>
       </c>
       <c r="E118" t="n">
         <v>0</v>
@@ -3747,13 +3767,13 @@
         <v>46139</v>
       </c>
       <c r="B119" s="5" t="n">
-        <v>167950.6</v>
+        <v>160151.51</v>
       </c>
       <c r="C119" s="5" t="n">
-        <v>1973.42</v>
+        <v>2226.11</v>
       </c>
       <c r="D119" s="5" t="n">
-        <v>165977.18</v>
+        <v>157925.4</v>
       </c>
       <c r="E119" t="n">
         <v>1</v>
@@ -3765,7 +3785,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME short (risk 1,973)</t>
+          <t>Bitcoin_Per_USD_CME short (risk 2,226)</t>
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
@@ -3775,13 +3795,13 @@
         <v>46140</v>
       </c>
       <c r="B120" s="5" t="n">
-        <v>172876.02</v>
+        <v>164371.95</v>
       </c>
       <c r="C120" s="5" t="n">
-        <v>1950.23</v>
+        <v>2195.16</v>
       </c>
       <c r="D120" s="5" t="n">
-        <v>170925.79</v>
+        <v>162176.78</v>
       </c>
       <c r="E120" t="n">
         <v>1</v>
@@ -3793,12 +3813,12 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini short (risk 1,950)</t>
+          <t>S_P_500_E_mini short (risk 2,195)</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME target_r (+4,925)</t>
+          <t>Bitcoin_Per_USD_CME target_r (+4,220)</t>
         </is>
       </c>
     </row>
@@ -3807,13 +3827,13 @@
         <v>46141</v>
       </c>
       <c r="B121" s="5" t="n">
-        <v>177749.27</v>
+        <v>168540.13</v>
       </c>
       <c r="C121" s="5" t="n">
-        <v>2008.38</v>
+        <v>2254.26</v>
       </c>
       <c r="D121" s="5" t="n">
-        <v>175740.89</v>
+        <v>166285.87</v>
       </c>
       <c r="E121" t="n">
         <v>1</v>
@@ -3825,12 +3845,12 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 2,008)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 2,254)</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini target_r (+4,873)</t>
+          <t>S_P_500_E_mini target_r (+4,168)</t>
         </is>
       </c>
     </row>
@@ -3839,13 +3859,13 @@
         <v>46142</v>
       </c>
       <c r="B122" s="5" t="n">
-        <v>182725.08</v>
+        <v>172772.56</v>
       </c>
       <c r="C122" s="5" t="n">
-        <v>2064.96</v>
+        <v>2311.37</v>
       </c>
       <c r="D122" s="5" t="n">
-        <v>180660.13</v>
+        <v>170461.19</v>
       </c>
       <c r="E122" t="n">
         <v>1</v>
@@ -3857,12 +3877,12 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures short (risk 2,065)</t>
+          <t>Corn_CBOT_Futures short (risk 2,311)</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT target_r (+4,976)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT target_r (+4,232)</t>
         </is>
       </c>
     </row>
@@ -3871,13 +3891,13 @@
         <v>46143</v>
       </c>
       <c r="B123" s="5" t="n">
-        <v>180225.4</v>
+        <v>178125.32</v>
       </c>
       <c r="C123" s="5" t="n">
-        <v>6293.74</v>
+        <v>7009.88</v>
       </c>
       <c r="D123" s="5" t="n">
-        <v>173931.66</v>
+        <v>171115.44</v>
       </c>
       <c r="E123" t="n">
         <v>3</v>
@@ -3889,12 +3909,12 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Japanese_Yen_Futures short (risk 2,123); Live_Cattle_Futures_CME short (risk 2,098); US_Dollar_Index_Futures long (risk 2,073)</t>
+          <t>Japanese_Yen_Futures short (risk 2,369); Live_Cattle_Futures_CME short (risk 2,336); US_Dollar_Index_Futures long (risk 2,304)</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures unknown_pl (-2,500)</t>
+          <t>Corn_CBOT_Futures target_r (+5,353)</t>
         </is>
       </c>
     </row>
@@ -3903,30 +3923,30 @@
         <v>46146</v>
       </c>
       <c r="B124" s="5" t="n">
-        <v>185436.37</v>
+        <v>186886.03</v>
       </c>
       <c r="C124" s="5" t="n">
-        <v>6239.62</v>
+        <v>4747.92</v>
       </c>
       <c r="D124" s="5" t="n">
-        <v>179196.75</v>
+        <v>182138.12</v>
       </c>
       <c r="E124" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Japanese_Yen_Futures, Nasdaq_100_E_mini, US_Dollar_Index_Futures</t>
+          <t>Japanese_Yen_Futures, Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini short (risk 2,044)</t>
+          <t>Nasdaq_100_E_mini short (risk 2,379)</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME target_r (+5,211)</t>
+          <t>Live_Cattle_Futures_CME target_r (+4,402); US_Dollar_Index_Futures target_r (+4,359)</t>
         </is>
       </c>
     </row>
@@ -3935,13 +3955,13 @@
         <v>46147</v>
       </c>
       <c r="B125" s="5" t="n">
-        <v>195714.38</v>
+        <v>184505.91</v>
       </c>
       <c r="C125" s="5" t="n">
-        <v>4228.32</v>
+        <v>4901.13</v>
       </c>
       <c r="D125" s="5" t="n">
-        <v>191486.06</v>
+        <v>179604.78</v>
       </c>
       <c r="E125" t="n">
         <v>2</v>
@@ -3953,12 +3973,12 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures short (risk 2,106)</t>
+          <t>Corn_CBOT_Futures short (risk 2,532)</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini target_r (+5,112); US_Dollar_Index_Futures target_r (+5,166)</t>
+          <t>Nasdaq_100_E_mini unknown_pl (-2,380)</t>
         </is>
       </c>
     </row>
@@ -3967,13 +3987,13 @@
         <v>46148</v>
       </c>
       <c r="B126" s="5" t="n">
-        <v>198243.21</v>
+        <v>186230.3</v>
       </c>
       <c r="C126" s="5" t="n">
-        <v>4473.49</v>
+        <v>4958.31</v>
       </c>
       <c r="D126" s="5" t="n">
-        <v>193769.73</v>
+        <v>181271.99</v>
       </c>
       <c r="E126" t="n">
         <v>2</v>
@@ -3985,12 +4005,12 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME short (risk 2,250); US_Dollar_Index_Futures long (risk 2,224)</t>
+          <t>Bitcoin_Per_USD_CME short (risk 2,497); US_Dollar_Index_Futures long (risk 2,462)</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures target_r (+4,881); Japanese_Yen_Futures stop (-2,352)</t>
+          <t>Corn_CBOT_Futures target_r (+4,350); Japanese_Yen_Futures stop (-2,626)</t>
         </is>
       </c>
     </row>
@@ -3999,13 +4019,13 @@
         <v>46149</v>
       </c>
       <c r="B127" s="5" t="n">
-        <v>203860.01</v>
+        <v>191016.35</v>
       </c>
       <c r="C127" s="5" t="n">
-        <v>6750.36</v>
+        <v>7466.14</v>
       </c>
       <c r="D127" s="5" t="n">
-        <v>197109.65</v>
+        <v>183550.2</v>
       </c>
       <c r="E127" t="n">
         <v>3</v>
@@ -4017,12 +4037,12 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>EURO_Futures short (risk 2,277); NY_Platinum_Futures short (risk 2,250)</t>
+          <t>EURO_Futures short (risk 2,520); NY_Platinum_Futures short (risk 2,485)</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME target_r (+5,617)</t>
+          <t>Bitcoin_Per_USD_CME target_r (+4,786)</t>
         </is>
       </c>
     </row>
@@ -4031,26 +4051,26 @@
         <v>46150</v>
       </c>
       <c r="B128" s="5" t="n">
-        <v>209595.89</v>
+        <v>202067.9</v>
       </c>
       <c r="C128" s="5" t="n">
-        <v>4473.57</v>
+        <v>2461.8</v>
       </c>
       <c r="D128" s="5" t="n">
-        <v>205122.32</v>
+        <v>199606.09</v>
       </c>
       <c r="E128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures, US_Dollar_Index_Futures</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
-          <t>EURO_Futures target_r (+5,736)</t>
+          <t>EURO_Futures target_r (+6,348); NY_Platinum_Futures target_r (+4,704)</t>
         </is>
       </c>
     </row>
@@ -4059,13 +4079,13 @@
         <v>46153</v>
       </c>
       <c r="B129" s="5" t="n">
-        <v>207314.92</v>
+        <v>202067.9</v>
       </c>
       <c r="C129" s="5" t="n">
-        <v>4633.71</v>
+        <v>5236.33</v>
       </c>
       <c r="D129" s="5" t="n">
-        <v>202681.21</v>
+        <v>196831.57</v>
       </c>
       <c r="E129" t="n">
         <v>2</v>
@@ -4077,27 +4097,23 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX short (risk 2,410)</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>NY_Platinum_Futures stop (-2,281)</t>
-        </is>
-      </c>
+          <t>Gold_Futures_COMEX short (risk 2,775)</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" s="4" t="n">
         <v>46154</v>
       </c>
       <c r="B130" s="5" t="n">
-        <v>210368.26</v>
+        <v>203861.92</v>
       </c>
       <c r="C130" s="5" t="n">
-        <v>2381.5</v>
+        <v>2735.96</v>
       </c>
       <c r="D130" s="5" t="n">
-        <v>207986.76</v>
+        <v>201125.96</v>
       </c>
       <c r="E130" t="n">
         <v>1</v>
@@ -4109,12 +4125,12 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX short (risk 2,382)</t>
+          <t>Silver_Futures_COMEX short (risk 2,736)</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX unknown_pl (-2,487); US_Dollar_Index_Futures target_r (+5,541)</t>
+          <t>Gold_Futures_COMEX unknown_pl (-2,863); US_Dollar_Index_Futures target_r (+4,657)</t>
         </is>
       </c>
     </row>
@@ -4123,13 +4139,13 @@
         <v>46155</v>
       </c>
       <c r="B131" s="5" t="n">
-        <v>207981.8</v>
+        <v>201120.26</v>
       </c>
       <c r="C131" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D131" s="5" t="n">
-        <v>207981.8</v>
+        <v>201120.26</v>
       </c>
       <c r="E131" t="n">
         <v>0</v>
@@ -4138,7 +4154,7 @@
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX stop (-2,386)</t>
+          <t>Silver_Futures_COMEX stop (-2,742)</t>
         </is>
       </c>
     </row>
@@ -4147,13 +4163,13 @@
         <v>46156</v>
       </c>
       <c r="B132" s="5" t="n">
-        <v>207981.8</v>
+        <v>201120.26</v>
       </c>
       <c r="C132" s="5" t="n">
-        <v>2443.79</v>
+        <v>2795.57</v>
       </c>
       <c r="D132" s="5" t="n">
-        <v>205538.01</v>
+        <v>198324.69</v>
       </c>
       <c r="E132" t="n">
         <v>1</v>
@@ -4165,7 +4181,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 2,444)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 2,796)</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
@@ -4175,13 +4191,13 @@
         <v>46157</v>
       </c>
       <c r="B133" s="5" t="n">
-        <v>214024.31</v>
+        <v>206355.26</v>
       </c>
       <c r="C133" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D133" s="5" t="n">
-        <v>214024.31</v>
+        <v>206355.26</v>
       </c>
       <c r="E133" t="n">
         <v>0</v>
@@ -4190,7 +4206,7 @@
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT target_r (+6,043)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT target_r (+5,235)</t>
         </is>
       </c>
     </row>
@@ -4199,13 +4215,13 @@
         <v>46160</v>
       </c>
       <c r="B134" s="5" t="n">
-        <v>214024.31</v>
+        <v>206355.26</v>
       </c>
       <c r="C134" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D134" s="5" t="n">
-        <v>214024.31</v>
+        <v>206355.26</v>
       </c>
       <c r="E134" t="n">
         <v>0</v>
@@ -4219,13 +4235,13 @@
         <v>46161</v>
       </c>
       <c r="B135" s="5" t="n">
-        <v>214024.31</v>
+        <v>206355.26</v>
       </c>
       <c r="C135" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D135" s="5" t="n">
-        <v>214024.31</v>
+        <v>206355.26</v>
       </c>
       <c r="E135" t="n">
         <v>0</v>
@@ -4239,13 +4255,13 @@
         <v>46162</v>
       </c>
       <c r="B136" s="5" t="n">
-        <v>214024.31</v>
+        <v>206355.26</v>
       </c>
       <c r="C136" s="5" t="n">
-        <v>2514.79</v>
+        <v>2868.34</v>
       </c>
       <c r="D136" s="5" t="n">
-        <v>211509.52</v>
+        <v>203486.92</v>
       </c>
       <c r="E136" t="n">
         <v>1</v>
@@ -4257,7 +4273,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures short (risk 2,515)</t>
+          <t>US_Dollar_Index_Futures short (risk 2,868)</t>
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
@@ -4267,13 +4283,13 @@
         <v>46163</v>
       </c>
       <c r="B137" s="5" t="n">
-        <v>214024.31</v>
+        <v>206355.26</v>
       </c>
       <c r="C137" s="5" t="n">
-        <v>5000.02</v>
+        <v>5696.81</v>
       </c>
       <c r="D137" s="5" t="n">
-        <v>209024.29</v>
+        <v>200658.45</v>
       </c>
       <c r="E137" t="n">
         <v>2</v>
@@ -4285,7 +4301,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures long (risk 2,485)</t>
+          <t>NY_Palladium_Futures long (risk 2,828)</t>
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
@@ -4295,13 +4311,13 @@
         <v>46164</v>
       </c>
       <c r="B138" s="5" t="n">
-        <v>220222.83</v>
+        <v>213409.84</v>
       </c>
       <c r="C138" s="5" t="n">
-        <v>2514.79</v>
+        <v>2868.34</v>
       </c>
       <c r="D138" s="5" t="n">
-        <v>217708.04</v>
+        <v>210541.5</v>
       </c>
       <c r="E138" t="n">
         <v>1</v>
@@ -4314,7 +4330,7 @@
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures target_r (+6,199)</t>
+          <t>NY_Palladium_Futures target_r (+7,055)</t>
         </is>
       </c>
     </row>
@@ -4323,13 +4339,13 @@
         <v>46167</v>
       </c>
       <c r="B139" s="5" t="n">
-        <v>226484</v>
+        <v>218830.26</v>
       </c>
       <c r="C139" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D139" s="5" t="n">
-        <v>226484</v>
+        <v>218830.26</v>
       </c>
       <c r="E139" t="n">
         <v>0</v>
@@ -4338,7 +4354,7 @@
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures target_r (+6,261)</t>
+          <t>US_Dollar_Index_Futures target_r (+5,420)</t>
         </is>
       </c>
     </row>
@@ -4347,13 +4363,13 @@
         <v>46168</v>
       </c>
       <c r="B140" s="5" t="n">
-        <v>226484</v>
+        <v>218830.26</v>
       </c>
       <c r="C140" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D140" s="5" t="n">
-        <v>226484</v>
+        <v>218830.26</v>
       </c>
       <c r="E140" t="n">
         <v>0</v>
@@ -4367,13 +4383,13 @@
         <v>46169</v>
       </c>
       <c r="B141" s="5" t="n">
-        <v>226484</v>
+        <v>218830.26</v>
       </c>
       <c r="C141" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D141" s="5" t="n">
-        <v>226484</v>
+        <v>218830.26</v>
       </c>
       <c r="E141" t="n">
         <v>0</v>
@@ -4387,13 +4403,13 @@
         <v>46170</v>
       </c>
       <c r="B142" s="5" t="n">
-        <v>226484</v>
+        <v>218830.26</v>
       </c>
       <c r="C142" s="5" t="n">
-        <v>5291.11</v>
+        <v>6041.2</v>
       </c>
       <c r="D142" s="5" t="n">
-        <v>221192.89</v>
+        <v>212789.06</v>
       </c>
       <c r="E142" t="n">
         <v>2</v>
@@ -4405,7 +4421,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX long (risk 2,661); US_Dollar_Index_Futures short (risk 2,630)</t>
+          <t>Silver_Futures_COMEX long (risk 3,042); US_Dollar_Index_Futures short (risk 2,999)</t>
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
@@ -4415,13 +4431,13 @@
         <v>46174</v>
       </c>
       <c r="B143" s="5" t="n">
-        <v>226484</v>
+        <v>218830.26</v>
       </c>
       <c r="C143" s="5" t="n">
-        <v>5291.11</v>
+        <v>6041.2</v>
       </c>
       <c r="D143" s="5" t="n">
-        <v>221192.89</v>
+        <v>212789.06</v>
       </c>
       <c r="E143" t="n">
         <v>2</v>
@@ -4439,50 +4455,50 @@
         <v>46175</v>
       </c>
       <c r="B144" s="5" t="n">
-        <v>226484</v>
+        <v>224606.27</v>
       </c>
       <c r="C144" s="5" t="n">
-        <v>5291.11</v>
+        <v>2999.46</v>
       </c>
       <c r="D144" s="5" t="n">
-        <v>221192.89</v>
+        <v>221606.81</v>
       </c>
       <c r="E144" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX, US_Dollar_Index_Futures</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="G144" t="inlineStr"/>
-      <c r="H144" t="inlineStr"/>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Silver_Futures_COMEX target_r (+5,776)</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="n">
         <v>46176</v>
       </c>
       <c r="B145" s="5" t="n">
-        <v>223812.83</v>
+        <v>221559.76</v>
       </c>
       <c r="C145" s="5" t="n">
-        <v>2661.19</v>
+        <v>-0</v>
       </c>
       <c r="D145" s="5" t="n">
-        <v>221151.64</v>
+        <v>221559.76</v>
       </c>
       <c r="E145" t="n">
-        <v>1</v>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>Silver_Futures_COMEX</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures stop (-2,671)</t>
+          <t>US_Dollar_Index_Futures stop (-3,047)</t>
         </is>
       </c>
     </row>
@@ -4491,22 +4507,18 @@
         <v>46177</v>
       </c>
       <c r="B146" s="5" t="n">
-        <v>223812.83</v>
+        <v>221559.76</v>
       </c>
       <c r="C146" s="5" t="n">
-        <v>2661.19</v>
+        <v>-0</v>
       </c>
       <c r="D146" s="5" t="n">
-        <v>221151.64</v>
+        <v>221559.76</v>
       </c>
       <c r="E146" t="n">
-        <v>1</v>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>Silver_Futures_COMEX</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr"/>
     </row>
@@ -4515,13 +4527,13 @@
         <v>46178</v>
       </c>
       <c r="B147" s="5" t="n">
-        <v>221145.87</v>
+        <v>221559.76</v>
       </c>
       <c r="C147" s="5" t="n">
-        <v>2598.53</v>
+        <v>3079.68</v>
       </c>
       <c r="D147" s="5" t="n">
-        <v>218547.34</v>
+        <v>218480.08</v>
       </c>
       <c r="E147" t="n">
         <v>1</v>
@@ -4533,27 +4545,23 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini short (risk 2,599)</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>Silver_Futures_COMEX stop (-2,667)</t>
-        </is>
-      </c>
+          <t>Dow_Futures_E_mini short (risk 3,080)</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="4" t="n">
         <v>46181</v>
       </c>
       <c r="B148" s="5" t="n">
-        <v>227593.17</v>
+        <v>227353.05</v>
       </c>
       <c r="C148" s="5" t="n">
-        <v>5105.69</v>
+        <v>6031.53</v>
       </c>
       <c r="D148" s="5" t="n">
-        <v>222487.48</v>
+        <v>221321.51</v>
       </c>
       <c r="E148" t="n">
         <v>2</v>
@@ -4565,12 +4573,12 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX long (risk 2,568); US_Dollar_Index_Futures short (risk 2,538)</t>
+          <t>Gold_Futures_COMEX long (risk 3,037); US_Dollar_Index_Futures short (risk 2,995)</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini target_r (+6,447)</t>
+          <t>Dow_Futures_E_mini target_r (+5,793)</t>
         </is>
       </c>
     </row>
@@ -4579,13 +4587,13 @@
         <v>46182</v>
       </c>
       <c r="B149" s="5" t="n">
-        <v>231313.05</v>
+        <v>229939.21</v>
       </c>
       <c r="C149" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D149" s="5" t="n">
-        <v>231313.05</v>
+        <v>229939.21</v>
       </c>
       <c r="E149" t="n">
         <v>0</v>
@@ -4594,7 +4602,7 @@
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX stop (-2,587); US_Dollar_Index_Futures target_r (+6,307)</t>
+          <t>Gold_Futures_COMEX stop (-3,059); US_Dollar_Index_Futures target_r (+5,645)</t>
         </is>
       </c>
     </row>
@@ -4603,13 +4611,13 @@
         <v>46183</v>
       </c>
       <c r="B150" s="5" t="n">
-        <v>231313.05</v>
+        <v>229939.21</v>
       </c>
       <c r="C150" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D150" s="5" t="n">
-        <v>231313.05</v>
+        <v>229939.21</v>
       </c>
       <c r="E150" t="n">
         <v>0</v>
@@ -4623,13 +4631,13 @@
         <v>46184</v>
       </c>
       <c r="B151" s="5" t="n">
-        <v>231313.05</v>
+        <v>229939.21</v>
       </c>
       <c r="C151" s="5" t="n">
-        <v>5403.92</v>
+        <v>6347.88</v>
       </c>
       <c r="D151" s="5" t="n">
-        <v>225909.13</v>
+        <v>223591.33</v>
       </c>
       <c r="E151" t="n">
         <v>2</v>
@@ -4641,7 +4649,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX long (risk 2,718); US_Dollar_Index_Futures short (risk 2,686)</t>
+          <t>Gold_Futures_COMEX long (risk 3,196); US_Dollar_Index_Futures short (risk 3,152)</t>
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
@@ -4651,13 +4659,13 @@
         <v>46185</v>
       </c>
       <c r="B152" s="5" t="n">
-        <v>244791.81</v>
+        <v>244951.56</v>
       </c>
       <c r="C152" s="5" t="n">
-        <v>2654.43</v>
+        <v>3107.92</v>
       </c>
       <c r="D152" s="5" t="n">
-        <v>242137.38</v>
+        <v>241843.64</v>
       </c>
       <c r="E152" t="n">
         <v>1</v>
@@ -4669,12 +4677,12 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures long (risk 2,654)</t>
+          <t>Corn_CBOT_Futures long (risk 3,108)</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX target_r (+6,785); US_Dollar_Index_Futures target_r (+6,693)</t>
+          <t>Gold_Futures_COMEX target_r (+7,398); US_Dollar_Index_Futures target_r (+7,615)</t>
         </is>
       </c>
     </row>
@@ -4683,13 +4691,13 @@
         <v>46188</v>
       </c>
       <c r="B153" s="5" t="n">
-        <v>241744.13</v>
+        <v>241383.21</v>
       </c>
       <c r="C153" s="5" t="n">
-        <v>2845.11</v>
+        <v>3361.63</v>
       </c>
       <c r="D153" s="5" t="n">
-        <v>238899.02</v>
+        <v>238021.58</v>
       </c>
       <c r="E153" t="n">
         <v>1</v>
@@ -4701,12 +4709,12 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT long (risk 2,845)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT long (risk 3,362)</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures stop (-3,048)</t>
+          <t>Corn_CBOT_Futures unknown_pl (-3,568)</t>
         </is>
       </c>
     </row>
@@ -4715,13 +4723,13 @@
         <v>46189</v>
       </c>
       <c r="B154" s="5" t="n">
-        <v>248770.7</v>
+        <v>247668.43</v>
       </c>
       <c r="C154" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D154" s="5" t="n">
-        <v>248770.7</v>
+        <v>247668.43</v>
       </c>
       <c r="E154" t="n">
         <v>0</v>
@@ -4730,7 +4738,7 @@
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT target_r (+7,027)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT target_r (+6,285)</t>
         </is>
       </c>
     </row>
@@ -4739,13 +4747,13 @@
         <v>46190</v>
       </c>
       <c r="B155" s="5" t="n">
-        <v>248770.7</v>
+        <v>247668.43</v>
       </c>
       <c r="C155" s="5" t="n">
-        <v>2923.06</v>
+        <v>3442.59</v>
       </c>
       <c r="D155" s="5" t="n">
-        <v>245847.65</v>
+        <v>244225.84</v>
       </c>
       <c r="E155" t="n">
         <v>1</v>
@@ -4757,7 +4765,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures short (risk 2,923)</t>
+          <t>US_Dollar_Index_Futures short (risk 3,443)</t>
         </is>
       </c>
       <c r="H155" t="inlineStr"/>
@@ -4767,13 +4775,13 @@
         <v>46191</v>
       </c>
       <c r="B156" s="5" t="n">
-        <v>245808.01</v>
+        <v>244179.16</v>
       </c>
       <c r="C156" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D156" s="5" t="n">
-        <v>245808.01</v>
+        <v>244179.16</v>
       </c>
       <c r="E156" t="n">
         <v>0</v>
@@ -4782,7 +4790,7 @@
       <c r="G156" t="inlineStr"/>
       <c r="H156" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures stop (-2,963)</t>
+          <t>US_Dollar_Index_Futures stop (-3,489)</t>
         </is>
       </c>
     </row>
@@ -4791,13 +4799,13 @@
         <v>46192</v>
       </c>
       <c r="B157" s="5" t="n">
-        <v>245808.01</v>
+        <v>244179.16</v>
       </c>
       <c r="C157" s="5" t="n">
-        <v>2888.24</v>
+        <v>3394.09</v>
       </c>
       <c r="D157" s="5" t="n">
-        <v>242919.77</v>
+        <v>240785.07</v>
       </c>
       <c r="E157" t="n">
         <v>1</v>
@@ -4809,7 +4817,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures short (risk 2,888)</t>
+          <t>US_Dollar_Index_Futures short (risk 3,394)</t>
         </is>
       </c>
       <c r="H157" t="inlineStr"/>
@@ -4819,13 +4827,13 @@
         <v>46195</v>
       </c>
       <c r="B158" s="5" t="n">
-        <v>245808.01</v>
+        <v>244179.16</v>
       </c>
       <c r="C158" s="5" t="n">
-        <v>2888.24</v>
+        <v>3394.09</v>
       </c>
       <c r="D158" s="5" t="n">
-        <v>242919.77</v>
+        <v>240785.07</v>
       </c>
       <c r="E158" t="n">
         <v>1</v>
@@ -4843,13 +4851,13 @@
         <v>46196</v>
       </c>
       <c r="B159" s="5" t="n">
-        <v>242879.93</v>
+        <v>240738.26</v>
       </c>
       <c r="C159" s="5" t="n">
-        <v>2854.31</v>
+        <v>3346.91</v>
       </c>
       <c r="D159" s="5" t="n">
-        <v>240025.62</v>
+        <v>237391.34</v>
       </c>
       <c r="E159" t="n">
         <v>1</v>
@@ -4861,12 +4869,12 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures long (risk 2,854)</t>
+          <t>NY_Platinum_Futures long (risk 3,347)</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures stop (-2,928)</t>
+          <t>US_Dollar_Index_Futures stop (-3,441)</t>
         </is>
       </c>
     </row>
@@ -4875,13 +4883,13 @@
         <v>46197</v>
       </c>
       <c r="B160" s="5" t="n">
-        <v>239969.93</v>
+        <v>237326.04</v>
       </c>
       <c r="C160" s="5" t="n">
-        <v>2820.3</v>
+        <v>3299.74</v>
       </c>
       <c r="D160" s="5" t="n">
-        <v>237149.63</v>
+        <v>234026.3</v>
       </c>
       <c r="E160" t="n">
         <v>1</v>
@@ -4893,12 +4901,12 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>EURO_Futures long (risk 2,820)</t>
+          <t>EURO_Futures long (risk 3,300)</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures stop (-2,910)</t>
+          <t>NY_Platinum_Futures stop (-3,412)</t>
         </is>
       </c>
     </row>
@@ -4907,13 +4915,13 @@
         <v>46198</v>
       </c>
       <c r="B161" s="5" t="n">
-        <v>239969.93</v>
+        <v>237326.04</v>
       </c>
       <c r="C161" s="5" t="n">
-        <v>13771.42</v>
+        <v>16042.81</v>
       </c>
       <c r="D161" s="5" t="n">
-        <v>226198.51</v>
+        <v>221283.23</v>
       </c>
       <c r="E161" t="n">
         <v>5</v>
@@ -4925,7 +4933,7 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures short (risk 2,787); NY_Palladium_Futures long (risk 2,754); NY_Platinum_Futures long (risk 2,721); US_Dollar_Index_Futures short (risk 2,689)</t>
+          <t>NY_Natural_Gas_Futures short (risk 3,253); NY_Palladium_Futures long (risk 3,208); NY_Platinum_Futures long (risk 3,163); US_Dollar_Index_Futures short (risk 3,119)</t>
         </is>
       </c>
       <c r="H161" t="inlineStr"/>
@@ -4935,26 +4943,22 @@
         <v>46199</v>
       </c>
       <c r="B162" s="5" t="n">
-        <v>257475.02</v>
+        <v>257926.99</v>
       </c>
       <c r="C162" s="5" t="n">
-        <v>2721.41</v>
+        <v>-0</v>
       </c>
       <c r="D162" s="5" t="n">
-        <v>254753.61</v>
+        <v>257926.99</v>
       </c>
       <c r="E162" t="n">
-        <v>1</v>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>NY_Platinum_Futures</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr">
         <is>
-          <t>EURO_Futures target_r (+7,030); NY_Natural_Gas_Futures stop (-3,014); NY_Palladium_Futures target_r (+6,812); US_Dollar_Index_Futures target_r (+6,677)</t>
+          <t>EURO_Futures target_r (+6,246); NY_Natural_Gas_Futures stop (-3,519); NY_Palladium_Futures target_r (+6,010); NY_Platinum_Futures target_r (+5,991); US_Dollar_Index_Futures target_r (+5,872)</t>
         </is>
       </c>
     </row>
@@ -4963,22 +4967,18 @@
         <v>46202</v>
       </c>
       <c r="B163" s="5" t="n">
-        <v>257475.02</v>
+        <v>257926.99</v>
       </c>
       <c r="C163" s="5" t="n">
-        <v>2721.41</v>
+        <v>-0</v>
       </c>
       <c r="D163" s="5" t="n">
-        <v>254753.61</v>
+        <v>257926.99</v>
       </c>
       <c r="E163" t="n">
-        <v>1</v>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>NY_Platinum_Futures</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr"/>
     </row>
@@ -4987,25 +4987,25 @@
         <v>46203</v>
       </c>
       <c r="B164" s="5" t="n">
-        <v>257475.02</v>
+        <v>257926.99</v>
       </c>
       <c r="C164" s="5" t="n">
-        <v>11596.37</v>
+        <v>10606.75</v>
       </c>
       <c r="D164" s="5" t="n">
-        <v>245878.65</v>
+        <v>247320.25</v>
       </c>
       <c r="E164" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT, German_Long_Bund, Gold_Futures_COMEX, NY_Platinum_Futures</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT, German_Long_Bund, Gold_Futures_COMEX</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT long (risk 2,993); German_Long_Bund short (risk 2,958); Gold_Futures_COMEX long (risk 2,923)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT long (risk 3,585); German_Long_Bund short (risk 3,535); Gold_Futures_COMEX long (risk 3,486)</t>
         </is>
       </c>
       <c r="H164" t="inlineStr"/>
@@ -5015,30 +5015,30 @@
         <v>46204</v>
       </c>
       <c r="B165" s="5" t="n">
-        <v>276485.29</v>
+        <v>277573.21</v>
       </c>
       <c r="C165" s="5" t="n">
-        <v>5744.2</v>
+        <v>10170.56</v>
       </c>
       <c r="D165" s="5" t="n">
-        <v>270741.09</v>
+        <v>267402.64</v>
       </c>
       <c r="E165" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini, Sugar_World_CSCE_Futures</t>
+          <t>Dow_Futures_E_mini, NY_Platinum_Futures, Sugar_World_CSCE_Futures</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini short (risk 2,889); Sugar_World_CSCE_Futures short (risk 2,855)</t>
+          <t>Dow_Futures_E_mini short (risk 3,438); NY_Platinum_Futures long (risk 3,390); Sugar_World_CSCE_Futures short (risk 3,343)</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT target_r (+7,337); German_Long_Bund target_r (+7,138); Gold_Futures_COMEX target_r (+7,288); NY_Platinum_Futures stop (-2,754)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT target_r (+6,637); German_Long_Bund target_r (+6,410); Gold_Futures_COMEX target_r (+6,600)</t>
         </is>
       </c>
     </row>
@@ -5047,13 +5047,13 @@
         <v>46205</v>
       </c>
       <c r="B166" s="5" t="n">
-        <v>273565.15</v>
+        <v>280504.66</v>
       </c>
       <c r="C166" s="5" t="n">
-        <v>2855.13</v>
+        <v>3342.85</v>
       </c>
       <c r="D166" s="5" t="n">
-        <v>270710.02</v>
+        <v>277161.81</v>
       </c>
       <c r="E166" t="n">
         <v>1</v>
@@ -5066,7 +5066,7 @@
       <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini stop (-2,920)</t>
+          <t>Dow_Futures_E_mini stop (-3,475); NY_Platinum_Futures target_r (+6,406)</t>
         </is>
       </c>
     </row>
@@ -5075,13 +5075,13 @@
         <v>46206</v>
       </c>
       <c r="B167" s="5" t="n">
-        <v>273565.15</v>
+        <v>280504.66</v>
       </c>
       <c r="C167" s="5" t="n">
-        <v>2855.13</v>
+        <v>3342.85</v>
       </c>
       <c r="D167" s="5" t="n">
-        <v>270710.02</v>
+        <v>277161.81</v>
       </c>
       <c r="E167" t="n">
         <v>1</v>
@@ -5099,13 +5099,13 @@
         <v>46210</v>
       </c>
       <c r="B168" s="5" t="n">
-        <v>270270.77</v>
+        <v>276647.53</v>
       </c>
       <c r="C168" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D168" s="5" t="n">
-        <v>270270.77</v>
+        <v>276647.53</v>
       </c>
       <c r="E168" t="n">
         <v>0</v>
@@ -5114,7 +5114,7 @@
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Sugar_World_CSCE_Futures stop (-3,294)</t>
+          <t>Sugar_World_CSCE_Futures stop (-3,857)</t>
         </is>
       </c>
     </row>
@@ -5123,13 +5123,13 @@
         <v>46211</v>
       </c>
       <c r="B169" s="5" t="n">
-        <v>270270.77</v>
+        <v>276647.53</v>
       </c>
       <c r="C169" s="5" t="n">
-        <v>6314.05</v>
+        <v>7637.35</v>
       </c>
       <c r="D169" s="5" t="n">
-        <v>263956.72</v>
+        <v>269010.18</v>
       </c>
       <c r="E169" t="n">
         <v>2</v>
@@ -5141,7 +5141,7 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME long (risk 3,176); NY_Natural_Gas_Futures short (risk 3,138)</t>
+          <t>Live_Cattle_Futures_CME long (risk 3,845); NY_Natural_Gas_Futures short (risk 3,792)</t>
         </is>
       </c>
       <c r="H169" t="inlineStr"/>
@@ -5151,13 +5151,13 @@
         <v>46212</v>
       </c>
       <c r="B170" s="5" t="n">
-        <v>285857.21</v>
+        <v>290918.23</v>
       </c>
       <c r="C170" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D170" s="5" t="n">
-        <v>285857.21</v>
+        <v>290918.23</v>
       </c>
       <c r="E170" t="n">
         <v>0</v>
@@ -5166,7 +5166,7 @@
       <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME target_r (+7,864); NY_Natural_Gas_Futures target_r (+7,723)</t>
+          <t>Live_Cattle_Futures_CME target_r (+7,215); NY_Natural_Gas_Futures target_r (+7,056)</t>
         </is>
       </c>
     </row>
@@ -5175,13 +5175,13 @@
         <v>46213</v>
       </c>
       <c r="B171" s="5" t="n">
-        <v>285857.21</v>
+        <v>290918.23</v>
       </c>
       <c r="C171" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D171" s="5" t="n">
-        <v>285857.21</v>
+        <v>290918.23</v>
       </c>
       <c r="E171" t="n">
         <v>0</v>
@@ -5195,13 +5195,13 @@
         <v>46216</v>
       </c>
       <c r="B172" s="5" t="n">
-        <v>285857.21</v>
+        <v>290918.23</v>
       </c>
       <c r="C172" s="5" t="n">
-        <v>3358.82</v>
+        <v>4043.76</v>
       </c>
       <c r="D172" s="5" t="n">
-        <v>282498.38</v>
+        <v>286874.47</v>
       </c>
       <c r="E172" t="n">
         <v>1</v>
@@ -5213,7 +5213,7 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 3,359)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 4,044)</t>
         </is>
       </c>
       <c r="H172" t="inlineStr"/>
@@ -5223,61 +5223,57 @@
         <v>46217</v>
       </c>
       <c r="B173" s="5" t="n">
-        <v>285857.21</v>
+        <v>298501.54</v>
       </c>
       <c r="C173" s="5" t="n">
-        <v>3358.82</v>
+        <v>-0</v>
       </c>
       <c r="D173" s="5" t="n">
-        <v>282498.38</v>
+        <v>298501.54</v>
       </c>
       <c r="E173" t="n">
-        <v>1</v>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F173" t="inlineStr"/>
       <c r="G173" t="inlineStr"/>
-      <c r="H173" t="inlineStr"/>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT target_r (+7,583)</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="4" t="n">
         <v>46218</v>
       </c>
       <c r="B174" s="5" t="n">
-        <v>282332.52</v>
+        <v>298501.54</v>
       </c>
       <c r="C174" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D174" s="5" t="n">
-        <v>282332.52</v>
+        <v>298501.54</v>
       </c>
       <c r="E174" t="n">
         <v>0</v>
       </c>
       <c r="F174" t="inlineStr"/>
       <c r="G174" t="inlineStr"/>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT stop (-3,525)</t>
-        </is>
-      </c>
+      <c r="H174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" s="4" t="n">
         <v>46219</v>
       </c>
       <c r="B175" s="5" t="n">
-        <v>282332.52</v>
+        <v>298501.54</v>
       </c>
       <c r="C175" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D175" s="5" t="n">
-        <v>282332.52</v>
+        <v>298501.54</v>
       </c>
       <c r="E175" t="n">
         <v>0</v>
@@ -5291,13 +5287,13 @@
         <v>46220</v>
       </c>
       <c r="B176" s="5" t="n">
-        <v>282332.52</v>
+        <v>298501.54</v>
       </c>
       <c r="C176" s="5" t="n">
-        <v>3317.41</v>
+        <v>4149.17</v>
       </c>
       <c r="D176" s="5" t="n">
-        <v>279015.11</v>
+        <v>294352.37</v>
       </c>
       <c r="E176" t="n">
         <v>1</v>
@@ -5309,7 +5305,7 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX long (risk 3,317)</t>
+          <t>Gold_Futures_COMEX long (risk 4,149)</t>
         </is>
       </c>
       <c r="H176" t="inlineStr"/>
@@ -5319,13 +5315,13 @@
         <v>46223</v>
       </c>
       <c r="B177" s="5" t="n">
-        <v>290594.59</v>
+        <v>306345.63</v>
       </c>
       <c r="C177" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D177" s="5" t="n">
-        <v>290594.59</v>
+        <v>306345.63</v>
       </c>
       <c r="E177" t="n">
         <v>0</v>
@@ -5334,7 +5330,7 @@
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX target_r (+8,262)</t>
+          <t>Gold_Futures_COMEX target_r (+7,844)</t>
         </is>
       </c>
     </row>
@@ -5343,13 +5339,13 @@
         <v>46224</v>
       </c>
       <c r="B178" s="5" t="n">
-        <v>290594.59</v>
+        <v>306345.63</v>
       </c>
       <c r="C178" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D178" s="5" t="n">
-        <v>290594.59</v>
+        <v>306345.63</v>
       </c>
       <c r="E178" t="n">
         <v>0</v>
@@ -5363,13 +5359,13 @@
         <v>46225</v>
       </c>
       <c r="B179" s="5" t="n">
-        <v>290594.59</v>
+        <v>306345.63</v>
       </c>
       <c r="C179" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D179" s="5" t="n">
-        <v>290594.59</v>
+        <v>306345.63</v>
       </c>
       <c r="E179" t="n">
         <v>0</v>
@@ -5383,13 +5379,13 @@
         <v>46226</v>
       </c>
       <c r="B180" s="5" t="n">
-        <v>290594.59</v>
+        <v>306345.63</v>
       </c>
       <c r="C180" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D180" s="5" t="n">
-        <v>290594.59</v>
+        <v>306345.63</v>
       </c>
       <c r="E180" t="n">
         <v>0</v>
@@ -5403,13 +5399,13 @@
         <v>46227</v>
       </c>
       <c r="B181" s="5" t="n">
-        <v>290445.81</v>
+        <v>306160.32</v>
       </c>
       <c r="C181" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="D181" s="5" t="n">
-        <v>290445.81</v>
+        <v>306160.32</v>
       </c>
       <c r="E181" t="n">
         <v>0</v>
@@ -5417,7 +5413,7 @@
       <c r="F181" t="inlineStr"/>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 3,414); Corn_CBOT_Futures short (risk 3,374)</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 4,258); Corn_CBOT_Futures short (risk 4,199)</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -5438,7 +5434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M87"/>
+  <dimension ref="A1:M91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -5560,13 +5556,13 @@
         <v>100000</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>1175</v>
+        <v>1390</v>
       </c>
       <c r="K2" s="6" t="n">
-        <v>9506.16</v>
+        <v>11245.59</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>109506.16</v>
+        <v>111245.59</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -5599,25 +5595,25 @@
         <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5</v>
+        <v>1.92</v>
       </c>
       <c r="G3" t="n">
         <v>0.007</v>
       </c>
       <c r="H3" t="n">
-        <v>2.493</v>
+        <v>1.913</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>109506.16</v>
+        <v>111245.59</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>1286.7</v>
+        <v>1546.31</v>
       </c>
       <c r="K3" s="6" t="n">
-        <v>3207.42</v>
+        <v>2958.18</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>112713.58</v>
+        <v>114203.77</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -5659,16 +5655,16 @@
         <v>-1.008</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>112713.58</v>
+        <v>114203.77</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>1324.38</v>
+        <v>1587.43</v>
       </c>
       <c r="K4" s="7" t="n">
-        <v>-1334.85</v>
+        <v>-1599.98</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>111378.73</v>
+        <v>112603.79</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -5701,25 +5697,25 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="G5" t="n">
         <v>0.002</v>
       </c>
       <c r="H5" t="n">
-        <v>2.498</v>
+        <v>1.898</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>111389.2</v>
+        <v>112616.34</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>1308.82</v>
+        <v>1565.37</v>
       </c>
       <c r="K5" s="6" t="n">
-        <v>3268.89</v>
+        <v>2970.41</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>114647.62</v>
+        <v>115574.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -5761,16 +5757,16 @@
         <v>-1.085</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>114647.62</v>
+        <v>115574.2</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>1347.11</v>
+        <v>1606.48</v>
       </c>
       <c r="K6" s="7" t="n">
-        <v>-1461.76</v>
+        <v>-1743.2</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>113185.86</v>
+        <v>113831</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -5803,25 +5799,25 @@
         <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="G7" t="n">
         <v>0.006</v>
       </c>
       <c r="H7" t="n">
-        <v>2.494</v>
+        <v>1.894</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>113185.86</v>
+        <v>113831</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>1329.93</v>
+        <v>1582.25</v>
       </c>
       <c r="K7" s="6" t="n">
-        <v>3316.8</v>
+        <v>2996.72</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>116502.66</v>
+        <v>116827.71</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -5863,16 +5859,16 @@
         <v>-3.054</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>116502.66</v>
+        <v>116827.71</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>1368.91</v>
+        <v>1623.91</v>
       </c>
       <c r="K8" s="7" t="n">
-        <v>-4181.22</v>
+        <v>-4960.09</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>112321.45</v>
+        <v>111867.62</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -5914,16 +5910,16 @@
         <v>-1.278</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>115133.76</v>
+        <v>115203.81</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>1352.82</v>
+        <v>1601.33</v>
       </c>
       <c r="K9" s="7" t="n">
-        <v>-1728.67</v>
+        <v>-2046.22</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>110592.78</v>
+        <v>109821.4</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -5965,16 +5961,16 @@
         <v>-1.069</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>110968.63</v>
+        <v>110266.29</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>1303.88</v>
+        <v>1532.7</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>-1393.8</v>
+        <v>-1638.4</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>109198.98</v>
+        <v>108183</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -6016,16 +6012,16 @@
         <v>-1.06</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>109664.74</v>
+        <v>108733.59</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>1288.56</v>
+        <v>1511.4</v>
       </c>
       <c r="K11" s="7" t="n">
-        <v>-1365.49</v>
+        <v>-1601.63</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>107833.49</v>
+        <v>106581.37</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -6067,16 +6063,16 @@
         <v>3.36</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>108376.18</v>
+        <v>107222.19</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>1273.42</v>
+        <v>1490.39</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>4278.42</v>
+        <v>5007.39</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>112111.91</v>
+        <v>111588.76</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -6102,36 +6098,36 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F13" t="n">
-        <v>-1</v>
+        <v>1.9</v>
       </c>
       <c r="G13" t="n">
-        <v>0.026</v>
+        <v>0.013</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.026</v>
+        <v>1.887</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>106726.92</v>
+        <v>105286.92</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>1254.04</v>
-      </c>
-      <c r="K13" s="7" t="n">
-        <v>-1287.04</v>
+        <v>1463.49</v>
+      </c>
+      <c r="K13" s="6" t="n">
+        <v>2761.37</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>113379.05</v>
+        <v>112816.15</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
@@ -6169,16 +6165,16 @@
         <v>-1.002</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>110857.87</v>
+        <v>110125.27</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>1302.58</v>
+        <v>1530.74</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>-1305.34</v>
+        <v>-1533.98</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>110806.57</v>
+        <v>110054.78</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -6220,16 +6216,16 @@
         <v>-1.004</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>109555.29</v>
+        <v>108594.53</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>1287.27</v>
+        <v>1509.46</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>-1292.68</v>
+        <v>-1515.8</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>109513.89</v>
+        <v>111300.35</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -6255,32 +6251,32 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="G16" t="n">
         <v>0.001</v>
       </c>
       <c r="H16" t="n">
-        <v>2.499</v>
+        <v>1.899</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>108268.01</v>
+        <v>107085.06</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>1272.15</v>
+        <v>1488.48</v>
       </c>
       <c r="K16" s="6" t="n">
-        <v>3179.52</v>
+        <v>2827.12</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>112693.42</v>
+        <v>114127.47</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -6291,7 +6287,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures</t>
+          <t>Cocoa_NYCSCE_Futures</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -6301,48 +6297,48 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
+          <t>2026-02-04</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
           <t>2026-02-05</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>2026-02-06</t>
-        </is>
-      </c>
       <c r="E17" t="n">
         <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>-1</v>
+        <v>1.9</v>
       </c>
       <c r="G17" t="n">
-        <v>0.005</v>
+        <v>0.03</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.005</v>
+        <v>1.87</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>106987.7</v>
+        <v>109811.87</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>1257.11</v>
-      </c>
-      <c r="K17" s="7" t="n">
-        <v>-1262.92</v>
+        <v>1526.38</v>
+      </c>
+      <c r="K17" s="6" t="n">
+        <v>2853.88</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>111430.5</v>
+        <v>116981.35</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance</t>
+          <t>NY_Copper_Futures</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -6352,88 +6348,88 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>2026-02-05</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
           <t>2026-02-06</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2026-02-07</t>
-        </is>
-      </c>
       <c r="E18" t="n">
         <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>2.5</v>
+        <v>-1</v>
       </c>
       <c r="G18" t="n">
-        <v>0.001</v>
+        <v>0.005</v>
       </c>
       <c r="H18" t="n">
-        <v>2.499</v>
+        <v>-1.005</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>110182.27</v>
+        <v>112601.09</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>1294.64</v>
-      </c>
-      <c r="K18" s="6" t="n">
-        <v>3235.59</v>
+        <v>1565.16</v>
+      </c>
+      <c r="K18" s="7" t="n">
+        <v>-1572.39</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>114666.09</v>
+        <v>115408.95</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EURO_STOXX_50_Index</t>
+          <t>Bitcoin_Per_USD_Binance</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-07</t>
         </is>
       </c>
       <c r="E19" t="n">
         <v>1</v>
       </c>
       <c r="F19" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="G19" t="n">
         <v>0.001</v>
       </c>
       <c r="H19" t="n">
-        <v>2.499</v>
+        <v>1.899</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>113412.05</v>
+        <v>115416.19</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>1332.59</v>
+        <v>1604.29</v>
       </c>
       <c r="K19" s="6" t="n">
-        <v>3330</v>
+        <v>3046.89</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>116709.05</v>
+        <v>118455.84</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -6444,22 +6440,22 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>Cocoa_NYCSCE_Futures</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t>2026-02-10</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -6469,22 +6465,22 @@
         <v>-1</v>
       </c>
       <c r="G20" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.121</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.009</v>
+        <v>-1.121</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>112079.46</v>
+        <v>118455.84</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>1316.93</v>
+        <v>1646.54</v>
       </c>
       <c r="K20" s="7" t="n">
-        <v>-1328.8</v>
+        <v>-1846.12</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>115380.25</v>
+        <v>116609.72</v>
       </c>
       <c r="M20" t="inlineStr">
         <is>
@@ -6495,7 +6491,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>EURO_STOXX_50_Index</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -6505,48 +6501,48 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>2026-02-12</t>
-        </is>
-      </c>
       <c r="E21" t="n">
         <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>-1</v>
+        <v>1.9</v>
       </c>
       <c r="G21" t="n">
-        <v>0.138</v>
+        <v>0.001</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.138</v>
+        <v>1.899</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>110729.52</v>
+        <v>116809.3</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>1301.07</v>
-      </c>
-      <c r="K21" s="7" t="n">
-        <v>-1480.53</v>
+        <v>1623.65</v>
+      </c>
+      <c r="K21" s="6" t="n">
+        <v>3083.14</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>113899.72</v>
+        <v>119692.86</v>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>EURO_STOXX_50_Index</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -6556,63 +6552,63 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E22" t="n">
         <v>1</v>
       </c>
       <c r="F22" t="n">
-        <v>2.5</v>
+        <v>-1</v>
       </c>
       <c r="G22" t="n">
-        <v>0.001</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>2.499</v>
+        <v>-1.009</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>114079.18</v>
+        <v>115185.66</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>1340.43</v>
-      </c>
-      <c r="K22" s="6" t="n">
-        <v>3350.39</v>
+        <v>1601.08</v>
+      </c>
+      <c r="K22" s="7" t="n">
+        <v>-1615.5</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>117250.11</v>
+        <v>118077.36</v>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>unknown_pl</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -6622,22 +6618,22 @@
         <v>-1</v>
       </c>
       <c r="G23" t="n">
-        <v>0.004</v>
+        <v>0.138</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.004</v>
+        <v>-1.138</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>112559.29</v>
+        <v>113384.99</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>1322.57</v>
+        <v>1576.05</v>
       </c>
       <c r="K23" s="7" t="n">
-        <v>-1328.2</v>
+        <v>-1793.44</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>115921.91</v>
+        <v>116283.92</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -6648,7 +6644,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>EURO_STOXX_50_Index</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -6658,37 +6654,37 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="G24" t="n">
-        <v>0.143</v>
+        <v>0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>2.357</v>
+        <v>1.899</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>115921.91</v>
+        <v>116501.3</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>1362.08</v>
+        <v>1619.37</v>
       </c>
       <c r="K24" s="6" t="n">
-        <v>3210.62</v>
+        <v>3075.97</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>125666.15</v>
+        <v>119359.88</v>
       </c>
       <c r="M24" t="inlineStr">
         <is>
@@ -6699,7 +6695,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cocoa_NYCSCE_Futures</t>
+          <t>NY_Copper_Futures</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -6709,88 +6705,88 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="E25" t="n">
         <v>1</v>
       </c>
       <c r="F25" t="n">
-        <v>2.538</v>
+        <v>-1</v>
       </c>
       <c r="G25" t="n">
-        <v>0.051</v>
+        <v>0.004</v>
       </c>
       <c r="H25" t="n">
-        <v>2.487</v>
+        <v>-1.004</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>114559.83</v>
+        <v>114664.55</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>1346.08</v>
-      </c>
-      <c r="K25" s="6" t="n">
-        <v>3347.99</v>
+        <v>1593.84</v>
+      </c>
+      <c r="K25" s="7" t="n">
+        <v>-1600.62</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>119269.9</v>
+        <v>117759.26</v>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ethereum_Per_USD_Binance</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
+          <t>2026-02-23</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
           <t>2026-02-24</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>2026-02-25</t>
-        </is>
-      </c>
       <c r="E26" t="n">
         <v>1</v>
       </c>
       <c r="F26" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="G26" t="n">
-        <v>0.105</v>
+        <v>0.143</v>
       </c>
       <c r="H26" t="n">
-        <v>2.395</v>
+        <v>1.757</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>113213.75</v>
+        <v>117759.26</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>1330.26</v>
+        <v>1636.85</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>3185.63</v>
+        <v>2876.19</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>122455.52</v>
+        <v>120635.45</v>
       </c>
       <c r="M26" t="inlineStr">
         <is>
@@ -6801,47 +6797,47 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX</t>
+          <t>Cocoa_NYCSCE_Futures</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E27" t="n">
         <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="G27" t="n">
-        <v>0.003</v>
+        <v>0.051</v>
       </c>
       <c r="H27" t="n">
-        <v>2.497</v>
+        <v>1.849</v>
       </c>
       <c r="I27" s="5" t="n">
-        <v>125666.15</v>
+        <v>116122.41</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>1476.58</v>
+        <v>1614.1</v>
       </c>
       <c r="K27" s="6" t="n">
-        <v>3687.56</v>
+        <v>2984.02</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>129353.71</v>
+        <v>123619.47</v>
       </c>
       <c r="M27" t="inlineStr">
         <is>
@@ -6852,109 +6848,109 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Ethereum_Per_USD_Binance</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E28" t="n">
         <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>-1</v>
+        <v>1.9</v>
       </c>
       <c r="G28" t="n">
-        <v>0.174</v>
+        <v>0.105</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.174</v>
+        <v>1.795</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>129353.71</v>
+        <v>114508.31</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>1519.91</v>
-      </c>
-      <c r="K28" s="7" t="n">
-        <v>-1784.24</v>
+        <v>1591.67</v>
+      </c>
+      <c r="K28" s="6" t="n">
+        <v>2856.62</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>127569.47</v>
+        <v>126476.09</v>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E29" t="n">
         <v>1</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.074</v>
+        <v>-1</v>
       </c>
       <c r="G29" t="n">
-        <v>0.002</v>
+        <v>0.5</v>
       </c>
       <c r="H29" t="n">
-        <v>-1.075</v>
+        <v>-1.5</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>127833.8</v>
+        <v>117429.68</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>1502.05</v>
+        <v>1632.27</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>-1615.14</v>
+        <v>-2448.41</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>125954.33</v>
+        <v>124027.68</v>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>unknown_pl</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Gold_Futures_COMEX</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -6964,48 +6960,48 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E30" t="n">
         <v>1</v>
       </c>
       <c r="F30" t="n">
-        <v>-1</v>
+        <v>1.9</v>
       </c>
       <c r="G30" t="n">
-        <v>0.091</v>
+        <v>0.003</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.091</v>
+        <v>1.897</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>126067.42</v>
+        <v>124027.68</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>1481.29</v>
-      </c>
-      <c r="K30" s="7" t="n">
-        <v>-1615.96</v>
+        <v>1723.98</v>
+      </c>
+      <c r="K30" s="6" t="n">
+        <v>3271.04</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>124338.38</v>
+        <v>127298.72</v>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -7015,190 +7011,190 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-03-18</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E31" t="n">
         <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>2.5</v>
+        <v>-1</v>
       </c>
       <c r="G31" t="n">
-        <v>0.003</v>
+        <v>0.174</v>
       </c>
       <c r="H31" t="n">
-        <v>2.497</v>
+        <v>-1.174</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>124338.38</v>
+        <v>127298.72</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>1460.98</v>
-      </c>
-      <c r="K31" s="6" t="n">
-        <v>3648.03</v>
+        <v>1769.45</v>
+      </c>
+      <c r="K31" s="7" t="n">
+        <v>-2077.18</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>127986.41</v>
+        <v>125221.54</v>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E32" t="n">
         <v>1</v>
       </c>
       <c r="F32" t="n">
-        <v>6.435</v>
+        <v>-1.074</v>
       </c>
       <c r="G32" t="n">
-        <v>0.015</v>
+        <v>0.002</v>
       </c>
       <c r="H32" t="n">
-        <v>6.42</v>
+        <v>-1.075</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>127986.41</v>
+        <v>125529.27</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>1503.84</v>
-      </c>
-      <c r="K32" s="6" t="n">
-        <v>9654.4</v>
+        <v>1744.86</v>
+      </c>
+      <c r="K32" s="7" t="n">
+        <v>-1876.23</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>137640.81</v>
+        <v>123345.31</v>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E33" t="n">
         <v>1</v>
       </c>
       <c r="F33" t="n">
-        <v>2.547</v>
+        <v>-1</v>
       </c>
       <c r="G33" t="n">
-        <v>0.003</v>
+        <v>0.091</v>
       </c>
       <c r="H33" t="n">
-        <v>2.545</v>
+        <v>-1.091</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>126482.57</v>
+        <v>123476.68</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>1486.17</v>
-      </c>
-      <c r="K33" s="6" t="n">
-        <v>3781.61</v>
+        <v>1716.33</v>
+      </c>
+      <c r="K33" s="7" t="n">
+        <v>-1872.36</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>141422.42</v>
+        <v>121472.95</v>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX</t>
+          <t>Bitcoin_Per_USD_Binance</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="E34" t="n">
         <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>4.809</v>
+        <v>1.9</v>
       </c>
       <c r="G34" t="n">
-        <v>0.007</v>
+        <v>0.003</v>
       </c>
       <c r="H34" t="n">
-        <v>4.802</v>
+        <v>1.897</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>136154.64</v>
+        <v>121472.95</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>1599.82</v>
+        <v>1688.47</v>
       </c>
       <c r="K34" s="6" t="n">
-        <v>7682.41</v>
+        <v>3203.01</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>149104.83</v>
+        <v>124675.96</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -7219,37 +7215,37 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E35" t="n">
         <v>1</v>
       </c>
       <c r="F35" t="n">
-        <v>2.5</v>
+        <v>6.435</v>
       </c>
       <c r="G35" t="n">
-        <v>0.026</v>
+        <v>0.015</v>
       </c>
       <c r="H35" t="n">
-        <v>2.474</v>
+        <v>6.42</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>149104.83</v>
+        <v>124675.96</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>1751.98</v>
+        <v>1733</v>
       </c>
       <c r="K35" s="6" t="n">
-        <v>4335.03</v>
+        <v>11125.54</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>153439.86</v>
+        <v>135801.5</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -7260,98 +7256,98 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_Binance</t>
+          <t>NY_Copper_Futures</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F36" t="n">
-        <v>-1</v>
+        <v>1.9</v>
       </c>
       <c r="G36" t="n">
-        <v>0.004</v>
+        <v>0.003</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.004</v>
+        <v>1.897</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>153439.86</v>
+        <v>122942.96</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>1802.92</v>
-      </c>
-      <c r="K36" s="7" t="n">
-        <v>-1809.24</v>
+        <v>1708.91</v>
+      </c>
+      <c r="K36" s="6" t="n">
+        <v>3241.85</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>160157.52</v>
+        <v>139043.35</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ethereum_Per_USD_Binance</t>
+          <t>Gold_Futures_COMEX</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="E37" t="n">
         <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="G37" t="n">
-        <v>0.125</v>
+        <v>0.007</v>
       </c>
       <c r="H37" t="n">
-        <v>2.375</v>
+        <v>1.893</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>151636.94</v>
+        <v>134092.59</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>1781.73</v>
+        <v>1863.89</v>
       </c>
       <c r="K37" s="6" t="n">
-        <v>4231.62</v>
+        <v>3528.44</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>157671.48</v>
+        <v>142571.79</v>
       </c>
       <c r="M37" t="inlineStr">
         <is>
@@ -7362,7 +7358,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME</t>
+          <t>United_States_Oil_Fund_LP</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -7372,37 +7368,37 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="E38" t="n">
         <v>1</v>
       </c>
       <c r="F38" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="G38" t="n">
-        <v>0.061</v>
+        <v>0.026</v>
       </c>
       <c r="H38" t="n">
-        <v>2.439</v>
+        <v>1.874</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>149855.21</v>
+        <v>142571.79</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>1760.8</v>
+        <v>1981.75</v>
       </c>
       <c r="K38" s="6" t="n">
-        <v>4295.28</v>
+        <v>3714.51</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>161966.76</v>
+        <v>146286.3</v>
       </c>
       <c r="M38" t="inlineStr">
         <is>
@@ -7413,7 +7409,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures</t>
+          <t>Bitcoin_Per_USD_Binance</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -7423,12 +7419,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -7438,22 +7434,22 @@
         <v>-1</v>
       </c>
       <c r="G39" t="n">
-        <v>0.008</v>
+        <v>0.004</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.008</v>
+        <v>-1.004</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>148094.41</v>
+        <v>146286.3</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>1740.11</v>
+        <v>2033.38</v>
       </c>
       <c r="K39" s="7" t="n">
-        <v>-1753.37</v>
+        <v>-2040.51</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>160145.53</v>
+        <v>151441.8</v>
       </c>
       <c r="M39" t="inlineStr">
         <is>
@@ -7464,58 +7460,58 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Ethereum_Per_USD_Binance</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="G40" t="n">
-        <v>0.065</v>
+        <v>0.125</v>
       </c>
       <c r="H40" t="n">
-        <v>0.9350000000000001</v>
+        <v>1.775</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>158423.73</v>
+        <v>144252.92</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>1861.48</v>
+        <v>2005.12</v>
       </c>
       <c r="K40" s="6" t="n">
-        <v>1741.38</v>
+        <v>3559.08</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>161898.9</v>
+        <v>149845.38</v>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>data_end</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini</t>
+          <t>Live_Cattle_Futures_CME</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -7525,37 +7521,37 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="E41" t="n">
         <v>1</v>
       </c>
       <c r="F41" t="n">
-        <v>4.18</v>
+        <v>1.9</v>
       </c>
       <c r="G41" t="n">
-        <v>0.033</v>
+        <v>0.061</v>
       </c>
       <c r="H41" t="n">
-        <v>4.148</v>
+        <v>1.839</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>160158.79</v>
+        <v>142247.81</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>1881.87</v>
+        <v>1977.24</v>
       </c>
       <c r="K41" s="6" t="n">
-        <v>7805.06</v>
+        <v>3636.93</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>167950.6</v>
+        <v>153482.31</v>
       </c>
       <c r="M41" t="inlineStr">
         <is>
@@ -7566,7 +7562,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME</t>
+          <t>NY_Copper_Futures</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -7576,99 +7572,99 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F42" t="n">
-        <v>2.5</v>
+        <v>-1</v>
       </c>
       <c r="G42" t="n">
-        <v>0.004</v>
+        <v>0.008</v>
       </c>
       <c r="H42" t="n">
-        <v>2.496</v>
+        <v>-1.008</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>167950.6</v>
+        <v>140270.56</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>1973.42</v>
-      </c>
-      <c r="K42" s="6" t="n">
-        <v>4925.43</v>
+        <v>1949.76</v>
+      </c>
+      <c r="K42" s="7" t="n">
+        <v>-1964.62</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>172876.02</v>
+        <v>151421.15</v>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="G43" t="n">
-        <v>0.001</v>
+        <v>0.065</v>
       </c>
       <c r="H43" t="n">
-        <v>2.499</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="I43" s="5" t="n">
-        <v>165977.18</v>
+        <v>149499.17</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>1950.23</v>
+        <v>2078.04</v>
       </c>
       <c r="K43" s="6" t="n">
-        <v>4873.25</v>
+        <v>1943.97</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>177749.27</v>
+        <v>153385.77</v>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>data_end</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT</t>
+          <t>Dow_Futures_E_mini</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -7678,37 +7674,37 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E44" t="n">
         <v>1</v>
       </c>
       <c r="F44" t="n">
-        <v>2.5</v>
+        <v>4.18</v>
       </c>
       <c r="G44" t="n">
-        <v>0.022</v>
+        <v>0.033</v>
       </c>
       <c r="H44" t="n">
-        <v>2.478</v>
+        <v>4.148</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>170925.79</v>
+        <v>151436.01</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>2008.38</v>
+        <v>2104.96</v>
       </c>
       <c r="K44" s="6" t="n">
-        <v>4975.81</v>
+        <v>8730.35</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>182725.08</v>
+        <v>160151.51</v>
       </c>
       <c r="M44" t="inlineStr">
         <is>
@@ -7719,7 +7715,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures</t>
+          <t>Bitcoin_Per_USD_CME</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -7729,48 +7725,48 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E45" t="n">
         <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>-1</v>
+        <v>1.9</v>
       </c>
       <c r="G45" t="n">
-        <v>0.211</v>
+        <v>0.004</v>
       </c>
       <c r="H45" t="n">
-        <v>-1.211</v>
+        <v>1.896</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>175740.89</v>
+        <v>160151.51</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>2064.96</v>
-      </c>
-      <c r="K45" s="7" t="n">
-        <v>-2499.68</v>
+        <v>2226.11</v>
+      </c>
+      <c r="K45" s="6" t="n">
+        <v>4220.44</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>180225.4</v>
+        <v>164371.95</v>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>unknown_pl</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Japanese_Yen_Futures</t>
+          <t>S_P_500_E_mini</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -7780,48 +7776,48 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F46" t="n">
-        <v>-1</v>
+        <v>1.9</v>
       </c>
       <c r="G46" t="n">
-        <v>0.108</v>
+        <v>0.001</v>
       </c>
       <c r="H46" t="n">
-        <v>-1.108</v>
+        <v>1.899</v>
       </c>
       <c r="I46" s="5" t="n">
-        <v>180660.13</v>
+        <v>157925.4</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>2122.76</v>
-      </c>
-      <c r="K46" s="7" t="n">
-        <v>-2352.24</v>
+        <v>2195.16</v>
+      </c>
+      <c r="K46" s="6" t="n">
+        <v>4168.18</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>198243.21</v>
+        <v>168540.13</v>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -7831,37 +7827,37 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="E47" t="n">
         <v>1</v>
       </c>
       <c r="F47" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="G47" t="n">
-        <v>0.016</v>
+        <v>0.022</v>
       </c>
       <c r="H47" t="n">
-        <v>2.484</v>
+        <v>1.878</v>
       </c>
       <c r="I47" s="5" t="n">
-        <v>178537.37</v>
+        <v>162176.78</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>2097.81</v>
+        <v>2254.26</v>
       </c>
       <c r="K47" s="6" t="n">
-        <v>5210.97</v>
+        <v>4232.43</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>185436.37</v>
+        <v>172772.56</v>
       </c>
       <c r="M47" t="inlineStr">
         <is>
@@ -7872,47 +7868,47 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>Corn_CBOT_Futures</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
       <c r="E48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F48" t="n">
-        <v>2.5</v>
+        <v>2.421</v>
       </c>
       <c r="G48" t="n">
-        <v>0.008</v>
+        <v>0.105</v>
       </c>
       <c r="H48" t="n">
-        <v>2.492</v>
+        <v>2.316</v>
       </c>
       <c r="I48" s="5" t="n">
-        <v>176439.56</v>
+        <v>166285.87</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>2073.16</v>
+        <v>2311.37</v>
       </c>
       <c r="K48" s="6" t="n">
-        <v>5165.99</v>
+        <v>5352.76</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>195714.38</v>
+        <v>178125.32</v>
       </c>
       <c r="M48" t="inlineStr">
         <is>
@@ -7923,7 +7919,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini</t>
+          <t>Japanese_Yen_Futures</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -7933,48 +7929,48 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F49" t="n">
-        <v>2.502</v>
+        <v>-1</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>0.108</v>
       </c>
       <c r="H49" t="n">
-        <v>2.501</v>
+        <v>-1.108</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>173931.66</v>
+        <v>170461.19</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>2043.7</v>
-      </c>
-      <c r="K49" s="6" t="n">
-        <v>5112.02</v>
+        <v>2369.41</v>
+      </c>
+      <c r="K49" s="7" t="n">
+        <v>-2625.56</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>190548.39</v>
+        <v>186230.3</v>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures</t>
+          <t>Live_Cattle_Futures_CME</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -7984,37 +7980,37 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E50" t="n">
         <v>1</v>
       </c>
       <c r="F50" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="G50" t="n">
-        <v>0.182</v>
+        <v>0.016</v>
       </c>
       <c r="H50" t="n">
-        <v>2.318</v>
+        <v>1.884</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>179196.75</v>
+        <v>168091.78</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>2105.56</v>
+        <v>2336.48</v>
       </c>
       <c r="K50" s="6" t="n">
-        <v>4881.08</v>
+        <v>4401.92</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>200595.45</v>
+        <v>182527.24</v>
       </c>
       <c r="M50" t="inlineStr">
         <is>
@@ -8025,47 +8021,47 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Bitcoin_Per_USD_CME</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E51" t="n">
         <v>1</v>
       </c>
       <c r="F51" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="G51" t="n">
-        <v>0.004</v>
+        <v>0.008</v>
       </c>
       <c r="H51" t="n">
-        <v>2.496</v>
+        <v>1.892</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>191486.06</v>
+        <v>165755.3</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>2249.96</v>
+        <v>2304</v>
       </c>
       <c r="K51" s="6" t="n">
-        <v>5616.8</v>
+        <v>4358.79</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>203860.01</v>
+        <v>186886.03</v>
       </c>
       <c r="M51" t="inlineStr">
         <is>
@@ -8076,58 +8072,58 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F52" t="n">
-        <v>2.5</v>
+        <v>-1</v>
       </c>
       <c r="G52" t="n">
-        <v>0.008</v>
+        <v>0.001</v>
       </c>
       <c r="H52" t="n">
-        <v>2.492</v>
+        <v>-1.001</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>189236.1</v>
+        <v>171115.44</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>2223.52</v>
-      </c>
-      <c r="K52" s="6" t="n">
-        <v>5540.66</v>
+        <v>2378.5</v>
+      </c>
+      <c r="K52" s="7" t="n">
+        <v>-2380.12</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>210368.26</v>
+        <v>184505.91</v>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>unknown_pl</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>EURO_Futures</t>
+          <t>Corn_CBOT_Futures</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -8137,37 +8133,37 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E53" t="n">
         <v>1</v>
       </c>
       <c r="F53" t="n">
-        <v>2.532</v>
+        <v>1.9</v>
       </c>
       <c r="G53" t="n">
-        <v>0.013</v>
+        <v>0.182</v>
       </c>
       <c r="H53" t="n">
-        <v>2.519</v>
+        <v>1.718</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>193769.73</v>
+        <v>182138.12</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>2276.79</v>
+        <v>2531.72</v>
       </c>
       <c r="K53" s="6" t="n">
-        <v>5735.88</v>
+        <v>4349.96</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>209595.89</v>
+        <v>188855.87</v>
       </c>
       <c r="M53" t="inlineStr">
         <is>
@@ -8178,7 +8174,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures</t>
+          <t>Bitcoin_Per_USD_CME</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -8188,58 +8184,58 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
       <c r="E54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F54" t="n">
-        <v>-1</v>
+        <v>1.921</v>
       </c>
       <c r="G54" t="n">
-        <v>0.014</v>
+        <v>0.004</v>
       </c>
       <c r="H54" t="n">
-        <v>-1.014</v>
+        <v>1.917</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>191492.93</v>
+        <v>179604.78</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>2250.04</v>
-      </c>
-      <c r="K54" s="7" t="n">
-        <v>-2280.97</v>
+        <v>2496.51</v>
+      </c>
+      <c r="K54" s="6" t="n">
+        <v>4786.04</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>207314.92</v>
+        <v>191016.35</v>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -8248,39 +8244,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F55" t="n">
-        <v>-1</v>
+        <v>1.9</v>
       </c>
       <c r="G55" t="n">
-        <v>0.032</v>
+        <v>0.008</v>
       </c>
       <c r="H55" t="n">
-        <v>-1.032</v>
+        <v>1.892</v>
       </c>
       <c r="I55" s="5" t="n">
-        <v>205122.32</v>
+        <v>177108.27</v>
       </c>
       <c r="J55" s="5" t="n">
-        <v>2410.19</v>
-      </c>
-      <c r="K55" s="7" t="n">
-        <v>-2487.31</v>
+        <v>2461.8</v>
+      </c>
+      <c r="K55" s="6" t="n">
+        <v>4657.33</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>204827.6</v>
+        <v>203861.92</v>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>unknown_pl</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>EURO_Futures</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -8290,48 +8286,48 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E56" t="n">
         <v>1</v>
       </c>
       <c r="F56" t="n">
-        <v>-1</v>
+        <v>2.532</v>
       </c>
       <c r="G56" t="n">
-        <v>0.002</v>
+        <v>0.013</v>
       </c>
       <c r="H56" t="n">
-        <v>-1.002</v>
+        <v>2.519</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>202681.21</v>
+        <v>181271.99</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>2381.5</v>
-      </c>
-      <c r="K56" s="7" t="n">
-        <v>-2386.47</v>
+        <v>2519.68</v>
+      </c>
+      <c r="K56" s="6" t="n">
+        <v>6347.78</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>207981.8</v>
+        <v>197364.13</v>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -8341,37 +8337,37 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="E57" t="n">
         <v>1</v>
       </c>
       <c r="F57" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="G57" t="n">
-        <v>0.027</v>
+        <v>0.007</v>
       </c>
       <c r="H57" t="n">
-        <v>2.473</v>
+        <v>1.893</v>
       </c>
       <c r="I57" s="5" t="n">
-        <v>207981.8</v>
+        <v>178752.31</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>2443.79</v>
+        <v>2484.66</v>
       </c>
       <c r="K57" s="6" t="n">
-        <v>6042.51</v>
+        <v>4703.77</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>214024.31</v>
+        <v>202067.9</v>
       </c>
       <c r="M57" t="inlineStr">
         <is>
@@ -8382,7 +8378,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>Gold_Futures_COMEX</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -8392,143 +8388,143 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F58" t="n">
-        <v>2.5</v>
+        <v>-1</v>
       </c>
       <c r="G58" t="n">
-        <v>0.01</v>
+        <v>0.032</v>
       </c>
       <c r="H58" t="n">
-        <v>2.49</v>
+        <v>-1.032</v>
       </c>
       <c r="I58" s="5" t="n">
-        <v>214024.31</v>
+        <v>199606.09</v>
       </c>
       <c r="J58" s="5" t="n">
-        <v>2514.79</v>
-      </c>
-      <c r="K58" s="6" t="n">
-        <v>6261.17</v>
+        <v>2774.52</v>
+      </c>
+      <c r="K58" s="7" t="n">
+        <v>-2863.31</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>226484</v>
+        <v>199204.59</v>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>unknown_pl</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="E59" t="n">
         <v>1</v>
       </c>
       <c r="F59" t="n">
-        <v>2.506</v>
+        <v>-1</v>
       </c>
       <c r="G59" t="n">
-        <v>0.012</v>
+        <v>0.002</v>
       </c>
       <c r="H59" t="n">
-        <v>2.494</v>
+        <v>-1.002</v>
       </c>
       <c r="I59" s="5" t="n">
-        <v>211509.52</v>
+        <v>196831.57</v>
       </c>
       <c r="J59" s="5" t="n">
-        <v>2485.24</v>
-      </c>
-      <c r="K59" s="6" t="n">
-        <v>6198.52</v>
+        <v>2735.96</v>
+      </c>
+      <c r="K59" s="7" t="n">
+        <v>-2741.66</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>220222.83</v>
+        <v>201120.26</v>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F60" t="n">
-        <v>-1</v>
+        <v>1.9</v>
       </c>
       <c r="G60" t="n">
-        <v>0.002</v>
+        <v>0.027</v>
       </c>
       <c r="H60" t="n">
-        <v>-1.002</v>
+        <v>1.873</v>
       </c>
       <c r="I60" s="5" t="n">
-        <v>226484</v>
+        <v>201120.26</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>2661.19</v>
-      </c>
-      <c r="K60" s="7" t="n">
-        <v>-2666.96</v>
+        <v>2795.57</v>
+      </c>
+      <c r="K60" s="6" t="n">
+        <v>5235</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>221145.87</v>
+        <v>206355.26</v>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
@@ -8545,88 +8541,88 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="E61" t="n">
         <v>3</v>
       </c>
       <c r="F61" t="n">
-        <v>-1</v>
+        <v>1.9</v>
       </c>
       <c r="G61" t="n">
-        <v>0.016</v>
+        <v>0.01</v>
       </c>
       <c r="H61" t="n">
-        <v>-1.016</v>
+        <v>1.89</v>
       </c>
       <c r="I61" s="5" t="n">
-        <v>223822.81</v>
+        <v>206355.26</v>
       </c>
       <c r="J61" s="5" t="n">
-        <v>2629.92</v>
-      </c>
-      <c r="K61" s="7" t="n">
-        <v>-2671.17</v>
+        <v>2868.34</v>
+      </c>
+      <c r="K61" s="6" t="n">
+        <v>5420.42</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>223812.83</v>
+        <v>218830.26</v>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini</t>
+          <t>NY_Palladium_Futures</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="E62" t="n">
         <v>1</v>
       </c>
       <c r="F62" t="n">
-        <v>2.5</v>
+        <v>2.506</v>
       </c>
       <c r="G62" t="n">
-        <v>0.019</v>
+        <v>0.012</v>
       </c>
       <c r="H62" t="n">
-        <v>2.481</v>
+        <v>2.494</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>221151.64</v>
+        <v>203486.92</v>
       </c>
       <c r="J62" s="5" t="n">
-        <v>2598.53</v>
+        <v>2828.47</v>
       </c>
       <c r="K62" s="6" t="n">
-        <v>6447.3</v>
+        <v>7054.58</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>227593.17</v>
+        <v>213409.84</v>
       </c>
       <c r="M62" t="inlineStr">
         <is>
@@ -8637,7 +8633,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -8647,41 +8643,41 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F63" t="n">
-        <v>-1</v>
+        <v>1.9</v>
       </c>
       <c r="G63" t="n">
-        <v>0.007</v>
+        <v>0.001</v>
       </c>
       <c r="H63" t="n">
-        <v>-1.007</v>
+        <v>1.899</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>218547.34</v>
+        <v>218830.26</v>
       </c>
       <c r="J63" s="5" t="n">
-        <v>2567.93</v>
-      </c>
-      <c r="K63" s="7" t="n">
-        <v>-2586.92</v>
+        <v>3041.74</v>
+      </c>
+      <c r="K63" s="6" t="n">
+        <v>5776.01</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>225006.25</v>
+        <v>224606.27</v>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
@@ -8698,88 +8694,88 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F64" t="n">
-        <v>2.5</v>
+        <v>-1</v>
       </c>
       <c r="G64" t="n">
-        <v>0.015</v>
+        <v>0.016</v>
       </c>
       <c r="H64" t="n">
-        <v>2.485</v>
+        <v>-1.016</v>
       </c>
       <c r="I64" s="5" t="n">
-        <v>215979.41</v>
+        <v>215788.52</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>2537.76</v>
-      </c>
-      <c r="K64" s="6" t="n">
-        <v>6306.8</v>
+        <v>2999.46</v>
+      </c>
+      <c r="K64" s="7" t="n">
+        <v>-3046.51</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>231313.05</v>
+        <v>221559.76</v>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX</t>
+          <t>Dow_Futures_E_mini</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E65" t="n">
         <v>1</v>
       </c>
       <c r="F65" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="G65" t="n">
-        <v>0.004</v>
+        <v>0.019</v>
       </c>
       <c r="H65" t="n">
-        <v>2.496</v>
+        <v>1.881</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>231313.05</v>
+        <v>221559.76</v>
       </c>
       <c r="J65" s="5" t="n">
-        <v>2717.93</v>
+        <v>3079.68</v>
       </c>
       <c r="K65" s="6" t="n">
-        <v>6785.27</v>
+        <v>5793.29</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>238098.32</v>
+        <v>227353.05</v>
       </c>
       <c r="M65" t="inlineStr">
         <is>
@@ -8790,109 +8786,109 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>Gold_Futures_COMEX</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E66" t="n">
         <v>1</v>
       </c>
       <c r="F66" t="n">
-        <v>2.5</v>
+        <v>-1</v>
       </c>
       <c r="G66" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="H66" t="n">
-        <v>2.492</v>
+        <v>-1.007</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>228595.12</v>
+        <v>218480.08</v>
       </c>
       <c r="J66" s="5" t="n">
-        <v>2685.99</v>
-      </c>
-      <c r="K66" s="6" t="n">
-        <v>6693.49</v>
+        <v>3036.87</v>
+      </c>
+      <c r="K66" s="7" t="n">
+        <v>-3059.33</v>
       </c>
       <c r="L66" s="5" t="n">
-        <v>244791.81</v>
+        <v>224293.72</v>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Corn_CBOT_Futures</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="E67" t="n">
         <v>1</v>
       </c>
       <c r="F67" t="n">
-        <v>-1</v>
+        <v>1.9</v>
       </c>
       <c r="G67" t="n">
-        <v>0.148</v>
+        <v>0.015</v>
       </c>
       <c r="H67" t="n">
-        <v>-1.148</v>
+        <v>1.885</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>225909.13</v>
+        <v>215443.21</v>
       </c>
       <c r="J67" s="5" t="n">
-        <v>2654.43</v>
-      </c>
-      <c r="K67" s="7" t="n">
-        <v>-3047.68</v>
+        <v>2994.66</v>
+      </c>
+      <c r="K67" s="6" t="n">
+        <v>5645.49</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>241744.13</v>
+        <v>229939.21</v>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT</t>
+          <t>Gold_Futures_COMEX</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -8902,37 +8898,37 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E68" t="n">
         <v>1</v>
       </c>
       <c r="F68" t="n">
-        <v>2.5</v>
+        <v>2.318</v>
       </c>
       <c r="G68" t="n">
-        <v>0.03</v>
+        <v>0.004</v>
       </c>
       <c r="H68" t="n">
-        <v>2.47</v>
+        <v>2.315</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>242137.38</v>
+        <v>229939.21</v>
       </c>
       <c r="J68" s="5" t="n">
-        <v>2845.11</v>
+        <v>3196.16</v>
       </c>
       <c r="K68" s="6" t="n">
-        <v>7026.57</v>
+        <v>7397.77</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>248770.7</v>
+        <v>237336.98</v>
       </c>
       <c r="M68" t="inlineStr">
         <is>
@@ -8953,99 +8949,99 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="E69" t="n">
         <v>1</v>
       </c>
       <c r="F69" t="n">
-        <v>-1</v>
+        <v>2.424</v>
       </c>
       <c r="G69" t="n">
-        <v>0.014</v>
+        <v>0.008</v>
       </c>
       <c r="H69" t="n">
-        <v>-1.014</v>
+        <v>2.416</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>248770.7</v>
+        <v>226743.06</v>
       </c>
       <c r="J69" s="5" t="n">
-        <v>2923.06</v>
-      </c>
-      <c r="K69" s="7" t="n">
-        <v>-2962.69</v>
+        <v>3151.73</v>
+      </c>
+      <c r="K69" s="6" t="n">
+        <v>7614.58</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>245808.01</v>
+        <v>244951.56</v>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>Corn_CBOT_Futures</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F70" t="n">
         <v>-1</v>
       </c>
       <c r="G70" t="n">
-        <v>0.014</v>
+        <v>0.148</v>
       </c>
       <c r="H70" t="n">
-        <v>-1.014</v>
+        <v>-1.148</v>
       </c>
       <c r="I70" s="5" t="n">
-        <v>245808.01</v>
+        <v>223591.33</v>
       </c>
       <c r="J70" s="5" t="n">
-        <v>2888.24</v>
+        <v>3107.92</v>
       </c>
       <c r="K70" s="7" t="n">
-        <v>-2928.08</v>
+        <v>-3568.35</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>242879.93</v>
+        <v>241383.21</v>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>unknown_pl</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -9055,99 +9051,99 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E71" t="n">
         <v>1</v>
       </c>
       <c r="F71" t="n">
-        <v>-1</v>
+        <v>1.9</v>
       </c>
       <c r="G71" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="H71" t="n">
-        <v>-1.02</v>
+        <v>1.87</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>242919.77</v>
+        <v>241843.64</v>
       </c>
       <c r="J71" s="5" t="n">
-        <v>2854.31</v>
-      </c>
-      <c r="K71" s="7" t="n">
-        <v>-2910</v>
+        <v>3361.63</v>
+      </c>
+      <c r="K71" s="6" t="n">
+        <v>6285.22</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>239969.93</v>
+        <v>247668.43</v>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>EURO_Futures</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F72" t="n">
-        <v>2.5</v>
+        <v>-1</v>
       </c>
       <c r="G72" t="n">
-        <v>0.007</v>
+        <v>0.014</v>
       </c>
       <c r="H72" t="n">
-        <v>2.493</v>
+        <v>-1.014</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>240025.62</v>
+        <v>247668.43</v>
       </c>
       <c r="J72" s="5" t="n">
-        <v>2820.3</v>
-      </c>
-      <c r="K72" s="6" t="n">
-        <v>7030.32</v>
+        <v>3442.59</v>
+      </c>
+      <c r="K72" s="7" t="n">
+        <v>-3489.27</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>247000.24</v>
+        <v>244179.16</v>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -9157,37 +9153,37 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" t="n">
         <v>-1</v>
       </c>
       <c r="G73" t="n">
-        <v>0.082</v>
+        <v>0.014</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.082</v>
+        <v>-1.014</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>237149.63</v>
+        <v>244179.16</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>2786.51</v>
+        <v>3394.09</v>
       </c>
       <c r="K73" s="7" t="n">
-        <v>-3013.98</v>
+        <v>-3440.91</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>243986.26</v>
+        <v>240738.26</v>
       </c>
       <c r="M73" t="inlineStr">
         <is>
@@ -9198,7 +9194,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -9208,48 +9204,48 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="E74" t="n">
         <v>1</v>
       </c>
       <c r="F74" t="n">
-        <v>2.5</v>
+        <v>-1</v>
       </c>
       <c r="G74" t="n">
-        <v>0.026</v>
+        <v>0.02</v>
       </c>
       <c r="H74" t="n">
-        <v>2.474</v>
+        <v>-1.02</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>234363.12</v>
+        <v>240785.07</v>
       </c>
       <c r="J74" s="5" t="n">
-        <v>2753.77</v>
-      </c>
-      <c r="K74" s="6" t="n">
-        <v>6811.95</v>
+        <v>3346.91</v>
+      </c>
+      <c r="K74" s="7" t="n">
+        <v>-3412.22</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>250798.21</v>
+        <v>237326.04</v>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures</t>
+          <t>EURO_Futures</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -9259,48 +9255,48 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F75" t="n">
-        <v>-1</v>
+        <v>1.9</v>
       </c>
       <c r="G75" t="n">
-        <v>0.012</v>
+        <v>0.007</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.012</v>
+        <v>1.893</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>231609.35</v>
+        <v>237391.34</v>
       </c>
       <c r="J75" s="5" t="n">
-        <v>2721.41</v>
-      </c>
-      <c r="K75" s="7" t="n">
-        <v>-2753.52</v>
+        <v>3299.74</v>
+      </c>
+      <c r="K75" s="6" t="n">
+        <v>6245.59</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>276485.29</v>
+        <v>243571.63</v>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>NY_Natural_Gas_Futures</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -9322,36 +9318,36 @@
         <v>1</v>
       </c>
       <c r="F76" t="n">
-        <v>2.5</v>
+        <v>-1</v>
       </c>
       <c r="G76" t="n">
-        <v>0.017</v>
+        <v>0.082</v>
       </c>
       <c r="H76" t="n">
-        <v>2.483</v>
+        <v>-1.082</v>
       </c>
       <c r="I76" s="5" t="n">
-        <v>228887.94</v>
+        <v>234026.3</v>
       </c>
       <c r="J76" s="5" t="n">
-        <v>2689.43</v>
-      </c>
-      <c r="K76" s="6" t="n">
-        <v>6676.81</v>
+        <v>3252.97</v>
+      </c>
+      <c r="K76" s="7" t="n">
+        <v>-3518.51</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>257475.02</v>
+        <v>240053.12</v>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT</t>
+          <t>NY_Palladium_Futures</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -9361,37 +9357,37 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E77" t="n">
         <v>1</v>
       </c>
       <c r="F77" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="G77" t="n">
-        <v>0.049</v>
+        <v>0.026</v>
       </c>
       <c r="H77" t="n">
-        <v>2.451</v>
+        <v>1.874</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>254753.61</v>
+        <v>230773.33</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>2993.35</v>
+        <v>3207.75</v>
       </c>
       <c r="K77" s="6" t="n">
-        <v>7337.37</v>
+        <v>6010.31</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>264812.39</v>
+        <v>246063.43</v>
       </c>
       <c r="M77" t="inlineStr">
         <is>
@@ -9402,47 +9398,47 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>German_Long_Bund</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E78" t="n">
         <v>1</v>
       </c>
       <c r="F78" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="G78" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.006</v>
       </c>
       <c r="H78" t="n">
-        <v>2.413</v>
+        <v>1.894</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>251760.26</v>
+        <v>227565.58</v>
       </c>
       <c r="J78" s="5" t="n">
-        <v>2958.18</v>
+        <v>3163.16</v>
       </c>
       <c r="K78" s="6" t="n">
-        <v>7138.22</v>
+        <v>5991.35</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>271950.62</v>
+        <v>252054.77</v>
       </c>
       <c r="M78" t="inlineStr">
         <is>
@@ -9453,47 +9449,47 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E79" t="n">
         <v>1</v>
       </c>
       <c r="F79" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="G79" t="n">
-        <v>0.007</v>
+        <v>0.017</v>
       </c>
       <c r="H79" t="n">
-        <v>2.493</v>
+        <v>1.883</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>248802.08</v>
+        <v>224402.42</v>
       </c>
       <c r="J79" s="5" t="n">
-        <v>2923.42</v>
+        <v>3119.19</v>
       </c>
       <c r="K79" s="6" t="n">
-        <v>7288.19</v>
+        <v>5872.22</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>279238.81</v>
+        <v>257926.99</v>
       </c>
       <c r="M79" t="inlineStr">
         <is>
@@ -9504,58 +9500,58 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Dow_Futures_E_mini</t>
+          <t>Chicago_SRW_Wheat_Futures_CBOT</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
       <c r="E80" t="n">
         <v>1</v>
       </c>
       <c r="F80" t="n">
-        <v>-1</v>
+        <v>1.9</v>
       </c>
       <c r="G80" t="n">
-        <v>0.011</v>
+        <v>0.049</v>
       </c>
       <c r="H80" t="n">
-        <v>-1.011</v>
+        <v>1.851</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>245878.65</v>
+        <v>257926.99</v>
       </c>
       <c r="J80" s="5" t="n">
-        <v>2889.07</v>
-      </c>
-      <c r="K80" s="7" t="n">
-        <v>-2920.14</v>
+        <v>3585.19</v>
+      </c>
+      <c r="K80" s="6" t="n">
+        <v>6636.96</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>273565.15</v>
+        <v>264563.96</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sugar_World_CSCE_Futures</t>
+          <t>German_Long_Bund</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -9565,48 +9561,48 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>2026-07-07</t>
-        </is>
-      </c>
       <c r="E81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F81" t="n">
-        <v>-1</v>
+        <v>1.9</v>
       </c>
       <c r="G81" t="n">
-        <v>0.154</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="H81" t="n">
-        <v>-1.154</v>
+        <v>1.813</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>242989.58</v>
+        <v>254341.81</v>
       </c>
       <c r="J81" s="5" t="n">
-        <v>2855.13</v>
-      </c>
-      <c r="K81" s="7" t="n">
-        <v>-3294.38</v>
+        <v>3535.35</v>
+      </c>
+      <c r="K81" s="6" t="n">
+        <v>6409.75</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>270270.77</v>
+        <v>270973.7</v>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME</t>
+          <t>Gold_Futures_COMEX</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -9616,37 +9612,37 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E82" t="n">
         <v>1</v>
       </c>
       <c r="F82" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="G82" t="n">
-        <v>0.024</v>
+        <v>0.007</v>
       </c>
       <c r="H82" t="n">
-        <v>2.476</v>
+        <v>1.893</v>
       </c>
       <c r="I82" s="5" t="n">
-        <v>270270.77</v>
+        <v>250806.46</v>
       </c>
       <c r="J82" s="5" t="n">
-        <v>3175.68</v>
+        <v>3486.21</v>
       </c>
       <c r="K82" s="6" t="n">
-        <v>7863.59</v>
+        <v>6599.5</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>278134.36</v>
+        <v>277573.21</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
@@ -9657,7 +9653,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures</t>
+          <t>Dow_Futures_E_mini</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -9667,227 +9663,431 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E83" t="n">
         <v>1</v>
       </c>
       <c r="F83" t="n">
-        <v>2.5</v>
+        <v>-1</v>
       </c>
       <c r="G83" t="n">
-        <v>0.039</v>
+        <v>0.011</v>
       </c>
       <c r="H83" t="n">
-        <v>2.461</v>
+        <v>-1.011</v>
       </c>
       <c r="I83" s="5" t="n">
-        <v>267095.09</v>
+        <v>247320.25</v>
       </c>
       <c r="J83" s="5" t="n">
-        <v>3138.37</v>
-      </c>
-      <c r="K83" s="6" t="n">
-        <v>7722.84</v>
+        <v>3437.75</v>
+      </c>
+      <c r="K83" s="7" t="n">
+        <v>-3474.72</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>285857.21</v>
+        <v>274098.49</v>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F84" t="n">
-        <v>-1</v>
+        <v>1.9</v>
       </c>
       <c r="G84" t="n">
-        <v>0.049</v>
+        <v>0.01</v>
       </c>
       <c r="H84" t="n">
-        <v>-1.049</v>
+        <v>1.89</v>
       </c>
       <c r="I84" s="5" t="n">
-        <v>285857.21</v>
+        <v>243882.5</v>
       </c>
       <c r="J84" s="5" t="n">
-        <v>3358.82</v>
-      </c>
-      <c r="K84" s="7" t="n">
-        <v>-3524.69</v>
+        <v>3389.97</v>
+      </c>
+      <c r="K84" s="6" t="n">
+        <v>6406.17</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>282332.52</v>
+        <v>280504.66</v>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>stop</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX</t>
+          <t>Sugar_World_CSCE_Futures</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F85" t="n">
-        <v>2.5</v>
+        <v>-1</v>
       </c>
       <c r="G85" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.154</v>
       </c>
       <c r="H85" t="n">
-        <v>2.491</v>
+        <v>-1.154</v>
       </c>
       <c r="I85" s="5" t="n">
-        <v>282332.52</v>
+        <v>240492.53</v>
       </c>
       <c r="J85" s="5" t="n">
-        <v>3317.41</v>
-      </c>
-      <c r="K85" s="6" t="n">
-        <v>8262.07</v>
+        <v>3342.85</v>
+      </c>
+      <c r="K85" s="7" t="n">
+        <v>-3857.13</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>290594.59</v>
+        <v>276647.53</v>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>target_r</t>
+          <t>stop</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT</t>
+          <t>Live_Cattle_Futures_CME</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>1</v>
       </c>
       <c r="F86" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="G86" t="n">
-        <v>0.019</v>
+        <v>0.024</v>
       </c>
       <c r="H86" t="n">
-        <v>-0.019</v>
+        <v>1.876</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>290594.59</v>
+        <v>276647.53</v>
       </c>
       <c r="J86" s="5" t="n">
-        <v>3414.49</v>
-      </c>
-      <c r="K86" s="7" t="n">
-        <v>-64.42</v>
+        <v>3845.4</v>
+      </c>
+      <c r="K86" s="6" t="n">
+        <v>7214.7</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>290530.17</v>
+        <v>283862.23</v>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>open_at_end</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
+          <t>NY_Natural_Gas_Futures</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="H87" t="n">
+        <v>1.861</v>
+      </c>
+      <c r="I87" s="5" t="n">
+        <v>272802.13</v>
+      </c>
+      <c r="J87" s="5" t="n">
+        <v>3791.95</v>
+      </c>
+      <c r="K87" s="6" t="n">
+        <v>7056</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>290918.23</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>target_r</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="H88" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="I88" s="5" t="n">
+        <v>290918.23</v>
+      </c>
+      <c r="J88" s="5" t="n">
+        <v>4043.76</v>
+      </c>
+      <c r="K88" s="6" t="n">
+        <v>7583.3</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>298501.54</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>target_r</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>1</v>
+      </c>
+      <c r="F89" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="H89" t="n">
+        <v>1.891</v>
+      </c>
+      <c r="I89" s="5" t="n">
+        <v>298501.54</v>
+      </c>
+      <c r="J89" s="5" t="n">
+        <v>4149.17</v>
+      </c>
+      <c r="K89" s="6" t="n">
+        <v>7844.1</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>306345.63</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>target_r</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="H90" t="n">
+        <v>-0.019</v>
+      </c>
+      <c r="I90" s="5" t="n">
+        <v>306345.63</v>
+      </c>
+      <c r="J90" s="5" t="n">
+        <v>4258.2</v>
+      </c>
+      <c r="K90" s="7" t="n">
+        <v>-80.34</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>306265.29</v>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
           <t>Corn_CBOT_Futures</t>
         </is>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B91" t="inlineStr">
         <is>
           <t>short</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C91" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="F87" t="n">
-        <v>0</v>
-      </c>
-      <c r="G87" t="n">
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="n">
         <v>0.025</v>
       </c>
-      <c r="H87" t="n">
+      <c r="H91" t="n">
         <v>-0.025</v>
       </c>
-      <c r="I87" s="5" t="n">
-        <v>287180.1</v>
-      </c>
-      <c r="J87" s="5" t="n">
-        <v>3374.37</v>
-      </c>
-      <c r="K87" s="7" t="n">
-        <v>-84.36</v>
-      </c>
-      <c r="L87" s="5" t="n">
-        <v>290445.81</v>
-      </c>
-      <c r="M87" t="inlineStr">
+      <c r="I91" s="5" t="n">
+        <v>302087.43</v>
+      </c>
+      <c r="J91" s="5" t="n">
+        <v>4199.02</v>
+      </c>
+      <c r="K91" s="7" t="n">
+        <v>-104.98</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>306160.32</v>
+      </c>
+      <c r="M91" t="inlineStr">
         <is>
           <t>open_at_end</t>
         </is>

--- a/output/quickfix_portfolio_daily.xlsx
+++ b/output/quickfix_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$181</f>
+              <f>'equity_curve'!$A$2:$A$182</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$181</f>
+              <f>'equity_curve'!$B$2:$B$182</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>306,160.32</t>
+          <t>322,043.71</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+206.16%</t>
+          <t>+222.04%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>321,399  (+221.40%)</t>
+          <t>338,258  (+238.26%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>8,177  (15.2 pts of return)</t>
+          <t>8,363  (16.2 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>34.4x</t>
+          <t>37.0x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>64.4%</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>+2.16R  (best +8.09R)</t>
+          <t>+2.15R  (best +8.09R)</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5,092  (+3.01%)</t>
+          <t>5,187  (+2.99%)</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>48% of trading days</t>
+          <t>49% of trading days</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-07-24</t>
+          <t>2025-12-18 -&gt; 2026-07-27</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H181"/>
+  <dimension ref="A1:H182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5399,26 +5399,50 @@
         <v>46227</v>
       </c>
       <c r="B181" s="5" t="n">
-        <v>306160.32</v>
+        <v>306345.63</v>
       </c>
       <c r="C181" s="5" t="n">
+        <v>8457.219999999999</v>
+      </c>
+      <c r="D181" s="5" t="n">
+        <v>297888.42</v>
+      </c>
+      <c r="E181" t="n">
+        <v>2</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT, Corn_CBOT_Futures</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 4,258); Corn_CBOT_Futures short (risk 4,199)</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="4" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B182" s="5" t="n">
+        <v>322043.71</v>
+      </c>
+      <c r="C182" s="5" t="n">
         <v>-0</v>
       </c>
-      <c r="D181" s="5" t="n">
-        <v>306160.32</v>
-      </c>
-      <c r="E181" t="n">
-        <v>0</v>
-      </c>
-      <c r="F181" t="inlineStr"/>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT short (risk 4,258); Corn_CBOT_Futures short (risk 4,199)</t>
-        </is>
-      </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>Chicago_SRW_Wheat_Futures_CBOT open_at_end (open-&gt;closed 0); Corn_CBOT_Futures open_at_end (open-&gt;closed 0)</t>
+      <c r="D182" s="5" t="n">
+        <v>322043.71</v>
+      </c>
+      <c r="E182" t="n">
+        <v>0</v>
+      </c>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Chicago_SRW_Wheat_Futures_CBOT target_r (+7,930); Corn_CBOT_Futures target_r (+7,768)</t>
         </is>
       </c>
     </row>
@@ -10023,14 +10047,22 @@
           <t>2026-07-24</t>
         </is>
       </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>1</v>
+      </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="G90" t="n">
-        <v>0.019</v>
+        <v>0.038</v>
       </c>
       <c r="H90" t="n">
-        <v>-0.019</v>
+        <v>1.862</v>
       </c>
       <c r="I90" s="5" t="n">
         <v>306345.63</v>
@@ -10038,15 +10070,15 @@
       <c r="J90" s="5" t="n">
         <v>4258.2</v>
       </c>
-      <c r="K90" s="7" t="n">
-        <v>-80.34</v>
+      <c r="K90" s="6" t="n">
+        <v>7929.9</v>
       </c>
       <c r="L90" s="5" t="n">
-        <v>306265.29</v>
+        <v>314275.54</v>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>open_at_end</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>
@@ -10066,14 +10098,22 @@
           <t>2026-07-24</t>
         </is>
       </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>1</v>
+      </c>
       <c r="F91" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="G91" t="n">
-        <v>0.025</v>
+        <v>0.05</v>
       </c>
       <c r="H91" t="n">
-        <v>-0.025</v>
+        <v>1.85</v>
       </c>
       <c r="I91" s="5" t="n">
         <v>302087.43</v>
@@ -10081,15 +10121,15 @@
       <c r="J91" s="5" t="n">
         <v>4199.02</v>
       </c>
-      <c r="K91" s="7" t="n">
-        <v>-104.98</v>
+      <c r="K91" s="6" t="n">
+        <v>7768.18</v>
       </c>
       <c r="L91" s="5" t="n">
-        <v>306160.32</v>
+        <v>322043.71</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>open_at_end</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>

--- a/output/quickfix_portfolio_daily.xlsx
+++ b/output/quickfix_portfolio_daily.xlsx
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">

--- a/output/quickfix_portfolio_daily.xlsx
+++ b/output/quickfix_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$182</f>
+              <f>'equity_curve'!$A$2:$A$184</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$182</f>
+              <f>'equity_curve'!$B$2:$B$184</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>322,043.71</t>
+          <t>330,260.41</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+222.04%</t>
+          <t>+230.26%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>338,258  (+238.26%)</t>
+          <t>347,191  (+247.19%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>8,363  (16.2 pts of return)</t>
+          <t>8,651  (16.9 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>37.0x</t>
+          <t>38.4x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.8%</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -774,7 +774,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5,187  (+2.99%)</t>
+          <t>5,242  (+2.99%)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-07-27</t>
+          <t>2025-12-18 -&gt; 2026-07-29</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H182"/>
+  <dimension ref="A1:H184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5446,6 +5446,62 @@
         </is>
       </c>
     </row>
+    <row r="183">
+      <c r="A183" s="4" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B183" s="5" t="n">
+        <v>322043.71</v>
+      </c>
+      <c r="C183" s="5" t="n">
+        <v>4476.41</v>
+      </c>
+      <c r="D183" s="5" t="n">
+        <v>317567.31</v>
+      </c>
+      <c r="E183" t="n">
+        <v>1</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>US_Dollar_Index_Futures short (risk 4,476)</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="4" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B184" s="5" t="n">
+        <v>330260.41</v>
+      </c>
+      <c r="C184" s="5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D184" s="5" t="n">
+        <v>330260.41</v>
+      </c>
+      <c r="E184" t="n">
+        <v>0</v>
+      </c>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>NY_Natural_Gas_Futures long (risk 4,414)</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>NY_Natural_Gas_Futures open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures target_r (+8,393)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5458,7 +5514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M91"/>
+  <dimension ref="A1:M93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -10133,6 +10189,100 @@
         </is>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="H92" t="n">
+        <v>1.875</v>
+      </c>
+      <c r="I92" s="5" t="n">
+        <v>322043.71</v>
+      </c>
+      <c r="J92" s="5" t="n">
+        <v>4476.41</v>
+      </c>
+      <c r="K92" s="6" t="n">
+        <v>8393.26</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>330260.41</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>target_r</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>NY_Natural_Gas_Futures</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H93" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="I93" s="5" t="n">
+        <v>317567.31</v>
+      </c>
+      <c r="J93" s="5" t="n">
+        <v>4414.19</v>
+      </c>
+      <c r="K93" s="7" t="n">
+        <v>-176.57</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>321867.15</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/quickfix_portfolio_daily.xlsx
+++ b/output/quickfix_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$184</f>
+              <f>'equity_curve'!$A$2:$A$185</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$184</f>
+              <f>'equity_curve'!$B$2:$B$185</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>330,260.41</t>
+          <t>338,470.80</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+230.26%</t>
+          <t>+238.47%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>347,191  (+247.19%)</t>
+          <t>356,000  (+256.00%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>8,651  (16.9 pts of return)</t>
+          <t>8,828  (17.5 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>38.4x</t>
+          <t>39.8x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>65.2%</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>+2.15R  (best +8.09R)</t>
+          <t>+2.14R  (best +8.09R)</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16">
@@ -774,7 +774,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5,242  (+2.99%)</t>
+          <t>5,288  (+2.98%)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-07-29</t>
+          <t>2025-12-18 -&gt; 2026-07-30</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H184"/>
+  <dimension ref="A1:H185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5479,26 +5479,54 @@
         <v>46232</v>
       </c>
       <c r="B184" s="5" t="n">
-        <v>330260.41</v>
+        <v>330436.98</v>
       </c>
       <c r="C184" s="5" t="n">
+        <v>4414.19</v>
+      </c>
+      <c r="D184" s="5" t="n">
+        <v>326022.79</v>
+      </c>
+      <c r="E184" t="n">
+        <v>1</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>NY_Natural_Gas_Futures</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>NY_Natural_Gas_Futures long (risk 4,414)</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>US_Dollar_Index_Futures target_r (+8,393)</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="4" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B185" s="5" t="n">
+        <v>338470.8</v>
+      </c>
+      <c r="C185" s="5" t="n">
         <v>-0</v>
       </c>
-      <c r="D184" s="5" t="n">
-        <v>330260.41</v>
-      </c>
-      <c r="E184" t="n">
-        <v>0</v>
-      </c>
-      <c r="F184" t="inlineStr"/>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>NY_Natural_Gas_Futures long (risk 4,414)</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>NY_Natural_Gas_Futures open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures target_r (+8,393)</t>
+      <c r="D185" s="5" t="n">
+        <v>338470.8</v>
+      </c>
+      <c r="E185" t="n">
+        <v>0</v>
+      </c>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>NY_Natural_Gas_Futures target_r (+8,034)</t>
         </is>
       </c>
     </row>
@@ -10232,7 +10260,7 @@
         <v>8393.26</v>
       </c>
       <c r="L92" s="5" t="n">
-        <v>330260.41</v>
+        <v>330436.98</v>
       </c>
       <c r="M92" t="inlineStr">
         <is>
@@ -10256,14 +10284,22 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>1</v>
+      </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="G93" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H93" t="n">
-        <v>-0.04</v>
+        <v>1.82</v>
       </c>
       <c r="I93" s="5" t="n">
         <v>317567.31</v>
@@ -10271,15 +10307,15 @@
       <c r="J93" s="5" t="n">
         <v>4414.19</v>
       </c>
-      <c r="K93" s="7" t="n">
-        <v>-176.57</v>
+      <c r="K93" s="6" t="n">
+        <v>8033.82</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>321867.15</v>
+        <v>338470.8</v>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>open_at_end</t>
+          <t>target_r</t>
         </is>
       </c>
     </row>

--- a/output/quickfix_portfolio_daily.xlsx
+++ b/output/quickfix_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$185</f>
+              <f>'equity_curve'!$A$2:$A$186</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$185</f>
+              <f>'equity_curve'!$B$2:$B$186</f>
             </numRef>
           </val>
         </ser>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-07-30</t>
+          <t>2025-12-18 -&gt; 2026-07-31</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H185"/>
+  <dimension ref="A1:H186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5529,6 +5529,26 @@
           <t>NY_Natural_Gas_Futures target_r (+8,034)</t>
         </is>
       </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="4" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B186" s="5" t="n">
+        <v>338470.8</v>
+      </c>
+      <c r="C186" s="5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D186" s="5" t="n">
+        <v>338470.8</v>
+      </c>
+      <c r="E186" t="n">
+        <v>0</v>
+      </c>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/quickfix_portfolio_daily.xlsx
+++ b/output/quickfix_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$186</f>
+              <f>'equity_curve'!$A$2:$A$188</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$186</f>
+              <f>'equity_curve'!$B$2:$B$188</f>
             </numRef>
           </val>
         </ser>
@@ -828,7 +828,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>49% of trading days</t>
+          <t>48% of trading days</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-07-31</t>
+          <t>2025-12-18 -&gt; 2026-08-04</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H186"/>
+  <dimension ref="A1:H188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5549,6 +5549,46 @@
       <c r="F186" t="inlineStr"/>
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="4" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B187" s="5" t="n">
+        <v>338470.8</v>
+      </c>
+      <c r="C187" s="5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D187" s="5" t="n">
+        <v>338470.8</v>
+      </c>
+      <c r="E187" t="n">
+        <v>0</v>
+      </c>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="4" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B188" s="5" t="n">
+        <v>338470.8</v>
+      </c>
+      <c r="C188" s="5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D188" s="5" t="n">
+        <v>338470.8</v>
+      </c>
+      <c r="E188" t="n">
+        <v>0</v>
+      </c>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/quickfix_portfolio_daily.xlsx
+++ b/output/quickfix_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$188</f>
+              <f>'equity_curve'!$A$2:$A$190</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$188</f>
+              <f>'equity_curve'!$B$2:$B$190</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>338,470.80</t>
+          <t>347,260.03</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+238.47%</t>
+          <t>+247.26%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>356,000  (+256.00%)</t>
+          <t>365,272  (+265.27%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>8,828  (17.5 pts of return)</t>
+          <t>8,853  (18.0 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>39.8x</t>
+          <t>41.2x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.6%</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
@@ -774,7 +774,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5,288  (+2.98%)</t>
+          <t>5,346  (+2.97%)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-08-04</t>
+          <t>2025-12-18 -&gt; 2026-08-06</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H188"/>
+  <dimension ref="A1:H190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5590,6 +5590,62 @@
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr"/>
     </row>
+    <row r="189">
+      <c r="A189" s="4" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B189" s="5" t="n">
+        <v>338470.8</v>
+      </c>
+      <c r="C189" s="5" t="n">
+        <v>13918.95</v>
+      </c>
+      <c r="D189" s="5" t="n">
+        <v>324551.84</v>
+      </c>
+      <c r="E189" t="n">
+        <v>3</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures, Nasdaq_100_E_mini, S_P_500_E_mini</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures short (risk 4,705); Nasdaq_100_E_mini short (risk 4,639); S_P_500_E_mini short (risk 4,575)</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B190" s="5" t="n">
+        <v>347260.03</v>
+      </c>
+      <c r="C190" s="5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D190" s="5" t="n">
+        <v>347260.03</v>
+      </c>
+      <c r="E190" t="n">
+        <v>0</v>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX short (risk 4,511)</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX open_at_end (open-&gt;closed 0); Nasdaq_100_E_mini target_r (+8,814); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini open_at_end (open-&gt;closed 0)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5602,7 +5658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M93"/>
+  <dimension ref="A1:M97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -10379,6 +10435,186 @@
         </is>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H94" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>338470.8</v>
+      </c>
+      <c r="J94" s="5" t="n">
+        <v>4704.74</v>
+      </c>
+      <c r="K94" s="7" t="n">
+        <v>-16.34</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>347261</v>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Nasdaq_100_E_mini</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I95" s="5" t="n">
+        <v>333766.05</v>
+      </c>
+      <c r="J95" s="5" t="n">
+        <v>4639.35</v>
+      </c>
+      <c r="K95" s="6" t="n">
+        <v>8814.25</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>347277.33</v>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>target_r</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>S_P_500_E_mini</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>-0</v>
+      </c>
+      <c r="I96" s="5" t="n">
+        <v>329126.7</v>
+      </c>
+      <c r="J96" s="5" t="n">
+        <v>4574.86</v>
+      </c>
+      <c r="K96" s="7" t="n">
+        <v>-0.97</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>347260.03</v>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H97" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="I97" s="5" t="n">
+        <v>324551.84</v>
+      </c>
+      <c r="J97" s="5" t="n">
+        <v>4511.27</v>
+      </c>
+      <c r="K97" s="7" t="n">
+        <v>-7.71</v>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v>338463.08</v>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/quickfix_portfolio_daily.xlsx
+++ b/output/quickfix_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$190</f>
+              <f>'equity_curve'!$A$2:$A$191</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$190</f>
+              <f>'equity_curve'!$B$2:$B$191</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>347,260.03</t>
+          <t>342,695.17</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+247.26%</t>
+          <t>+242.70%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>365,272  (+265.27%)</t>
+          <t>360,527  (+260.53%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>8,853  (18.0 pts of return)</t>
+          <t>8,907  (17.8 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>41.2x</t>
+          <t>40.5x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>64.9%</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-2,463  (-1.58%)</t>
+          <t>-2,526  (-1.57%)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-08-06</t>
+          <t>2025-12-18 -&gt; 2026-08-07</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H190"/>
+  <dimension ref="A1:H191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5623,26 +5623,58 @@
         <v>46240</v>
       </c>
       <c r="B190" s="5" t="n">
-        <v>347260.03</v>
+        <v>347285.05</v>
       </c>
       <c r="C190" s="5" t="n">
+        <v>13790.88</v>
+      </c>
+      <c r="D190" s="5" t="n">
+        <v>333494.17</v>
+      </c>
+      <c r="E190" t="n">
+        <v>3</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX, NY_Platinum_Futures, S_P_500_E_mini</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX short (risk 4,511)</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Nasdaq_100_E_mini target_r (+8,814)</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="4" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B191" s="5" t="n">
+        <v>342695.17</v>
+      </c>
+      <c r="C191" s="5" t="n">
         <v>-0</v>
       </c>
-      <c r="D190" s="5" t="n">
-        <v>347260.03</v>
-      </c>
-      <c r="E190" t="n">
-        <v>0</v>
-      </c>
-      <c r="F190" t="inlineStr"/>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>Gold_Futures_COMEX short (risk 4,511)</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>Gold_Futures_COMEX open_at_end (open-&gt;closed 0); Nasdaq_100_E_mini target_r (+8,814); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini open_at_end (open-&gt;closed 0)</t>
+      <c r="D191" s="5" t="n">
+        <v>342695.17</v>
+      </c>
+      <c r="E191" t="n">
+        <v>0</v>
+      </c>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>NY_Copper_Futures short (risk 4,636); NY_Palladium_Futures short (risk 4,571)</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX stop (-4,542); NY_Copper_Futures open_at_end (open-&gt;closed 0); NY_Palladium_Futures open_at_end (open-&gt;closed 0); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini open_at_end (open-&gt;closed 0)</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M97"/>
+  <dimension ref="A1:M99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -10470,7 +10502,7 @@
         <v>-16.34</v>
       </c>
       <c r="L94" s="5" t="n">
-        <v>347261</v>
+        <v>342696.14</v>
       </c>
       <c r="M94" t="inlineStr">
         <is>
@@ -10521,7 +10553,7 @@
         <v>8814.25</v>
       </c>
       <c r="L95" s="5" t="n">
-        <v>347277.33</v>
+        <v>347285.05</v>
       </c>
       <c r="M95" t="inlineStr">
         <is>
@@ -10564,7 +10596,7 @@
         <v>-0.97</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>347260.03</v>
+        <v>342695.17</v>
       </c>
       <c r="M96" t="inlineStr">
         <is>
@@ -10588,14 +10620,22 @@
           <t>2026-08-06</t>
         </is>
       </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>1</v>
+      </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G97" t="n">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="H97" t="n">
-        <v>-0.002</v>
+        <v>-1.007</v>
       </c>
       <c r="I97" s="5" t="n">
         <v>324551.84</v>
@@ -10604,12 +10644,98 @@
         <v>4511.27</v>
       </c>
       <c r="K97" s="7" t="n">
-        <v>-7.71</v>
+        <v>-4542.12</v>
       </c>
       <c r="L97" s="5" t="n">
-        <v>338463.08</v>
+        <v>342742.93</v>
       </c>
       <c r="M97" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>NY_Copper_Futures</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>0</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H98" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="I98" s="5" t="n">
+        <v>333494.17</v>
+      </c>
+      <c r="J98" s="5" t="n">
+        <v>4635.57</v>
+      </c>
+      <c r="K98" s="7" t="n">
+        <v>-12.53</v>
+      </c>
+      <c r="L98" s="5" t="n">
+        <v>342730.4</v>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>NY_Palladium_Futures</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>0</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="H99" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="I99" s="5" t="n">
+        <v>328858.6</v>
+      </c>
+      <c r="J99" s="5" t="n">
+        <v>4571.13</v>
+      </c>
+      <c r="K99" s="7" t="n">
+        <v>-17.93</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>342712.47</v>
+      </c>
+      <c r="M99" t="inlineStr">
         <is>
           <t>open_at_end</t>
         </is>
